--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC75027-9905-440C-A586-E1AE04ADFBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147848EE-97A9-492C-B829-8CDEB0A023BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7404" yWindow="3900" windowWidth="23484" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3337,10 +3337,6 @@
   </si>
   <si>
     <t>佩佩,神秘之光,mrfz,明日方舟,舟,粥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>银魂,昙天,阴天,云天</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4212,6 +4208,10 @@
   </si>
   <si>
     <t>纸飞机,一莲托生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银魂,昙天,阴天,云天,雾天</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4659,7 +4659,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4670,7 +4670,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,7 +4681,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,7 +4780,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,7 +4802,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,7 +4857,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,7 +4890,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,7 +4967,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,7 +4978,7 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -5055,7 +5055,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5066,7 +5066,7 @@
         <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5110,7 +5110,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5275,7 +5275,7 @@
         <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5415,10 +5415,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C71" t="s">
         <v>1152</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,7 +5506,7 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -5572,7 +5572,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5726,7 +5726,7 @@
         <v>171</v>
       </c>
       <c r="C99" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>186</v>
       </c>
       <c r="C107" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -5891,7 +5891,7 @@
         <v>199</v>
       </c>
       <c r="C114" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -5957,7 +5957,7 @@
         <v>210</v>
       </c>
       <c r="C120" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6045,7 +6045,7 @@
         <v>225</v>
       </c>
       <c r="C128" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6287,7 +6287,7 @@
         <v>267</v>
       </c>
       <c r="C150" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6331,7 +6331,7 @@
         <v>274</v>
       </c>
       <c r="C154" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6419,7 +6419,7 @@
         <v>289</v>
       </c>
       <c r="C162" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6507,7 +6507,7 @@
         <v>304</v>
       </c>
       <c r="C170" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -7156,7 +7156,7 @@
         <v>421</v>
       </c>
       <c r="C229" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7167,7 +7167,7 @@
         <v>422</v>
       </c>
       <c r="C230" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7387,7 +7387,7 @@
         <v>460</v>
       </c>
       <c r="C250" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7398,7 +7398,7 @@
         <v>461</v>
       </c>
       <c r="C251" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7464,7 +7464,7 @@
         <v>471</v>
       </c>
       <c r="C257" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7497,7 +7497,7 @@
         <v>476</v>
       </c>
       <c r="C260" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7585,7 +7585,7 @@
         <v>491</v>
       </c>
       <c r="C268" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7706,7 +7706,7 @@
         <v>512</v>
       </c>
       <c r="C279" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7717,7 +7717,7 @@
         <v>513</v>
       </c>
       <c r="C280" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7783,7 +7783,7 @@
         <v>524</v>
       </c>
       <c r="C286" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7882,7 +7882,7 @@
         <v>541</v>
       </c>
       <c r="C295" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -8102,7 +8102,7 @@
         <v>579</v>
       </c>
       <c r="C315" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8231,10 +8231,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C327" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8476,7 +8476,7 @@
         <v>643</v>
       </c>
       <c r="C349" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8520,7 +8520,7 @@
         <v>649</v>
       </c>
       <c r="C353" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8751,7 +8751,7 @@
         <v>690</v>
       </c>
       <c r="C374" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8784,7 +8784,7 @@
         <v>695</v>
       </c>
       <c r="C377" t="s">
-        <v>1097</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8806,7 +8806,7 @@
         <v>698</v>
       </c>
       <c r="C379" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8883,7 +8883,7 @@
         <v>711</v>
       </c>
       <c r="C386" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -9059,7 +9059,7 @@
         <v>742</v>
       </c>
       <c r="C402" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9100,10 +9100,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C406" t="s">
         <v>1210</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9114,7 +9114,7 @@
         <v>749</v>
       </c>
       <c r="C407" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9166,7 +9166,7 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C412" t="s">
         <v>758</v>
@@ -9177,7 +9177,7 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C413" t="s">
         <v>759</v>
@@ -9235,7 +9235,7 @@
         <v>768</v>
       </c>
       <c r="C418" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9246,7 +9246,7 @@
         <v>769</v>
       </c>
       <c r="C419" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9290,7 +9290,7 @@
         <v>776</v>
       </c>
       <c r="C423" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9312,7 +9312,7 @@
         <v>779</v>
       </c>
       <c r="C425" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9389,7 +9389,7 @@
         <v>790</v>
       </c>
       <c r="C432" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9554,7 +9554,7 @@
         <v>819</v>
       </c>
       <c r="C447" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9576,7 +9576,7 @@
         <v>822</v>
       </c>
       <c r="C449" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9598,7 +9598,7 @@
         <v>698</v>
       </c>
       <c r="C451" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9609,7 +9609,7 @@
         <v>825</v>
       </c>
       <c r="C452" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9653,7 +9653,7 @@
         <v>738</v>
       </c>
       <c r="C456" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9738,7 +9738,7 @@
         <v>843</v>
       </c>
       <c r="C464" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9749,7 +9749,7 @@
         <v>844</v>
       </c>
       <c r="C465" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>851</v>
       </c>
       <c r="C469" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9834,10 +9834,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C473" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9848,7 +9848,7 @@
         <v>858</v>
       </c>
       <c r="C474" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9881,7 +9881,7 @@
         <v>863</v>
       </c>
       <c r="C477" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9914,7 +9914,7 @@
         <v>867</v>
       </c>
       <c r="C480" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -10131,7 +10131,7 @@
         <v>905</v>
       </c>
       <c r="C500" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10161,10 +10161,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C503" t="s">
         <v>1112</v>
-      </c>
-      <c r="C503" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10186,7 +10186,7 @@
         <v>912</v>
       </c>
       <c r="C505" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10208,7 +10208,7 @@
         <v>915</v>
       </c>
       <c r="C507" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10274,7 +10274,7 @@
         <v>926</v>
       </c>
       <c r="C513" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10318,7 +10318,7 @@
         <v>931</v>
       </c>
       <c r="C517" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10337,7 +10337,7 @@
         <v>933</v>
       </c>
       <c r="C519" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10359,7 +10359,7 @@
         <v>936</v>
       </c>
       <c r="C521" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10370,7 +10370,7 @@
         <v>937</v>
       </c>
       <c r="C522" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10469,7 +10469,7 @@
         <v>954</v>
       </c>
       <c r="C531" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10524,7 +10524,7 @@
         <v>963</v>
       </c>
       <c r="C536" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10535,7 +10535,7 @@
         <v>964</v>
       </c>
       <c r="C537" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10546,7 +10546,7 @@
         <v>965</v>
       </c>
       <c r="C538" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10675,7 +10675,7 @@
         <v>986</v>
       </c>
       <c r="C550" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10741,7 +10741,7 @@
         <v>996</v>
       </c>
       <c r="C556" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10837,7 +10837,7 @@
         <v>1011</v>
       </c>
       <c r="C565" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10845,10 +10845,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C566" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10881,7 +10881,7 @@
         <v>1016</v>
       </c>
       <c r="C569" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10903,7 +10903,7 @@
         <v>1019</v>
       </c>
       <c r="C571" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10914,7 +10914,7 @@
         <v>1020</v>
       </c>
       <c r="C572" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10958,7 +10958,7 @@
         <v>1024</v>
       </c>
       <c r="C576" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -10969,7 +10969,7 @@
         <v>859</v>
       </c>
       <c r="C577" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -10980,7 +10980,7 @@
         <v>861</v>
       </c>
       <c r="C578" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11002,7 +11002,7 @@
         <v>1027</v>
       </c>
       <c r="C580" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11010,10 +11010,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C581" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11035,7 +11035,7 @@
         <v>1030</v>
       </c>
       <c r="C583" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11068,7 +11068,7 @@
         <v>1084</v>
       </c>
       <c r="C586" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11090,7 +11090,7 @@
         <v>1037</v>
       </c>
       <c r="C588" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11101,7 +11101,7 @@
         <v>1038</v>
       </c>
       <c r="C589" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11142,10 +11142,10 @@
         <v>644</v>
       </c>
       <c r="B593" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C593" t="s">
         <v>1266</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11156,7 +11156,7 @@
         <v>1045</v>
       </c>
       <c r="C594" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11164,10 +11164,10 @@
         <v>649</v>
       </c>
       <c r="B595" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C595" t="s">
         <v>1201</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11208,10 +11208,10 @@
         <v>654</v>
       </c>
       <c r="B599" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C599" t="s">
         <v>1155</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11230,10 +11230,10 @@
         <v>660</v>
       </c>
       <c r="B601" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C601" t="s">
         <v>1199</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11255,7 +11255,7 @@
         <v>1071</v>
       </c>
       <c r="C603" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11266,7 +11266,7 @@
         <v>1056</v>
       </c>
       <c r="C604" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11277,7 +11277,7 @@
         <v>1057</v>
       </c>
       <c r="C605" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11288,7 +11288,7 @@
         <v>1058</v>
       </c>
       <c r="C606" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11307,10 +11307,10 @@
         <v>681</v>
       </c>
       <c r="B608" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C608" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11332,7 +11332,7 @@
         <v>1070</v>
       </c>
       <c r="C610" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11373,10 +11373,10 @@
         <v>697</v>
       </c>
       <c r="B614" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C614" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11384,10 +11384,10 @@
         <v>701</v>
       </c>
       <c r="B615" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C615" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11395,10 +11395,10 @@
         <v>702</v>
       </c>
       <c r="B616" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C616" t="s">
         <v>1260</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11406,10 +11406,10 @@
         <v>704</v>
       </c>
       <c r="B617" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C617" t="s">
         <v>1098</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11417,10 +11417,10 @@
         <v>705</v>
       </c>
       <c r="B618" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C618" t="s">
         <v>1274</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11428,10 +11428,10 @@
         <v>710</v>
       </c>
       <c r="B619" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C619" t="s">
         <v>1194</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11439,10 +11439,10 @@
         <v>711</v>
       </c>
       <c r="B620" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C620" t="s">
         <v>1257</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11450,10 +11450,10 @@
         <v>713</v>
       </c>
       <c r="B621" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C621" t="s">
         <v>1255</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11461,10 +11461,10 @@
         <v>714</v>
       </c>
       <c r="B622" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C622" t="s">
         <v>1253</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11472,10 +11472,10 @@
         <v>717</v>
       </c>
       <c r="B623" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C623" t="s">
         <v>1251</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11483,10 +11483,10 @@
         <v>718</v>
       </c>
       <c r="B624" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C624" t="s">
         <v>1249</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11494,10 +11494,10 @@
         <v>719</v>
       </c>
       <c r="B625" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C625" t="s">
         <v>1247</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11505,10 +11505,10 @@
         <v>721</v>
       </c>
       <c r="B626" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C626" t="s">
         <v>1245</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11516,10 +11516,10 @@
         <v>722</v>
       </c>
       <c r="B627" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C627" t="s">
         <v>1243</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11527,10 +11527,10 @@
         <v>723</v>
       </c>
       <c r="B628" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C628" t="s">
         <v>1241</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11538,10 +11538,10 @@
         <v>725</v>
       </c>
       <c r="B629" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C629" t="s">
         <v>1239</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11549,10 +11549,10 @@
         <v>726</v>
       </c>
       <c r="B630" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C630" t="s">
         <v>1237</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11560,10 +11560,10 @@
         <v>727</v>
       </c>
       <c r="B631" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C631" t="s">
         <v>1235</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11571,10 +11571,10 @@
         <v>728</v>
       </c>
       <c r="B632" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C632" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="633" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11582,10 +11582,10 @@
         <v>729</v>
       </c>
       <c r="B633" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C633" t="s">
         <v>1232</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11593,10 +11593,10 @@
         <v>730</v>
       </c>
       <c r="B634" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C634" t="s">
         <v>1230</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11604,10 +11604,10 @@
         <v>731</v>
       </c>
       <c r="B635" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C635" t="s">
         <v>1228</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11615,10 +11615,10 @@
         <v>733</v>
       </c>
       <c r="B636" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C636" t="s">
         <v>1226</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11626,10 +11626,10 @@
         <v>735</v>
       </c>
       <c r="B637" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C637" t="s">
         <v>1224</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11637,10 +11637,10 @@
         <v>736</v>
       </c>
       <c r="B638" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C638" t="s">
         <v>1222</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11648,10 +11648,10 @@
         <v>737</v>
       </c>
       <c r="B639" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C639" t="s">
         <v>1263</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11659,10 +11659,10 @@
         <v>738</v>
       </c>
       <c r="B640" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C640" t="s">
         <v>1220</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11670,10 +11670,10 @@
         <v>739</v>
       </c>
       <c r="B641" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C641" t="s">
         <v>1218</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11681,10 +11681,10 @@
         <v>740</v>
       </c>
       <c r="B642" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C642" t="s">
         <v>1216</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11692,10 +11692,10 @@
         <v>741</v>
       </c>
       <c r="B643" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C643" t="s">
         <v>1214</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11703,10 +11703,10 @@
         <v>742</v>
       </c>
       <c r="B644" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C644" t="s">
         <v>1276</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11714,10 +11714,10 @@
         <v>743</v>
       </c>
       <c r="B645" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C645" t="s">
         <v>1278</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11725,10 +11725,10 @@
         <v>744</v>
       </c>
       <c r="B646" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C646" t="s">
         <v>1280</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="647" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11736,10 +11736,10 @@
         <v>745</v>
       </c>
       <c r="B647" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C647" t="s">
         <v>1282</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11747,10 +11747,10 @@
         <v>746</v>
       </c>
       <c r="B648" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C648" t="s">
         <v>1284</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11758,10 +11758,10 @@
         <v>747</v>
       </c>
       <c r="B649" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C649" t="s">
         <v>1286</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147848EE-97A9-492C-B829-8CDEB0A023BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D180F51-2942-4753-8B46-4382496C0AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12192" yWindow="1776" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="1293">
   <si>
     <t>Id</t>
   </si>
@@ -4212,6 +4212,22 @@
   </si>
   <si>
     <t>银魂,昙天,阴天,云天,雾天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聿日箋秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Imprisoned XI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香草祥子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>书日,一日,春秋,書日千秋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4631,7 +4647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C651"/>
+  <dimension ref="A1:C653"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -11271,518 +11287,540 @@
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B605" t="s">
-        <v>1057</v>
+        <v>1290</v>
       </c>
       <c r="C605" t="s">
-        <v>1116</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B606" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C606" t="s">
-        <v>1196</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B607" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C607" t="s">
-        <v>1076</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B608" t="s">
-        <v>1195</v>
+        <v>1059</v>
       </c>
       <c r="C608" t="s">
-        <v>1197</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B609" t="s">
-        <v>1060</v>
+        <v>1195</v>
       </c>
       <c r="C609" t="s">
-        <v>1061</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B610" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="C610" t="s">
-        <v>1167</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B611" t="s">
-        <v>1062</v>
+        <v>1289</v>
       </c>
       <c r="C611" t="s">
-        <v>1063</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B612" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C612" t="s">
-        <v>1065</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B613" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C613" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="B614" t="s">
-        <v>1148</v>
+        <v>1064</v>
       </c>
       <c r="C614" t="s">
-        <v>1270</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="B615" t="s">
-        <v>1183</v>
+        <v>1066</v>
       </c>
       <c r="C615" t="s">
-        <v>1182</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="B616" t="s">
-        <v>1259</v>
+        <v>1148</v>
       </c>
       <c r="C616" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B617" t="s">
-        <v>1097</v>
+        <v>1183</v>
       </c>
       <c r="C617" t="s">
-        <v>1098</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B618" t="s">
-        <v>1273</v>
+        <v>1259</v>
       </c>
       <c r="C618" t="s">
-        <v>1274</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B619" t="s">
-        <v>1193</v>
+        <v>1097</v>
       </c>
       <c r="C619" t="s">
-        <v>1194</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B620" t="s">
-        <v>1256</v>
+        <v>1273</v>
       </c>
       <c r="C620" t="s">
-        <v>1257</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B621" t="s">
-        <v>1254</v>
+        <v>1193</v>
       </c>
       <c r="C621" t="s">
-        <v>1255</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B622" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="C622" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B623" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="C623" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B624" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="C624" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B625" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="C625" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B626" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="C626" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B627" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="C627" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A628">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B628" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="C628" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>725</v>
-      </c>
-      <c r="B629" s="1" t="s">
-        <v>1238</v>
+        <v>722</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1242</v>
       </c>
       <c r="C629" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B630" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="C630" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631">
+        <v>725</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C631" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A632">
+        <v>726</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C632" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A633">
         <v>727</v>
       </c>
-      <c r="B631" t="s">
+      <c r="B633" t="s">
         <v>1234</v>
       </c>
-      <c r="C631" t="s">
+      <c r="C633" t="s">
         <v>1235</v>
       </c>
     </row>
-    <row r="632" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A632">
+    <row r="634" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A634">
         <v>728</v>
       </c>
-      <c r="B632" t="s">
+      <c r="B634" t="s">
         <v>1233</v>
       </c>
-      <c r="C632" t="s">
+      <c r="C634" t="s">
         <v>1258</v>
       </c>
     </row>
-    <row r="633" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A633">
+    <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A635">
         <v>729</v>
       </c>
-      <c r="B633" t="s">
+      <c r="B635" t="s">
         <v>1231</v>
       </c>
-      <c r="C633" t="s">
+      <c r="C635" t="s">
         <v>1232</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A634">
-        <v>730</v>
-      </c>
-      <c r="B634" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A635">
-        <v>731</v>
-      </c>
-      <c r="B635" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B636" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="C636" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B637" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="C637" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B638" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="C638" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B639" t="s">
-        <v>1262</v>
+        <v>1223</v>
       </c>
       <c r="C639" t="s">
-        <v>1263</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B640" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C640" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B641" t="s">
-        <v>1217</v>
+        <v>1262</v>
       </c>
       <c r="C641" t="s">
-        <v>1218</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B642" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="C642" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B643" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="C643" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B644" t="s">
-        <v>1275</v>
+        <v>1215</v>
       </c>
       <c r="C644" t="s">
-        <v>1276</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B645" t="s">
-        <v>1277</v>
+        <v>1213</v>
       </c>
       <c r="C645" t="s">
-        <v>1278</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B646" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="C646" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>745</v>
-      </c>
-      <c r="B647" s="2" t="s">
-        <v>1281</v>
+        <v>743</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1277</v>
       </c>
       <c r="C647" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>746</v>
-      </c>
-      <c r="B648" s="2" t="s">
-        <v>1283</v>
+        <v>744</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1279</v>
       </c>
       <c r="C648" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A649">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="C649" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>10001</v>
-      </c>
-      <c r="B650" t="s">
-        <v>1068</v>
+        <v>746</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>1283</v>
       </c>
       <c r="C650" t="s">
-        <v>1069</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651">
+        <v>747</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C651" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A652">
+        <v>10001</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C652" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A653">
         <v>10003</v>
       </c>
-      <c r="B651" t="s">
+      <c r="B653" t="s">
         <v>1095</v>
       </c>
-      <c r="C651" t="s">
+      <c r="C653" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -11791,7 +11829,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A650:C650 A315:B315 A316:C326 A352:C352 A351:B351 A587:C587 A575 A574:B574 A460:C463 A459:B459 A609:C609 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A611:C613 A258:C259 A257:B257 A6:C7 A573:C573 A571:B571 A567:C568 A566 A602:C602 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A604:B607 A576:B578 A514:C514 A513:B513 A501:C502 A500:B500 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A279:B279 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C144 A128:B128 A71 A9:C12 A8:B8 A590:C592 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A536:B537 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A596:C598 A594:B594 A588:B589 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A600:C600 A584:C585 A583:B583 A572:B572 A24:C27 A23:B23 A499:B499 A414:C417 A413 C413 A412 C412 A406 A375:C376 A374:B374 A280:B280 A538:B538 A474:B474" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A652:C652 A315:B315 A316:C326 A352:C352 A351:B351 A587:C587 A575 A574:B574 A460:C463 A459:B459 A610:C610 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A613:C615 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A602:C602 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A606:B608 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C144 A128:B128 A71 A9:C12 A8:B8 A590:C592 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A596:C598 A594:B594 A588:B589 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A600:C600 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A604:B604" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D180F51-2942-4753-8B46-4382496C0AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24996190-B04E-4BC8-9964-E8C22CBE0022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12192" yWindow="1776" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="1293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="1297">
   <si>
     <t>Id</t>
   </si>
@@ -4228,6 +4228,22 @@
   </si>
   <si>
     <t>书日,一日,春秋,書日千秋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>クラクラ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kurakura,kura kura</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名無声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名无声,名无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4647,7 +4663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C653"/>
+  <dimension ref="A1:C655"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -11089,738 +11105,760 @@
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B587" t="s">
-        <v>1035</v>
+        <v>1295</v>
       </c>
       <c r="C587" t="s">
-        <v>1036</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B588" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C588" t="s">
-        <v>1180</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B589" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C589" t="s">
-        <v>1103</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B590" t="s">
-        <v>1039</v>
+        <v>1293</v>
       </c>
       <c r="C590" t="s">
-        <v>1040</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B591" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C591" t="s">
-        <v>1042</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="B592" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="C592" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B593" t="s">
-        <v>1265</v>
+        <v>1041</v>
       </c>
       <c r="C593" t="s">
-        <v>1266</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B594" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C594" t="s">
-        <v>1179</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="B595" t="s">
-        <v>1200</v>
+        <v>1265</v>
       </c>
       <c r="C595" t="s">
-        <v>1201</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B596" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C596" t="s">
-        <v>1047</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B597" t="s">
-        <v>1048</v>
+        <v>1200</v>
       </c>
       <c r="C597" t="s">
-        <v>1049</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B598" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="C598" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B599" t="s">
-        <v>1154</v>
+        <v>1048</v>
       </c>
       <c r="C599" t="s">
-        <v>1155</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B600" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C600" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B601" t="s">
-        <v>1198</v>
+        <v>1154</v>
       </c>
       <c r="C601" t="s">
-        <v>1199</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B602" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C602" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B603" t="s">
-        <v>1071</v>
+        <v>1198</v>
       </c>
       <c r="C603" t="s">
-        <v>1261</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="B604" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C604" t="s">
-        <v>1126</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="B605" t="s">
-        <v>1290</v>
+        <v>1071</v>
       </c>
       <c r="C605" t="s">
-        <v>1291</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="B606" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C606" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B607" t="s">
-        <v>1058</v>
+        <v>1290</v>
       </c>
       <c r="C607" t="s">
-        <v>1196</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="B608" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C608" t="s">
-        <v>1076</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B609" t="s">
-        <v>1195</v>
+        <v>1058</v>
       </c>
       <c r="C609" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B610" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C610" t="s">
-        <v>1061</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B611" t="s">
-        <v>1289</v>
+        <v>1195</v>
       </c>
       <c r="C611" t="s">
-        <v>1292</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B612" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="C612" t="s">
-        <v>1167</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B613" t="s">
-        <v>1062</v>
+        <v>1289</v>
       </c>
       <c r="C613" t="s">
-        <v>1063</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B614" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="C614" t="s">
-        <v>1065</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B615" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C615" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="B616" t="s">
-        <v>1148</v>
+        <v>1064</v>
       </c>
       <c r="C616" t="s">
-        <v>1270</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="B617" t="s">
-        <v>1183</v>
+        <v>1066</v>
       </c>
       <c r="C617" t="s">
-        <v>1182</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="B618" t="s">
-        <v>1259</v>
+        <v>1148</v>
       </c>
       <c r="C618" t="s">
-        <v>1260</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B619" t="s">
-        <v>1097</v>
+        <v>1183</v>
       </c>
       <c r="C619" t="s">
-        <v>1098</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B620" t="s">
-        <v>1273</v>
+        <v>1259</v>
       </c>
       <c r="C620" t="s">
-        <v>1274</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B621" t="s">
-        <v>1193</v>
+        <v>1097</v>
       </c>
       <c r="C621" t="s">
-        <v>1194</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B622" t="s">
-        <v>1256</v>
+        <v>1273</v>
       </c>
       <c r="C622" t="s">
-        <v>1257</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B623" t="s">
-        <v>1254</v>
+        <v>1193</v>
       </c>
       <c r="C623" t="s">
-        <v>1255</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B624" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="C624" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B625" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="C625" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B626" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="C626" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B627" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="C627" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B628" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="C628" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B629" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="C629" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A630">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B630" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="C630" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631">
-        <v>725</v>
-      </c>
-      <c r="B631" s="1" t="s">
-        <v>1238</v>
+        <v>722</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1242</v>
       </c>
       <c r="C631" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B632" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="C632" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633">
+        <v>725</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C633" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A634">
+        <v>726</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C634" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A635">
         <v>727</v>
       </c>
-      <c r="B633" t="s">
+      <c r="B635" t="s">
         <v>1234</v>
       </c>
-      <c r="C633" t="s">
+      <c r="C635" t="s">
         <v>1235</v>
       </c>
     </row>
-    <row r="634" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A634">
+    <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A636">
         <v>728</v>
       </c>
-      <c r="B634" t="s">
+      <c r="B636" t="s">
         <v>1233</v>
       </c>
-      <c r="C634" t="s">
+      <c r="C636" t="s">
         <v>1258</v>
       </c>
     </row>
-    <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A635">
+    <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A637">
         <v>729</v>
       </c>
-      <c r="B635" t="s">
+      <c r="B637" t="s">
         <v>1231</v>
       </c>
-      <c r="C635" t="s">
+      <c r="C637" t="s">
         <v>1232</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A636">
-        <v>730</v>
-      </c>
-      <c r="B636" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A637">
-        <v>731</v>
-      </c>
-      <c r="B637" t="s">
-        <v>1227</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B638" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="C638" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B639" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="C639" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B640" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="C640" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B641" t="s">
-        <v>1262</v>
+        <v>1223</v>
       </c>
       <c r="C641" t="s">
-        <v>1263</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B642" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C642" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B643" t="s">
-        <v>1217</v>
+        <v>1262</v>
       </c>
       <c r="C643" t="s">
-        <v>1218</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B644" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="C644" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B645" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="C645" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B646" t="s">
-        <v>1275</v>
+        <v>1215</v>
       </c>
       <c r="C646" t="s">
-        <v>1276</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B647" t="s">
-        <v>1277</v>
+        <v>1213</v>
       </c>
       <c r="C647" t="s">
-        <v>1278</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B648" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="C648" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>745</v>
-      </c>
-      <c r="B649" s="2" t="s">
-        <v>1281</v>
+        <v>743</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1277</v>
       </c>
       <c r="C649" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>746</v>
-      </c>
-      <c r="B650" s="2" t="s">
-        <v>1283</v>
+        <v>744</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1279</v>
       </c>
       <c r="C650" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A651">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="C651" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652">
-        <v>10001</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1068</v>
+        <v>746</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>1283</v>
       </c>
       <c r="C652" t="s">
-        <v>1069</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653">
+        <v>747</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C653" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A654">
+        <v>10001</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A655">
         <v>10003</v>
       </c>
-      <c r="B653" t="s">
+      <c r="B655" t="s">
         <v>1095</v>
       </c>
-      <c r="C653" t="s">
+      <c r="C655" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -11829,7 +11867,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A652:C652 A315:B315 A316:C326 A352:C352 A351:B351 A587:C587 A575 A574:B574 A460:C463 A459:B459 A610:C610 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A613:C615 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A602:C602 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A606:B608 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C144 A128:B128 A71 A9:C12 A8:B8 A590:C592 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A596:C598 A594:B594 A588:B589 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A600:C600 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A604:B604" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A654:C654 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C144 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24996190-B04E-4BC8-9964-E8C22CBE0022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5197F6A-2B9C-4D84-BB7F-3B9114FE1C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="1297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="1305">
   <si>
     <t>Id</t>
   </si>
@@ -4244,6 +4244,38 @@
   </si>
   <si>
     <t>名无声,名无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drown Out the Noise and Push Through the Trash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屏蔽噪音,穿过垃圾堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手を叩け今ここで祈るだけ願うだけ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拍拍手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恋人がサンタクロース</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恋人,圣诞老人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まぶしいねっ☆ そのえがお！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迷人的笑容,笑容迷人,迷人笑容</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4663,7 +4695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C655"/>
+  <dimension ref="A1:C659"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -11842,23 +11874,67 @@
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654">
-        <v>10001</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1068</v>
+        <v>748</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>1303</v>
       </c>
       <c r="C654" t="s">
-        <v>1069</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
+        <v>749</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C655" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A656">
+        <v>753</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C656" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A657">
+        <v>755</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C657" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A658">
+        <v>10001</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C658" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A659">
         <v>10003</v>
       </c>
-      <c r="B655" t="s">
+      <c r="B659" t="s">
         <v>1095</v>
       </c>
-      <c r="C655" t="s">
+      <c r="C659" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -11867,7 +11943,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A654:C654 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C144 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A658:C658 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C144 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5197F6A-2B9C-4D84-BB7F-3B9114FE1C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B943BB9-34E9-46AB-8B58-EB5A53E3DA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12792" yWindow="3396" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -727,9 +727,6 @@
     <t>GO! GO! MANIAC</t>
   </si>
   <si>
-    <t>锅盖面,ggm,k-on,kon,轻音少女</t>
-  </si>
-  <si>
     <t>Sanctuary</t>
   </si>
   <si>
@@ -3341,10 +3338,6 @@
   </si>
   <si>
     <t>ロケットサイダー</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>漂流瓶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4276,6 +4269,14 @@
   </si>
   <si>
     <t>迷人的笑容,笑容迷人,迷人笑容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漂流瓶,火箭苹果酒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锅盖面,ggm,k-on,kon,轻音少女,鬼歌,鬼哥</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4723,7 +4724,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4734,7 +4735,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4745,7 +4746,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4756,7 +4757,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4789,7 +4790,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4844,7 +4845,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4866,7 +4867,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4921,7 +4922,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4954,7 +4955,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5009,7 +5010,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5031,7 +5032,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5042,7 +5043,7 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -5119,7 +5120,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5130,7 +5131,7 @@
         <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5174,7 +5175,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5262,7 +5263,7 @@
         <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -5284,7 +5285,7 @@
         <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -5295,7 +5296,7 @@
         <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -5339,7 +5340,7 @@
         <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5471,7 +5472,7 @@
         <v>120</v>
       </c>
       <c r="C70" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -5479,10 +5480,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C71" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -5570,7 +5571,7 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -5636,7 +5637,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5724,7 +5725,7 @@
         <v>161</v>
       </c>
       <c r="C93" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -5735,7 +5736,7 @@
         <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -5790,7 +5791,7 @@
         <v>171</v>
       </c>
       <c r="C99" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -5878,7 +5879,7 @@
         <v>186</v>
       </c>
       <c r="C107" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -5955,7 +5956,7 @@
         <v>199</v>
       </c>
       <c r="C114" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -6021,7 +6022,7 @@
         <v>210</v>
       </c>
       <c r="C120" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6109,7 +6110,7 @@
         <v>225</v>
       </c>
       <c r="C128" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6164,7 +6165,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>235</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6172,10 +6173,10 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
+        <v>235</v>
+      </c>
+      <c r="C134" t="s">
         <v>236</v>
-      </c>
-      <c r="C134" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -6183,10 +6184,10 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
+        <v>237</v>
+      </c>
+      <c r="C135" t="s">
         <v>238</v>
-      </c>
-      <c r="C135" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -6194,10 +6195,10 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
+        <v>239</v>
+      </c>
+      <c r="C136" t="s">
         <v>240</v>
-      </c>
-      <c r="C136" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -6205,10 +6206,10 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
+        <v>241</v>
+      </c>
+      <c r="C137" t="s">
         <v>242</v>
-      </c>
-      <c r="C137" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -6216,10 +6217,10 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
+        <v>243</v>
+      </c>
+      <c r="C138" t="s">
         <v>244</v>
-      </c>
-      <c r="C138" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -6227,10 +6228,10 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
+        <v>245</v>
+      </c>
+      <c r="C139" t="s">
         <v>246</v>
-      </c>
-      <c r="C139" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -6238,10 +6239,10 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
+        <v>247</v>
+      </c>
+      <c r="C140" t="s">
         <v>248</v>
-      </c>
-      <c r="C140" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -6249,10 +6250,10 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
+        <v>249</v>
+      </c>
+      <c r="C141" t="s">
         <v>250</v>
-      </c>
-      <c r="C141" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -6260,10 +6261,10 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
+        <v>251</v>
+      </c>
+      <c r="C142" t="s">
         <v>252</v>
-      </c>
-      <c r="C142" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -6271,10 +6272,10 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
+        <v>253</v>
+      </c>
+      <c r="C143" t="s">
         <v>254</v>
-      </c>
-      <c r="C143" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -6282,10 +6283,10 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
+        <v>255</v>
+      </c>
+      <c r="C144" t="s">
         <v>256</v>
-      </c>
-      <c r="C144" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -6293,10 +6294,10 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C145" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6304,10 +6305,10 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
+        <v>258</v>
+      </c>
+      <c r="C146" t="s">
         <v>259</v>
-      </c>
-      <c r="C146" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -6315,10 +6316,10 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
+        <v>260</v>
+      </c>
+      <c r="C147" t="s">
         <v>261</v>
-      </c>
-      <c r="C147" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -6326,10 +6327,10 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
+        <v>262</v>
+      </c>
+      <c r="C148" t="s">
         <v>263</v>
-      </c>
-      <c r="C148" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -6337,10 +6338,10 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
+        <v>264</v>
+      </c>
+      <c r="C149" t="s">
         <v>265</v>
-      </c>
-      <c r="C149" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -6348,10 +6349,10 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6359,10 +6360,10 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
+        <v>267</v>
+      </c>
+      <c r="C151" t="s">
         <v>268</v>
-      </c>
-      <c r="C151" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -6370,10 +6371,10 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
+        <v>269</v>
+      </c>
+      <c r="C152" t="s">
         <v>270</v>
-      </c>
-      <c r="C152" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -6381,10 +6382,10 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
+        <v>271</v>
+      </c>
+      <c r="C153" t="s">
         <v>272</v>
-      </c>
-      <c r="C153" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -6392,10 +6393,10 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C154" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6403,10 +6404,10 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
+        <v>274</v>
+      </c>
+      <c r="C155" t="s">
         <v>275</v>
-      </c>
-      <c r="C155" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -6414,10 +6415,10 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
+        <v>276</v>
+      </c>
+      <c r="C156" t="s">
         <v>277</v>
-      </c>
-      <c r="C156" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -6425,10 +6426,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
+        <v>278</v>
+      </c>
+      <c r="C157" t="s">
         <v>279</v>
-      </c>
-      <c r="C157" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -6436,10 +6437,10 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
+        <v>280</v>
+      </c>
+      <c r="C158" t="s">
         <v>281</v>
-      </c>
-      <c r="C158" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -6447,10 +6448,10 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
+        <v>282</v>
+      </c>
+      <c r="C159" t="s">
         <v>283</v>
-      </c>
-      <c r="C159" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -6458,10 +6459,10 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
+        <v>284</v>
+      </c>
+      <c r="C160" t="s">
         <v>285</v>
-      </c>
-      <c r="C160" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -6469,10 +6470,10 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
+        <v>286</v>
+      </c>
+      <c r="C161" t="s">
         <v>287</v>
-      </c>
-      <c r="C161" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -6480,10 +6481,10 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C162" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6491,10 +6492,10 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
+        <v>289</v>
+      </c>
+      <c r="C163" t="s">
         <v>290</v>
-      </c>
-      <c r="C163" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -6502,10 +6503,10 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
+        <v>291</v>
+      </c>
+      <c r="C164" t="s">
         <v>292</v>
-      </c>
-      <c r="C164" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -6513,10 +6514,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
+        <v>293</v>
+      </c>
+      <c r="C165" t="s">
         <v>294</v>
-      </c>
-      <c r="C165" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -6524,10 +6525,10 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
+        <v>295</v>
+      </c>
+      <c r="C166" t="s">
         <v>296</v>
-      </c>
-      <c r="C166" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -6535,10 +6536,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
+        <v>297</v>
+      </c>
+      <c r="C167" t="s">
         <v>298</v>
-      </c>
-      <c r="C167" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6546,10 +6547,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>299</v>
+      </c>
+      <c r="C168" t="s">
         <v>300</v>
-      </c>
-      <c r="C168" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6557,10 +6558,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>301</v>
+      </c>
+      <c r="C169" t="s">
         <v>302</v>
-      </c>
-      <c r="C169" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6568,10 +6569,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C170" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6579,10 +6580,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>304</v>
+      </c>
+      <c r="C171" t="s">
         <v>305</v>
-      </c>
-      <c r="C171" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6590,10 +6591,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>306</v>
+      </c>
+      <c r="C172" t="s">
         <v>307</v>
-      </c>
-      <c r="C172" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6601,10 +6602,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>308</v>
+      </c>
+      <c r="C173" t="s">
         <v>309</v>
-      </c>
-      <c r="C173" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6612,10 +6613,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>310</v>
+      </c>
+      <c r="C174" t="s">
         <v>311</v>
-      </c>
-      <c r="C174" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6623,10 +6624,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>312</v>
+      </c>
+      <c r="C175" t="s">
         <v>313</v>
-      </c>
-      <c r="C175" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6634,10 +6635,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>314</v>
+      </c>
+      <c r="C176" t="s">
         <v>315</v>
-      </c>
-      <c r="C176" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6645,10 +6646,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>316</v>
+      </c>
+      <c r="C177" t="s">
         <v>317</v>
-      </c>
-      <c r="C177" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6656,10 +6657,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>318</v>
+      </c>
+      <c r="C178" t="s">
         <v>319</v>
-      </c>
-      <c r="C178" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6667,10 +6668,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>320</v>
+      </c>
+      <c r="C179" t="s">
         <v>321</v>
-      </c>
-      <c r="C179" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6678,10 +6679,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>322</v>
+      </c>
+      <c r="C180" t="s">
         <v>323</v>
-      </c>
-      <c r="C180" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6689,10 +6690,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>324</v>
+      </c>
+      <c r="C181" t="s">
         <v>325</v>
-      </c>
-      <c r="C181" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6700,10 +6701,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>326</v>
+      </c>
+      <c r="C182" t="s">
         <v>327</v>
-      </c>
-      <c r="C182" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6711,10 +6712,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>328</v>
+      </c>
+      <c r="C183" t="s">
         <v>329</v>
-      </c>
-      <c r="C183" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6722,10 +6723,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>330</v>
+      </c>
+      <c r="C184" t="s">
         <v>331</v>
-      </c>
-      <c r="C184" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6733,10 +6734,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>332</v>
+      </c>
+      <c r="C185" t="s">
         <v>333</v>
-      </c>
-      <c r="C185" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6744,10 +6745,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>334</v>
+      </c>
+      <c r="C186" t="s">
         <v>335</v>
-      </c>
-      <c r="C186" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6755,10 +6756,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>336</v>
+      </c>
+      <c r="C187" t="s">
         <v>337</v>
-      </c>
-      <c r="C187" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6766,10 +6767,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>338</v>
+      </c>
+      <c r="C188" t="s">
         <v>339</v>
-      </c>
-      <c r="C188" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -6777,10 +6778,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>340</v>
+      </c>
+      <c r="C189" t="s">
         <v>341</v>
-      </c>
-      <c r="C189" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -6788,10 +6789,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>342</v>
+      </c>
+      <c r="C190" t="s">
         <v>343</v>
-      </c>
-      <c r="C190" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -6799,10 +6800,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>344</v>
+      </c>
+      <c r="C191" t="s">
         <v>345</v>
-      </c>
-      <c r="C191" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -6810,10 +6811,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>346</v>
+      </c>
+      <c r="C192" t="s">
         <v>347</v>
-      </c>
-      <c r="C192" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -6821,10 +6822,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>348</v>
+      </c>
+      <c r="C193" t="s">
         <v>349</v>
-      </c>
-      <c r="C193" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -6832,10 +6833,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>350</v>
+      </c>
+      <c r="C194" t="s">
         <v>351</v>
-      </c>
-      <c r="C194" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -6843,10 +6844,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>352</v>
+      </c>
+      <c r="C195" t="s">
         <v>353</v>
-      </c>
-      <c r="C195" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -6854,10 +6855,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>354</v>
+      </c>
+      <c r="C196" t="s">
         <v>355</v>
-      </c>
-      <c r="C196" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -6865,10 +6866,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>356</v>
+      </c>
+      <c r="C197" t="s">
         <v>357</v>
-      </c>
-      <c r="C197" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -6876,10 +6877,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>358</v>
+      </c>
+      <c r="C198" t="s">
         <v>359</v>
-      </c>
-      <c r="C198" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -6887,10 +6888,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>360</v>
+      </c>
+      <c r="C199" t="s">
         <v>361</v>
-      </c>
-      <c r="C199" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -6898,10 +6899,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>362</v>
+      </c>
+      <c r="C200" t="s">
         <v>363</v>
-      </c>
-      <c r="C200" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -6909,10 +6910,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>364</v>
+      </c>
+      <c r="C201" t="s">
         <v>365</v>
-      </c>
-      <c r="C201" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -6920,10 +6921,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>366</v>
+      </c>
+      <c r="C202" t="s">
         <v>367</v>
-      </c>
-      <c r="C202" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -6931,10 +6932,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>368</v>
+      </c>
+      <c r="C203" t="s">
         <v>369</v>
-      </c>
-      <c r="C203" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -6942,10 +6943,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>370</v>
+      </c>
+      <c r="C204" t="s">
         <v>371</v>
-      </c>
-      <c r="C204" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -6953,10 +6954,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>372</v>
+      </c>
+      <c r="C205" t="s">
         <v>373</v>
-      </c>
-      <c r="C205" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -6964,10 +6965,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>374</v>
+      </c>
+      <c r="C206" t="s">
         <v>375</v>
-      </c>
-      <c r="C206" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -6975,10 +6976,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>376</v>
+      </c>
+      <c r="C207" t="s">
         <v>377</v>
-      </c>
-      <c r="C207" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -6986,10 +6987,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
+        <v>378</v>
+      </c>
+      <c r="C208" t="s">
         <v>379</v>
-      </c>
-      <c r="C208" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -6997,10 +6998,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
+        <v>380</v>
+      </c>
+      <c r="C209" t="s">
         <v>381</v>
-      </c>
-      <c r="C209" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7008,10 +7009,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
+        <v>382</v>
+      </c>
+      <c r="C210" t="s">
         <v>383</v>
-      </c>
-      <c r="C210" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -7019,10 +7020,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
+        <v>384</v>
+      </c>
+      <c r="C211" t="s">
         <v>385</v>
-      </c>
-      <c r="C211" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -7030,10 +7031,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>386</v>
+      </c>
+      <c r="C212" t="s">
         <v>387</v>
-      </c>
-      <c r="C212" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -7041,10 +7042,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>388</v>
+      </c>
+      <c r="C213" t="s">
         <v>389</v>
-      </c>
-      <c r="C213" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7052,10 +7053,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>390</v>
+      </c>
+      <c r="C214" t="s">
         <v>391</v>
-      </c>
-      <c r="C214" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7063,10 +7064,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>392</v>
+      </c>
+      <c r="C215" t="s">
         <v>393</v>
-      </c>
-      <c r="C215" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7074,10 +7075,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>394</v>
+      </c>
+      <c r="C216" t="s">
         <v>395</v>
-      </c>
-      <c r="C216" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7085,10 +7086,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>396</v>
+      </c>
+      <c r="C217" t="s">
         <v>397</v>
-      </c>
-      <c r="C217" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7096,10 +7097,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>398</v>
+      </c>
+      <c r="C218" t="s">
         <v>399</v>
-      </c>
-      <c r="C218" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7107,10 +7108,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>400</v>
+      </c>
+      <c r="C219" t="s">
         <v>401</v>
-      </c>
-      <c r="C219" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7118,10 +7119,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>402</v>
+      </c>
+      <c r="C220" t="s">
         <v>403</v>
-      </c>
-      <c r="C220" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7129,10 +7130,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>404</v>
+      </c>
+      <c r="C221" t="s">
         <v>405</v>
-      </c>
-      <c r="C221" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7140,10 +7141,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>406</v>
+      </c>
+      <c r="C222" t="s">
         <v>407</v>
-      </c>
-      <c r="C222" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7151,10 +7152,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>408</v>
+      </c>
+      <c r="C223" t="s">
         <v>409</v>
-      </c>
-      <c r="C223" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7162,10 +7163,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
+        <v>410</v>
+      </c>
+      <c r="C224" t="s">
         <v>411</v>
-      </c>
-      <c r="C224" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7173,10 +7174,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>412</v>
+      </c>
+      <c r="C225" t="s">
         <v>413</v>
-      </c>
-      <c r="C225" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7184,10 +7185,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>414</v>
+      </c>
+      <c r="C226" t="s">
         <v>415</v>
-      </c>
-      <c r="C226" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7195,10 +7196,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>416</v>
+      </c>
+      <c r="C227" t="s">
         <v>417</v>
-      </c>
-      <c r="C227" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7206,10 +7207,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>418</v>
+      </c>
+      <c r="C228" t="s">
         <v>419</v>
-      </c>
-      <c r="C228" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7217,10 +7218,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C229" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7228,10 +7229,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C230" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7239,10 +7240,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>422</v>
+      </c>
+      <c r="C231" t="s">
         <v>423</v>
-      </c>
-      <c r="C231" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7250,10 +7251,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>424</v>
+      </c>
+      <c r="C232" t="s">
         <v>425</v>
-      </c>
-      <c r="C232" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7261,10 +7262,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>426</v>
+      </c>
+      <c r="C233" t="s">
         <v>427</v>
-      </c>
-      <c r="C233" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7272,10 +7273,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C234" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7283,10 +7284,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>429</v>
+      </c>
+      <c r="C235" t="s">
         <v>430</v>
-      </c>
-      <c r="C235" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7294,10 +7295,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>431</v>
+      </c>
+      <c r="C236" t="s">
         <v>432</v>
-      </c>
-      <c r="C236" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7305,10 +7306,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>433</v>
+      </c>
+      <c r="C237" t="s">
         <v>434</v>
-      </c>
-      <c r="C237" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7316,10 +7317,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>435</v>
+      </c>
+      <c r="C238" t="s">
         <v>436</v>
-      </c>
-      <c r="C238" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7327,10 +7328,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>437</v>
+      </c>
+      <c r="C239" t="s">
         <v>438</v>
-      </c>
-      <c r="C239" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7338,10 +7339,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>439</v>
+      </c>
+      <c r="C240" t="s">
         <v>440</v>
-      </c>
-      <c r="C240" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7349,10 +7350,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>441</v>
+      </c>
+      <c r="C241" t="s">
         <v>442</v>
-      </c>
-      <c r="C241" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7360,10 +7361,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>443</v>
+      </c>
+      <c r="C242" t="s">
         <v>444</v>
-      </c>
-      <c r="C242" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7371,10 +7372,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>445</v>
+      </c>
+      <c r="C243" t="s">
         <v>446</v>
-      </c>
-      <c r="C243" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7382,10 +7383,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>447</v>
+      </c>
+      <c r="C244" t="s">
         <v>448</v>
-      </c>
-      <c r="C244" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7393,10 +7394,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>449</v>
+      </c>
+      <c r="C245" t="s">
         <v>450</v>
-      </c>
-      <c r="C245" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7404,10 +7405,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>451</v>
+      </c>
+      <c r="C246" t="s">
         <v>452</v>
-      </c>
-      <c r="C246" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7415,10 +7416,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>453</v>
+      </c>
+      <c r="C247" t="s">
         <v>454</v>
-      </c>
-      <c r="C247" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7426,10 +7427,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>455</v>
+      </c>
+      <c r="C248" t="s">
         <v>456</v>
-      </c>
-      <c r="C248" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7437,10 +7438,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>457</v>
+      </c>
+      <c r="C249" t="s">
         <v>458</v>
-      </c>
-      <c r="C249" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7448,10 +7449,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C250" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7459,10 +7460,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C251" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7470,10 +7471,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C252" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7481,10 +7482,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>462</v>
+      </c>
+      <c r="C253" t="s">
         <v>463</v>
-      </c>
-      <c r="C253" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7492,10 +7493,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>464</v>
+      </c>
+      <c r="C254" t="s">
         <v>465</v>
-      </c>
-      <c r="C254" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7503,10 +7504,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>466</v>
+      </c>
+      <c r="C255" t="s">
         <v>467</v>
-      </c>
-      <c r="C255" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7514,10 +7515,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>468</v>
+      </c>
+      <c r="C256" t="s">
         <v>469</v>
-      </c>
-      <c r="C256" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7525,10 +7526,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C257" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7536,10 +7537,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>471</v>
+      </c>
+      <c r="C258" t="s">
         <v>472</v>
-      </c>
-      <c r="C258" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7547,10 +7548,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>473</v>
+      </c>
+      <c r="C259" t="s">
         <v>474</v>
-      </c>
-      <c r="C259" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7558,10 +7559,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C260" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7569,10 +7570,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>476</v>
+      </c>
+      <c r="C261" t="s">
         <v>477</v>
-      </c>
-      <c r="C261" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7580,10 +7581,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>478</v>
+      </c>
+      <c r="C262" t="s">
         <v>479</v>
-      </c>
-      <c r="C262" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7591,10 +7592,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>480</v>
+      </c>
+      <c r="C263" t="s">
         <v>481</v>
-      </c>
-      <c r="C263" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7602,10 +7603,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>482</v>
+      </c>
+      <c r="C264" t="s">
         <v>483</v>
-      </c>
-      <c r="C264" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7613,10 +7614,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>484</v>
+      </c>
+      <c r="C265" t="s">
         <v>485</v>
-      </c>
-      <c r="C265" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7624,10 +7625,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>486</v>
+      </c>
+      <c r="C266" t="s">
         <v>487</v>
-      </c>
-      <c r="C266" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7635,10 +7636,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>488</v>
+      </c>
+      <c r="C267" t="s">
         <v>489</v>
-      </c>
-      <c r="C267" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7646,10 +7647,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C268" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7657,10 +7658,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>491</v>
+      </c>
+      <c r="C269" t="s">
         <v>492</v>
-      </c>
-      <c r="C269" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7668,10 +7669,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>493</v>
+      </c>
+      <c r="C270" t="s">
         <v>494</v>
-      </c>
-      <c r="C270" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7679,10 +7680,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
+        <v>495</v>
+      </c>
+      <c r="C271" t="s">
         <v>496</v>
-      </c>
-      <c r="C271" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7690,10 +7691,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>497</v>
+      </c>
+      <c r="C272" t="s">
         <v>498</v>
-      </c>
-      <c r="C272" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7701,10 +7702,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>499</v>
+      </c>
+      <c r="C273" t="s">
         <v>500</v>
-      </c>
-      <c r="C273" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7712,10 +7713,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>501</v>
+      </c>
+      <c r="C274" t="s">
         <v>502</v>
-      </c>
-      <c r="C274" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7723,10 +7724,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>503</v>
+      </c>
+      <c r="C275" t="s">
         <v>504</v>
-      </c>
-      <c r="C275" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7734,10 +7735,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>505</v>
+      </c>
+      <c r="C276" t="s">
         <v>506</v>
-      </c>
-      <c r="C276" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7745,10 +7746,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>507</v>
+      </c>
+      <c r="C277" t="s">
         <v>508</v>
-      </c>
-      <c r="C277" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7756,10 +7757,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>509</v>
+      </c>
+      <c r="C278" t="s">
         <v>510</v>
-      </c>
-      <c r="C278" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7767,10 +7768,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C279" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7778,10 +7779,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C280" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7789,10 +7790,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>513</v>
+      </c>
+      <c r="C281" t="s">
         <v>514</v>
-      </c>
-      <c r="C281" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -7800,10 +7801,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>515</v>
+      </c>
+      <c r="C282" t="s">
         <v>516</v>
-      </c>
-      <c r="C282" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -7811,10 +7812,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>517</v>
+      </c>
+      <c r="C283" t="s">
         <v>518</v>
-      </c>
-      <c r="C283" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -7822,10 +7823,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>519</v>
+      </c>
+      <c r="C284" t="s">
         <v>520</v>
-      </c>
-      <c r="C284" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -7833,10 +7834,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>521</v>
+      </c>
+      <c r="C285" t="s">
         <v>522</v>
-      </c>
-      <c r="C285" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7844,10 +7845,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C286" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7855,10 +7856,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>524</v>
+      </c>
+      <c r="C287" t="s">
         <v>525</v>
-      </c>
-      <c r="C287" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -7866,10 +7867,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>526</v>
+      </c>
+      <c r="C288" t="s">
         <v>527</v>
-      </c>
-      <c r="C288" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -7877,10 +7878,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>528</v>
+      </c>
+      <c r="C289" t="s">
         <v>529</v>
-      </c>
-      <c r="C289" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -7888,10 +7889,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>530</v>
+      </c>
+      <c r="C290" t="s">
         <v>531</v>
-      </c>
-      <c r="C290" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -7899,10 +7900,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>532</v>
+      </c>
+      <c r="C291" t="s">
         <v>533</v>
-      </c>
-      <c r="C291" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -7910,10 +7911,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>534</v>
+      </c>
+      <c r="C292" t="s">
         <v>535</v>
-      </c>
-      <c r="C292" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -7921,10 +7922,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>536</v>
+      </c>
+      <c r="C293" t="s">
         <v>537</v>
-      </c>
-      <c r="C293" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -7932,10 +7933,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>538</v>
+      </c>
+      <c r="C294" t="s">
         <v>539</v>
-      </c>
-      <c r="C294" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -7943,10 +7944,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C295" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -7954,10 +7955,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
+        <v>541</v>
+      </c>
+      <c r="C296" t="s">
         <v>542</v>
-      </c>
-      <c r="C296" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7965,10 +7966,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>543</v>
+      </c>
+      <c r="C297" t="s">
         <v>544</v>
-      </c>
-      <c r="C297" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7976,10 +7977,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>545</v>
+      </c>
+      <c r="C298" t="s">
         <v>546</v>
-      </c>
-      <c r="C298" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -7987,10 +7988,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>547</v>
+      </c>
+      <c r="C299" t="s">
         <v>548</v>
-      </c>
-      <c r="C299" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -7998,10 +7999,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>549</v>
+      </c>
+      <c r="C300" t="s">
         <v>550</v>
-      </c>
-      <c r="C300" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8009,10 +8010,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>551</v>
+      </c>
+      <c r="C301" t="s">
         <v>552</v>
-      </c>
-      <c r="C301" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8020,10 +8021,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>553</v>
+      </c>
+      <c r="C302" t="s">
         <v>554</v>
-      </c>
-      <c r="C302" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8031,10 +8032,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>555</v>
+      </c>
+      <c r="C303" t="s">
         <v>556</v>
-      </c>
-      <c r="C303" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8042,10 +8043,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>557</v>
+      </c>
+      <c r="C304" t="s">
         <v>558</v>
-      </c>
-      <c r="C304" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8053,10 +8054,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>559</v>
+      </c>
+      <c r="C305" t="s">
         <v>560</v>
-      </c>
-      <c r="C305" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8064,10 +8065,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>561</v>
+      </c>
+      <c r="C306" t="s">
         <v>562</v>
-      </c>
-      <c r="C306" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8075,10 +8076,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C307" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8086,10 +8087,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>564</v>
+      </c>
+      <c r="C308" t="s">
         <v>565</v>
-      </c>
-      <c r="C308" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8097,10 +8098,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>566</v>
+      </c>
+      <c r="C309" t="s">
         <v>567</v>
-      </c>
-      <c r="C309" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8108,10 +8109,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>568</v>
+      </c>
+      <c r="C310" t="s">
         <v>569</v>
-      </c>
-      <c r="C310" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8119,10 +8120,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>570</v>
+      </c>
+      <c r="C311" t="s">
         <v>571</v>
-      </c>
-      <c r="C311" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8130,10 +8131,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>572</v>
+      </c>
+      <c r="C312" t="s">
         <v>573</v>
-      </c>
-      <c r="C312" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8141,10 +8142,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>574</v>
+      </c>
+      <c r="C313" t="s">
         <v>575</v>
-      </c>
-      <c r="C313" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8152,10 +8153,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>576</v>
+      </c>
+      <c r="C314" t="s">
         <v>577</v>
-      </c>
-      <c r="C314" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8163,10 +8164,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C315" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8174,10 +8175,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>579</v>
+      </c>
+      <c r="C316" t="s">
         <v>580</v>
-      </c>
-      <c r="C316" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8185,10 +8186,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>581</v>
+      </c>
+      <c r="C317" t="s">
         <v>582</v>
-      </c>
-      <c r="C317" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8196,10 +8197,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>583</v>
+      </c>
+      <c r="C318" t="s">
         <v>584</v>
-      </c>
-      <c r="C318" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8207,10 +8208,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>585</v>
+      </c>
+      <c r="C319" t="s">
         <v>586</v>
-      </c>
-      <c r="C319" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8218,10 +8219,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>587</v>
+      </c>
+      <c r="C320" t="s">
         <v>588</v>
-      </c>
-      <c r="C320" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8229,10 +8230,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>589</v>
+      </c>
+      <c r="C321" t="s">
         <v>590</v>
-      </c>
-      <c r="C321" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8240,10 +8241,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>591</v>
+      </c>
+      <c r="C322" t="s">
         <v>592</v>
-      </c>
-      <c r="C322" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8251,10 +8252,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>593</v>
+      </c>
+      <c r="C323" t="s">
         <v>594</v>
-      </c>
-      <c r="C323" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8262,10 +8263,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>595</v>
+      </c>
+      <c r="C324" t="s">
         <v>596</v>
-      </c>
-      <c r="C324" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8273,10 +8274,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>597</v>
+      </c>
+      <c r="C325" t="s">
         <v>598</v>
-      </c>
-      <c r="C325" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8284,10 +8285,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>599</v>
+      </c>
+      <c r="C326" t="s">
         <v>600</v>
-      </c>
-      <c r="C326" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8295,10 +8296,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C327" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8306,10 +8307,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>601</v>
+      </c>
+      <c r="C328" t="s">
         <v>602</v>
-      </c>
-      <c r="C328" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8317,10 +8318,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>603</v>
+      </c>
+      <c r="C329" t="s">
         <v>604</v>
-      </c>
-      <c r="C329" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8328,10 +8329,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>605</v>
+      </c>
+      <c r="C330" t="s">
         <v>606</v>
-      </c>
-      <c r="C330" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8339,10 +8340,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>607</v>
+      </c>
+      <c r="C331" t="s">
         <v>608</v>
-      </c>
-      <c r="C331" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8350,10 +8351,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>609</v>
+      </c>
+      <c r="C332" t="s">
         <v>610</v>
-      </c>
-      <c r="C332" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8361,10 +8362,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>611</v>
+      </c>
+      <c r="C333" t="s">
         <v>612</v>
-      </c>
-      <c r="C333" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8372,10 +8373,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>613</v>
+      </c>
+      <c r="C334" t="s">
         <v>614</v>
-      </c>
-      <c r="C334" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8383,10 +8384,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>615</v>
+      </c>
+      <c r="C335" t="s">
         <v>616</v>
-      </c>
-      <c r="C335" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8394,10 +8395,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>617</v>
+      </c>
+      <c r="C336" t="s">
         <v>618</v>
-      </c>
-      <c r="C336" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8405,10 +8406,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>619</v>
+      </c>
+      <c r="C337" t="s">
         <v>620</v>
-      </c>
-      <c r="C337" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8416,10 +8417,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
+        <v>621</v>
+      </c>
+      <c r="C338" t="s">
         <v>622</v>
-      </c>
-      <c r="C338" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8427,10 +8428,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
+        <v>623</v>
+      </c>
+      <c r="C339" t="s">
         <v>624</v>
-      </c>
-      <c r="C339" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8438,10 +8439,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>625</v>
+      </c>
+      <c r="C340" t="s">
         <v>626</v>
-      </c>
-      <c r="C340" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8449,10 +8450,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>627</v>
+      </c>
+      <c r="C341" t="s">
         <v>628</v>
-      </c>
-      <c r="C341" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8460,10 +8461,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>629</v>
+      </c>
+      <c r="C342" t="s">
         <v>630</v>
-      </c>
-      <c r="C342" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8471,10 +8472,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>631</v>
+      </c>
+      <c r="C343" t="s">
         <v>632</v>
-      </c>
-      <c r="C343" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8482,10 +8483,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>633</v>
+      </c>
+      <c r="C344" t="s">
         <v>634</v>
-      </c>
-      <c r="C344" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8493,10 +8494,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C345" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8504,10 +8505,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>636</v>
+      </c>
+      <c r="C346" t="s">
         <v>637</v>
-      </c>
-      <c r="C346" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8515,10 +8516,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>638</v>
+      </c>
+      <c r="C347" t="s">
         <v>639</v>
-      </c>
-      <c r="C347" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8526,10 +8527,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>640</v>
+      </c>
+      <c r="C348" t="s">
         <v>641</v>
-      </c>
-      <c r="C348" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8537,10 +8538,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C349" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8548,10 +8549,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>643</v>
+      </c>
+      <c r="C350" t="s">
         <v>644</v>
-      </c>
-      <c r="C350" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8559,10 +8560,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C351" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8570,10 +8571,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>646</v>
+      </c>
+      <c r="C352" t="s">
         <v>647</v>
-      </c>
-      <c r="C352" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8581,10 +8582,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C353" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8592,10 +8593,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>649</v>
+      </c>
+      <c r="C354" t="s">
         <v>650</v>
-      </c>
-      <c r="C354" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8603,10 +8604,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>651</v>
+      </c>
+      <c r="C355" t="s">
         <v>652</v>
-      </c>
-      <c r="C355" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8614,10 +8615,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>653</v>
+      </c>
+      <c r="C356" t="s">
         <v>654</v>
-      </c>
-      <c r="C356" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8625,10 +8626,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>655</v>
+      </c>
+      <c r="C357" t="s">
         <v>656</v>
-      </c>
-      <c r="C357" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8636,10 +8637,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>657</v>
+      </c>
+      <c r="C358" t="s">
         <v>658</v>
-      </c>
-      <c r="C358" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8647,10 +8648,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>659</v>
+      </c>
+      <c r="C359" t="s">
         <v>660</v>
-      </c>
-      <c r="C359" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8658,10 +8659,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>661</v>
+      </c>
+      <c r="C360" t="s">
         <v>662</v>
-      </c>
-      <c r="C360" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8669,10 +8670,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>663</v>
+      </c>
+      <c r="C361" t="s">
         <v>664</v>
-      </c>
-      <c r="C361" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8680,10 +8681,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>665</v>
+      </c>
+      <c r="C362" t="s">
         <v>666</v>
-      </c>
-      <c r="C362" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8691,10 +8692,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>667</v>
+      </c>
+      <c r="C363" t="s">
         <v>668</v>
-      </c>
-      <c r="C363" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8702,10 +8703,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>669</v>
+      </c>
+      <c r="C364" t="s">
         <v>670</v>
-      </c>
-      <c r="C364" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8713,10 +8714,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>671</v>
+      </c>
+      <c r="C365" t="s">
         <v>672</v>
-      </c>
-      <c r="C365" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8724,10 +8725,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>673</v>
+      </c>
+      <c r="C366" t="s">
         <v>674</v>
-      </c>
-      <c r="C366" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8735,10 +8736,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>675</v>
+      </c>
+      <c r="C367" t="s">
         <v>676</v>
-      </c>
-      <c r="C367" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8746,10 +8747,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>677</v>
+      </c>
+      <c r="C368" t="s">
         <v>678</v>
-      </c>
-      <c r="C368" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8757,10 +8758,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>679</v>
+      </c>
+      <c r="C369" t="s">
         <v>680</v>
-      </c>
-      <c r="C369" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8768,10 +8769,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>681</v>
+      </c>
+      <c r="C370" t="s">
         <v>682</v>
-      </c>
-      <c r="C370" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8779,10 +8780,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>683</v>
+      </c>
+      <c r="C371" t="s">
         <v>684</v>
-      </c>
-      <c r="C371" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8790,10 +8791,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>685</v>
+      </c>
+      <c r="C372" t="s">
         <v>686</v>
-      </c>
-      <c r="C372" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8801,10 +8802,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>687</v>
+      </c>
+      <c r="C373" t="s">
         <v>688</v>
-      </c>
-      <c r="C373" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8812,10 +8813,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C374" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8823,10 +8824,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>690</v>
+      </c>
+      <c r="C375" t="s">
         <v>691</v>
-      </c>
-      <c r="C375" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8834,10 +8835,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>692</v>
+      </c>
+      <c r="C376" t="s">
         <v>693</v>
-      </c>
-      <c r="C376" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8845,10 +8846,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C377" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8856,10 +8857,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>695</v>
+      </c>
+      <c r="C378" t="s">
         <v>696</v>
-      </c>
-      <c r="C378" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8867,10 +8868,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C379" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8878,10 +8879,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>698</v>
+      </c>
+      <c r="C380" t="s">
         <v>699</v>
-      </c>
-      <c r="C380" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8889,10 +8890,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>700</v>
+      </c>
+      <c r="C381" t="s">
         <v>701</v>
-      </c>
-      <c r="C381" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8900,10 +8901,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>702</v>
+      </c>
+      <c r="C382" t="s">
         <v>703</v>
-      </c>
-      <c r="C382" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8911,10 +8912,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>704</v>
+      </c>
+      <c r="C383" t="s">
         <v>705</v>
-      </c>
-      <c r="C383" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8922,10 +8923,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>706</v>
+      </c>
+      <c r="C384" t="s">
         <v>707</v>
-      </c>
-      <c r="C384" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8933,10 +8934,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>708</v>
+      </c>
+      <c r="C385" t="s">
         <v>709</v>
-      </c>
-      <c r="C385" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8944,10 +8945,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C386" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8955,10 +8956,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>711</v>
+      </c>
+      <c r="C387" t="s">
         <v>712</v>
-      </c>
-      <c r="C387" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8966,10 +8967,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>713</v>
+      </c>
+      <c r="C388" t="s">
         <v>714</v>
-      </c>
-      <c r="C388" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8977,10 +8978,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>715</v>
+      </c>
+      <c r="C389" t="s">
         <v>716</v>
-      </c>
-      <c r="C389" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -8988,10 +8989,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>717</v>
+      </c>
+      <c r="C390" t="s">
         <v>718</v>
-      </c>
-      <c r="C390" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -8999,10 +9000,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>719</v>
+      </c>
+      <c r="C391" t="s">
         <v>720</v>
-      </c>
-      <c r="C391" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
@@ -9010,10 +9011,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>721</v>
+      </c>
+      <c r="C392" t="s">
         <v>722</v>
-      </c>
-      <c r="C392" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9021,10 +9022,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>723</v>
+      </c>
+      <c r="C393" t="s">
         <v>724</v>
-      </c>
-      <c r="C393" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9032,10 +9033,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>725</v>
+      </c>
+      <c r="C394" t="s">
         <v>726</v>
-      </c>
-      <c r="C394" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9043,10 +9044,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>727</v>
+      </c>
+      <c r="C395" t="s">
         <v>728</v>
-      </c>
-      <c r="C395" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9054,10 +9055,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>729</v>
+      </c>
+      <c r="C396" t="s">
         <v>730</v>
-      </c>
-      <c r="C396" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9065,10 +9066,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>731</v>
+      </c>
+      <c r="C397" t="s">
         <v>732</v>
-      </c>
-      <c r="C397" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9076,10 +9077,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>733</v>
+      </c>
+      <c r="C398" t="s">
         <v>734</v>
-      </c>
-      <c r="C398" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9087,10 +9088,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>735</v>
+      </c>
+      <c r="C399" t="s">
         <v>736</v>
-      </c>
-      <c r="C399" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9098,10 +9099,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>737</v>
+      </c>
+      <c r="C400" t="s">
         <v>738</v>
-      </c>
-      <c r="C400" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9109,10 +9110,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>739</v>
+      </c>
+      <c r="C401" t="s">
         <v>740</v>
-      </c>
-      <c r="C401" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9120,10 +9121,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C402" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9131,10 +9132,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>742</v>
+      </c>
+      <c r="C403" t="s">
         <v>743</v>
-      </c>
-      <c r="C403" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9142,10 +9143,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>744</v>
+      </c>
+      <c r="C404" t="s">
         <v>745</v>
-      </c>
-      <c r="C404" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9153,10 +9154,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>746</v>
+      </c>
+      <c r="C405" t="s">
         <v>747</v>
-      </c>
-      <c r="C405" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9164,10 +9165,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C406" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9175,10 +9176,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C407" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9186,10 +9187,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>749</v>
+      </c>
+      <c r="C408" t="s">
         <v>750</v>
-      </c>
-      <c r="C408" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9197,10 +9198,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>751</v>
+      </c>
+      <c r="C409" t="s">
         <v>752</v>
-      </c>
-      <c r="C409" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9208,10 +9209,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>753</v>
+      </c>
+      <c r="C410" t="s">
         <v>754</v>
-      </c>
-      <c r="C410" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9219,10 +9220,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>755</v>
+      </c>
+      <c r="C411" t="s">
         <v>756</v>
-      </c>
-      <c r="C411" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9230,10 +9231,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C412" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9241,10 +9242,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C413" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9252,10 +9253,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>759</v>
+      </c>
+      <c r="C414" t="s">
         <v>760</v>
-      </c>
-      <c r="C414" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9263,10 +9264,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>761</v>
+      </c>
+      <c r="C415" t="s">
         <v>762</v>
-      </c>
-      <c r="C415" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9274,10 +9275,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>763</v>
+      </c>
+      <c r="C416" t="s">
         <v>764</v>
-      </c>
-      <c r="C416" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9285,10 +9286,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>765</v>
+      </c>
+      <c r="C417" t="s">
         <v>766</v>
-      </c>
-      <c r="C417" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9296,10 +9297,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C418" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9307,10 +9308,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C419" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9318,10 +9319,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>769</v>
+      </c>
+      <c r="C420" t="s">
         <v>770</v>
-      </c>
-      <c r="C420" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9329,10 +9330,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>771</v>
+      </c>
+      <c r="C421" t="s">
         <v>772</v>
-      </c>
-      <c r="C421" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9340,10 +9341,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>773</v>
+      </c>
+      <c r="C422" t="s">
         <v>774</v>
-      </c>
-      <c r="C422" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9351,10 +9352,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C423" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9362,10 +9363,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>776</v>
+      </c>
+      <c r="C424" t="s">
         <v>777</v>
-      </c>
-      <c r="C424" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9373,10 +9374,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C425" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9384,10 +9385,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>779</v>
+      </c>
+      <c r="C426" t="s">
         <v>780</v>
-      </c>
-      <c r="C426" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9395,10 +9396,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>781</v>
+      </c>
+      <c r="C427" t="s">
         <v>782</v>
-      </c>
-      <c r="C427" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9406,10 +9407,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C428" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9417,10 +9418,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C429" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9428,10 +9429,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>785</v>
+      </c>
+      <c r="C430" t="s">
         <v>786</v>
-      </c>
-      <c r="C430" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9439,10 +9440,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>787</v>
+      </c>
+      <c r="C431" t="s">
         <v>788</v>
-      </c>
-      <c r="C431" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9450,10 +9451,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C432" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9461,10 +9462,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>790</v>
+      </c>
+      <c r="C433" t="s">
         <v>791</v>
-      </c>
-      <c r="C433" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9472,10 +9473,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>792</v>
+      </c>
+      <c r="C434" t="s">
         <v>793</v>
-      </c>
-      <c r="C434" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9483,10 +9484,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>794</v>
+      </c>
+      <c r="C435" t="s">
         <v>795</v>
-      </c>
-      <c r="C435" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9494,10 +9495,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>796</v>
+      </c>
+      <c r="C436" t="s">
         <v>797</v>
-      </c>
-      <c r="C436" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9505,10 +9506,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>798</v>
+      </c>
+      <c r="C437" t="s">
         <v>799</v>
-      </c>
-      <c r="C437" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9516,10 +9517,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>800</v>
+      </c>
+      <c r="C438" t="s">
         <v>801</v>
-      </c>
-      <c r="C438" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9527,10 +9528,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>802</v>
+      </c>
+      <c r="C439" t="s">
         <v>803</v>
-      </c>
-      <c r="C439" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9538,10 +9539,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>804</v>
+      </c>
+      <c r="C440" t="s">
         <v>805</v>
-      </c>
-      <c r="C440" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9549,10 +9550,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>806</v>
+      </c>
+      <c r="C441" t="s">
         <v>807</v>
-      </c>
-      <c r="C441" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9560,10 +9561,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>808</v>
+      </c>
+      <c r="C442" t="s">
         <v>809</v>
-      </c>
-      <c r="C442" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9571,10 +9572,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>810</v>
+      </c>
+      <c r="C443" t="s">
         <v>811</v>
-      </c>
-      <c r="C443" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9582,10 +9583,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>812</v>
+      </c>
+      <c r="C444" t="s">
         <v>813</v>
-      </c>
-      <c r="C444" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9593,10 +9594,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>814</v>
+      </c>
+      <c r="C445" t="s">
         <v>815</v>
-      </c>
-      <c r="C445" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9604,10 +9605,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>816</v>
+      </c>
+      <c r="C446" t="s">
         <v>817</v>
-      </c>
-      <c r="C446" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9615,10 +9616,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C447" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9626,10 +9627,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>819</v>
+      </c>
+      <c r="C448" t="s">
         <v>820</v>
-      </c>
-      <c r="C448" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9637,10 +9638,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C449" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9648,10 +9649,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>822</v>
+      </c>
+      <c r="C450" t="s">
         <v>823</v>
-      </c>
-      <c r="C450" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9659,10 +9660,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C451" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9670,10 +9671,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C452" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9681,10 +9682,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>825</v>
+      </c>
+      <c r="C453" t="s">
         <v>826</v>
-      </c>
-      <c r="C453" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9692,10 +9693,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>827</v>
+      </c>
+      <c r="C454" t="s">
         <v>828</v>
-      </c>
-      <c r="C454" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9703,10 +9704,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C455" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9714,10 +9715,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C456" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9725,10 +9726,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>830</v>
+      </c>
+      <c r="C457" t="s">
         <v>831</v>
-      </c>
-      <c r="C457" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9736,10 +9737,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>832</v>
+      </c>
+      <c r="C458" t="s">
         <v>833</v>
-      </c>
-      <c r="C458" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9747,10 +9748,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C459" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9758,7 +9759,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9766,10 +9767,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>836</v>
+      </c>
+      <c r="C461" t="s">
         <v>837</v>
-      </c>
-      <c r="C461" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9777,10 +9778,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>838</v>
+      </c>
+      <c r="C462" t="s">
         <v>839</v>
-      </c>
-      <c r="C462" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9788,10 +9789,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>840</v>
+      </c>
+      <c r="C463" t="s">
         <v>841</v>
-      </c>
-      <c r="C463" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9799,10 +9800,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C464" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9810,10 +9811,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C465" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9821,10 +9822,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>844</v>
+      </c>
+      <c r="C466" t="s">
         <v>845</v>
-      </c>
-      <c r="C466" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9832,10 +9833,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
+        <v>846</v>
+      </c>
+      <c r="C467" t="s">
         <v>847</v>
-      </c>
-      <c r="C467" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9843,10 +9844,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>848</v>
+      </c>
+      <c r="C468" t="s">
         <v>849</v>
-      </c>
-      <c r="C468" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9854,10 +9855,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C469" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9865,10 +9866,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>851</v>
+      </c>
+      <c r="C470" t="s">
         <v>852</v>
-      </c>
-      <c r="C470" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9876,10 +9877,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>853</v>
+      </c>
+      <c r="C471" t="s">
         <v>854</v>
-      </c>
-      <c r="C471" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9887,10 +9888,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>855</v>
+      </c>
+      <c r="C472" t="s">
         <v>856</v>
-      </c>
-      <c r="C472" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9898,10 +9899,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C473" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9909,10 +9910,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C474" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9920,10 +9921,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>858</v>
+      </c>
+      <c r="C475" t="s">
         <v>859</v>
-      </c>
-      <c r="C475" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9931,10 +9932,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>860</v>
+      </c>
+      <c r="C476" t="s">
         <v>861</v>
-      </c>
-      <c r="C476" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9942,10 +9943,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C477" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9953,10 +9954,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C478" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9964,10 +9965,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>864</v>
+      </c>
+      <c r="C479" t="s">
         <v>865</v>
-      </c>
-      <c r="C479" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9975,10 +9976,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C480" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -9986,10 +9987,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>867</v>
+      </c>
+      <c r="C481" t="s">
         <v>868</v>
-      </c>
-      <c r="C481" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -9997,10 +9998,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>869</v>
+      </c>
+      <c r="C482" t="s">
         <v>870</v>
-      </c>
-      <c r="C482" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10008,10 +10009,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>871</v>
+      </c>
+      <c r="C483" t="s">
         <v>872</v>
-      </c>
-      <c r="C483" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10019,10 +10020,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>873</v>
+      </c>
+      <c r="C484" t="s">
         <v>874</v>
-      </c>
-      <c r="C484" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10030,10 +10031,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>875</v>
+      </c>
+      <c r="C485" t="s">
         <v>876</v>
-      </c>
-      <c r="C485" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10041,10 +10042,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>877</v>
+      </c>
+      <c r="C486" t="s">
         <v>878</v>
-      </c>
-      <c r="C486" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10052,10 +10053,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>879</v>
+      </c>
+      <c r="C487" t="s">
         <v>880</v>
-      </c>
-      <c r="C487" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10063,10 +10064,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>881</v>
+      </c>
+      <c r="C488" t="s">
         <v>882</v>
-      </c>
-      <c r="C488" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10074,10 +10075,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>883</v>
+      </c>
+      <c r="C489" t="s">
         <v>884</v>
-      </c>
-      <c r="C489" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10085,10 +10086,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>885</v>
+      </c>
+      <c r="C490" t="s">
         <v>886</v>
-      </c>
-      <c r="C490" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10096,10 +10097,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>887</v>
+      </c>
+      <c r="C491" t="s">
         <v>888</v>
-      </c>
-      <c r="C491" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10107,10 +10108,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>889</v>
+      </c>
+      <c r="C492" t="s">
         <v>890</v>
-      </c>
-      <c r="C492" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10118,10 +10119,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>891</v>
+      </c>
+      <c r="C493" t="s">
         <v>892</v>
-      </c>
-      <c r="C493" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10129,10 +10130,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>893</v>
+      </c>
+      <c r="C494" t="s">
         <v>894</v>
-      </c>
-      <c r="C494" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10140,10 +10141,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>895</v>
+      </c>
+      <c r="C495" t="s">
         <v>896</v>
-      </c>
-      <c r="C495" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10151,10 +10152,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>897</v>
+      </c>
+      <c r="C496" t="s">
         <v>898</v>
-      </c>
-      <c r="C496" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10162,10 +10163,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>899</v>
+      </c>
+      <c r="C497" t="s">
         <v>900</v>
-      </c>
-      <c r="C497" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10173,10 +10174,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>901</v>
+      </c>
+      <c r="C498" t="s">
         <v>902</v>
-      </c>
-      <c r="C498" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10184,7 +10185,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10192,10 +10193,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C500" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10203,10 +10204,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>905</v>
+      </c>
+      <c r="C501" t="s">
         <v>906</v>
-      </c>
-      <c r="C501" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10214,10 +10215,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>907</v>
+      </c>
+      <c r="C502" t="s">
         <v>908</v>
-      </c>
-      <c r="C502" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10225,10 +10226,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C503" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10236,10 +10237,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>909</v>
+      </c>
+      <c r="C504" t="s">
         <v>910</v>
-      </c>
-      <c r="C504" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10247,10 +10248,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C505" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10258,10 +10259,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>912</v>
+      </c>
+      <c r="C506" t="s">
         <v>913</v>
-      </c>
-      <c r="C506" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10269,10 +10270,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C507" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10280,10 +10281,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>915</v>
+      </c>
+      <c r="C508" t="s">
         <v>916</v>
-      </c>
-      <c r="C508" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10291,10 +10292,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>917</v>
+      </c>
+      <c r="C509" t="s">
         <v>918</v>
-      </c>
-      <c r="C509" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10302,10 +10303,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>919</v>
+      </c>
+      <c r="C510" t="s">
         <v>920</v>
-      </c>
-      <c r="C510" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10313,10 +10314,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>921</v>
+      </c>
+      <c r="C511" t="s">
         <v>922</v>
-      </c>
-      <c r="C511" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10324,10 +10325,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>923</v>
+      </c>
+      <c r="C512" t="s">
         <v>924</v>
-      </c>
-      <c r="C512" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10335,10 +10336,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C513" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10346,10 +10347,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>926</v>
+      </c>
+      <c r="C514" t="s">
         <v>927</v>
-      </c>
-      <c r="C514" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10357,10 +10358,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C515" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10368,10 +10369,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C516" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10379,10 +10380,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C517" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10390,7 +10391,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10398,10 +10399,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C519" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10409,10 +10410,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>933</v>
+      </c>
+      <c r="C520" t="s">
         <v>934</v>
-      </c>
-      <c r="C520" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10420,10 +10421,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C521" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10431,10 +10432,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C522" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10442,10 +10443,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>937</v>
+      </c>
+      <c r="C523" t="s">
         <v>938</v>
-      </c>
-      <c r="C523" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10453,10 +10454,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>939</v>
+      </c>
+      <c r="C524" t="s">
         <v>940</v>
-      </c>
-      <c r="C524" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10464,10 +10465,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>941</v>
+      </c>
+      <c r="C525" t="s">
         <v>942</v>
-      </c>
-      <c r="C525" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10475,10 +10476,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>943</v>
+      </c>
+      <c r="C526" t="s">
         <v>944</v>
-      </c>
-      <c r="C526" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10486,10 +10487,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>945</v>
+      </c>
+      <c r="C527" t="s">
         <v>946</v>
-      </c>
-      <c r="C527" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10497,10 +10498,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>947</v>
+      </c>
+      <c r="C528" t="s">
         <v>948</v>
-      </c>
-      <c r="C528" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10508,10 +10509,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>949</v>
+      </c>
+      <c r="C529" t="s">
         <v>950</v>
-      </c>
-      <c r="C529" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10519,10 +10520,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>951</v>
+      </c>
+      <c r="C530" t="s">
         <v>952</v>
-      </c>
-      <c r="C530" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10530,10 +10531,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C531" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10541,10 +10542,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>954</v>
+      </c>
+      <c r="C532" t="s">
         <v>955</v>
-      </c>
-      <c r="C532" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10552,10 +10553,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>956</v>
+      </c>
+      <c r="C533" t="s">
         <v>957</v>
-      </c>
-      <c r="C533" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10563,10 +10564,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>958</v>
+      </c>
+      <c r="C534" t="s">
         <v>959</v>
-      </c>
-      <c r="C534" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10574,10 +10575,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>960</v>
+      </c>
+      <c r="C535" t="s">
         <v>961</v>
-      </c>
-      <c r="C535" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10585,10 +10586,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C536" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10596,10 +10597,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C537" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10607,10 +10608,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C538" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10618,10 +10619,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>965</v>
+      </c>
+      <c r="C539" t="s">
         <v>966</v>
-      </c>
-      <c r="C539" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10629,10 +10630,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C540" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10640,10 +10641,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>968</v>
+      </c>
+      <c r="C541" t="s">
         <v>969</v>
-      </c>
-      <c r="C541" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10651,10 +10652,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>970</v>
+      </c>
+      <c r="C542" t="s">
         <v>971</v>
-      </c>
-      <c r="C542" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10662,10 +10663,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>972</v>
+      </c>
+      <c r="C543" t="s">
         <v>973</v>
-      </c>
-      <c r="C543" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10673,10 +10674,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>974</v>
+      </c>
+      <c r="C544" t="s">
         <v>975</v>
-      </c>
-      <c r="C544" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10684,10 +10685,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>976</v>
+      </c>
+      <c r="C545" t="s">
         <v>977</v>
-      </c>
-      <c r="C545" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10695,10 +10696,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>978</v>
+      </c>
+      <c r="C546" t="s">
         <v>979</v>
-      </c>
-      <c r="C546" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10706,7 +10707,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10714,10 +10715,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>981</v>
+      </c>
+      <c r="C548" t="s">
         <v>982</v>
-      </c>
-      <c r="C548" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10725,10 +10726,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>983</v>
+      </c>
+      <c r="C549" t="s">
         <v>984</v>
-      </c>
-      <c r="C549" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10736,10 +10737,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C550" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10747,10 +10748,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>986</v>
+      </c>
+      <c r="C551" t="s">
         <v>987</v>
-      </c>
-      <c r="C551" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10758,10 +10759,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>988</v>
+      </c>
+      <c r="C552" t="s">
         <v>989</v>
-      </c>
-      <c r="C552" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10769,10 +10770,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C553" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10780,10 +10781,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>991</v>
+      </c>
+      <c r="C554" t="s">
         <v>992</v>
-      </c>
-      <c r="C554" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10791,10 +10792,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>993</v>
+      </c>
+      <c r="C555" t="s">
         <v>994</v>
-      </c>
-      <c r="C555" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10802,10 +10803,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C556" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10813,10 +10814,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C557" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10824,10 +10825,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>997</v>
+      </c>
+      <c r="C558" t="s">
         <v>998</v>
-      </c>
-      <c r="C558" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10835,7 +10836,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10843,10 +10844,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C560" t="s">
         <v>1001</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10854,10 +10855,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C561" t="s">
         <v>1003</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10865,10 +10866,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C562" t="s">
         <v>1005</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10876,10 +10877,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C563" t="s">
         <v>1007</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10887,10 +10888,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C564" t="s">
         <v>1009</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10898,10 +10899,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C565" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10909,10 +10910,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C566" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10920,10 +10921,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C567" t="s">
         <v>1012</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10931,10 +10932,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C568" t="s">
         <v>1014</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10942,10 +10943,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C569" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10953,10 +10954,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C570" t="s">
         <v>1017</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10964,10 +10965,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C571" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10975,10 +10976,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C572" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10986,10 +10987,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C573" t="s">
         <v>1021</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -10997,10 +10998,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C574" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11008,10 +11009,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C575" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11019,10 +11020,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C576" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11030,10 +11031,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C577" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11041,10 +11042,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C578" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11052,10 +11053,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C579" t="s">
         <v>1025</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11063,10 +11064,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C580" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11074,10 +11075,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C581" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11085,10 +11086,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C582" t="s">
         <v>1028</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11096,10 +11097,10 @@
         <v>612</v>
       </c>
       <c r="B583" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C583" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11107,10 +11108,10 @@
         <v>617</v>
       </c>
       <c r="B584" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C584" t="s">
         <v>1031</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11118,10 +11119,10 @@
         <v>618</v>
       </c>
       <c r="B585" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C585" t="s">
         <v>1033</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11129,10 +11130,10 @@
         <v>625</v>
       </c>
       <c r="B586" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C586" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11140,10 +11141,10 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C587" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11151,10 +11152,10 @@
         <v>626</v>
       </c>
       <c r="B588" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C588" t="s">
         <v>1035</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11162,10 +11163,10 @@
         <v>629</v>
       </c>
       <c r="B589" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C589" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11173,10 +11174,10 @@
         <v>630</v>
       </c>
       <c r="B590" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C590" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11184,10 +11185,10 @@
         <v>633</v>
       </c>
       <c r="B591" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C591" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11195,10 +11196,10 @@
         <v>635</v>
       </c>
       <c r="B592" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C592" t="s">
         <v>1039</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11206,10 +11207,10 @@
         <v>636</v>
       </c>
       <c r="B593" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C593" t="s">
         <v>1041</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11217,10 +11218,10 @@
         <v>642</v>
       </c>
       <c r="B594" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C594" t="s">
         <v>1043</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11228,10 +11229,10 @@
         <v>644</v>
       </c>
       <c r="B595" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C595" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11239,10 +11240,10 @@
         <v>646</v>
       </c>
       <c r="B596" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C596" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11250,10 +11251,10 @@
         <v>649</v>
       </c>
       <c r="B597" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C597" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11261,10 +11262,10 @@
         <v>650</v>
       </c>
       <c r="B598" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C598" t="s">
         <v>1046</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11272,10 +11273,10 @@
         <v>651</v>
       </c>
       <c r="B599" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C599" t="s">
         <v>1048</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11283,10 +11284,10 @@
         <v>653</v>
       </c>
       <c r="B600" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C600" t="s">
         <v>1050</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11294,10 +11295,10 @@
         <v>654</v>
       </c>
       <c r="B601" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C601" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11305,10 +11306,10 @@
         <v>655</v>
       </c>
       <c r="B602" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C602" t="s">
         <v>1052</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11316,10 +11317,10 @@
         <v>660</v>
       </c>
       <c r="B603" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C603" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11327,10 +11328,10 @@
         <v>661</v>
       </c>
       <c r="B604" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C604" t="s">
         <v>1054</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11338,10 +11339,10 @@
         <v>663</v>
       </c>
       <c r="B605" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C605" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11349,10 +11350,10 @@
         <v>667</v>
       </c>
       <c r="B606" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C606" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11360,10 +11361,10 @@
         <v>670</v>
       </c>
       <c r="B607" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C607" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11371,10 +11372,10 @@
         <v>673</v>
       </c>
       <c r="B608" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C608" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11382,10 +11383,10 @@
         <v>674</v>
       </c>
       <c r="B609" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C609" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11393,10 +11394,10 @@
         <v>680</v>
       </c>
       <c r="B610" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C610" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11404,10 +11405,10 @@
         <v>681</v>
       </c>
       <c r="B611" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C611" t="s">
         <v>1195</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11415,10 +11416,10 @@
         <v>682</v>
       </c>
       <c r="B612" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C612" t="s">
         <v>1060</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11426,10 +11427,10 @@
         <v>683</v>
       </c>
       <c r="B613" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C613" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11437,10 +11438,10 @@
         <v>684</v>
       </c>
       <c r="B614" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C614" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11448,10 +11449,10 @@
         <v>685</v>
       </c>
       <c r="B615" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C615" t="s">
         <v>1062</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11459,10 +11460,10 @@
         <v>686</v>
       </c>
       <c r="B616" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C616" t="s">
         <v>1064</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11470,10 +11471,10 @@
         <v>689</v>
       </c>
       <c r="B617" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C617" t="s">
         <v>1066</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11481,10 +11482,10 @@
         <v>697</v>
       </c>
       <c r="B618" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C618" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11492,10 +11493,10 @@
         <v>701</v>
       </c>
       <c r="B619" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C619" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11503,10 +11504,10 @@
         <v>702</v>
       </c>
       <c r="B620" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C620" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11514,10 +11515,10 @@
         <v>704</v>
       </c>
       <c r="B621" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C621" t="s">
-        <v>1098</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11525,10 +11526,10 @@
         <v>705</v>
       </c>
       <c r="B622" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C622" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11536,10 +11537,10 @@
         <v>710</v>
       </c>
       <c r="B623" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C623" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11547,10 +11548,10 @@
         <v>711</v>
       </c>
       <c r="B624" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C624" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11558,10 +11559,10 @@
         <v>712</v>
       </c>
       <c r="B625" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C625" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11569,10 +11570,10 @@
         <v>714</v>
       </c>
       <c r="B626" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C626" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11580,10 +11581,10 @@
         <v>717</v>
       </c>
       <c r="B627" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C627" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11591,10 +11592,10 @@
         <v>718</v>
       </c>
       <c r="B628" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C628" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11602,10 +11603,10 @@
         <v>719</v>
       </c>
       <c r="B629" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C629" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11613,10 +11614,10 @@
         <v>721</v>
       </c>
       <c r="B630" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C630" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11624,10 +11625,10 @@
         <v>722</v>
       </c>
       <c r="B631" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C631" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11635,10 +11636,10 @@
         <v>723</v>
       </c>
       <c r="B632" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="C632" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11646,10 +11647,10 @@
         <v>725</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C633" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11657,10 +11658,10 @@
         <v>726</v>
       </c>
       <c r="B634" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C634" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11668,10 +11669,10 @@
         <v>727</v>
       </c>
       <c r="B635" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C635" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11679,10 +11680,10 @@
         <v>728</v>
       </c>
       <c r="B636" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C636" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11690,10 +11691,10 @@
         <v>729</v>
       </c>
       <c r="B637" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C637" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11701,10 +11702,10 @@
         <v>730</v>
       </c>
       <c r="B638" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C638" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11712,10 +11713,10 @@
         <v>731</v>
       </c>
       <c r="B639" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C639" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11723,10 +11724,10 @@
         <v>733</v>
       </c>
       <c r="B640" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C640" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11734,10 +11735,10 @@
         <v>735</v>
       </c>
       <c r="B641" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C641" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11745,10 +11746,10 @@
         <v>736</v>
       </c>
       <c r="B642" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C642" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11756,10 +11757,10 @@
         <v>737</v>
       </c>
       <c r="B643" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C643" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11767,10 +11768,10 @@
         <v>738</v>
       </c>
       <c r="B644" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C644" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11778,10 +11779,10 @@
         <v>739</v>
       </c>
       <c r="B645" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C645" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11789,10 +11790,10 @@
         <v>740</v>
       </c>
       <c r="B646" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C646" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11800,10 +11801,10 @@
         <v>741</v>
       </c>
       <c r="B647" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C647" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11811,10 +11812,10 @@
         <v>742</v>
       </c>
       <c r="B648" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C648" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11822,10 +11823,10 @@
         <v>743</v>
       </c>
       <c r="B649" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C649" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11833,10 +11834,10 @@
         <v>744</v>
       </c>
       <c r="B650" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C650" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="651" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11844,10 +11845,10 @@
         <v>745</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C651" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11855,10 +11856,10 @@
         <v>746</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C652" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11866,10 +11867,10 @@
         <v>747</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C653" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11877,10 +11878,10 @@
         <v>748</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C654" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11888,10 +11889,10 @@
         <v>749</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C655" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11899,10 +11900,10 @@
         <v>753</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C656" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11910,10 +11911,10 @@
         <v>755</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C657" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11921,10 +11922,10 @@
         <v>10001</v>
       </c>
       <c r="B658" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C658" t="s">
         <v>1068</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11932,10 +11933,10 @@
         <v>10003</v>
       </c>
       <c r="B659" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C659" t="s">
         <v>1095</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1096</v>
       </c>
     </row>
   </sheetData>
@@ -11943,7 +11944,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A658:C658 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C144 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A658:C658 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589 A134:C144 A133:B133" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B943BB9-34E9-46AB-8B58-EB5A53E3DA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916D4A80-4C2C-46BB-BDCC-AF934074B712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12792" yWindow="3396" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13320" yWindow="1008" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2801,9 +2801,6 @@
   </si>
   <si>
     <t>燦々</t>
-  </si>
-  <si>
-    <t>sansan,尾杀一万级,1081combo</t>
   </si>
   <si>
     <t>ほな！</t>
@@ -4277,6 +4274,10 @@
   </si>
   <si>
     <t>锅盖面,ggm,k-on,kon,轻音少女,鬼歌,鬼哥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sansan,尾杀一万级,1081combo,燦然,灿然,璨然</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4724,7 +4725,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4735,7 +4736,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4746,7 +4747,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4757,7 +4758,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4790,7 +4791,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4845,7 +4846,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4867,7 +4868,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4922,7 +4923,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4955,7 +4956,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5010,7 +5011,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5032,7 +5033,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5043,7 +5044,7 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -5120,7 +5121,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5131,7 +5132,7 @@
         <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5175,7 +5176,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5263,7 +5264,7 @@
         <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -5285,7 +5286,7 @@
         <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -5296,7 +5297,7 @@
         <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -5340,7 +5341,7 @@
         <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5472,7 +5473,7 @@
         <v>120</v>
       </c>
       <c r="C70" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -5480,10 +5481,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C71" t="s">
         <v>1149</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -5571,7 +5572,7 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -5637,7 +5638,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5725,7 +5726,7 @@
         <v>161</v>
       </c>
       <c r="C93" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -5736,7 +5737,7 @@
         <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -5791,7 +5792,7 @@
         <v>171</v>
       </c>
       <c r="C99" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -5879,7 +5880,7 @@
         <v>186</v>
       </c>
       <c r="C107" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -5956,7 +5957,7 @@
         <v>199</v>
       </c>
       <c r="C114" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -6022,7 +6023,7 @@
         <v>210</v>
       </c>
       <c r="C120" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6110,7 +6111,7 @@
         <v>225</v>
       </c>
       <c r="C128" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6165,7 +6166,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6297,7 +6298,7 @@
         <v>257</v>
       </c>
       <c r="C145" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6352,7 +6353,7 @@
         <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6396,7 +6397,7 @@
         <v>273</v>
       </c>
       <c r="C154" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6484,7 +6485,7 @@
         <v>288</v>
       </c>
       <c r="C162" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6572,7 +6573,7 @@
         <v>303</v>
       </c>
       <c r="C170" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -7221,7 +7222,7 @@
         <v>420</v>
       </c>
       <c r="C229" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7232,7 +7233,7 @@
         <v>421</v>
       </c>
       <c r="C230" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7276,7 +7277,7 @@
         <v>428</v>
       </c>
       <c r="C234" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7452,7 +7453,7 @@
         <v>459</v>
       </c>
       <c r="C250" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7463,7 +7464,7 @@
         <v>460</v>
       </c>
       <c r="C251" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7529,7 +7530,7 @@
         <v>470</v>
       </c>
       <c r="C257" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7562,7 +7563,7 @@
         <v>475</v>
       </c>
       <c r="C260" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7650,7 +7651,7 @@
         <v>490</v>
       </c>
       <c r="C268" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7771,7 +7772,7 @@
         <v>511</v>
       </c>
       <c r="C279" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7782,7 +7783,7 @@
         <v>512</v>
       </c>
       <c r="C280" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7848,7 +7849,7 @@
         <v>523</v>
       </c>
       <c r="C286" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7947,7 +7948,7 @@
         <v>540</v>
       </c>
       <c r="C295" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -8079,7 +8080,7 @@
         <v>563</v>
       </c>
       <c r="C307" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8167,7 +8168,7 @@
         <v>578</v>
       </c>
       <c r="C315" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8296,10 +8297,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C327" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8497,7 +8498,7 @@
         <v>635</v>
       </c>
       <c r="C345" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8541,7 +8542,7 @@
         <v>642</v>
       </c>
       <c r="C349" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8563,7 +8564,7 @@
         <v>645</v>
       </c>
       <c r="C351" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8585,7 +8586,7 @@
         <v>648</v>
       </c>
       <c r="C353" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8816,7 +8817,7 @@
         <v>689</v>
       </c>
       <c r="C374" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8849,7 +8850,7 @@
         <v>694</v>
       </c>
       <c r="C377" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8871,7 +8872,7 @@
         <v>697</v>
       </c>
       <c r="C379" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8948,7 +8949,7 @@
         <v>710</v>
       </c>
       <c r="C386" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -9124,7 +9125,7 @@
         <v>741</v>
       </c>
       <c r="C402" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9165,10 +9166,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C406" t="s">
         <v>1207</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9179,7 +9180,7 @@
         <v>748</v>
       </c>
       <c r="C407" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9231,7 +9232,7 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C412" t="s">
         <v>757</v>
@@ -9242,7 +9243,7 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C413" t="s">
         <v>758</v>
@@ -9300,7 +9301,7 @@
         <v>767</v>
       </c>
       <c r="C418" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9311,7 +9312,7 @@
         <v>768</v>
       </c>
       <c r="C419" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9355,7 +9356,7 @@
         <v>775</v>
       </c>
       <c r="C423" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9377,7 +9378,7 @@
         <v>778</v>
       </c>
       <c r="C425" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9454,7 +9455,7 @@
         <v>789</v>
       </c>
       <c r="C432" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9619,7 +9620,7 @@
         <v>818</v>
       </c>
       <c r="C447" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9641,7 +9642,7 @@
         <v>821</v>
       </c>
       <c r="C449" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9663,7 +9664,7 @@
         <v>697</v>
       </c>
       <c r="C451" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9674,7 +9675,7 @@
         <v>824</v>
       </c>
       <c r="C452" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9707,7 +9708,7 @@
         <v>829</v>
       </c>
       <c r="C455" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9718,7 +9719,7 @@
         <v>737</v>
       </c>
       <c r="C456" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9751,7 +9752,7 @@
         <v>834</v>
       </c>
       <c r="C459" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9803,7 +9804,7 @@
         <v>842</v>
       </c>
       <c r="C464" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9814,7 +9815,7 @@
         <v>843</v>
       </c>
       <c r="C465" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9858,7 +9859,7 @@
         <v>850</v>
       </c>
       <c r="C469" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9899,10 +9900,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C473" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9913,7 +9914,7 @@
         <v>857</v>
       </c>
       <c r="C474" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9946,7 +9947,7 @@
         <v>862</v>
       </c>
       <c r="C477" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9979,7 +9980,7 @@
         <v>866</v>
       </c>
       <c r="C480" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -10196,7 +10197,7 @@
         <v>904</v>
       </c>
       <c r="C500" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10226,10 +10227,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C503" t="s">
         <v>1109</v>
-      </c>
-      <c r="C503" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10251,7 +10252,7 @@
         <v>911</v>
       </c>
       <c r="C505" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10273,7 +10274,7 @@
         <v>914</v>
       </c>
       <c r="C507" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10339,7 +10340,7 @@
         <v>925</v>
       </c>
       <c r="C513" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10350,7 +10351,7 @@
         <v>926</v>
       </c>
       <c r="C514" t="s">
-        <v>927</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10358,10 +10359,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C515" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10372,7 +10373,7 @@
         <v>675</v>
       </c>
       <c r="C516" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10380,10 +10381,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C517" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10391,7 +10392,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10399,10 +10400,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C519" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10410,10 +10411,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>932</v>
+      </c>
+      <c r="C520" t="s">
         <v>933</v>
-      </c>
-      <c r="C520" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10421,10 +10422,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C521" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10432,10 +10433,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C522" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10443,10 +10444,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>936</v>
+      </c>
+      <c r="C523" t="s">
         <v>937</v>
-      </c>
-      <c r="C523" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10454,10 +10455,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>938</v>
+      </c>
+      <c r="C524" t="s">
         <v>939</v>
-      </c>
-      <c r="C524" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10465,10 +10466,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>940</v>
+      </c>
+      <c r="C525" t="s">
         <v>941</v>
-      </c>
-      <c r="C525" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10476,10 +10477,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>942</v>
+      </c>
+      <c r="C526" t="s">
         <v>943</v>
-      </c>
-      <c r="C526" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10487,10 +10488,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>944</v>
+      </c>
+      <c r="C527" t="s">
         <v>945</v>
-      </c>
-      <c r="C527" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10498,10 +10499,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>946</v>
+      </c>
+      <c r="C528" t="s">
         <v>947</v>
-      </c>
-      <c r="C528" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10509,10 +10510,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>948</v>
+      </c>
+      <c r="C529" t="s">
         <v>949</v>
-      </c>
-      <c r="C529" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10520,10 +10521,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>950</v>
+      </c>
+      <c r="C530" t="s">
         <v>951</v>
-      </c>
-      <c r="C530" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10531,10 +10532,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C531" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10542,10 +10543,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>953</v>
+      </c>
+      <c r="C532" t="s">
         <v>954</v>
-      </c>
-      <c r="C532" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10553,10 +10554,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>955</v>
+      </c>
+      <c r="C533" t="s">
         <v>956</v>
-      </c>
-      <c r="C533" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10564,10 +10565,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>957</v>
+      </c>
+      <c r="C534" t="s">
         <v>958</v>
-      </c>
-      <c r="C534" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10575,10 +10576,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>959</v>
+      </c>
+      <c r="C535" t="s">
         <v>960</v>
-      </c>
-      <c r="C535" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10586,10 +10587,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C536" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10597,10 +10598,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C537" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10608,10 +10609,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C538" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10619,10 +10620,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>964</v>
+      </c>
+      <c r="C539" t="s">
         <v>965</v>
-      </c>
-      <c r="C539" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10630,10 +10631,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C540" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10641,10 +10642,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>967</v>
+      </c>
+      <c r="C541" t="s">
         <v>968</v>
-      </c>
-      <c r="C541" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10652,10 +10653,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>969</v>
+      </c>
+      <c r="C542" t="s">
         <v>970</v>
-      </c>
-      <c r="C542" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10663,10 +10664,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>971</v>
+      </c>
+      <c r="C543" t="s">
         <v>972</v>
-      </c>
-      <c r="C543" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10674,10 +10675,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>973</v>
+      </c>
+      <c r="C544" t="s">
         <v>974</v>
-      </c>
-      <c r="C544" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10685,10 +10686,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>975</v>
+      </c>
+      <c r="C545" t="s">
         <v>976</v>
-      </c>
-      <c r="C545" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10696,10 +10697,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>977</v>
+      </c>
+      <c r="C546" t="s">
         <v>978</v>
-      </c>
-      <c r="C546" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10707,7 +10708,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10715,10 +10716,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>980</v>
+      </c>
+      <c r="C548" t="s">
         <v>981</v>
-      </c>
-      <c r="C548" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10726,10 +10727,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>982</v>
+      </c>
+      <c r="C549" t="s">
         <v>983</v>
-      </c>
-      <c r="C549" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10737,10 +10738,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C550" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10748,10 +10749,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>985</v>
+      </c>
+      <c r="C551" t="s">
         <v>986</v>
-      </c>
-      <c r="C551" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10759,10 +10760,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>987</v>
+      </c>
+      <c r="C552" t="s">
         <v>988</v>
-      </c>
-      <c r="C552" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10770,10 +10771,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C553" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10781,10 +10782,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>990</v>
+      </c>
+      <c r="C554" t="s">
         <v>991</v>
-      </c>
-      <c r="C554" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10792,10 +10793,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>992</v>
+      </c>
+      <c r="C555" t="s">
         <v>993</v>
-      </c>
-      <c r="C555" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10803,10 +10804,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C556" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10814,10 +10815,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C557" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10825,10 +10826,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>996</v>
+      </c>
+      <c r="C558" t="s">
         <v>997</v>
-      </c>
-      <c r="C558" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10836,7 +10837,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10844,10 +10845,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>999</v>
+      </c>
+      <c r="C560" t="s">
         <v>1000</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10855,10 +10856,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C561" t="s">
         <v>1002</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10866,10 +10867,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C562" t="s">
         <v>1004</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10877,10 +10878,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C563" t="s">
         <v>1006</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10888,10 +10889,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C564" t="s">
         <v>1008</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10899,10 +10900,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C565" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10910,10 +10911,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C566" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10921,10 +10922,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C567" t="s">
         <v>1011</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10932,10 +10933,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C568" t="s">
         <v>1013</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10943,10 +10944,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C569" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10954,10 +10955,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C570" t="s">
         <v>1016</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10965,10 +10966,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C571" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10976,10 +10977,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C572" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10987,10 +10988,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C573" t="s">
         <v>1020</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -10998,10 +10999,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C574" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11009,10 +11010,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C575" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11020,10 +11021,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C576" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11034,7 +11035,7 @@
         <v>858</v>
       </c>
       <c r="C577" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11045,7 +11046,7 @@
         <v>860</v>
       </c>
       <c r="C578" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11053,10 +11054,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C579" t="s">
         <v>1024</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11064,10 +11065,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C580" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11075,10 +11076,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C581" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11086,10 +11087,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C582" t="s">
         <v>1027</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11097,10 +11098,10 @@
         <v>612</v>
       </c>
       <c r="B583" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C583" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11108,10 +11109,10 @@
         <v>617</v>
       </c>
       <c r="B584" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C584" t="s">
         <v>1030</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11119,10 +11120,10 @@
         <v>618</v>
       </c>
       <c r="B585" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C585" t="s">
         <v>1032</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11130,10 +11131,10 @@
         <v>625</v>
       </c>
       <c r="B586" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C586" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11141,10 +11142,10 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C587" t="s">
         <v>1293</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11152,10 +11153,10 @@
         <v>626</v>
       </c>
       <c r="B588" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C588" t="s">
         <v>1034</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11163,10 +11164,10 @@
         <v>629</v>
       </c>
       <c r="B589" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C589" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11174,10 +11175,10 @@
         <v>630</v>
       </c>
       <c r="B590" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C590" t="s">
         <v>1291</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11185,10 +11186,10 @@
         <v>633</v>
       </c>
       <c r="B591" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C591" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11196,10 +11197,10 @@
         <v>635</v>
       </c>
       <c r="B592" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C592" t="s">
         <v>1038</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11207,10 +11208,10 @@
         <v>636</v>
       </c>
       <c r="B593" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C593" t="s">
         <v>1040</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11218,10 +11219,10 @@
         <v>642</v>
       </c>
       <c r="B594" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C594" t="s">
         <v>1042</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11229,10 +11230,10 @@
         <v>644</v>
       </c>
       <c r="B595" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C595" t="s">
         <v>1263</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11240,10 +11241,10 @@
         <v>646</v>
       </c>
       <c r="B596" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C596" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11251,10 +11252,10 @@
         <v>649</v>
       </c>
       <c r="B597" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C597" t="s">
         <v>1198</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11262,10 +11263,10 @@
         <v>650</v>
       </c>
       <c r="B598" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C598" t="s">
         <v>1045</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11273,10 +11274,10 @@
         <v>651</v>
       </c>
       <c r="B599" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C599" t="s">
         <v>1047</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11284,10 +11285,10 @@
         <v>653</v>
       </c>
       <c r="B600" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C600" t="s">
         <v>1049</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11295,10 +11296,10 @@
         <v>654</v>
       </c>
       <c r="B601" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C601" t="s">
         <v>1152</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11306,10 +11307,10 @@
         <v>655</v>
       </c>
       <c r="B602" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C602" t="s">
         <v>1051</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11317,10 +11318,10 @@
         <v>660</v>
       </c>
       <c r="B603" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C603" t="s">
         <v>1196</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11328,10 +11329,10 @@
         <v>661</v>
       </c>
       <c r="B604" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C604" t="s">
         <v>1053</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11339,10 +11340,10 @@
         <v>663</v>
       </c>
       <c r="B605" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C605" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11350,10 +11351,10 @@
         <v>667</v>
       </c>
       <c r="B606" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C606" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11361,10 +11362,10 @@
         <v>670</v>
       </c>
       <c r="B607" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C607" t="s">
         <v>1288</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11372,10 +11373,10 @@
         <v>673</v>
       </c>
       <c r="B608" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C608" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11383,10 +11384,10 @@
         <v>674</v>
       </c>
       <c r="B609" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C609" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11394,10 +11395,10 @@
         <v>680</v>
       </c>
       <c r="B610" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C610" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11405,10 +11406,10 @@
         <v>681</v>
       </c>
       <c r="B611" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C611" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11416,10 +11417,10 @@
         <v>682</v>
       </c>
       <c r="B612" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C612" t="s">
         <v>1059</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11427,10 +11428,10 @@
         <v>683</v>
       </c>
       <c r="B613" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C613" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11438,10 +11439,10 @@
         <v>684</v>
       </c>
       <c r="B614" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C614" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11449,10 +11450,10 @@
         <v>685</v>
       </c>
       <c r="B615" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C615" t="s">
         <v>1061</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11460,10 +11461,10 @@
         <v>686</v>
       </c>
       <c r="B616" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C616" t="s">
         <v>1063</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11471,10 +11472,10 @@
         <v>689</v>
       </c>
       <c r="B617" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C617" t="s">
         <v>1065</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11482,10 +11483,10 @@
         <v>697</v>
       </c>
       <c r="B618" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C618" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11493,10 +11494,10 @@
         <v>701</v>
       </c>
       <c r="B619" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C619" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11504,10 +11505,10 @@
         <v>702</v>
       </c>
       <c r="B620" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C620" t="s">
         <v>1257</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11515,10 +11516,10 @@
         <v>704</v>
       </c>
       <c r="B621" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C621" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11526,10 +11527,10 @@
         <v>705</v>
       </c>
       <c r="B622" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C622" t="s">
         <v>1271</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11537,10 +11538,10 @@
         <v>710</v>
       </c>
       <c r="B623" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C623" t="s">
         <v>1191</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11548,10 +11549,10 @@
         <v>711</v>
       </c>
       <c r="B624" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C624" t="s">
         <v>1254</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11559,10 +11560,10 @@
         <v>712</v>
       </c>
       <c r="B625" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C625" t="s">
         <v>1252</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11570,10 +11571,10 @@
         <v>714</v>
       </c>
       <c r="B626" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C626" t="s">
         <v>1250</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11581,10 +11582,10 @@
         <v>717</v>
       </c>
       <c r="B627" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C627" t="s">
         <v>1248</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11592,10 +11593,10 @@
         <v>718</v>
       </c>
       <c r="B628" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C628" t="s">
         <v>1246</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11603,10 +11604,10 @@
         <v>719</v>
       </c>
       <c r="B629" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C629" t="s">
         <v>1244</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11614,10 +11615,10 @@
         <v>721</v>
       </c>
       <c r="B630" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C630" t="s">
         <v>1242</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11625,10 +11626,10 @@
         <v>722</v>
       </c>
       <c r="B631" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C631" t="s">
         <v>1240</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11636,10 +11637,10 @@
         <v>723</v>
       </c>
       <c r="B632" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C632" t="s">
         <v>1238</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11647,10 +11648,10 @@
         <v>725</v>
       </c>
       <c r="B633" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C633" t="s">
         <v>1236</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11658,10 +11659,10 @@
         <v>726</v>
       </c>
       <c r="B634" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C634" t="s">
         <v>1234</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11669,10 +11670,10 @@
         <v>727</v>
       </c>
       <c r="B635" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C635" t="s">
         <v>1232</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11680,10 +11681,10 @@
         <v>728</v>
       </c>
       <c r="B636" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C636" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11691,10 +11692,10 @@
         <v>729</v>
       </c>
       <c r="B637" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C637" t="s">
         <v>1229</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11702,10 +11703,10 @@
         <v>730</v>
       </c>
       <c r="B638" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C638" t="s">
         <v>1227</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11713,10 +11714,10 @@
         <v>731</v>
       </c>
       <c r="B639" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C639" t="s">
         <v>1225</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11724,10 +11725,10 @@
         <v>733</v>
       </c>
       <c r="B640" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C640" t="s">
         <v>1223</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11735,10 +11736,10 @@
         <v>735</v>
       </c>
       <c r="B641" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C641" t="s">
         <v>1221</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11746,10 +11747,10 @@
         <v>736</v>
       </c>
       <c r="B642" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C642" t="s">
         <v>1219</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11757,10 +11758,10 @@
         <v>737</v>
       </c>
       <c r="B643" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C643" t="s">
         <v>1260</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11768,10 +11769,10 @@
         <v>738</v>
       </c>
       <c r="B644" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C644" t="s">
         <v>1217</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11779,10 +11780,10 @@
         <v>739</v>
       </c>
       <c r="B645" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C645" t="s">
         <v>1215</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11790,10 +11791,10 @@
         <v>740</v>
       </c>
       <c r="B646" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C646" t="s">
         <v>1213</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11801,10 +11802,10 @@
         <v>741</v>
       </c>
       <c r="B647" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C647" t="s">
         <v>1211</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11812,10 +11813,10 @@
         <v>742</v>
       </c>
       <c r="B648" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C648" t="s">
         <v>1273</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11823,10 +11824,10 @@
         <v>743</v>
       </c>
       <c r="B649" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C649" t="s">
         <v>1275</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11834,10 +11835,10 @@
         <v>744</v>
       </c>
       <c r="B650" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C650" t="s">
         <v>1277</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="651" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11845,10 +11846,10 @@
         <v>745</v>
       </c>
       <c r="B651" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C651" t="s">
         <v>1279</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11856,10 +11857,10 @@
         <v>746</v>
       </c>
       <c r="B652" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C652" t="s">
         <v>1281</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11867,10 +11868,10 @@
         <v>747</v>
       </c>
       <c r="B653" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C653" t="s">
         <v>1283</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11878,10 +11879,10 @@
         <v>748</v>
       </c>
       <c r="B654" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C654" t="s">
         <v>1301</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11889,10 +11890,10 @@
         <v>749</v>
       </c>
       <c r="B655" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C655" t="s">
         <v>1299</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11900,10 +11901,10 @@
         <v>753</v>
       </c>
       <c r="B656" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C656" t="s">
         <v>1297</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11911,10 +11912,10 @@
         <v>755</v>
       </c>
       <c r="B657" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C657" t="s">
         <v>1295</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11922,10 +11923,10 @@
         <v>10001</v>
       </c>
       <c r="B658" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C658" t="s">
         <v>1067</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11933,10 +11934,10 @@
         <v>10003</v>
       </c>
       <c r="B659" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C659" t="s">
         <v>1094</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1095</v>
       </c>
     </row>
   </sheetData>
@@ -11944,7 +11945,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A658:C658 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:C514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589 A134:C144 A133:B133" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A658:C658 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589 A134:C144 A133:B133" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916D4A80-4C2C-46BB-BDCC-AF934074B712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C1E499-D76D-43B0-86D7-30FF453774F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13320" yWindow="1008" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="1305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="1307">
   <si>
     <t>Id</t>
   </si>
@@ -4193,10 +4193,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>白雪,白雪公主</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>纸飞机,一莲托生</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4278,6 +4274,18 @@
   </si>
   <si>
     <t>sansan,尾杀一万级,1081combo,燦然,灿然,璨然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白雪,白雪公主,白如雪的公主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝命之吻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KiLLKiSS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4697,7 +4705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C659"/>
+  <dimension ref="A1:C660"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -6166,7 +6174,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -8850,7 +8858,7 @@
         <v>694</v>
       </c>
       <c r="C377" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -10351,7 +10359,7 @@
         <v>926</v>
       </c>
       <c r="C514" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -11079,7 +11087,7 @@
         <v>1188</v>
       </c>
       <c r="C581" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11142,10 +11150,10 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C587" t="s">
         <v>1292</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11175,10 +11183,10 @@
         <v>630</v>
       </c>
       <c r="B590" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C590" t="s">
         <v>1290</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11315,628 +11323,639 @@
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B603" t="s">
-        <v>1195</v>
+        <v>1306</v>
       </c>
       <c r="C603" t="s">
-        <v>1196</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B604" t="s">
-        <v>1052</v>
+        <v>1195</v>
       </c>
       <c r="C604" t="s">
-        <v>1053</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B605" t="s">
-        <v>1069</v>
+        <v>1052</v>
       </c>
       <c r="C605" t="s">
-        <v>1258</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B606" t="s">
-        <v>1054</v>
+        <v>1069</v>
       </c>
       <c r="C606" t="s">
-        <v>1123</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B607" t="s">
-        <v>1287</v>
+        <v>1054</v>
       </c>
       <c r="C607" t="s">
-        <v>1288</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B608" t="s">
-        <v>1055</v>
+        <v>1286</v>
       </c>
       <c r="C608" t="s">
-        <v>1113</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B609" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C609" t="s">
-        <v>1193</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="B610" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C610" t="s">
-        <v>1074</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B611" t="s">
-        <v>1192</v>
+        <v>1057</v>
       </c>
       <c r="C611" t="s">
-        <v>1194</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B612" t="s">
-        <v>1058</v>
+        <v>1192</v>
       </c>
       <c r="C612" t="s">
-        <v>1059</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B613" t="s">
-        <v>1286</v>
+        <v>1058</v>
       </c>
       <c r="C613" t="s">
-        <v>1289</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B614" t="s">
-        <v>1068</v>
+        <v>1285</v>
       </c>
       <c r="C614" t="s">
-        <v>1164</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B615" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="C615" t="s">
-        <v>1061</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B616" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C616" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B617" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C617" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B618" t="s">
-        <v>1145</v>
+        <v>1064</v>
       </c>
       <c r="C618" t="s">
-        <v>1267</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B619" t="s">
-        <v>1180</v>
+        <v>1145</v>
       </c>
       <c r="C619" t="s">
-        <v>1179</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B620" t="s">
-        <v>1256</v>
+        <v>1180</v>
       </c>
       <c r="C620" t="s">
-        <v>1257</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B621" t="s">
-        <v>1095</v>
+        <v>1256</v>
       </c>
       <c r="C621" t="s">
-        <v>1302</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B622" t="s">
-        <v>1270</v>
+        <v>1095</v>
       </c>
       <c r="C622" t="s">
-        <v>1271</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B623" t="s">
-        <v>1190</v>
+        <v>1270</v>
       </c>
       <c r="C623" t="s">
-        <v>1191</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B624" t="s">
-        <v>1253</v>
+        <v>1190</v>
       </c>
       <c r="C624" t="s">
-        <v>1254</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B625" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="C625" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B626" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="C626" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B627" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="C627" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B628" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C628" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
+        <v>718</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C629" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A630">
         <v>719</v>
       </c>
-      <c r="B629" t="s">
+      <c r="B630" t="s">
         <v>1243</v>
       </c>
-      <c r="C629" t="s">
+      <c r="C630" t="s">
         <v>1244</v>
       </c>
     </row>
-    <row r="630" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A630">
+    <row r="631" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A631">
         <v>721</v>
       </c>
-      <c r="B630" t="s">
+      <c r="B631" t="s">
         <v>1241</v>
       </c>
-      <c r="C630" t="s">
+      <c r="C631" t="s">
         <v>1242</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A631">
-        <v>722</v>
-      </c>
-      <c r="B631" t="s">
-        <v>1239</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B632" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C632" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633">
-        <v>725</v>
-      </c>
-      <c r="B633" s="1" t="s">
-        <v>1235</v>
+        <v>723</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1237</v>
       </c>
       <c r="C633" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634">
-        <v>726</v>
-      </c>
-      <c r="B634" t="s">
-        <v>1233</v>
+        <v>725</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>1235</v>
       </c>
       <c r="C634" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635">
+        <v>726</v>
+      </c>
+      <c r="B635" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C635" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A636">
         <v>727</v>
       </c>
-      <c r="B635" t="s">
+      <c r="B636" t="s">
         <v>1231</v>
       </c>
-      <c r="C635" t="s">
+      <c r="C636" t="s">
         <v>1232</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A636">
-        <v>728</v>
-      </c>
-      <c r="B636" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A637">
+        <v>728</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C637" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A638">
         <v>729</v>
       </c>
-      <c r="B637" t="s">
+      <c r="B638" t="s">
         <v>1228</v>
       </c>
-      <c r="C637" t="s">
+      <c r="C638" t="s">
         <v>1229</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A638">
-        <v>730</v>
-      </c>
-      <c r="B638" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B639" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="C639" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B640" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C640" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B641" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C641" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B642" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C642" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B643" t="s">
-        <v>1259</v>
+        <v>1218</v>
       </c>
       <c r="C643" t="s">
-        <v>1260</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B644" t="s">
-        <v>1216</v>
+        <v>1259</v>
       </c>
       <c r="C644" t="s">
-        <v>1217</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B645" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C645" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B646" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C646" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B647" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C647" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B648" t="s">
-        <v>1272</v>
+        <v>1210</v>
       </c>
       <c r="C648" t="s">
-        <v>1273</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B649" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C649" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
+        <v>743</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C650" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A651">
         <v>744</v>
       </c>
-      <c r="B650" t="s">
+      <c r="B651" t="s">
         <v>1276</v>
       </c>
-      <c r="C650" t="s">
+      <c r="C651" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="651" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A651">
+    <row r="652" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A652">
         <v>745</v>
       </c>
-      <c r="B651" s="2" t="s">
+      <c r="B652" s="2" t="s">
         <v>1278</v>
       </c>
-      <c r="C651" t="s">
+      <c r="C652" t="s">
         <v>1279</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A652">
-        <v>746</v>
-      </c>
-      <c r="B652" s="2" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C653" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1300</v>
+        <v>1282</v>
       </c>
       <c r="C654" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C655" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C656" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C657" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658">
-        <v>10001</v>
-      </c>
-      <c r="B658" t="s">
-        <v>1066</v>
+        <v>755</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>1293</v>
       </c>
       <c r="C658" t="s">
-        <v>1067</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659">
+        <v>10001</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C659" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A660">
         <v>10003</v>
       </c>
-      <c r="B659" t="s">
+      <c r="B660" t="s">
         <v>1093</v>
       </c>
-      <c r="C659" t="s">
+      <c r="C660" t="s">
         <v>1094</v>
       </c>
     </row>
@@ -11945,7 +11964,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A658:C658 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A612:C612 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A615:C617 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A604:C604 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A608:B610 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A606:B606 A589:B589 A134:C144 A133:B133" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A659:C659 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C1E499-D76D-43B0-86D7-30FF453774F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FE15B4-2BCB-47D1-84D5-1F678E9659C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4281,11 +4281,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>绝命之吻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KiLLKiSS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝命之吻,kk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11326,10 +11326,10 @@
         <v>659</v>
       </c>
       <c r="B603" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C603" t="s">
         <v>1306</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FE15B4-2BCB-47D1-84D5-1F678E9659C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2235BEE5-64E4-4CFE-A653-0CDBEA363C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -916,9 +916,6 @@
     <t>Ringing Bloom</t>
   </si>
   <si>
-    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花</t>
-  </si>
-  <si>
     <t>Baby Sweet Berry Love</t>
   </si>
   <si>
@@ -1159,9 +1156,6 @@
     <t>[FULL] 二重の虹(ダブルレインボウ)</t>
   </si>
   <si>
-    <t>召唤巨大彩虹喷流,二重虹full</t>
-  </si>
-  <si>
     <t>ファティマ</t>
   </si>
   <si>
@@ -1588,9 +1582,6 @@
     <t>Nevereverland</t>
   </si>
   <si>
-    <t>永无岛,梦国</t>
-  </si>
-  <si>
     <t>セツナトリップ</t>
   </si>
   <si>
@@ -1747,9 +1738,6 @@
     <t>Synchrogazer</t>
   </si>
   <si>
-    <t>战姬绝唱,脑梗14+</t>
-  </si>
-  <si>
     <t>るんっ♪てぃてぃー！</t>
   </si>
   <si>
@@ -2176,9 +2164,6 @@
     <t>CATASTROPHE BANQUET</t>
   </si>
   <si>
-    <t>灾宴,除了纱夜全是妈,cb,魔王,王道,灾厄宴会,boss,cata</t>
-  </si>
-  <si>
     <t>月光花</t>
   </si>
   <si>
@@ -2338,15 +2323,9 @@
     <t>ROZEN HORIZON</t>
   </si>
   <si>
-    <t>火鸟2.0,各位群友傍晚好,RH,纱夜模拟器,短绿条,火鸡2,火鸟2</t>
-  </si>
-  <si>
     <t>SOUL SOLDIER</t>
   </si>
   <si>
-    <t>灵魂战士,ss,前奏爆一百遍,喜欢我24分吗</t>
-  </si>
-  <si>
     <t>大好き！</t>
   </si>
   <si>
@@ -2662,9 +2641,6 @@
     <t>アイウエ</t>
   </si>
   <si>
-    <t>aiue,AIUE,新福星小子,爱之上</t>
-  </si>
-  <si>
     <t>Angel's Ladder</t>
   </si>
   <si>
@@ -3070,9 +3046,6 @@
     <t>ノンブレス・オブリージュ</t>
   </si>
   <si>
-    <t>non-breath oblige,无呼吸义务</t>
-  </si>
-  <si>
     <t>きゅうくらりん</t>
   </si>
   <si>
@@ -3339,10 +3312,6 @@
   </si>
   <si>
     <t>前卫派,史诗,agh,前卫派历史,前位派</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跳车,跳,蒋平,jump,姜萍</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3810,10 +3779,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>炸梦,是的炸梦,爆炸梦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>トーキョーワンダー。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4090,27 +4055,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>35lzn,超高难易度六兆年,超高难度六兆年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>33hoh,超高难易度hoh,超高难度hoh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>33ssfk,33ssfkk,超高难易度ssfkk,超高难度ssfkk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The Peak,最高到达点,最高达到点,到达最高点,达到最高点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>格里,格力,格立,格利,ggg,gg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>别怕,我们遇到什么困难也不要怕,别怂,别慌,dont be afraid,dba,afraid,gg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4277,15 +4226,75 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>白雪,白雪公主,白如雪的公主</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KiLLKiSS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>绝命之吻,kk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白雪,白雪公主,白如雪的公主,白如雪公主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸梦,是的炸梦,爆炸梦,yes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳车,跳,蒋平,jump,姜萍,黄跳,红跳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>non-breath oblige,无呼吸义务,烤羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战姬绝唱,脑梗14+,syn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤巨大彩虹喷流,二重虹full,full二重虹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火鸟2.0,各位群友傍晚好,RH,纱夜模拟器,短绿条,火鸡2,火鸟2,水鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aiue,AIUE,新福星小子,爱之上,爱上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>永无岛,梦国,永无島</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>别怕,我们遇到什么困难也不要怕,别怂,别慌,dont be afraid,dba,afraid,gg,别害怕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>00boom,rb,燐燐开花,燐燐爆炸,给大佬比心,大失所望,敷衍了事,官谱摆烂,开花,00开花,00 开花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灾宴,除了纱夜全是妈,cb,魔王,王道,灾厄宴会,boss,cata,大灾宴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33hoh,超高难易度hoh,超高难度hoh,hohssp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33ssfk,33ssfkk,超高难易度ssfkk,超高难度ssfkk,ssfkkssp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>35lzn,超高难易度六兆年,超高难度六兆年,lznssp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵魂战士,ss,前奏爆一百遍,喜欢我24分吗,魂兵</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4733,7 +4742,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1203</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4744,7 +4753,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>1119</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4755,7 +4764,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>1120</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4766,7 +4775,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4799,7 +4808,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4854,7 +4863,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4876,7 +4885,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>1162</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4931,7 +4940,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>1101</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4964,7 +4973,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>1201</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5019,7 +5028,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>1081</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5041,7 +5050,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5052,7 +5061,7 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>1161</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -5129,7 +5138,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1269</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5140,7 +5149,7 @@
         <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5184,7 +5193,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>1175</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5272,7 +5281,7 @@
         <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -5294,7 +5303,7 @@
         <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -5305,7 +5314,7 @@
         <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>1085</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -5349,7 +5358,7 @@
         <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>1144</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5481,7 +5490,7 @@
         <v>120</v>
       </c>
       <c r="C70" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -5489,10 +5498,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>1148</v>
+        <v>1138</v>
       </c>
       <c r="C71" t="s">
-        <v>1149</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -5580,7 +5589,7 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>1106</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -5646,7 +5655,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5734,7 +5743,7 @@
         <v>161</v>
       </c>
       <c r="C93" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -5745,7 +5754,7 @@
         <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -5800,7 +5809,7 @@
         <v>171</v>
       </c>
       <c r="C99" t="s">
-        <v>1174</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -5888,7 +5897,7 @@
         <v>186</v>
       </c>
       <c r="C107" t="s">
-        <v>1143</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -5965,7 +5974,7 @@
         <v>199</v>
       </c>
       <c r="C114" t="s">
-        <v>1102</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -6031,7 +6040,7 @@
         <v>210</v>
       </c>
       <c r="C120" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6119,7 +6128,7 @@
         <v>225</v>
       </c>
       <c r="C128" t="s">
-        <v>1147</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6174,7 +6183,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>1302</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6306,7 +6315,7 @@
         <v>257</v>
       </c>
       <c r="C145" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6361,7 +6370,7 @@
         <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>1202</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6405,7 +6414,7 @@
         <v>273</v>
       </c>
       <c r="C154" t="s">
-        <v>1146</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6493,7 +6502,7 @@
         <v>288</v>
       </c>
       <c r="C162" t="s">
-        <v>1097</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6548,7 +6557,7 @@
         <v>297</v>
       </c>
       <c r="C167" t="s">
-        <v>298</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6556,10 +6565,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>298</v>
+      </c>
+      <c r="C168" t="s">
         <v>299</v>
-      </c>
-      <c r="C168" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6567,10 +6576,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>300</v>
+      </c>
+      <c r="C169" t="s">
         <v>301</v>
-      </c>
-      <c r="C169" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6578,10 +6587,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C170" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6589,10 +6598,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>303</v>
+      </c>
+      <c r="C171" t="s">
         <v>304</v>
-      </c>
-      <c r="C171" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6600,10 +6609,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>305</v>
+      </c>
+      <c r="C172" t="s">
         <v>306</v>
-      </c>
-      <c r="C172" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6611,10 +6620,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>307</v>
+      </c>
+      <c r="C173" t="s">
         <v>308</v>
-      </c>
-      <c r="C173" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6622,10 +6631,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>309</v>
+      </c>
+      <c r="C174" t="s">
         <v>310</v>
-      </c>
-      <c r="C174" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6633,10 +6642,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>311</v>
+      </c>
+      <c r="C175" t="s">
         <v>312</v>
-      </c>
-      <c r="C175" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6644,10 +6653,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>313</v>
+      </c>
+      <c r="C176" t="s">
         <v>314</v>
-      </c>
-      <c r="C176" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6655,10 +6664,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>315</v>
+      </c>
+      <c r="C177" t="s">
         <v>316</v>
-      </c>
-      <c r="C177" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6666,10 +6675,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>317</v>
+      </c>
+      <c r="C178" t="s">
         <v>318</v>
-      </c>
-      <c r="C178" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6677,10 +6686,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>319</v>
+      </c>
+      <c r="C179" t="s">
         <v>320</v>
-      </c>
-      <c r="C179" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6688,10 +6697,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>321</v>
+      </c>
+      <c r="C180" t="s">
         <v>322</v>
-      </c>
-      <c r="C180" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6699,10 +6708,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>323</v>
+      </c>
+      <c r="C181" t="s">
         <v>324</v>
-      </c>
-      <c r="C181" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6710,10 +6719,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>325</v>
+      </c>
+      <c r="C182" t="s">
         <v>326</v>
-      </c>
-      <c r="C182" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6721,10 +6730,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>327</v>
+      </c>
+      <c r="C183" t="s">
         <v>328</v>
-      </c>
-      <c r="C183" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6732,10 +6741,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>329</v>
+      </c>
+      <c r="C184" t="s">
         <v>330</v>
-      </c>
-      <c r="C184" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6743,10 +6752,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>331</v>
+      </c>
+      <c r="C185" t="s">
         <v>332</v>
-      </c>
-      <c r="C185" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6754,10 +6763,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>333</v>
+      </c>
+      <c r="C186" t="s">
         <v>334</v>
-      </c>
-      <c r="C186" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6765,10 +6774,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>335</v>
+      </c>
+      <c r="C187" t="s">
         <v>336</v>
-      </c>
-      <c r="C187" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6776,10 +6785,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>337</v>
+      </c>
+      <c r="C188" t="s">
         <v>338</v>
-      </c>
-      <c r="C188" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -6787,10 +6796,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>339</v>
+      </c>
+      <c r="C189" t="s">
         <v>340</v>
-      </c>
-      <c r="C189" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -6798,10 +6807,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>341</v>
+      </c>
+      <c r="C190" t="s">
         <v>342</v>
-      </c>
-      <c r="C190" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -6809,10 +6818,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>343</v>
+      </c>
+      <c r="C191" t="s">
         <v>344</v>
-      </c>
-      <c r="C191" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -6820,10 +6829,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>345</v>
+      </c>
+      <c r="C192" t="s">
         <v>346</v>
-      </c>
-      <c r="C192" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -6831,10 +6840,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>347</v>
+      </c>
+      <c r="C193" t="s">
         <v>348</v>
-      </c>
-      <c r="C193" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -6842,10 +6851,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>349</v>
+      </c>
+      <c r="C194" t="s">
         <v>350</v>
-      </c>
-      <c r="C194" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -6853,10 +6862,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>351</v>
+      </c>
+      <c r="C195" t="s">
         <v>352</v>
-      </c>
-      <c r="C195" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -6864,10 +6873,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>353</v>
+      </c>
+      <c r="C196" t="s">
         <v>354</v>
-      </c>
-      <c r="C196" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -6875,10 +6884,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>355</v>
+      </c>
+      <c r="C197" t="s">
         <v>356</v>
-      </c>
-      <c r="C197" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -6886,10 +6895,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>357</v>
+      </c>
+      <c r="C198" t="s">
         <v>358</v>
-      </c>
-      <c r="C198" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -6897,10 +6906,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>359</v>
+      </c>
+      <c r="C199" t="s">
         <v>360</v>
-      </c>
-      <c r="C199" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -6908,10 +6917,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>361</v>
+      </c>
+      <c r="C200" t="s">
         <v>362</v>
-      </c>
-      <c r="C200" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -6919,10 +6928,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>363</v>
+      </c>
+      <c r="C201" t="s">
         <v>364</v>
-      </c>
-      <c r="C201" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -6930,10 +6939,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>365</v>
+      </c>
+      <c r="C202" t="s">
         <v>366</v>
-      </c>
-      <c r="C202" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -6941,10 +6950,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>367</v>
+      </c>
+      <c r="C203" t="s">
         <v>368</v>
-      </c>
-      <c r="C203" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -6952,10 +6961,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>369</v>
+      </c>
+      <c r="C204" t="s">
         <v>370</v>
-      </c>
-      <c r="C204" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -6963,10 +6972,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>371</v>
+      </c>
+      <c r="C205" t="s">
         <v>372</v>
-      </c>
-      <c r="C205" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -6974,10 +6983,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>373</v>
+      </c>
+      <c r="C206" t="s">
         <v>374</v>
-      </c>
-      <c r="C206" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -6985,10 +6994,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>375</v>
+      </c>
+      <c r="C207" t="s">
         <v>376</v>
-      </c>
-      <c r="C207" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -6996,10 +7005,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C208" t="s">
-        <v>379</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7007,10 +7016,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C209" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7018,10 +7027,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C210" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -7029,10 +7038,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C211" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -7040,10 +7049,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C212" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -7051,10 +7060,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C213" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7062,10 +7071,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C214" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7073,10 +7082,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C215" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7084,10 +7093,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C216" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7095,10 +7104,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C217" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7106,10 +7115,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C218" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7117,10 +7126,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C219" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7128,10 +7137,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C220" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7139,10 +7148,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C221" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7150,10 +7159,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C222" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7161,10 +7170,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C223" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7172,10 +7181,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C224" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7183,10 +7192,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C225" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7194,10 +7203,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C226" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7205,10 +7214,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C227" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7216,10 +7225,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C228" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7227,10 +7236,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C229" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7238,10 +7247,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C230" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7249,10 +7258,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C231" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7260,10 +7269,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C232" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7271,10 +7280,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C233" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7282,10 +7291,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C234" t="s">
-        <v>1083</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7293,10 +7302,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C235" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7304,10 +7313,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C236" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7315,10 +7324,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C237" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7326,10 +7335,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C238" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7337,10 +7346,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C239" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7348,10 +7357,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C240" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7359,10 +7368,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C241" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7370,10 +7379,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C242" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7381,10 +7390,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C243" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7392,10 +7401,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C244" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7403,10 +7412,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C245" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7414,10 +7423,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C246" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7425,10 +7434,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C247" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7436,10 +7445,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C248" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7447,10 +7456,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C249" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7458,10 +7467,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C250" t="s">
-        <v>1140</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7469,10 +7478,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C251" t="s">
-        <v>1139</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7480,10 +7489,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C252" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7491,10 +7500,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C253" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7502,10 +7511,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C254" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7513,10 +7522,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C255" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7524,10 +7533,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C256" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7535,10 +7544,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C257" t="s">
-        <v>1096</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7546,10 +7555,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C258" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7557,10 +7566,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C259" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7568,10 +7577,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C260" t="s">
-        <v>1138</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7579,10 +7588,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C261" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7590,10 +7599,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C262" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7601,10 +7610,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C263" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7612,10 +7621,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C264" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7623,10 +7632,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C265" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7634,10 +7643,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C266" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7645,10 +7654,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C267" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7656,10 +7665,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C268" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7667,10 +7676,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C269" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7678,10 +7687,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C270" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7689,10 +7698,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C271" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7700,10 +7709,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C272" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7711,10 +7720,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C273" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7722,10 +7731,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C274" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7733,10 +7742,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C275" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7744,10 +7753,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C276" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7755,10 +7764,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C277" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7766,10 +7775,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C278" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7777,10 +7786,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C279" t="s">
-        <v>1136</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7788,10 +7797,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C280" t="s">
-        <v>1209</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7799,10 +7808,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C281" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -7810,10 +7819,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C282" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -7821,10 +7830,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C283" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -7832,10 +7841,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C284" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -7843,10 +7852,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C285" t="s">
-        <v>522</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7854,10 +7863,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C286" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7865,10 +7874,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C287" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -7876,10 +7885,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C288" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -7887,10 +7896,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C289" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -7898,10 +7907,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C290" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -7909,10 +7918,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C291" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -7920,10 +7929,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C292" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -7931,10 +7940,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C293" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -7942,10 +7951,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C294" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -7953,10 +7962,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C295" t="s">
-        <v>1173</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -7964,10 +7973,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C296" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7975,10 +7984,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C297" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7986,10 +7995,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C298" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -7997,10 +8006,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C299" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -8008,10 +8017,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C300" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -8019,10 +8028,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C301" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8030,10 +8039,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C302" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8041,10 +8050,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C303" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8052,10 +8061,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C304" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8063,10 +8072,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C305" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8074,10 +8083,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C306" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8085,10 +8094,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C307" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8096,10 +8105,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C308" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8107,10 +8116,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C309" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8118,10 +8127,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C310" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8129,10 +8138,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C311" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8140,10 +8149,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C312" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8151,10 +8160,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C313" t="s">
-        <v>575</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8162,10 +8171,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="C314" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8173,10 +8182,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C315" t="s">
-        <v>1163</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8184,10 +8193,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C316" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8195,10 +8204,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C317" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8206,10 +8215,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C318" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8217,10 +8226,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C319" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8228,10 +8237,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C320" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8239,10 +8248,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C321" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8250,10 +8259,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C322" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8261,10 +8270,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C323" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8272,10 +8281,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C324" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8283,10 +8292,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C325" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8294,10 +8303,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C326" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8305,10 +8314,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
-        <v>1172</v>
+        <v>1162</v>
       </c>
       <c r="C327" t="s">
-        <v>1171</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8316,10 +8325,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C328" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8327,10 +8336,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C329" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8338,10 +8347,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C330" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8349,10 +8358,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C331" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8360,10 +8369,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C332" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8371,10 +8380,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C333" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8382,10 +8391,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C334" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8393,10 +8402,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C335" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8404,10 +8413,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C336" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8415,10 +8424,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C337" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8426,10 +8435,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C338" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8437,10 +8446,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C339" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8448,10 +8457,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C340" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8459,10 +8468,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C341" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8470,10 +8479,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C342" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8481,10 +8490,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C343" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8492,10 +8501,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C344" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8503,10 +8512,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C345" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8514,10 +8523,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C346" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8525,10 +8534,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C347" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8536,10 +8545,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C348" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8547,10 +8556,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C349" t="s">
-        <v>1181</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8558,10 +8567,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C350" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8569,10 +8578,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C351" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8580,10 +8589,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C352" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8591,10 +8600,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C353" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8602,10 +8611,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C354" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8613,10 +8622,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C355" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8624,10 +8633,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C356" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8635,10 +8644,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C357" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8646,10 +8655,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C358" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8657,10 +8666,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C359" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8668,10 +8677,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C360" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8679,10 +8688,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C361" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8690,10 +8699,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C362" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8701,10 +8710,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C363" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8712,10 +8721,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C364" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8723,10 +8732,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C365" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8734,10 +8743,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C366" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8745,10 +8754,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C367" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8756,10 +8765,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C368" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8767,10 +8776,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C369" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8778,10 +8787,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C370" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8789,10 +8798,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C371" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8800,10 +8809,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C372" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8811,10 +8820,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C373" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8822,10 +8831,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C374" t="s">
-        <v>1208</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8833,10 +8842,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C375" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8844,10 +8853,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C376" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8855,10 +8864,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C377" t="s">
-        <v>1284</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8866,10 +8875,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C378" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8877,10 +8886,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C379" t="s">
-        <v>1154</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8888,10 +8897,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C380" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8899,10 +8908,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C381" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8910,10 +8919,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C382" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8921,10 +8930,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C383" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8932,10 +8941,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C384" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8943,10 +8952,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C385" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8954,10 +8963,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C386" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8965,10 +8974,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C387" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8976,10 +8985,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C388" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8987,10 +8996,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C389" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -8998,10 +9007,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C390" t="s">
-        <v>718</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9009,10 +9018,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C391" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
@@ -9020,10 +9029,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="C392" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9031,10 +9040,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C393" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9042,10 +9051,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C394" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9053,10 +9062,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C395" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9064,10 +9073,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C396" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9075,10 +9084,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="C397" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9086,10 +9095,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C398" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9097,10 +9106,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C399" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9108,10 +9117,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="C400" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9119,10 +9128,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="C401" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9130,10 +9139,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C402" t="s">
-        <v>1135</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9141,10 +9150,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C403" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9152,10 +9161,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C404" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9163,10 +9172,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="C405" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9174,10 +9183,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>1206</v>
+        <v>1195</v>
       </c>
       <c r="C406" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9185,10 +9194,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C407" t="s">
-        <v>1169</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9196,10 +9205,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C408" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9207,10 +9216,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C409" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9218,10 +9227,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C410" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9229,10 +9238,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="C411" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9240,10 +9249,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>1205</v>
+        <v>1194</v>
       </c>
       <c r="C412" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9251,10 +9260,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>1204</v>
+        <v>1193</v>
       </c>
       <c r="C413" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9262,10 +9271,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="C414" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9273,10 +9282,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="C415" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9284,10 +9293,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C416" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9295,10 +9304,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C417" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9306,10 +9315,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="C418" t="s">
-        <v>1104</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9317,10 +9326,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C419" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9328,10 +9337,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C420" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9339,10 +9348,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C421" t="s">
-        <v>772</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9350,10 +9359,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="C422" t="s">
-        <v>774</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9361,10 +9370,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C423" t="s">
-        <v>1134</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9372,10 +9381,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="C424" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9383,10 +9392,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="C425" t="s">
-        <v>1133</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9394,10 +9403,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="C426" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9405,10 +9414,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="C427" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9416,10 +9425,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="C428" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9427,10 +9436,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="C429" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9438,10 +9447,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="C430" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9449,10 +9458,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="C431" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9460,10 +9469,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="C432" t="s">
-        <v>1132</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9471,10 +9480,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="C433" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9482,10 +9491,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="C434" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9493,10 +9502,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="C435" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9504,10 +9513,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="C436" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9515,10 +9524,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="C437" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9526,10 +9535,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C438" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9537,10 +9546,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="C439" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9548,10 +9557,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="C440" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9559,10 +9568,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="C441" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9570,10 +9579,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="C442" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9581,10 +9590,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="C443" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9592,10 +9601,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="C444" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9603,10 +9612,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="C445" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9614,10 +9623,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="C446" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9625,10 +9634,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="C447" t="s">
-        <v>1131</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9636,10 +9645,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="C448" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9647,10 +9656,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="C449" t="s">
-        <v>1125</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9658,10 +9667,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="C450" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9669,10 +9678,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C451" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9680,10 +9689,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="C452" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9691,10 +9700,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="C453" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9702,10 +9711,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="C454" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9713,10 +9722,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="C455" t="s">
-        <v>1086</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9724,10 +9733,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="C456" t="s">
-        <v>1160</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9735,10 +9744,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="C457" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9746,10 +9755,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="C458" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9757,10 +9766,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="C459" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9768,7 +9777,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9776,10 +9785,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="C461" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9787,10 +9796,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="C462" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9798,10 +9807,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="C463" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9809,10 +9818,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="C464" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9820,10 +9829,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="C465" t="s">
-        <v>1130</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9831,10 +9840,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="C466" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9842,10 +9851,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="C467" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9853,10 +9862,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="C468" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9864,10 +9873,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="C469" t="s">
-        <v>1159</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9875,10 +9884,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
-        <v>851</v>
+        <v>844</v>
       </c>
       <c r="C470" t="s">
-        <v>852</v>
+        <v>845</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9886,10 +9895,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="C471" t="s">
-        <v>854</v>
+        <v>847</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9897,10 +9906,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
-        <v>855</v>
+        <v>848</v>
       </c>
       <c r="C472" t="s">
-        <v>856</v>
+        <v>849</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9908,10 +9917,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="C473" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9919,10 +9928,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
       <c r="C474" t="s">
-        <v>1268</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9930,10 +9939,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="C475" t="s">
-        <v>859</v>
+        <v>852</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9941,10 +9950,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="C476" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9952,10 +9961,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="C477" t="s">
-        <v>1168</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9963,10 +9972,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="C478" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9974,10 +9983,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="C479" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9985,10 +9994,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="C480" t="s">
-        <v>1110</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -9996,10 +10005,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="C481" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10007,10 +10016,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="C482" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10018,10 +10027,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="C483" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10029,10 +10038,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C484" t="s">
-        <v>874</v>
+        <v>867</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10040,10 +10049,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="C485" t="s">
-        <v>876</v>
+        <v>869</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10051,10 +10060,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="C486" t="s">
-        <v>878</v>
+        <v>871</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10062,10 +10071,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
-        <v>879</v>
+        <v>872</v>
       </c>
       <c r="C487" t="s">
-        <v>880</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10073,10 +10082,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C488" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10084,10 +10093,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="C489" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10095,10 +10104,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="C490" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10106,10 +10115,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="C491" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10117,10 +10126,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="C492" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10128,10 +10137,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="C493" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10139,10 +10148,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="C494" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10150,10 +10159,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="C495" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10161,10 +10170,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="C496" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10172,10 +10181,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
       <c r="C497" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10183,10 +10192,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="C498" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10194,7 +10203,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10202,10 +10211,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="C500" t="s">
-        <v>1116</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10213,10 +10222,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="C501" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10224,10 +10233,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="C502" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10235,10 +10244,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
       <c r="C503" t="s">
-        <v>1109</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10246,10 +10255,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="C504" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10257,10 +10266,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="C505" t="s">
-        <v>1158</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10268,10 +10277,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="C506" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10279,10 +10288,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="C507" t="s">
-        <v>1129</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10290,10 +10299,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="C508" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10301,10 +10310,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="C509" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10312,10 +10321,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
       <c r="C510" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10323,10 +10332,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="C511" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10334,10 +10343,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="C512" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10345,10 +10354,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="C513" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10356,10 +10365,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="C514" t="s">
-        <v>1303</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10367,10 +10376,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="C515" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10378,10 +10387,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C516" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10389,10 +10398,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="C517" t="s">
-        <v>1128</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10400,7 +10409,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10408,10 +10417,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="C519" t="s">
-        <v>1111</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10419,10 +10428,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="C520" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10430,10 +10439,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="C521" t="s">
-        <v>1157</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10441,10 +10450,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="C522" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10452,10 +10461,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="C523" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10463,10 +10472,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="C524" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10474,10 +10483,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="C525" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10485,10 +10494,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="C526" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10496,10 +10505,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C527" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10507,10 +10516,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="C528" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10518,10 +10527,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="C529" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10529,10 +10538,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="C530" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10540,10 +10549,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="C531" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10551,10 +10560,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="C532" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10562,10 +10571,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="C533" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10573,10 +10582,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="C534" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10584,10 +10593,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
-        <v>959</v>
+        <v>951</v>
       </c>
       <c r="C535" t="s">
-        <v>960</v>
+        <v>952</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10595,10 +10604,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="C536" t="s">
-        <v>1127</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10606,10 +10615,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="C537" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10617,10 +10626,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="C538" t="s">
-        <v>1261</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10628,10 +10637,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="C539" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10639,10 +10648,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="C540" t="s">
-        <v>1080</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10650,10 +10659,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="C541" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10661,10 +10670,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="C542" t="s">
-        <v>970</v>
+        <v>962</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10672,10 +10681,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="C543" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10683,10 +10692,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="C544" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10694,10 +10703,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="C545" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10705,10 +10714,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="C546" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10716,7 +10725,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10724,10 +10733,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="C548" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10735,10 +10744,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="C549" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10746,10 +10755,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="C550" t="s">
-        <v>1126</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10757,10 +10766,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="C551" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10768,10 +10777,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="C552" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10779,10 +10788,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="C553" t="s">
-        <v>1089</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10790,10 +10799,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="C554" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10801,10 +10810,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="C555" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10812,10 +10821,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="C556" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10823,10 +10832,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="C557" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10834,10 +10843,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="C558" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10845,7 +10854,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10853,10 +10862,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="C560" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10864,10 +10873,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="C561" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10875,10 +10884,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="C562" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10886,10 +10895,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="C563" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10897,10 +10906,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="C564" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10908,10 +10917,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="C565" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10919,10 +10928,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
       <c r="C566" t="s">
-        <v>1114</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10930,10 +10939,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="C567" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10941,10 +10950,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="C568" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10952,10 +10961,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="C569" t="s">
-        <v>1124</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10963,10 +10972,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="C570" t="s">
-        <v>1016</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10974,10 +10983,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="C571" t="s">
-        <v>1153</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10985,10 +10994,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
       <c r="C572" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10996,10 +11005,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="C573" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11007,10 +11016,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="C574" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11018,10 +11027,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
       <c r="C575" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11029,10 +11038,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="C576" t="s">
-        <v>1266</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11040,10 +11049,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="C577" t="s">
-        <v>1265</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11051,10 +11060,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="C578" t="s">
-        <v>1264</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11062,10 +11071,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="C579" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11073,10 +11082,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="C580" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11084,10 +11093,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="C581" t="s">
-        <v>1283</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11095,10 +11104,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="C582" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11106,10 +11115,10 @@
         <v>612</v>
       </c>
       <c r="B583" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="C583" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11117,10 +11126,10 @@
         <v>617</v>
       </c>
       <c r="B584" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
       <c r="C584" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11128,10 +11137,10 @@
         <v>618</v>
       </c>
       <c r="B585" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="C585" t="s">
-        <v>1032</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11139,10 +11148,10 @@
         <v>625</v>
       </c>
       <c r="B586" t="s">
-        <v>1082</v>
+        <v>1073</v>
       </c>
       <c r="C586" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11150,10 +11159,10 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
-        <v>1291</v>
+        <v>1276</v>
       </c>
       <c r="C587" t="s">
-        <v>1292</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11161,10 +11170,10 @@
         <v>626</v>
       </c>
       <c r="B588" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="C588" t="s">
-        <v>1034</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11172,10 +11181,10 @@
         <v>629</v>
       </c>
       <c r="B589" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
       <c r="C589" t="s">
-        <v>1177</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11183,10 +11192,10 @@
         <v>630</v>
       </c>
       <c r="B590" t="s">
-        <v>1289</v>
+        <v>1274</v>
       </c>
       <c r="C590" t="s">
-        <v>1290</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11194,10 +11203,10 @@
         <v>633</v>
       </c>
       <c r="B591" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
       <c r="C591" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11205,10 +11214,10 @@
         <v>635</v>
       </c>
       <c r="B592" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="C592" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11216,10 +11225,10 @@
         <v>636</v>
       </c>
       <c r="B593" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="C593" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11227,10 +11236,10 @@
         <v>642</v>
       </c>
       <c r="B594" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="C594" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11238,10 +11247,10 @@
         <v>644</v>
       </c>
       <c r="B595" t="s">
-        <v>1262</v>
+        <v>1251</v>
       </c>
       <c r="C595" t="s">
-        <v>1263</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11249,10 +11258,10 @@
         <v>646</v>
       </c>
       <c r="B596" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="C596" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11260,10 +11269,10 @@
         <v>649</v>
       </c>
       <c r="B597" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="C597" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11271,10 +11280,10 @@
         <v>650</v>
       </c>
       <c r="B598" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="C598" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11282,10 +11291,10 @@
         <v>651</v>
       </c>
       <c r="B599" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="C599" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11293,10 +11302,10 @@
         <v>653</v>
       </c>
       <c r="B600" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="C600" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11304,10 +11313,10 @@
         <v>654</v>
       </c>
       <c r="B601" t="s">
-        <v>1151</v>
+        <v>1141</v>
       </c>
       <c r="C601" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11315,10 +11324,10 @@
         <v>655</v>
       </c>
       <c r="B602" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="C602" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11326,10 +11335,10 @@
         <v>659</v>
       </c>
       <c r="B603" t="s">
-        <v>1305</v>
+        <v>1289</v>
       </c>
       <c r="C603" t="s">
-        <v>1306</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11337,10 +11346,10 @@
         <v>660</v>
       </c>
       <c r="B604" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="C604" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11348,10 +11357,10 @@
         <v>661</v>
       </c>
       <c r="B605" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="C605" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11359,10 +11368,10 @@
         <v>663</v>
       </c>
       <c r="B606" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
       <c r="C606" t="s">
-        <v>1258</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11370,10 +11379,10 @@
         <v>667</v>
       </c>
       <c r="B607" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="C607" t="s">
-        <v>1123</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11381,10 +11390,10 @@
         <v>670</v>
       </c>
       <c r="B608" t="s">
-        <v>1286</v>
+        <v>1271</v>
       </c>
       <c r="C608" t="s">
-        <v>1287</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11392,10 +11401,10 @@
         <v>673</v>
       </c>
       <c r="B609" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="C609" t="s">
-        <v>1113</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11403,10 +11412,10 @@
         <v>674</v>
       </c>
       <c r="B610" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="C610" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11414,10 +11423,10 @@
         <v>680</v>
       </c>
       <c r="B611" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="C611" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11425,10 +11434,10 @@
         <v>681</v>
       </c>
       <c r="B612" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="C612" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11436,10 +11445,10 @@
         <v>682</v>
       </c>
       <c r="B613" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="C613" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11447,10 +11456,10 @@
         <v>683</v>
       </c>
       <c r="B614" t="s">
-        <v>1285</v>
+        <v>1270</v>
       </c>
       <c r="C614" t="s">
-        <v>1288</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11458,10 +11467,10 @@
         <v>684</v>
       </c>
       <c r="B615" t="s">
-        <v>1068</v>
+        <v>1059</v>
       </c>
       <c r="C615" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11469,10 +11478,10 @@
         <v>685</v>
       </c>
       <c r="B616" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="C616" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11480,10 +11489,10 @@
         <v>686</v>
       </c>
       <c r="B617" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="C617" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11491,10 +11500,10 @@
         <v>689</v>
       </c>
       <c r="B618" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
       <c r="C618" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11502,10 +11511,10 @@
         <v>697</v>
       </c>
       <c r="B619" t="s">
-        <v>1145</v>
+        <v>1135</v>
       </c>
       <c r="C619" t="s">
-        <v>1267</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11513,10 +11522,10 @@
         <v>701</v>
       </c>
       <c r="B620" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="C620" t="s">
-        <v>1179</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11524,10 +11533,10 @@
         <v>702</v>
       </c>
       <c r="B621" t="s">
-        <v>1256</v>
+        <v>1245</v>
       </c>
       <c r="C621" t="s">
-        <v>1257</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11535,10 +11544,10 @@
         <v>704</v>
       </c>
       <c r="B622" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="C622" t="s">
-        <v>1301</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11546,10 +11555,10 @@
         <v>705</v>
       </c>
       <c r="B623" t="s">
-        <v>1270</v>
+        <v>1255</v>
       </c>
       <c r="C623" t="s">
-        <v>1271</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11557,10 +11566,10 @@
         <v>710</v>
       </c>
       <c r="B624" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="C624" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11568,10 +11577,10 @@
         <v>711</v>
       </c>
       <c r="B625" t="s">
-        <v>1253</v>
+        <v>1242</v>
       </c>
       <c r="C625" t="s">
-        <v>1254</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11579,10 +11588,10 @@
         <v>712</v>
       </c>
       <c r="B626" t="s">
-        <v>1251</v>
+        <v>1240</v>
       </c>
       <c r="C626" t="s">
-        <v>1252</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11590,10 +11599,10 @@
         <v>714</v>
       </c>
       <c r="B627" t="s">
-        <v>1249</v>
+        <v>1238</v>
       </c>
       <c r="C627" t="s">
-        <v>1250</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11601,10 +11610,10 @@
         <v>717</v>
       </c>
       <c r="B628" t="s">
-        <v>1247</v>
+        <v>1236</v>
       </c>
       <c r="C628" t="s">
-        <v>1248</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11612,10 +11621,10 @@
         <v>718</v>
       </c>
       <c r="B629" t="s">
-        <v>1245</v>
+        <v>1234</v>
       </c>
       <c r="C629" t="s">
-        <v>1246</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11623,10 +11632,10 @@
         <v>719</v>
       </c>
       <c r="B630" t="s">
-        <v>1243</v>
+        <v>1232</v>
       </c>
       <c r="C630" t="s">
-        <v>1244</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11634,10 +11643,10 @@
         <v>721</v>
       </c>
       <c r="B631" t="s">
-        <v>1241</v>
+        <v>1230</v>
       </c>
       <c r="C631" t="s">
-        <v>1242</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11645,10 +11654,10 @@
         <v>722</v>
       </c>
       <c r="B632" t="s">
-        <v>1239</v>
+        <v>1228</v>
       </c>
       <c r="C632" t="s">
-        <v>1240</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11656,10 +11665,10 @@
         <v>723</v>
       </c>
       <c r="B633" t="s">
-        <v>1237</v>
+        <v>1226</v>
       </c>
       <c r="C633" t="s">
-        <v>1238</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11667,10 +11676,10 @@
         <v>725</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1235</v>
+        <v>1224</v>
       </c>
       <c r="C634" t="s">
-        <v>1236</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11678,10 +11687,10 @@
         <v>726</v>
       </c>
       <c r="B635" t="s">
-        <v>1233</v>
+        <v>1222</v>
       </c>
       <c r="C635" t="s">
-        <v>1234</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11689,10 +11698,10 @@
         <v>727</v>
       </c>
       <c r="B636" t="s">
-        <v>1231</v>
+        <v>1220</v>
       </c>
       <c r="C636" t="s">
-        <v>1232</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11700,10 +11709,10 @@
         <v>728</v>
       </c>
       <c r="B637" t="s">
-        <v>1230</v>
+        <v>1219</v>
       </c>
       <c r="C637" t="s">
-        <v>1255</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11711,10 +11720,10 @@
         <v>729</v>
       </c>
       <c r="B638" t="s">
-        <v>1228</v>
+        <v>1217</v>
       </c>
       <c r="C638" t="s">
-        <v>1229</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11722,10 +11731,10 @@
         <v>730</v>
       </c>
       <c r="B639" t="s">
-        <v>1226</v>
+        <v>1215</v>
       </c>
       <c r="C639" t="s">
-        <v>1227</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11733,10 +11742,10 @@
         <v>731</v>
       </c>
       <c r="B640" t="s">
-        <v>1224</v>
+        <v>1213</v>
       </c>
       <c r="C640" t="s">
-        <v>1225</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11744,10 +11753,10 @@
         <v>733</v>
       </c>
       <c r="B641" t="s">
-        <v>1222</v>
+        <v>1211</v>
       </c>
       <c r="C641" t="s">
-        <v>1223</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11755,10 +11764,10 @@
         <v>735</v>
       </c>
       <c r="B642" t="s">
-        <v>1220</v>
+        <v>1209</v>
       </c>
       <c r="C642" t="s">
-        <v>1221</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11766,10 +11775,10 @@
         <v>736</v>
       </c>
       <c r="B643" t="s">
-        <v>1218</v>
+        <v>1207</v>
       </c>
       <c r="C643" t="s">
-        <v>1219</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11777,10 +11786,10 @@
         <v>737</v>
       </c>
       <c r="B644" t="s">
-        <v>1259</v>
+        <v>1248</v>
       </c>
       <c r="C644" t="s">
-        <v>1260</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11788,10 +11797,10 @@
         <v>738</v>
       </c>
       <c r="B645" t="s">
-        <v>1216</v>
+        <v>1205</v>
       </c>
       <c r="C645" t="s">
-        <v>1217</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11799,10 +11808,10 @@
         <v>739</v>
       </c>
       <c r="B646" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
       <c r="C646" t="s">
-        <v>1215</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11810,10 +11819,10 @@
         <v>740</v>
       </c>
       <c r="B647" t="s">
-        <v>1212</v>
+        <v>1201</v>
       </c>
       <c r="C647" t="s">
-        <v>1213</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11821,10 +11830,10 @@
         <v>741</v>
       </c>
       <c r="B648" t="s">
-        <v>1210</v>
+        <v>1199</v>
       </c>
       <c r="C648" t="s">
-        <v>1211</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11832,10 +11841,10 @@
         <v>742</v>
       </c>
       <c r="B649" t="s">
-        <v>1272</v>
+        <v>1257</v>
       </c>
       <c r="C649" t="s">
-        <v>1273</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11843,10 +11852,10 @@
         <v>743</v>
       </c>
       <c r="B650" t="s">
-        <v>1274</v>
+        <v>1259</v>
       </c>
       <c r="C650" t="s">
-        <v>1275</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11854,10 +11863,10 @@
         <v>744</v>
       </c>
       <c r="B651" t="s">
-        <v>1276</v>
+        <v>1261</v>
       </c>
       <c r="C651" t="s">
-        <v>1277</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="652" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11865,10 +11874,10 @@
         <v>745</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1278</v>
+        <v>1263</v>
       </c>
       <c r="C652" t="s">
-        <v>1279</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11876,10 +11885,10 @@
         <v>746</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1280</v>
+        <v>1265</v>
       </c>
       <c r="C653" t="s">
-        <v>1281</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11887,10 +11896,10 @@
         <v>747</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1282</v>
+        <v>1267</v>
       </c>
       <c r="C654" t="s">
-        <v>1304</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11898,10 +11907,10 @@
         <v>748</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1299</v>
+        <v>1284</v>
       </c>
       <c r="C655" t="s">
-        <v>1300</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11909,10 +11918,10 @@
         <v>749</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1297</v>
+        <v>1282</v>
       </c>
       <c r="C656" t="s">
-        <v>1298</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11920,10 +11929,10 @@
         <v>753</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1295</v>
+        <v>1280</v>
       </c>
       <c r="C657" t="s">
-        <v>1296</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11931,10 +11940,10 @@
         <v>755</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1293</v>
+        <v>1278</v>
       </c>
       <c r="C658" t="s">
-        <v>1294</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11942,10 +11951,10 @@
         <v>10001</v>
       </c>
       <c r="B659" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="C659" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11953,10 +11962,10 @@
         <v>10003</v>
       </c>
       <c r="B660" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
       <c r="C660" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
     </row>
   </sheetData>
@@ -11964,7 +11973,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A659:C659 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C314 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C169 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C422 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C498 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:C570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C285 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C401 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C228 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A659:C659 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:B570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A422:B422 A421:B421 A488:C498 A487:B487 A285:B285 A168:C169 A167:B167 A391:C401 A390:B390" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2235BEE5-64E4-4CFE-A653-0CDBEA363C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017D7AEA-8D55-444A-BA09-2588912015E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2168,12 +2168,6 @@
   </si>
   <si>
     <t>冬之花</t>
-  </si>
-  <si>
-    <t>CiRCLE THANKS MUSiC♪</t>
-  </si>
-  <si>
-    <t>瑟科感谢音乐,听我说谢谢你,ctm,CiRCLE THANKS MUSiC</t>
   </si>
   <si>
     <t>ヴァンパイア</t>
@@ -3482,10 +3476,6 @@
   </si>
   <si>
     <t>最喜欢了！,最喜欢了!,daisuki,最喜欢,最喜欢了,大好</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>听我说谢谢你,谢谢full</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4295,6 +4285,29 @@
   </si>
   <si>
     <t>灵魂战士,ss,前奏爆一百遍,喜欢我24分吗,魂兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑟科感谢音乐,听我说谢谢你,ctm,CiRCLE THANKS MUSiC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CiRCLE THANKS MUSiC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>♪</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>听我说谢谢你,谢谢full,ctmfull,fullctm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4742,7 +4755,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4753,7 +4766,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -4764,7 +4777,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -4775,7 +4788,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -4808,7 +4821,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -4863,7 +4876,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4885,7 +4898,7 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -4940,7 +4953,7 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -4973,7 +4986,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5028,7 +5041,7 @@
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -5050,7 +5063,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5061,7 +5074,7 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -5138,7 +5151,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5149,7 +5162,7 @@
         <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5193,7 +5206,7 @@
         <v>71</v>
       </c>
       <c r="C43" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -5281,7 +5294,7 @@
         <v>86</v>
       </c>
       <c r="C51" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -5303,7 +5316,7 @@
         <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -5314,7 +5327,7 @@
         <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -5358,7 +5371,7 @@
         <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -5490,7 +5503,7 @@
         <v>120</v>
       </c>
       <c r="C70" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -5498,10 +5511,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C71" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -5589,7 +5602,7 @@
         <v>135</v>
       </c>
       <c r="C79" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -5655,7 +5668,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -5743,7 +5756,7 @@
         <v>161</v>
       </c>
       <c r="C93" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -5754,7 +5767,7 @@
         <v>162</v>
       </c>
       <c r="C94" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -5809,7 +5822,7 @@
         <v>171</v>
       </c>
       <c r="C99" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -5897,7 +5910,7 @@
         <v>186</v>
       </c>
       <c r="C107" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -5974,7 +5987,7 @@
         <v>199</v>
       </c>
       <c r="C114" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -6040,7 +6053,7 @@
         <v>210</v>
       </c>
       <c r="C120" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -6128,7 +6141,7 @@
         <v>225</v>
       </c>
       <c r="C128" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6183,7 +6196,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6315,7 +6328,7 @@
         <v>257</v>
       </c>
       <c r="C145" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6370,7 +6383,7 @@
         <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6414,7 +6427,7 @@
         <v>273</v>
       </c>
       <c r="C154" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6502,7 +6515,7 @@
         <v>288</v>
       </c>
       <c r="C162" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6557,7 +6570,7 @@
         <v>297</v>
       </c>
       <c r="C167" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6590,7 +6603,7 @@
         <v>302</v>
       </c>
       <c r="C170" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -7008,7 +7021,7 @@
         <v>377</v>
       </c>
       <c r="C208" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7239,7 +7252,7 @@
         <v>418</v>
       </c>
       <c r="C229" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7250,7 +7263,7 @@
         <v>419</v>
       </c>
       <c r="C230" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7294,7 +7307,7 @@
         <v>426</v>
       </c>
       <c r="C234" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7470,7 +7483,7 @@
         <v>457</v>
       </c>
       <c r="C250" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7481,7 +7494,7 @@
         <v>458</v>
       </c>
       <c r="C251" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7547,7 +7560,7 @@
         <v>468</v>
       </c>
       <c r="C257" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7580,7 +7593,7 @@
         <v>473</v>
       </c>
       <c r="C260" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7668,7 +7681,7 @@
         <v>488</v>
       </c>
       <c r="C268" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7789,7 +7802,7 @@
         <v>509</v>
       </c>
       <c r="C279" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7800,7 +7813,7 @@
         <v>510</v>
       </c>
       <c r="C280" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7855,7 +7868,7 @@
         <v>519</v>
       </c>
       <c r="C285" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7866,7 +7879,7 @@
         <v>520</v>
       </c>
       <c r="C286" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7965,7 +7978,7 @@
         <v>537</v>
       </c>
       <c r="C295" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -8097,7 +8110,7 @@
         <v>560</v>
       </c>
       <c r="C307" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8163,7 +8176,7 @@
         <v>571</v>
       </c>
       <c r="C313" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8185,7 +8198,7 @@
         <v>574</v>
       </c>
       <c r="C315" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8314,10 +8327,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="C327" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8515,7 +8528,7 @@
         <v>631</v>
       </c>
       <c r="C345" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8559,7 +8572,7 @@
         <v>638</v>
       </c>
       <c r="C349" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8581,7 +8594,7 @@
         <v>641</v>
       </c>
       <c r="C351" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8603,7 +8616,7 @@
         <v>644</v>
       </c>
       <c r="C353" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8834,7 +8847,7 @@
         <v>685</v>
       </c>
       <c r="C374" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8867,7 +8880,7 @@
         <v>690</v>
       </c>
       <c r="C377" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8889,7 +8902,7 @@
         <v>693</v>
       </c>
       <c r="C379" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8966,7 +8979,7 @@
         <v>706</v>
       </c>
       <c r="C386" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -9010,7 +9023,7 @@
         <v>713</v>
       </c>
       <c r="C390" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9024,15 +9037,15 @@
         <v>715</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>716</v>
+        <v>1305</v>
       </c>
       <c r="C392" t="s">
-        <v>717</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9040,10 +9053,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C393" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9051,10 +9064,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C394" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9062,10 +9075,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C395" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9073,10 +9086,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C396" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9084,10 +9097,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C397" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9095,10 +9108,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C398" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9106,10 +9119,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C399" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9117,10 +9130,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C400" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9128,10 +9141,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C401" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9139,10 +9152,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C402" t="s">
-        <v>1125</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9150,10 +9163,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C403" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9161,10 +9174,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C404" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9172,10 +9185,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C405" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9183,10 +9196,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="C406" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9194,10 +9207,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C407" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9205,10 +9218,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C408" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9216,10 +9229,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C409" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9227,10 +9240,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C410" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9238,10 +9251,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C411" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9249,10 +9262,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="C412" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9260,10 +9273,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C413" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9271,10 +9284,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C414" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9282,10 +9295,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C415" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9293,10 +9306,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C416" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9304,10 +9317,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C417" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9315,10 +9328,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C418" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9326,10 +9339,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C419" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9337,10 +9350,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C420" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9348,10 +9361,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C421" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9359,10 +9372,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C422" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9370,10 +9383,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C423" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9381,10 +9394,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C424" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9392,10 +9405,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C425" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9403,10 +9416,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C426" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9414,10 +9427,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C427" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9425,10 +9438,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C428" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9436,10 +9449,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C429" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9447,10 +9460,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C430" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9458,10 +9471,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C431" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9469,10 +9482,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C432" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9480,10 +9493,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C433" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9491,10 +9504,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C434" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9502,10 +9515,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C435" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9513,10 +9526,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C436" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9524,10 +9537,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C437" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9535,10 +9548,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C438" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9546,10 +9559,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C439" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9557,10 +9570,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C440" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9568,10 +9581,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C441" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9579,10 +9592,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C442" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9590,10 +9603,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C443" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9601,10 +9614,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C444" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9612,10 +9625,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C445" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9623,10 +9636,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C446" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9634,10 +9647,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C447" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9645,10 +9658,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C448" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9656,10 +9669,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C449" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9667,10 +9680,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C450" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9681,7 +9694,7 @@
         <v>693</v>
       </c>
       <c r="C451" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9689,10 +9702,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C452" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9700,10 +9713,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C453" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9711,10 +9724,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C454" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9722,10 +9735,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C455" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9733,10 +9746,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C456" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9744,10 +9757,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C457" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9755,10 +9768,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C458" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9766,10 +9779,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C459" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9777,7 +9790,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9785,10 +9798,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C461" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9796,10 +9809,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C462" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9807,10 +9820,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C463" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9818,10 +9831,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C464" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9829,10 +9842,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C465" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9840,10 +9853,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C466" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9851,10 +9864,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C467" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9862,10 +9875,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C468" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9873,10 +9886,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C469" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9884,10 +9897,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C470" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9895,10 +9908,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C471" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9906,10 +9919,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C472" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9917,10 +9930,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="C473" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9928,10 +9941,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C474" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9939,10 +9952,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C475" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9950,10 +9963,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C476" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9961,10 +9974,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C477" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9972,10 +9985,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C478" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9983,10 +9996,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C479" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9994,10 +10007,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C480" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -10005,10 +10018,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C481" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -10016,10 +10029,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C482" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -10027,10 +10040,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C483" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10038,10 +10051,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C484" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10049,10 +10062,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C485" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10060,10 +10073,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C486" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10071,10 +10084,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C487" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10082,10 +10095,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C488" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10093,10 +10106,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C489" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10104,10 +10117,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C490" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10115,10 +10128,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C491" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10126,10 +10139,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C492" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10137,10 +10150,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C493" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10148,10 +10161,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C494" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10159,10 +10172,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C495" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10170,10 +10183,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C496" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10181,10 +10194,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C497" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10192,10 +10205,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C498" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10203,7 +10216,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10211,10 +10224,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C500" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10222,10 +10235,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C501" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10233,10 +10246,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C502" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10244,10 +10257,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C503" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10255,10 +10268,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C504" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10266,10 +10279,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C505" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10277,10 +10290,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C506" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10288,10 +10301,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C507" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10299,10 +10312,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C508" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10310,10 +10323,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C509" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10321,10 +10334,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C510" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10332,10 +10345,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C511" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10343,10 +10356,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C512" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10354,10 +10367,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C513" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10365,10 +10378,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C514" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10376,10 +10389,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C515" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10390,7 +10403,7 @@
         <v>671</v>
       </c>
       <c r="C516" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10398,10 +10411,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C517" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10409,7 +10422,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10417,10 +10430,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C519" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10428,10 +10441,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C520" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10439,10 +10452,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C521" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10450,10 +10463,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C522" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10461,10 +10474,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C523" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10472,10 +10485,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C524" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10483,10 +10496,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C525" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10494,10 +10507,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C526" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10505,10 +10518,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C527" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10516,10 +10529,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C528" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10527,10 +10540,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C529" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10538,10 +10551,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C530" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10549,10 +10562,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C531" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10560,10 +10573,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C532" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10571,10 +10584,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C533" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10582,10 +10595,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C534" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10593,10 +10606,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C535" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10604,10 +10617,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C536" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10615,10 +10628,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C537" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10626,10 +10639,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C538" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10637,10 +10650,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C539" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10648,10 +10661,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C540" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10659,10 +10672,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C541" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10670,10 +10683,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C542" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10681,10 +10694,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C543" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10692,10 +10705,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C544" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10703,10 +10716,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C545" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10714,10 +10727,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C546" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10725,7 +10738,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10733,10 +10746,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C548" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10744,10 +10757,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C549" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10755,10 +10768,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C550" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10766,10 +10779,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C551" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10777,10 +10790,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C552" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10788,10 +10801,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C553" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10799,10 +10812,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C554" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10810,10 +10823,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C555" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10821,10 +10834,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C556" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10832,10 +10845,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C557" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10843,10 +10856,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C558" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10854,7 +10867,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10862,10 +10875,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C560" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10873,10 +10886,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C561" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10884,10 +10897,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C562" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10895,10 +10908,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C563" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10906,10 +10919,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C564" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10917,10 +10930,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C565" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10928,10 +10941,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C566" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10939,10 +10952,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C567" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10950,10 +10963,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C568" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10961,10 +10974,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C569" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10972,10 +10985,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C570" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10983,10 +10996,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C571" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10994,10 +11007,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C572" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -11005,10 +11018,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C573" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -11016,10 +11029,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C574" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -11027,10 +11040,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C575" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11038,10 +11051,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C576" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11049,10 +11062,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C577" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11060,10 +11073,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C578" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11071,10 +11084,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C579" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11082,10 +11095,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C580" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11093,10 +11106,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="C581" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11104,10 +11117,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C582" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11115,10 +11128,10 @@
         <v>612</v>
       </c>
       <c r="B583" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C583" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11126,10 +11139,10 @@
         <v>617</v>
       </c>
       <c r="B584" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C584" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11137,10 +11150,10 @@
         <v>618</v>
       </c>
       <c r="B585" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C585" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11148,10 +11161,10 @@
         <v>625</v>
       </c>
       <c r="B586" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C586" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11159,10 +11172,10 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C587" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11170,10 +11183,10 @@
         <v>626</v>
       </c>
       <c r="B588" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C588" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11181,10 +11194,10 @@
         <v>629</v>
       </c>
       <c r="B589" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C589" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11192,10 +11205,10 @@
         <v>630</v>
       </c>
       <c r="B590" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C590" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11203,10 +11216,10 @@
         <v>633</v>
       </c>
       <c r="B591" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C591" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11214,10 +11227,10 @@
         <v>635</v>
       </c>
       <c r="B592" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C592" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11225,10 +11238,10 @@
         <v>636</v>
       </c>
       <c r="B593" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C593" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11236,10 +11249,10 @@
         <v>642</v>
       </c>
       <c r="B594" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C594" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11247,10 +11260,10 @@
         <v>644</v>
       </c>
       <c r="B595" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="C595" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11258,10 +11271,10 @@
         <v>646</v>
       </c>
       <c r="B596" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C596" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11269,10 +11282,10 @@
         <v>649</v>
       </c>
       <c r="B597" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="C597" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11280,10 +11293,10 @@
         <v>650</v>
       </c>
       <c r="B598" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C598" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11291,10 +11304,10 @@
         <v>651</v>
       </c>
       <c r="B599" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C599" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11302,10 +11315,10 @@
         <v>653</v>
       </c>
       <c r="B600" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C600" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11313,10 +11326,10 @@
         <v>654</v>
       </c>
       <c r="B601" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="C601" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11324,10 +11337,10 @@
         <v>655</v>
       </c>
       <c r="B602" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C602" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11335,10 +11348,10 @@
         <v>659</v>
       </c>
       <c r="B603" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C603" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11346,10 +11359,10 @@
         <v>660</v>
       </c>
       <c r="B604" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="C604" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11357,10 +11370,10 @@
         <v>661</v>
       </c>
       <c r="B605" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C605" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11368,10 +11381,10 @@
         <v>663</v>
       </c>
       <c r="B606" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C606" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11379,10 +11392,10 @@
         <v>667</v>
       </c>
       <c r="B607" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C607" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11390,10 +11403,10 @@
         <v>670</v>
       </c>
       <c r="B608" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C608" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11401,10 +11414,10 @@
         <v>673</v>
       </c>
       <c r="B609" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C609" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11412,10 +11425,10 @@
         <v>674</v>
       </c>
       <c r="B610" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C610" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11423,10 +11436,10 @@
         <v>680</v>
       </c>
       <c r="B611" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C611" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11434,10 +11447,10 @@
         <v>681</v>
       </c>
       <c r="B612" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C612" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11445,10 +11458,10 @@
         <v>682</v>
       </c>
       <c r="B613" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C613" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11456,10 +11469,10 @@
         <v>683</v>
       </c>
       <c r="B614" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C614" t="s">
         <v>1270</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11467,10 +11480,10 @@
         <v>684</v>
       </c>
       <c r="B615" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C615" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11478,10 +11491,10 @@
         <v>685</v>
       </c>
       <c r="B616" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C616" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11489,10 +11502,10 @@
         <v>686</v>
       </c>
       <c r="B617" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C617" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11500,10 +11513,10 @@
         <v>689</v>
       </c>
       <c r="B618" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C618" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11511,10 +11524,10 @@
         <v>697</v>
       </c>
       <c r="B619" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="C619" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11522,10 +11535,10 @@
         <v>701</v>
       </c>
       <c r="B620" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C620" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11533,10 +11546,10 @@
         <v>702</v>
       </c>
       <c r="B621" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="C621" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11544,10 +11557,10 @@
         <v>704</v>
       </c>
       <c r="B622" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C622" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11555,10 +11568,10 @@
         <v>705</v>
       </c>
       <c r="B623" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="C623" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11566,10 +11579,10 @@
         <v>710</v>
       </c>
       <c r="B624" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C624" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11577,10 +11590,10 @@
         <v>711</v>
       </c>
       <c r="B625" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="C625" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11588,10 +11601,10 @@
         <v>712</v>
       </c>
       <c r="B626" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="C626" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11599,10 +11612,10 @@
         <v>714</v>
       </c>
       <c r="B627" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="C627" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11610,10 +11623,10 @@
         <v>717</v>
       </c>
       <c r="B628" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="C628" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11621,10 +11634,10 @@
         <v>718</v>
       </c>
       <c r="B629" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="C629" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11632,10 +11645,10 @@
         <v>719</v>
       </c>
       <c r="B630" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="C630" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11643,10 +11656,10 @@
         <v>721</v>
       </c>
       <c r="B631" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="C631" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11654,10 +11667,10 @@
         <v>722</v>
       </c>
       <c r="B632" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="C632" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11665,10 +11678,10 @@
         <v>723</v>
       </c>
       <c r="B633" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C633" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11676,10 +11689,10 @@
         <v>725</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="C634" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11687,10 +11700,10 @@
         <v>726</v>
       </c>
       <c r="B635" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="C635" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11698,10 +11711,10 @@
         <v>727</v>
       </c>
       <c r="B636" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C636" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11709,10 +11722,10 @@
         <v>728</v>
       </c>
       <c r="B637" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C637" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11720,10 +11733,10 @@
         <v>729</v>
       </c>
       <c r="B638" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C638" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11731,10 +11744,10 @@
         <v>730</v>
       </c>
       <c r="B639" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C639" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11742,10 +11755,10 @@
         <v>731</v>
       </c>
       <c r="B640" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C640" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11753,10 +11766,10 @@
         <v>733</v>
       </c>
       <c r="B641" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C641" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11764,10 +11777,10 @@
         <v>735</v>
       </c>
       <c r="B642" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="C642" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11775,10 +11788,10 @@
         <v>736</v>
       </c>
       <c r="B643" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="C643" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11786,10 +11799,10 @@
         <v>737</v>
       </c>
       <c r="B644" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="C644" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11797,10 +11810,10 @@
         <v>738</v>
       </c>
       <c r="B645" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="C645" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11808,10 +11821,10 @@
         <v>739</v>
       </c>
       <c r="B646" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="C646" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11819,10 +11832,10 @@
         <v>740</v>
       </c>
       <c r="B647" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="C647" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11830,10 +11843,10 @@
         <v>741</v>
       </c>
       <c r="B648" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="C648" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11841,10 +11854,10 @@
         <v>742</v>
       </c>
       <c r="B649" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C649" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11852,10 +11865,10 @@
         <v>743</v>
       </c>
       <c r="B650" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C650" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11863,10 +11876,10 @@
         <v>744</v>
       </c>
       <c r="B651" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C651" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="652" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11874,10 +11887,10 @@
         <v>745</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C652" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11885,10 +11898,10 @@
         <v>746</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C653" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11896,10 +11909,10 @@
         <v>747</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C654" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11907,10 +11920,10 @@
         <v>748</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="C655" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11918,10 +11931,10 @@
         <v>749</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C656" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11929,10 +11942,10 @@
         <v>753</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="C657" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11940,10 +11953,10 @@
         <v>755</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="C658" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11951,10 +11964,10 @@
         <v>10001</v>
       </c>
       <c r="B659" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C659" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11962,10 +11975,10 @@
         <v>10003</v>
       </c>
       <c r="B660" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C660" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
   </sheetData>
@@ -11973,7 +11986,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A659:C659 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:B570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A422:B422 A421:B421 A488:C498 A487:B487 A285:B285 A168:C169 A167:B167 A391:C401 A390:B390" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A659:C659 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:B570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A422:B422 A421:B421 A488:C498 A487:B487 A285:B285 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017D7AEA-8D55-444A-BA09-2588912015E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87206153-05C4-4CF8-9FEC-156656F5947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13260" yWindow="1524" windowWidth="16824" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3640,10 +3640,6 @@
   </si>
   <si>
     <t>说茄子,say cheese,cheese,茄子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>人狂热者,人mania</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4308,6 +4304,10 @@
   </si>
   <si>
     <t>听我说谢谢你,谢谢full,ctmfull,fullctm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人狂热者,人mania,人狂热症</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4755,7 +4755,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -4986,7 +4986,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5063,7 +5063,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5151,7 +5151,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5162,7 +5162,7 @@
         <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5668,7 +5668,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -6196,7 +6196,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6383,7 +6383,7 @@
         <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6515,7 +6515,7 @@
         <v>288</v>
       </c>
       <c r="C162" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6570,7 +6570,7 @@
         <v>297</v>
       </c>
       <c r="C167" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6603,7 +6603,7 @@
         <v>302</v>
       </c>
       <c r="C170" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
         <v>377</v>
       </c>
       <c r="C208" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7813,7 +7813,7 @@
         <v>510</v>
       </c>
       <c r="C280" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7868,7 +7868,7 @@
         <v>519</v>
       </c>
       <c r="C285" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -8176,7 +8176,7 @@
         <v>571</v>
       </c>
       <c r="C313" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8572,7 +8572,7 @@
         <v>638</v>
       </c>
       <c r="C349" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8616,7 +8616,7 @@
         <v>644</v>
       </c>
       <c r="C353" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8847,7 +8847,7 @@
         <v>685</v>
       </c>
       <c r="C374" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8880,7 +8880,7 @@
         <v>690</v>
       </c>
       <c r="C377" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -9023,7 +9023,7 @@
         <v>713</v>
       </c>
       <c r="C390" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9042,10 +9042,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C392" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9155,7 +9155,7 @@
         <v>734</v>
       </c>
       <c r="C402" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9196,10 +9196,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C406" t="s">
         <v>1192</v>
-      </c>
-      <c r="C406" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9262,7 +9262,7 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C412" t="s">
         <v>750</v>
@@ -9273,7 +9273,7 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C413" t="s">
         <v>751</v>
@@ -9364,7 +9364,7 @@
         <v>764</v>
       </c>
       <c r="C421" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9375,7 +9375,7 @@
         <v>765</v>
       </c>
       <c r="C422" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9834,7 +9834,7 @@
         <v>833</v>
       </c>
       <c r="C464" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9930,10 +9930,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C473" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9944,7 +9944,7 @@
         <v>848</v>
       </c>
       <c r="C474" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -10087,7 +10087,7 @@
         <v>870</v>
       </c>
       <c r="C487" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>916</v>
       </c>
       <c r="C514" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10642,7 +10642,7 @@
         <v>953</v>
       </c>
       <c r="C538" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10988,7 +10988,7 @@
         <v>1005</v>
       </c>
       <c r="C570" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -11010,7 +11010,7 @@
         <v>1007</v>
       </c>
       <c r="C572" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -11054,7 +11054,7 @@
         <v>1011</v>
       </c>
       <c r="C576" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11065,7 +11065,7 @@
         <v>849</v>
       </c>
       <c r="C577" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11076,7 +11076,7 @@
         <v>851</v>
       </c>
       <c r="C578" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11106,10 +11106,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C581" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11131,7 +11131,7 @@
         <v>1017</v>
       </c>
       <c r="C583" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11172,10 +11172,10 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C587" t="s">
         <v>1273</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11197,7 +11197,7 @@
         <v>1024</v>
       </c>
       <c r="C589" t="s">
-        <v>1164</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11205,10 +11205,10 @@
         <v>630</v>
       </c>
       <c r="B590" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C590" t="s">
         <v>1271</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11260,10 +11260,10 @@
         <v>644</v>
       </c>
       <c r="B595" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C595" t="s">
         <v>1248</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11282,10 +11282,10 @@
         <v>649</v>
       </c>
       <c r="B597" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C597" t="s">
         <v>1184</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11348,10 +11348,10 @@
         <v>659</v>
       </c>
       <c r="B603" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C603" t="s">
         <v>1286</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11359,10 +11359,10 @@
         <v>660</v>
       </c>
       <c r="B604" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C604" t="s">
         <v>1182</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11384,7 +11384,7 @@
         <v>1058</v>
       </c>
       <c r="C606" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11403,10 +11403,10 @@
         <v>670</v>
       </c>
       <c r="B608" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C608" t="s">
         <v>1268</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11428,7 +11428,7 @@
         <v>1045</v>
       </c>
       <c r="C610" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11447,10 +11447,10 @@
         <v>681</v>
       </c>
       <c r="B612" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C612" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11469,10 +11469,10 @@
         <v>683</v>
       </c>
       <c r="B614" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C614" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11527,7 +11527,7 @@
         <v>1132</v>
       </c>
       <c r="C619" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11535,10 +11535,10 @@
         <v>701</v>
       </c>
       <c r="B620" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C620" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11546,10 +11546,10 @@
         <v>702</v>
       </c>
       <c r="B621" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C621" t="s">
         <v>1242</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11560,7 +11560,7 @@
         <v>1084</v>
       </c>
       <c r="C622" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11568,10 +11568,10 @@
         <v>705</v>
       </c>
       <c r="B623" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C623" t="s">
         <v>1252</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11579,10 +11579,10 @@
         <v>710</v>
       </c>
       <c r="B624" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C624" t="s">
         <v>1177</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11590,10 +11590,10 @@
         <v>711</v>
       </c>
       <c r="B625" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C625" t="s">
         <v>1239</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11601,10 +11601,10 @@
         <v>712</v>
       </c>
       <c r="B626" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C626" t="s">
         <v>1237</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11612,10 +11612,10 @@
         <v>714</v>
       </c>
       <c r="B627" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C627" t="s">
         <v>1235</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11623,10 +11623,10 @@
         <v>717</v>
       </c>
       <c r="B628" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C628" t="s">
         <v>1233</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11634,10 +11634,10 @@
         <v>718</v>
       </c>
       <c r="B629" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C629" t="s">
         <v>1231</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11645,10 +11645,10 @@
         <v>719</v>
       </c>
       <c r="B630" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C630" t="s">
         <v>1229</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11656,10 +11656,10 @@
         <v>721</v>
       </c>
       <c r="B631" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C631" t="s">
         <v>1227</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11667,10 +11667,10 @@
         <v>722</v>
       </c>
       <c r="B632" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C632" t="s">
         <v>1225</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11678,10 +11678,10 @@
         <v>723</v>
       </c>
       <c r="B633" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C633" t="s">
         <v>1223</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11689,10 +11689,10 @@
         <v>725</v>
       </c>
       <c r="B634" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C634" t="s">
         <v>1221</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
@@ -11700,10 +11700,10 @@
         <v>726</v>
       </c>
       <c r="B635" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C635" t="s">
         <v>1219</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11711,10 +11711,10 @@
         <v>727</v>
       </c>
       <c r="B636" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C636" t="s">
         <v>1217</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11722,10 +11722,10 @@
         <v>728</v>
       </c>
       <c r="B637" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C637" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11733,10 +11733,10 @@
         <v>729</v>
       </c>
       <c r="B638" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C638" t="s">
         <v>1214</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11744,10 +11744,10 @@
         <v>730</v>
       </c>
       <c r="B639" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C639" t="s">
         <v>1212</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11755,10 +11755,10 @@
         <v>731</v>
       </c>
       <c r="B640" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C640" t="s">
         <v>1210</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -11766,10 +11766,10 @@
         <v>733</v>
       </c>
       <c r="B641" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C641" t="s">
         <v>1208</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
@@ -11777,10 +11777,10 @@
         <v>735</v>
       </c>
       <c r="B642" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C642" t="s">
         <v>1206</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11788,10 +11788,10 @@
         <v>736</v>
       </c>
       <c r="B643" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C643" t="s">
         <v>1204</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11799,10 +11799,10 @@
         <v>737</v>
       </c>
       <c r="B644" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C644" t="s">
         <v>1245</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11810,10 +11810,10 @@
         <v>738</v>
       </c>
       <c r="B645" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C645" t="s">
         <v>1202</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11821,10 +11821,10 @@
         <v>739</v>
       </c>
       <c r="B646" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C646" t="s">
         <v>1200</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11832,10 +11832,10 @@
         <v>740</v>
       </c>
       <c r="B647" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C647" t="s">
         <v>1198</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11843,10 +11843,10 @@
         <v>741</v>
       </c>
       <c r="B648" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C648" t="s">
         <v>1196</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11854,10 +11854,10 @@
         <v>742</v>
       </c>
       <c r="B649" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C649" t="s">
         <v>1254</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11865,10 +11865,10 @@
         <v>743</v>
       </c>
       <c r="B650" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C650" t="s">
         <v>1256</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11876,10 +11876,10 @@
         <v>744</v>
       </c>
       <c r="B651" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C651" t="s">
         <v>1258</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="652" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11887,10 +11887,10 @@
         <v>745</v>
       </c>
       <c r="B652" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C652" t="s">
         <v>1260</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11898,10 +11898,10 @@
         <v>746</v>
       </c>
       <c r="B653" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C653" t="s">
         <v>1262</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11909,10 +11909,10 @@
         <v>747</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C654" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11920,10 +11920,10 @@
         <v>748</v>
       </c>
       <c r="B655" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C655" t="s">
         <v>1281</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11931,10 +11931,10 @@
         <v>749</v>
       </c>
       <c r="B656" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C656" t="s">
         <v>1279</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11942,10 +11942,10 @@
         <v>753</v>
       </c>
       <c r="B657" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C657" t="s">
         <v>1277</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11953,10 +11953,10 @@
         <v>755</v>
       </c>
       <c r="B658" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C658" t="s">
         <v>1275</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87206153-05C4-4CF8-9FEC-156656F5947A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AC6351-66D9-4D39-8E12-B6F634BF3BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13260" yWindow="1524" windowWidth="16824" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3974,10 +3974,6 @@
   </si>
   <si>
     <t>Requiem for Fate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命运安魂,命运</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4308,6 +4304,10 @@
   </si>
   <si>
     <t>人狂热者,人mania,人狂热症</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命运安魂,命运,命运交响曲,命运镇魂曲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4755,7 +4755,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5151,7 +5151,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -6196,7 +6196,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6515,7 +6515,7 @@
         <v>288</v>
       </c>
       <c r="C162" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6570,7 +6570,7 @@
         <v>297</v>
       </c>
       <c r="C167" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -7021,7 +7021,7 @@
         <v>377</v>
       </c>
       <c r="C208" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7868,7 +7868,7 @@
         <v>519</v>
       </c>
       <c r="C285" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -8176,7 +8176,7 @@
         <v>571</v>
       </c>
       <c r="C313" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8880,7 +8880,7 @@
         <v>690</v>
       </c>
       <c r="C377" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -9023,7 +9023,7 @@
         <v>713</v>
       </c>
       <c r="C390" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9042,10 +9042,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C392" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9155,7 +9155,7 @@
         <v>734</v>
       </c>
       <c r="C402" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9364,7 +9364,7 @@
         <v>764</v>
       </c>
       <c r="C421" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9375,7 +9375,7 @@
         <v>765</v>
       </c>
       <c r="C422" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9944,7 +9944,7 @@
         <v>848</v>
       </c>
       <c r="C474" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -10087,7 +10087,7 @@
         <v>870</v>
       </c>
       <c r="C487" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>916</v>
       </c>
       <c r="C514" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10642,7 +10642,7 @@
         <v>953</v>
       </c>
       <c r="C538" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10988,7 +10988,7 @@
         <v>1005</v>
       </c>
       <c r="C570" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -11054,7 +11054,7 @@
         <v>1011</v>
       </c>
       <c r="C576" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11065,7 +11065,7 @@
         <v>849</v>
       </c>
       <c r="C577" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11076,7 +11076,7 @@
         <v>851</v>
       </c>
       <c r="C578" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11109,7 +11109,7 @@
         <v>1174</v>
       </c>
       <c r="C581" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11172,10 +11172,10 @@
         <v>624</v>
       </c>
       <c r="B587" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C587" t="s">
         <v>1272</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11197,7 +11197,7 @@
         <v>1024</v>
       </c>
       <c r="C589" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11205,10 +11205,10 @@
         <v>630</v>
       </c>
       <c r="B590" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C590" t="s">
         <v>1270</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11260,10 +11260,10 @@
         <v>644</v>
       </c>
       <c r="B595" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C595" t="s">
         <v>1247</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11348,10 +11348,10 @@
         <v>659</v>
       </c>
       <c r="B603" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C603" t="s">
         <v>1285</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11384,7 +11384,7 @@
         <v>1058</v>
       </c>
       <c r="C606" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11403,10 +11403,10 @@
         <v>670</v>
       </c>
       <c r="B608" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C608" t="s">
         <v>1267</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11469,10 +11469,10 @@
         <v>683</v>
       </c>
       <c r="B614" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C614" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11527,7 +11527,7 @@
         <v>1132</v>
       </c>
       <c r="C619" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11546,10 +11546,10 @@
         <v>702</v>
       </c>
       <c r="B621" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C621" t="s">
         <v>1241</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11560,7 +11560,7 @@
         <v>1084</v>
       </c>
       <c r="C622" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11568,10 +11568,10 @@
         <v>705</v>
       </c>
       <c r="B623" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C623" t="s">
         <v>1251</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11590,10 +11590,10 @@
         <v>711</v>
       </c>
       <c r="B625" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C625" t="s">
         <v>1238</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11601,10 +11601,10 @@
         <v>712</v>
       </c>
       <c r="B626" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C626" t="s">
         <v>1236</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11612,10 +11612,10 @@
         <v>714</v>
       </c>
       <c r="B627" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C627" t="s">
         <v>1234</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11626,7 +11626,7 @@
         <v>1232</v>
       </c>
       <c r="C628" t="s">
-        <v>1233</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11725,7 +11725,7 @@
         <v>1215</v>
       </c>
       <c r="C637" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11799,10 +11799,10 @@
         <v>737</v>
       </c>
       <c r="B644" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C644" t="s">
         <v>1244</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11854,10 +11854,10 @@
         <v>742</v>
       </c>
       <c r="B649" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C649" t="s">
         <v>1253</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11865,10 +11865,10 @@
         <v>743</v>
       </c>
       <c r="B650" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C650" t="s">
         <v>1255</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11876,10 +11876,10 @@
         <v>744</v>
       </c>
       <c r="B651" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C651" t="s">
         <v>1257</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="652" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11887,10 +11887,10 @@
         <v>745</v>
       </c>
       <c r="B652" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C652" t="s">
         <v>1259</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11898,10 +11898,10 @@
         <v>746</v>
       </c>
       <c r="B653" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C653" t="s">
         <v>1261</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11909,10 +11909,10 @@
         <v>747</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C654" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11920,10 +11920,10 @@
         <v>748</v>
       </c>
       <c r="B655" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C655" t="s">
         <v>1280</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
@@ -11931,10 +11931,10 @@
         <v>749</v>
       </c>
       <c r="B656" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C656" t="s">
         <v>1278</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11942,10 +11942,10 @@
         <v>753</v>
       </c>
       <c r="B657" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C657" t="s">
         <v>1276</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11953,10 +11953,10 @@
         <v>755</v>
       </c>
       <c r="B658" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C658" t="s">
         <v>1274</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AC6351-66D9-4D39-8E12-B6F634BF3BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE66B692-B6F9-4899-AC41-8D6AFE3AE3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12888" yWindow="1260" windowWidth="16824" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="1323">
   <si>
     <t>Id</t>
   </si>
@@ -4308,6 +4308,70 @@
   </si>
   <si>
     <t>命运安魂,命运,命运交响曲,命运镇魂曲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I wonder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想,我想要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松健桑巴,松健桑巴2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>マツケンサンバII</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Same Blue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同蓝,同样的蓝色,sb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>デビルじゃないもん</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不是魔鬼,才不是恶魔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>イケナイ太陽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顽皮的太阳,调皮的太阳,顽皮太阳,调皮太阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>きゅ〜まい＊flower(パラレルver.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>q花平行,平行,Q花平行,平行q花,平行Q花</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Determination Symphony(パラレルver.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平行交响曲,决议交响曲平行,平行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熱色スターマイン(パラレルver.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>热色平行,平行热色,熟色平行,平行熟色,平行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4727,7 +4791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C660"/>
+  <dimension ref="A1:C668"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -11961,23 +12025,111 @@
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659">
-        <v>10001</v>
-      </c>
-      <c r="B659" t="s">
-        <v>1055</v>
+        <v>756</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>1307</v>
       </c>
       <c r="C659" t="s">
-        <v>1056</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
+        <v>757</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C660" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A661">
+        <v>758</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C661" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A662">
+        <v>759</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C662" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A663">
+        <v>760</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C663" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A664">
+        <v>761</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C664" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A665">
+        <v>762</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C665" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A666">
+        <v>763</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C666" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A667">
+        <v>10001</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C667" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A668">
         <v>10003</v>
       </c>
-      <c r="B660" t="s">
+      <c r="B668" t="s">
         <v>1082</v>
       </c>
-      <c r="C660" t="s">
+      <c r="C668" t="s">
         <v>1083</v>
       </c>
     </row>
@@ -11986,7 +12138,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A659:C659 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:B570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A422:B422 A421:B421 A488:C498 A487:B487 A285:B285 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A667:C667 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:B570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A422:B422 A421:B421 A488:C498 A487:B487 A285:B285 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE66B692-B6F9-4899-AC41-8D6AFE3AE3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1374E11E-2631-4392-8485-3F34A249BD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12888" yWindow="1260" windowWidth="16824" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4363,15 +4363,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>平行交响曲,决议交响曲平行,平行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>熱色スターマイン(パラレルver.)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>热色平行,平行热色,熟色平行,平行熟色,平行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平行交响曲,决意交响曲平行,平行,决议交响曲平行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12097,7 +12097,7 @@
         <v>1319</v>
       </c>
       <c r="C665" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12105,10 +12105,10 @@
         <v>763</v>
       </c>
       <c r="B666" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C666" t="s">
         <v>1321</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1374E11E-2631-4392-8485-3F34A249BD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0949EA05-A49F-4694-85E5-58DA7C74BF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13140" yWindow="3744" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="1323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="1325">
   <si>
     <t>Id</t>
   </si>
@@ -4372,6 +4372,14 @@
   </si>
   <si>
     <t>平行交响曲,决意交响曲平行,平行,决议交响曲平行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最上級にかわいいの！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最上级,最上层</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4791,7 +4799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C668"/>
+  <dimension ref="A1:C669"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -11497,639 +11505,650 @@
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B611" t="s">
-        <v>1046</v>
+        <v>1323</v>
       </c>
       <c r="C611" t="s">
-        <v>1063</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B612" t="s">
-        <v>1178</v>
+        <v>1046</v>
       </c>
       <c r="C612" t="s">
-        <v>1180</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B613" t="s">
-        <v>1047</v>
+        <v>1178</v>
       </c>
       <c r="C613" t="s">
-        <v>1048</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B614" t="s">
-        <v>1265</v>
+        <v>1047</v>
       </c>
       <c r="C614" t="s">
-        <v>1268</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B615" t="s">
-        <v>1057</v>
+        <v>1265</v>
       </c>
       <c r="C615" t="s">
-        <v>1151</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B616" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="C616" t="s">
-        <v>1050</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B617" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C617" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B618" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C618" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B619" t="s">
-        <v>1132</v>
+        <v>1053</v>
       </c>
       <c r="C619" t="s">
-        <v>1248</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B620" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C620" t="s">
-        <v>1165</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B621" t="s">
-        <v>1240</v>
+        <v>1166</v>
       </c>
       <c r="C621" t="s">
-        <v>1241</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B622" t="s">
-        <v>1084</v>
+        <v>1240</v>
       </c>
       <c r="C622" t="s">
-        <v>1281</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B623" t="s">
-        <v>1250</v>
+        <v>1084</v>
       </c>
       <c r="C623" t="s">
-        <v>1251</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B624" t="s">
-        <v>1176</v>
+        <v>1250</v>
       </c>
       <c r="C624" t="s">
-        <v>1177</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B625" t="s">
-        <v>1237</v>
+        <v>1176</v>
       </c>
       <c r="C625" t="s">
-        <v>1238</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B626" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="C626" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B627" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C627" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B628" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C628" t="s">
-        <v>1306</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B629" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C629" t="s">
-        <v>1231</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630">
+        <v>718</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C630" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A631">
         <v>719</v>
       </c>
-      <c r="B630" t="s">
+      <c r="B631" t="s">
         <v>1228</v>
       </c>
-      <c r="C630" t="s">
+      <c r="C631" t="s">
         <v>1229</v>
       </c>
     </row>
-    <row r="631" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A631">
+    <row r="632" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A632">
         <v>721</v>
       </c>
-      <c r="B631" t="s">
+      <c r="B632" t="s">
         <v>1226</v>
       </c>
-      <c r="C631" t="s">
+      <c r="C632" t="s">
         <v>1227</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A632">
-        <v>722</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B633" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C633" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634">
-        <v>725</v>
-      </c>
-      <c r="B634" s="1" t="s">
-        <v>1220</v>
+        <v>723</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1222</v>
       </c>
       <c r="C634" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635">
-        <v>726</v>
-      </c>
-      <c r="B635" t="s">
-        <v>1218</v>
+        <v>725</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>1220</v>
       </c>
       <c r="C635" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636">
+        <v>726</v>
+      </c>
+      <c r="B636" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C636" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A637">
         <v>727</v>
       </c>
-      <c r="B636" t="s">
+      <c r="B637" t="s">
         <v>1216</v>
       </c>
-      <c r="C636" t="s">
+      <c r="C637" t="s">
         <v>1217</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A637">
-        <v>728</v>
-      </c>
-      <c r="B637" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A638">
+        <v>728</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C638" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A639">
         <v>729</v>
       </c>
-      <c r="B638" t="s">
+      <c r="B639" t="s">
         <v>1213</v>
       </c>
-      <c r="C638" t="s">
+      <c r="C639" t="s">
         <v>1214</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A639">
-        <v>730</v>
-      </c>
-      <c r="B639" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B640" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C640" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B641" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C641" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B642" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C642" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B643" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="C643" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B644" t="s">
-        <v>1243</v>
+        <v>1203</v>
       </c>
       <c r="C644" t="s">
-        <v>1244</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B645" t="s">
-        <v>1201</v>
+        <v>1243</v>
       </c>
       <c r="C645" t="s">
-        <v>1202</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B646" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C646" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B647" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="C647" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B648" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C648" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B649" t="s">
-        <v>1252</v>
+        <v>1195</v>
       </c>
       <c r="C649" t="s">
-        <v>1253</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B650" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C650" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651">
+        <v>743</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C651" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A652">
         <v>744</v>
       </c>
-      <c r="B651" t="s">
+      <c r="B652" t="s">
         <v>1256</v>
       </c>
-      <c r="C651" t="s">
+      <c r="C652" t="s">
         <v>1257</v>
       </c>
     </row>
-    <row r="652" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A652">
+    <row r="653" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A653">
         <v>745</v>
       </c>
-      <c r="B652" s="2" t="s">
+      <c r="B653" s="2" t="s">
         <v>1258</v>
       </c>
-      <c r="C652" t="s">
+      <c r="C653" t="s">
         <v>1259</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A653">
-        <v>746</v>
-      </c>
-      <c r="B653" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C654" t="s">
-        <v>1286</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1279</v>
+        <v>1262</v>
       </c>
       <c r="C655" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C656" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C657" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C658" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1307</v>
+        <v>1273</v>
       </c>
       <c r="C659" t="s">
-        <v>1308</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="C660" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C661" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C662" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C663" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C664" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C665" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C666" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667">
-        <v>10001</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1055</v>
+        <v>763</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>1320</v>
       </c>
       <c r="C667" t="s">
-        <v>1056</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668">
+        <v>10001</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A669">
         <v>10003</v>
       </c>
-      <c r="B668" t="s">
+      <c r="B669" t="s">
         <v>1082</v>
       </c>
-      <c r="C668" t="s">
+      <c r="C669" t="s">
         <v>1083</v>
       </c>
     </row>
@@ -12138,7 +12157,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A667:C667 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A613:C613 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A515:B515 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A616:C618 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A286:B286 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A609:B611 A576:B578 A514:B514 A513:B513 A501:C502 A453:C454 A424:C424 A423:B423 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A570:B570 A569:B569 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A571:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A422:B422 A421:B421 A488:C498 A487:B487 A285:B285 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A668:C668 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A614:C614 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A617:C619 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A612:B612 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A609:B610" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0949EA05-A49F-4694-85E5-58DA7C74BF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A998D-A539-4A58-BAFE-CBD0CF588DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13140" yWindow="3744" windowWidth="13152" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4307,10 +4307,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>命运安魂,命运,命运交响曲,命运镇魂曲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>I wonder</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4380,6 +4376,10 @@
   </si>
   <si>
     <t>最上级,最上层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命运安魂,命运,命运交响曲,命运镇魂曲,rff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11508,10 +11508,10 @@
         <v>675</v>
       </c>
       <c r="B611" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C611" t="s">
         <v>1323</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11709,7 +11709,7 @@
         <v>1232</v>
       </c>
       <c r="C629" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -12047,10 +12047,10 @@
         <v>756</v>
       </c>
       <c r="B660" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C660" t="s">
         <v>1307</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -12058,10 +12058,10 @@
         <v>757</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C661" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -12069,10 +12069,10 @@
         <v>758</v>
       </c>
       <c r="B662" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C662" t="s">
         <v>1311</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -12080,10 +12080,10 @@
         <v>759</v>
       </c>
       <c r="B663" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C663" t="s">
         <v>1313</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -12091,10 +12091,10 @@
         <v>760</v>
       </c>
       <c r="B664" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C664" t="s">
         <v>1315</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -12102,10 +12102,10 @@
         <v>761</v>
       </c>
       <c r="B665" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C665" t="s">
         <v>1317</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -12113,10 +12113,10 @@
         <v>762</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C666" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12124,10 +12124,10 @@
         <v>763</v>
       </c>
       <c r="B667" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C667" t="s">
         <v>1320</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A998D-A539-4A58-BAFE-CBD0CF588DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818FAEE8-2711-412C-8A38-8A640BD2EA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="1325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1336" uniqueCount="1327">
   <si>
     <t>Id</t>
   </si>
@@ -3659,10 +3659,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3Dkzn,3D kizunamusic,kzn3d,新手教程3d</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>キズナミュージック</t>
     </r>
@@ -3757,10 +3753,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>op1,心跳体验,op,第一首歌,新手村,新手教学</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>羁绊歌,kzn,kizuna music,kznmusic,羁绊</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4034,10 +4026,6 @@
   </si>
   <si>
     <t>遥之彼方,遥彼方</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Peak,最高到达点,最高达到点,到达最高点,达到最高点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4380,6 +4368,26 @@
   </si>
   <si>
     <t>命运安魂,命运,命运交响曲,命运镇魂曲,rff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魂汤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOULSOUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3Dkzn,3D kizunamusic,kzn3d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>op1,心跳体验,op,第一首歌,新手村,新手教学,新手教程,新手入门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Peak,最高到达点,最高达到点,到达最高点,达到最高点,理塘歌,礼堂歌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4799,7 +4807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C669"/>
+  <dimension ref="A1:C670"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -4827,7 +4835,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,7 +5066,7 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>1187</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,7 +5143,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -5223,7 +5231,7 @@
         <v>63</v>
       </c>
       <c r="C38" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -5234,7 +5242,7 @@
         <v>64</v>
       </c>
       <c r="C39" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -5740,7 +5748,7 @@
         <v>146</v>
       </c>
       <c r="C85" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -6268,7 +6276,7 @@
         <v>234</v>
       </c>
       <c r="C133" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6455,7 +6463,7 @@
         <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6587,7 +6595,7 @@
         <v>288</v>
       </c>
       <c r="C162" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6642,7 +6650,7 @@
         <v>297</v>
       </c>
       <c r="C167" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6675,7 +6683,7 @@
         <v>302</v>
       </c>
       <c r="C170" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -7093,7 +7101,7 @@
         <v>377</v>
       </c>
       <c r="C208" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7885,7 +7893,7 @@
         <v>510</v>
       </c>
       <c r="C280" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7940,7 +7948,7 @@
         <v>519</v>
       </c>
       <c r="C285" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -8248,7 +8256,7 @@
         <v>571</v>
       </c>
       <c r="C313" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8919,7 +8927,7 @@
         <v>685</v>
       </c>
       <c r="C374" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8952,7 +8960,7 @@
         <v>690</v>
       </c>
       <c r="C377" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -9095,7 +9103,7 @@
         <v>713</v>
       </c>
       <c r="C390" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -9114,10 +9122,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="C392" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9227,7 +9235,7 @@
         <v>734</v>
       </c>
       <c r="C402" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9268,10 +9276,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C406" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9334,7 +9342,7 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C412" t="s">
         <v>750</v>
@@ -9345,7 +9353,7 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C413" t="s">
         <v>751</v>
@@ -9436,7 +9444,7 @@
         <v>764</v>
       </c>
       <c r="C421" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9447,7 +9455,7 @@
         <v>765</v>
       </c>
       <c r="C422" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9906,7 +9914,7 @@
         <v>833</v>
       </c>
       <c r="C464" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -10002,10 +10010,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C473" t="s">
-        <v>1168</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -10016,7 +10024,7 @@
         <v>848</v>
       </c>
       <c r="C474" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -10159,7 +10167,7 @@
         <v>870</v>
       </c>
       <c r="C487" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10453,7 +10461,7 @@
         <v>916</v>
       </c>
       <c r="C514" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10714,7 +10722,7 @@
         <v>953</v>
       </c>
       <c r="C538" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -11060,7 +11068,7 @@
         <v>1005</v>
       </c>
       <c r="C570" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -11082,7 +11090,7 @@
         <v>1007</v>
       </c>
       <c r="C572" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -11126,7 +11134,7 @@
         <v>1011</v>
       </c>
       <c r="C576" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11137,7 +11145,7 @@
         <v>849</v>
       </c>
       <c r="C577" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11148,7 +11156,7 @@
         <v>851</v>
       </c>
       <c r="C578" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11178,10 +11186,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C581" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11203,485 +11211,485 @@
         <v>1017</v>
       </c>
       <c r="C583" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B584" t="s">
-        <v>1018</v>
+        <v>1323</v>
       </c>
       <c r="C584" t="s">
-        <v>1019</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B585" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C585" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="B586" t="s">
-        <v>1071</v>
+        <v>1020</v>
       </c>
       <c r="C586" t="s">
-        <v>1109</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B587" t="s">
-        <v>1271</v>
+        <v>1071</v>
       </c>
       <c r="C587" t="s">
-        <v>1272</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B588" t="s">
-        <v>1022</v>
+        <v>1268</v>
       </c>
       <c r="C588" t="s">
-        <v>1023</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B589" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C589" t="s">
-        <v>1305</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B590" t="s">
-        <v>1269</v>
+        <v>1024</v>
       </c>
       <c r="C590" t="s">
-        <v>1270</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B591" t="s">
-        <v>1025</v>
+        <v>1266</v>
       </c>
       <c r="C591" t="s">
-        <v>1088</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B592" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C592" t="s">
-        <v>1027</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B593" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C593" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B594" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C594" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B595" t="s">
-        <v>1246</v>
+        <v>1030</v>
       </c>
       <c r="C595" t="s">
-        <v>1247</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B596" t="s">
-        <v>1032</v>
+        <v>1244</v>
       </c>
       <c r="C596" t="s">
-        <v>1163</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B597" t="s">
-        <v>1183</v>
+        <v>1032</v>
       </c>
       <c r="C597" t="s">
-        <v>1184</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B598" t="s">
-        <v>1033</v>
+        <v>1182</v>
       </c>
       <c r="C598" t="s">
-        <v>1034</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B599" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C599" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B600" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C600" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B601" t="s">
-        <v>1138</v>
+        <v>1037</v>
       </c>
       <c r="C601" t="s">
-        <v>1139</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B602" t="s">
-        <v>1039</v>
+        <v>1138</v>
       </c>
       <c r="C602" t="s">
-        <v>1040</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B603" t="s">
-        <v>1284</v>
+        <v>1039</v>
       </c>
       <c r="C603" t="s">
-        <v>1285</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B604" t="s">
-        <v>1181</v>
+        <v>1281</v>
       </c>
       <c r="C604" t="s">
-        <v>1182</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B605" t="s">
-        <v>1041</v>
+        <v>1180</v>
       </c>
       <c r="C605" t="s">
-        <v>1042</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B606" t="s">
-        <v>1058</v>
+        <v>1041</v>
       </c>
       <c r="C606" t="s">
-        <v>1242</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B607" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="C607" t="s">
-        <v>1111</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B608" t="s">
-        <v>1266</v>
+        <v>1043</v>
       </c>
       <c r="C608" t="s">
-        <v>1267</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B609" t="s">
-        <v>1044</v>
+        <v>1263</v>
       </c>
       <c r="C609" t="s">
-        <v>1101</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B610" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C610" t="s">
-        <v>1179</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B611" t="s">
-        <v>1322</v>
+        <v>1045</v>
       </c>
       <c r="C611" t="s">
-        <v>1323</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B612" t="s">
-        <v>1046</v>
+        <v>1319</v>
       </c>
       <c r="C612" t="s">
-        <v>1063</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B613" t="s">
-        <v>1178</v>
+        <v>1046</v>
       </c>
       <c r="C613" t="s">
-        <v>1180</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B614" t="s">
-        <v>1047</v>
+        <v>1177</v>
       </c>
       <c r="C614" t="s">
-        <v>1048</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B615" t="s">
-        <v>1265</v>
+        <v>1047</v>
       </c>
       <c r="C615" t="s">
-        <v>1268</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B616" t="s">
-        <v>1057</v>
+        <v>1262</v>
       </c>
       <c r="C616" t="s">
-        <v>1151</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B617" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="C617" t="s">
-        <v>1050</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B618" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C618" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B619" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C619" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B620" t="s">
-        <v>1132</v>
+        <v>1053</v>
       </c>
       <c r="C620" t="s">
-        <v>1248</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B621" t="s">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="C621" t="s">
-        <v>1165</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B622" t="s">
-        <v>1240</v>
+        <v>1166</v>
       </c>
       <c r="C622" t="s">
-        <v>1241</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B623" t="s">
-        <v>1084</v>
+        <v>1238</v>
       </c>
       <c r="C623" t="s">
-        <v>1281</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B624" t="s">
-        <v>1250</v>
+        <v>1084</v>
       </c>
       <c r="C624" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B625" t="s">
-        <v>1176</v>
+        <v>1247</v>
       </c>
       <c r="C625" t="s">
-        <v>1177</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B626" t="s">
-        <v>1237</v>
+        <v>1175</v>
       </c>
       <c r="C626" t="s">
-        <v>1238</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B627" t="s">
         <v>1235</v>
@@ -11692,7 +11700,7 @@
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B628" t="s">
         <v>1233</v>
@@ -11703,29 +11711,29 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B629" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C629" t="s">
         <v>1232</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B630" t="s">
         <v>1230</v>
       </c>
       <c r="C630" t="s">
-        <v>1231</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B631" t="s">
         <v>1228</v>
@@ -11734,9 +11742,9 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="632" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B632" t="s">
         <v>1226</v>
@@ -11745,9 +11753,9 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A633">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B633" t="s">
         <v>1224</v>
@@ -11758,7 +11766,7 @@
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B634" t="s">
         <v>1222</v>
@@ -11769,9 +11777,9 @@
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635">
-        <v>725</v>
-      </c>
-      <c r="B635" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B635" t="s">
         <v>1220</v>
       </c>
       <c r="C635" t="s">
@@ -11780,9 +11788,9 @@
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636">
-        <v>726</v>
-      </c>
-      <c r="B636" t="s">
+        <v>725</v>
+      </c>
+      <c r="B636" s="1" t="s">
         <v>1218</v>
       </c>
       <c r="C636" t="s">
@@ -11791,7 +11799,7 @@
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B637" t="s">
         <v>1216</v>
@@ -11800,31 +11808,31 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="638" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B638" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C638" t="s">
         <v>1215</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="639" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A639">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B639" t="s">
         <v>1213</v>
       </c>
       <c r="C639" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A640">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B640" t="s">
         <v>1211</v>
@@ -11835,7 +11843,7 @@
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B641" t="s">
         <v>1209</v>
@@ -11846,7 +11854,7 @@
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B642" t="s">
         <v>1207</v>
@@ -11857,7 +11865,7 @@
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B643" t="s">
         <v>1205</v>
@@ -11868,7 +11876,7 @@
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B644" t="s">
         <v>1203</v>
@@ -11879,29 +11887,29 @@
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B645" t="s">
-        <v>1243</v>
+        <v>1201</v>
       </c>
       <c r="C645" t="s">
-        <v>1244</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B646" t="s">
-        <v>1201</v>
+        <v>1241</v>
       </c>
       <c r="C646" t="s">
-        <v>1202</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B647" t="s">
         <v>1199</v>
@@ -11912,7 +11920,7 @@
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B648" t="s">
         <v>1197</v>
@@ -11923,7 +11931,7 @@
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B649" t="s">
         <v>1195</v>
@@ -11934,221 +11942,232 @@
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B650" t="s">
-        <v>1252</v>
+        <v>1193</v>
       </c>
       <c r="C650" t="s">
-        <v>1253</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B651" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="C651" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652">
+        <v>743</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C652" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A653">
         <v>744</v>
       </c>
-      <c r="B652" t="s">
+      <c r="B653" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C653" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+      <c r="A654">
+        <v>745</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C654" t="s">
         <v>1256</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A653">
-        <v>745</v>
-      </c>
-      <c r="B653" s="2" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A654">
-        <v>746</v>
-      </c>
-      <c r="B654" s="2" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="C655" t="s">
-        <v>1286</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1279</v>
+        <v>1259</v>
       </c>
       <c r="C656" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B657" s="2" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C657" t="s">
         <v>1277</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B658" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C658" t="s">
         <v>1275</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B659" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C659" t="s">
         <v>1273</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1306</v>
+        <v>1270</v>
       </c>
       <c r="C660" t="s">
-        <v>1307</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1309</v>
+        <v>1303</v>
       </c>
       <c r="C661" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C662" t="s">
-        <v>1311</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="C663" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="C664" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="C665" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="C666" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C667" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668">
-        <v>10001</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1055</v>
+        <v>763</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>1316</v>
       </c>
       <c r="C668" t="s">
-        <v>1056</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669">
+        <v>10001</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A670">
         <v>10003</v>
       </c>
-      <c r="B669" t="s">
+      <c r="B670" t="s">
         <v>1082</v>
       </c>
-      <c r="C669" t="s">
+      <c r="C670" t="s">
         <v>1083</v>
       </c>
     </row>
@@ -12157,7 +12176,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A668:C668 A315:B315 A316:C326 A352:C352 A351:B351 A588:C588 A575 A574:B574 A460:C463 A459:B459 A614:C614 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A617:C619 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A605:C605 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A612:B612 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A592:C594 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A598:C600 A596:B596 A591:B591 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A602:C602 A584:C585 A583:B583 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A607:B607 A589:B589 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A609:B610" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1 A121:C127 A120:B120 A669:C669 A315:B315 A316:C326 A352:C352 A351:B351 A589:C589 A575 A574:B574 A460:C463 A459:B459 A615:C615 A235:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A618:C620 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A606:C606 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A613:B613 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A426:C431 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A593:C595 A380:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A32:C37 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A599:C601 A597:B597 A592:B592 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A603:C603 A585:C586 A583:B583 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A608:B608 A590:B590 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A610:B611" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{ED1E17C9-00FD-7944-A412-AF35E3021851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9555" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21600" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="1334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="1335">
   <si>
     <t>Id</t>
   </si>
@@ -2659,7 +2658,7 @@
     <t>独創収差</t>
   </si>
   <si>
-    <t>独创收差,TK,带带我,独创</t>
+    <t>独创收差,TK,带带我,独创,独创收割</t>
   </si>
   <si>
     <t>うちゃパ！で ぱっぴかポーんっ！</t>
@@ -3494,7 +3493,7 @@
     <t>きゅうくらりん</t>
   </si>
   <si>
-    <t>kyu-kurarin,心跳不止,心动不止,心动不已</t>
+    <t>kyu-kurarin,心跳不止,心动不止,心动不已,断心不止,断心不已</t>
   </si>
   <si>
     <t>かくれんぼ</t>
@@ -3555,6 +3554,12 @@
   </si>
   <si>
     <t>五彩调色盘,toridori palette,toridori,トリドリ</t>
+  </si>
+  <si>
+    <t>V.I.P MONSTER</t>
+  </si>
+  <si>
+    <t>vipm,vip m,千客万来</t>
   </si>
   <si>
     <t>Wreath of Brave</t>
@@ -3992,7 +3997,7 @@
     <t>Mas?uerade Rhapsody Re?uest</t>
   </si>
   <si>
-    <t>12兆年,十二兆年</t>
+    <t>12兆年,十二兆年,mas,mas?,mas？,Mas,Mas?,Mas？</t>
   </si>
   <si>
     <t>Part of the Life</t>
@@ -4165,29 +4170,35 @@
     <t>start,拉帮结派,拉邦结派</t>
   </si>
   <si>
+    <t>Choco Typhooooon!!</t>
+  </si>
+  <si>
+    <t>台风</t>
+  </si>
+  <si>
+    <t>Mystic Light Quest</t>
+  </si>
+  <si>
+    <t>佩佩,神秘之光,mrfz,明日方舟,舟,粥</t>
+  </si>
+  <si>
     <t>彩虹节拍</t>
   </si>
   <si>
     <t>彩虹答辩</t>
-  </si>
-  <si>
-    <t>Mystic Light Quest</t>
-  </si>
-  <si>
-    <t>佩佩,神秘之光,mrfz,明日方舟,舟,粥</t>
-  </si>
-  <si>
-    <t>V.I.P MONSTER</t>
-  </si>
-  <si>
-    <t>vipm,vip m</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4202,10 +4213,155 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -4219,16 +4375,208 @@
       <name val="Segoe UI Emoji"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -4236,26 +4584,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4577,22 +5211,22 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C673"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C677"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="10.8515625" customWidth="1"/>
-    <col min="2" max="2" width="50.8046875" customWidth="1"/>
-    <col min="3" max="3" width="65.84765625" customWidth="1"/>
-    <col min="4" max="4" width="55.734375" customWidth="1"/>
+    <col min="1" max="1" width="10.85" customWidth="1"/>
+    <col min="2" max="2" width="50.8083333333333" customWidth="1"/>
+    <col min="3" max="3" width="65.85" customWidth="1"/>
+    <col min="4" max="4" width="55.7333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4603,7 +5237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4614,7 +5248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4625,7 +5259,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4636,7 +5270,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4647,7 +5281,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4658,7 +5292,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4669,7 +5303,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4680,7 +5314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4691,7 +5325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4702,7 +5336,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4713,7 +5347,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4724,7 +5358,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4735,7 +5369,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4746,7 +5380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4757,7 +5391,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4768,7 +5402,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4779,7 +5413,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4790,7 +5424,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4801,7 +5435,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="20" ht="17.25" spans="1:3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4812,7 +5446,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4823,7 +5457,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4834,7 +5468,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>24</v>
       </c>
@@ -4845,7 +5479,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>25</v>
       </c>
@@ -4856,7 +5490,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>26</v>
       </c>
@@ -4867,7 +5501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>27</v>
       </c>
@@ -4878,7 +5512,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>28</v>
       </c>
@@ -4889,7 +5523,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>29</v>
       </c>
@@ -4900,7 +5534,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>30</v>
       </c>
@@ -4911,7 +5545,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>31</v>
       </c>
@@ -4922,7 +5556,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>32</v>
       </c>
@@ -4933,7 +5567,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="32" spans="1:3">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4944,7 +5578,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>34</v>
       </c>
@@ -4955,7 +5589,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>35</v>
       </c>
@@ -4966,7 +5600,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4977,7 +5611,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4988,7 +5622,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>40</v>
       </c>
@@ -4999,7 +5633,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5010,7 +5644,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5021,7 +5655,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5032,7 +5666,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5043,7 +5677,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5054,7 +5688,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5065,7 +5699,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5076,7 +5710,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5087,7 +5721,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5098,7 +5732,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5109,7 +5743,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5120,7 +5754,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5131,7 +5765,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5142,7 +5776,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5153,7 +5787,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5164,7 +5798,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5175,7 +5809,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5186,7 +5820,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5197,7 +5831,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5208,7 +5842,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5219,7 +5853,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5230,7 +5864,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5241,7 +5875,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5252,7 +5886,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5263,7 +5897,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5274,7 +5908,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5285,7 +5919,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5296,7 +5930,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5307,7 +5941,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5318,7 +5952,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5329,7 +5963,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5340,7 +5974,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5351,7 +5985,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5362,7 +5996,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5373,7 +6007,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5384,7 +6018,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5395,7 +6029,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5406,7 +6040,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="75" spans="1:3">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5417,7 +6051,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5428,7 +6062,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5439,7 +6073,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="78" spans="1:3">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5450,7 +6084,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5461,7 +6095,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5472,7 +6106,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="81" spans="1:3">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5483,7 +6117,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5494,7 +6128,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="83" spans="1:3">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5505,7 +6139,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5516,7 +6150,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5527,7 +6161,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5538,7 +6172,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="87" spans="1:3">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5549,7 +6183,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5560,7 +6194,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="89" spans="1:3">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5571,7 +6205,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="90" spans="1:3">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5582,7 +6216,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="91" spans="1:3">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5593,7 +6227,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="92" spans="1:3">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5604,7 +6238,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="93" spans="1:3">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5615,7 +6249,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="94" spans="1:3">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5626,7 +6260,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="95" spans="1:3">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5637,7 +6271,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="96" spans="1:3">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5648,7 +6282,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="97" spans="1:3">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5659,7 +6293,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="98" spans="1:3">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5670,7 +6304,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="99" spans="1:3">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5681,7 +6315,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="100" spans="1:3">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5692,7 +6326,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="101" spans="1:3">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5703,7 +6337,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="102" spans="1:3">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5714,7 +6348,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="103" spans="1:3">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5725,7 +6359,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="104" spans="1:3">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5736,7 +6370,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="105" spans="1:3">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5747,7 +6381,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="106" spans="1:3">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5758,7 +6392,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="107" spans="1:3">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5769,7 +6403,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="108" spans="1:3">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5780,7 +6414,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="109" spans="1:3">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5791,7 +6425,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="110" spans="1:3">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5802,7 +6436,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="111" spans="1:3">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5813,7 +6447,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="112" spans="1:3">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5824,7 +6458,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="113" spans="1:3">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5835,7 +6469,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="114" spans="1:3">
       <c r="A114">
         <v>122</v>
       </c>
@@ -5846,7 +6480,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="115" spans="1:3">
       <c r="A115">
         <v>123</v>
       </c>
@@ -5857,7 +6491,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="116" spans="1:3">
       <c r="A116">
         <v>124</v>
       </c>
@@ -5868,7 +6502,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="117" spans="1:3">
       <c r="A117">
         <v>125</v>
       </c>
@@ -5879,7 +6513,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="118" spans="1:3">
       <c r="A118">
         <v>126</v>
       </c>
@@ -5890,7 +6524,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="119" spans="1:3">
       <c r="A119">
         <v>127</v>
       </c>
@@ -5901,7 +6535,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="120" spans="1:3">
       <c r="A120">
         <v>128</v>
       </c>
@@ -5912,7 +6546,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="121" spans="1:3">
       <c r="A121">
         <v>129</v>
       </c>
@@ -5923,7 +6557,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="122" spans="1:3">
       <c r="A122">
         <v>130</v>
       </c>
@@ -5934,7 +6568,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="123" spans="1:3">
       <c r="A123">
         <v>131</v>
       </c>
@@ -5945,7 +6579,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="124" spans="1:3">
       <c r="A124">
         <v>132</v>
       </c>
@@ -5956,7 +6590,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="125" spans="1:3">
       <c r="A125">
         <v>133</v>
       </c>
@@ -5967,7 +6601,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="126" spans="1:3">
       <c r="A126">
         <v>134</v>
       </c>
@@ -5978,7 +6612,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="127" spans="1:3">
       <c r="A127">
         <v>135</v>
       </c>
@@ -5989,7 +6623,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="128" spans="1:3">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6000,7 +6634,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="129" spans="1:3">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6011,7 +6645,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="130" spans="1:3">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6022,7 +6656,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="131" spans="1:3">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6033,7 +6667,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="132" spans="1:3">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6044,7 +6678,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="133" spans="1:3">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6055,7 +6689,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="134" spans="1:3">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6066,7 +6700,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="135" spans="1:3">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6077,7 +6711,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="136" spans="1:3">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6088,7 +6722,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="137" spans="1:3">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6099,7 +6733,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="138" spans="1:3">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6110,7 +6744,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="139" spans="1:3">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6121,7 +6755,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="140" spans="1:3">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6132,7 +6766,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="141" spans="1:3">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6143,7 +6777,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="142" spans="1:3">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6154,7 +6788,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="143" spans="1:3">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6165,7 +6799,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="144" spans="1:3">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6176,7 +6810,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="145" spans="1:3">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6187,7 +6821,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="146" spans="1:3">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6198,7 +6832,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="147" spans="1:3">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6209,7 +6843,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="148" spans="1:3">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6220,7 +6854,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="149" spans="1:3">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6231,7 +6865,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="150" spans="1:3">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6242,7 +6876,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="151" spans="1:3">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6253,7 +6887,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="152" spans="1:3">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6264,7 +6898,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="153" spans="1:3">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6275,7 +6909,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="154" spans="1:3">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6286,7 +6920,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="155" spans="1:3">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6297,7 +6931,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="156" spans="1:3">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6308,7 +6942,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="157" spans="1:3">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6319,7 +6953,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="158" spans="1:3">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6330,7 +6964,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="159" spans="1:3">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6341,7 +6975,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="160" spans="1:3">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6352,7 +6986,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="161" spans="1:3">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6363,7 +6997,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="162" spans="1:3">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6374,7 +7008,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="163" spans="1:3">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6385,7 +7019,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="164" spans="1:3">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6396,7 +7030,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="165" spans="1:3">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6407,7 +7041,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="166" spans="1:3">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6418,7 +7052,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="167" spans="1:3">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6429,7 +7063,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="168" spans="1:3">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6440,7 +7074,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="169" spans="1:3">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6451,7 +7085,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="170" spans="1:3">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6462,7 +7096,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="171" spans="1:3">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6473,7 +7107,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="172" spans="1:3">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6484,7 +7118,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="173" spans="1:3">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6495,7 +7129,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="174" spans="1:3">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6506,7 +7140,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="175" spans="1:3">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6517,7 +7151,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="176" spans="1:3">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6528,7 +7162,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="177" spans="1:3">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6539,7 +7173,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="178" spans="1:3">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6550,7 +7184,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="179" spans="1:3">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6561,7 +7195,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="180" spans="1:3">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6572,7 +7206,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="181" spans="1:3">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6583,7 +7217,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="182" spans="1:3">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6594,7 +7228,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="183" spans="1:3">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6605,7 +7239,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="184" spans="1:3">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6616,7 +7250,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="185" spans="1:3">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6627,7 +7261,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="186" spans="1:3">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6638,7 +7272,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="187" spans="1:3">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6649,7 +7283,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="188" spans="1:3">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6660,7 +7294,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="189" spans="1:3">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6671,7 +7305,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="190" spans="1:3">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6682,7 +7316,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="191" spans="1:3">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6693,7 +7327,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="192" spans="1:3">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6704,7 +7338,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="193" spans="1:3">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6715,7 +7349,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="194" spans="1:3">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6726,7 +7360,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="195" spans="1:3">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6737,7 +7371,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="196" spans="1:3">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6748,7 +7382,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="197" spans="1:3">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6759,7 +7393,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="198" spans="1:3">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6770,7 +7404,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="199" spans="1:3">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6781,7 +7415,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="200" spans="1:3">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6792,7 +7426,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="201" spans="1:3">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6803,7 +7437,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="202" spans="1:3">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6814,7 +7448,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="203" spans="1:3">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6825,7 +7459,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="204" spans="1:3">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6836,7 +7470,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="205" spans="1:3">
       <c r="A205">
         <v>213</v>
       </c>
@@ -6847,7 +7481,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="206" spans="1:3">
       <c r="A206">
         <v>214</v>
       </c>
@@ -6858,7 +7492,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="207" spans="1:3">
       <c r="A207">
         <v>215</v>
       </c>
@@ -6869,7 +7503,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="208" spans="1:3">
       <c r="A208">
         <v>217</v>
       </c>
@@ -6880,7 +7514,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="209" spans="1:3">
       <c r="A209">
         <v>218</v>
       </c>
@@ -6891,7 +7525,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="210" spans="1:3">
       <c r="A210">
         <v>219</v>
       </c>
@@ -6902,7 +7536,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="211" spans="1:3">
       <c r="A211">
         <v>220</v>
       </c>
@@ -6913,7 +7547,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="212" spans="1:3">
       <c r="A212">
         <v>221</v>
       </c>
@@ -6924,7 +7558,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="213" spans="1:3">
       <c r="A213">
         <v>222</v>
       </c>
@@ -6935,7 +7569,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="214" spans="1:3">
       <c r="A214">
         <v>223</v>
       </c>
@@ -6946,7 +7580,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="215" spans="1:3">
       <c r="A215">
         <v>224</v>
       </c>
@@ -6957,7 +7591,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="216" spans="1:3">
       <c r="A216">
         <v>225</v>
       </c>
@@ -6968,7 +7602,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="217" spans="1:3">
       <c r="A217">
         <v>226</v>
       </c>
@@ -6979,7 +7613,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="218" spans="1:3">
       <c r="A218">
         <v>227</v>
       </c>
@@ -6990,7 +7624,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="219" spans="1:3">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7001,7 +7635,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="220" spans="1:3">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7012,7 +7646,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="221" spans="1:3">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7023,7 +7657,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="222" spans="1:3">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7034,7 +7668,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="223" spans="1:3">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7045,7 +7679,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="224" spans="1:3">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7056,7 +7690,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="225" spans="1:3">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7067,7 +7701,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="226" spans="1:3">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7078,7 +7712,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="227" spans="1:3">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7089,7 +7723,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="228" spans="1:3">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7100,7 +7734,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="229" spans="1:3">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7111,7 +7745,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="230" spans="1:3">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7122,7 +7756,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="231" spans="1:3">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7133,7 +7767,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="232" spans="1:3">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7144,7 +7778,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="233" spans="1:3">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7155,7 +7789,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="234" spans="1:3">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7166,7 +7800,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="235" spans="1:3">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7177,7 +7811,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="236" spans="1:3">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7188,7 +7822,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="237" spans="1:3">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7199,7 +7833,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="238" spans="1:3">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7210,7 +7844,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="239" spans="1:3">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7221,7 +7855,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="240" spans="1:3">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7232,7 +7866,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="241" spans="1:3">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7243,7 +7877,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="242" spans="1:3">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7254,7 +7888,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="243" spans="1:3">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7265,7 +7899,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="244" spans="1:3">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7276,7 +7910,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="245" spans="1:3">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7287,7 +7921,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="246" spans="1:3">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7298,7 +7932,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="247" spans="1:3">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7309,7 +7943,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="248" spans="1:3">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7320,7 +7954,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="249" spans="1:3">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7331,7 +7965,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="250" spans="1:3">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7342,7 +7976,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="251" spans="1:3">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7353,7 +7987,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="252" spans="1:3">
       <c r="A252">
         <v>261</v>
       </c>
@@ -7364,7 +7998,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="253" spans="1:3">
       <c r="A253">
         <v>262</v>
       </c>
@@ -7375,7 +8009,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="254" spans="1:3">
       <c r="A254">
         <v>263</v>
       </c>
@@ -7386,7 +8020,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="255" spans="1:3">
       <c r="A255">
         <v>264</v>
       </c>
@@ -7397,7 +8031,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="256" spans="1:3">
       <c r="A256">
         <v>265</v>
       </c>
@@ -7408,7 +8042,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="257" spans="1:3">
       <c r="A257">
         <v>266</v>
       </c>
@@ -7419,7 +8053,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="258" spans="1:3">
       <c r="A258">
         <v>267</v>
       </c>
@@ -7430,7 +8064,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="259" spans="1:3">
       <c r="A259">
         <v>268</v>
       </c>
@@ -7441,7 +8075,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="260" spans="1:3">
       <c r="A260">
         <v>269</v>
       </c>
@@ -7452,7 +8086,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="261" spans="1:3">
       <c r="A261">
         <v>270</v>
       </c>
@@ -7463,7 +8097,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="262" spans="1:3">
       <c r="A262">
         <v>271</v>
       </c>
@@ -7474,7 +8108,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="263" spans="1:3">
       <c r="A263">
         <v>272</v>
       </c>
@@ -7485,7 +8119,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="264" spans="1:3">
       <c r="A264">
         <v>274</v>
       </c>
@@ -7496,7 +8130,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="265" spans="1:3">
       <c r="A265">
         <v>275</v>
       </c>
@@ -7507,7 +8141,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="266" spans="1:3">
       <c r="A266">
         <v>276</v>
       </c>
@@ -7518,7 +8152,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="267" spans="1:3">
       <c r="A267">
         <v>277</v>
       </c>
@@ -7529,7 +8163,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="268" spans="1:3">
       <c r="A268">
         <v>278</v>
       </c>
@@ -7540,7 +8174,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="269" spans="1:3">
       <c r="A269">
         <v>279</v>
       </c>
@@ -7551,7 +8185,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="270" spans="1:3">
       <c r="A270">
         <v>280</v>
       </c>
@@ -7562,7 +8196,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="271" spans="1:3">
       <c r="A271">
         <v>281</v>
       </c>
@@ -7573,7 +8207,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="272" spans="1:3">
       <c r="A272">
         <v>282</v>
       </c>
@@ -7584,7 +8218,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="273" spans="1:3">
       <c r="A273">
         <v>283</v>
       </c>
@@ -7595,7 +8229,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="274" spans="1:3">
       <c r="A274">
         <v>284</v>
       </c>
@@ -7606,7 +8240,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="275" spans="1:3">
       <c r="A275">
         <v>285</v>
       </c>
@@ -7617,7 +8251,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="276" spans="1:3">
       <c r="A276">
         <v>286</v>
       </c>
@@ -7628,7 +8262,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="277" spans="1:3">
       <c r="A277">
         <v>287</v>
       </c>
@@ -7639,7 +8273,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="278" spans="1:3">
       <c r="A278">
         <v>288</v>
       </c>
@@ -7650,7 +8284,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="279" spans="1:3">
       <c r="A279">
         <v>289</v>
       </c>
@@ -7661,7 +8295,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="280" spans="1:3">
       <c r="A280">
         <v>290</v>
       </c>
@@ -7672,7 +8306,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="281" spans="1:3">
       <c r="A281">
         <v>291</v>
       </c>
@@ -7683,7 +8317,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="282" spans="1:3">
       <c r="A282">
         <v>292</v>
       </c>
@@ -7694,7 +8328,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="283" spans="1:3">
       <c r="A283">
         <v>293</v>
       </c>
@@ -7705,7 +8339,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="284" spans="1:3">
       <c r="A284">
         <v>294</v>
       </c>
@@ -7716,7 +8350,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="285" spans="1:3">
       <c r="A285">
         <v>295</v>
       </c>
@@ -7727,7 +8361,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="286" spans="1:3">
       <c r="A286">
         <v>296</v>
       </c>
@@ -7738,7 +8372,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="287" spans="1:3">
       <c r="A287">
         <v>297</v>
       </c>
@@ -7749,7 +8383,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="288" spans="1:3">
       <c r="A288">
         <v>298</v>
       </c>
@@ -7760,7 +8394,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="289" spans="1:3">
       <c r="A289">
         <v>299</v>
       </c>
@@ -7771,7 +8405,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="290" spans="1:3">
       <c r="A290">
         <v>300</v>
       </c>
@@ -7782,7 +8416,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="291" spans="1:3">
       <c r="A291">
         <v>301</v>
       </c>
@@ -7793,7 +8427,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="292" spans="1:3">
       <c r="A292">
         <v>302</v>
       </c>
@@ -7804,7 +8438,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="293" spans="1:3">
       <c r="A293">
         <v>303</v>
       </c>
@@ -7815,7 +8449,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="294" spans="1:3">
       <c r="A294">
         <v>304</v>
       </c>
@@ -7826,7 +8460,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="295" spans="1:3">
       <c r="A295">
         <v>305</v>
       </c>
@@ -7837,7 +8471,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="296" spans="1:3">
       <c r="A296">
         <v>306</v>
       </c>
@@ -7848,7 +8482,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="297" spans="1:3">
       <c r="A297">
         <v>307</v>
       </c>
@@ -7859,7 +8493,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="298" spans="1:3">
       <c r="A298">
         <v>308</v>
       </c>
@@ -7870,7 +8504,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="299" spans="1:3">
       <c r="A299">
         <v>309</v>
       </c>
@@ -7881,7 +8515,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="300" spans="1:3">
       <c r="A300">
         <v>310</v>
       </c>
@@ -7892,7 +8526,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="301" spans="1:3">
       <c r="A301">
         <v>311</v>
       </c>
@@ -7903,7 +8537,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="302" spans="1:3">
       <c r="A302">
         <v>312</v>
       </c>
@@ -7914,7 +8548,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="303" spans="1:3">
       <c r="A303">
         <v>313</v>
       </c>
@@ -7925,7 +8559,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="304" spans="1:3">
       <c r="A304">
         <v>314</v>
       </c>
@@ -7936,7 +8570,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="305" spans="1:3">
       <c r="A305">
         <v>315</v>
       </c>
@@ -7947,7 +8581,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="306" spans="1:3">
       <c r="A306">
         <v>316</v>
       </c>
@@ -7958,7 +8592,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="307" spans="1:3">
       <c r="A307">
         <v>317</v>
       </c>
@@ -7969,7 +8603,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="308" spans="1:3">
       <c r="A308">
         <v>318</v>
       </c>
@@ -7980,7 +8614,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="309" spans="1:3">
       <c r="A309">
         <v>319</v>
       </c>
@@ -7991,7 +8625,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="310" spans="1:3">
       <c r="A310">
         <v>320</v>
       </c>
@@ -8002,7 +8636,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="311" spans="1:3">
       <c r="A311">
         <v>321</v>
       </c>
@@ -8013,7 +8647,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="312" spans="1:3">
       <c r="A312">
         <v>322</v>
       </c>
@@ -8024,7 +8658,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="313" spans="1:3">
       <c r="A313">
         <v>323</v>
       </c>
@@ -8035,7 +8669,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="314" spans="1:3">
       <c r="A314">
         <v>324</v>
       </c>
@@ -8046,7 +8680,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="315" spans="1:3">
       <c r="A315">
         <v>325</v>
       </c>
@@ -8057,7 +8691,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="316" spans="1:3">
       <c r="A316">
         <v>326</v>
       </c>
@@ -8068,7 +8702,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="317" spans="1:3">
       <c r="A317">
         <v>327</v>
       </c>
@@ -8079,7 +8713,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="318" spans="1:3">
       <c r="A318">
         <v>328</v>
       </c>
@@ -8090,7 +8724,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="319" spans="1:3">
       <c r="A319">
         <v>329</v>
       </c>
@@ -8101,7 +8735,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="320" spans="1:3">
       <c r="A320">
         <v>330</v>
       </c>
@@ -8112,7 +8746,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="321" spans="1:3">
       <c r="A321">
         <v>331</v>
       </c>
@@ -8123,7 +8757,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="322" spans="1:3">
       <c r="A322">
         <v>332</v>
       </c>
@@ -8134,7 +8768,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="323" spans="1:3">
       <c r="A323">
         <v>333</v>
       </c>
@@ -8145,7 +8779,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="324" spans="1:3">
       <c r="A324">
         <v>334</v>
       </c>
@@ -8156,7 +8790,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="325" spans="1:3">
       <c r="A325">
         <v>335</v>
       </c>
@@ -8167,7 +8801,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="326" spans="1:3">
       <c r="A326">
         <v>336</v>
       </c>
@@ -8178,7 +8812,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="327" spans="1:3">
       <c r="A327">
         <v>337</v>
       </c>
@@ -8189,7 +8823,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="328" spans="1:3">
       <c r="A328">
         <v>338</v>
       </c>
@@ -8200,7 +8834,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="329" spans="1:3">
       <c r="A329">
         <v>339</v>
       </c>
@@ -8211,7 +8845,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="330" spans="1:3">
       <c r="A330">
         <v>340</v>
       </c>
@@ -8222,7 +8856,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="331" spans="1:3">
       <c r="A331">
         <v>341</v>
       </c>
@@ -8233,7 +8867,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="332" spans="1:3">
       <c r="A332">
         <v>342</v>
       </c>
@@ -8244,7 +8878,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="333" spans="1:3">
       <c r="A333">
         <v>343</v>
       </c>
@@ -8255,7 +8889,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="334" spans="1:3">
       <c r="A334">
         <v>344</v>
       </c>
@@ -8266,7 +8900,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="335" spans="1:3">
       <c r="A335">
         <v>345</v>
       </c>
@@ -8277,7 +8911,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="336" spans="1:3">
       <c r="A336">
         <v>346</v>
       </c>
@@ -8288,7 +8922,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="337" spans="1:3">
       <c r="A337">
         <v>347</v>
       </c>
@@ -8299,7 +8933,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="338" spans="1:3">
       <c r="A338">
         <v>348</v>
       </c>
@@ -8310,7 +8944,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="339" spans="1:3">
       <c r="A339">
         <v>349</v>
       </c>
@@ -8321,7 +8955,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="340" spans="1:3">
       <c r="A340">
         <v>350</v>
       </c>
@@ -8332,7 +8966,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="341" spans="1:3">
       <c r="A341">
         <v>351</v>
       </c>
@@ -8343,7 +8977,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="342" spans="1:3">
       <c r="A342">
         <v>352</v>
       </c>
@@ -8354,7 +8988,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="343" spans="1:3">
       <c r="A343">
         <v>353</v>
       </c>
@@ -8365,7 +8999,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="344" spans="1:3">
       <c r="A344">
         <v>354</v>
       </c>
@@ -8376,7 +9010,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="345" spans="1:3">
       <c r="A345">
         <v>355</v>
       </c>
@@ -8387,7 +9021,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="346" spans="1:3">
       <c r="A346">
         <v>356</v>
       </c>
@@ -8398,7 +9032,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="347" spans="1:3">
       <c r="A347">
         <v>357</v>
       </c>
@@ -8409,7 +9043,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="348" spans="1:3">
       <c r="A348">
         <v>358</v>
       </c>
@@ -8420,7 +9054,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="349" spans="1:3">
       <c r="A349">
         <v>359</v>
       </c>
@@ -8431,7 +9065,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="350" spans="1:3">
       <c r="A350">
         <v>360</v>
       </c>
@@ -8442,7 +9076,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="351" spans="1:3">
       <c r="A351">
         <v>361</v>
       </c>
@@ -8453,7 +9087,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="352" spans="1:3">
       <c r="A352">
         <v>362</v>
       </c>
@@ -8464,7 +9098,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="353" spans="1:3">
       <c r="A353">
         <v>363</v>
       </c>
@@ -8475,7 +9109,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="354" spans="1:3">
       <c r="A354">
         <v>364</v>
       </c>
@@ -8486,7 +9120,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="355" spans="1:3">
       <c r="A355">
         <v>365</v>
       </c>
@@ -8497,7 +9131,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="356" spans="1:3">
       <c r="A356">
         <v>366</v>
       </c>
@@ -8508,7 +9142,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="357" spans="1:3">
       <c r="A357">
         <v>367</v>
       </c>
@@ -8519,7 +9153,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="358" spans="1:3">
       <c r="A358">
         <v>368</v>
       </c>
@@ -8530,7 +9164,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="359" spans="1:3">
       <c r="A359">
         <v>369</v>
       </c>
@@ -8541,7 +9175,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="360" spans="1:3">
       <c r="A360">
         <v>370</v>
       </c>
@@ -8552,7 +9186,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="361" spans="1:3">
       <c r="A361">
         <v>371</v>
       </c>
@@ -8563,7 +9197,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="362" spans="1:3">
       <c r="A362">
         <v>372</v>
       </c>
@@ -8574,7 +9208,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="363" spans="1:3">
       <c r="A363">
         <v>373</v>
       </c>
@@ -8585,7 +9219,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="364" spans="1:3">
       <c r="A364">
         <v>374</v>
       </c>
@@ -8596,7 +9230,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="365" spans="1:3">
       <c r="A365">
         <v>375</v>
       </c>
@@ -8607,7 +9241,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="366" spans="1:3">
       <c r="A366">
         <v>376</v>
       </c>
@@ -8618,7 +9252,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="367" spans="1:3">
       <c r="A367">
         <v>377</v>
       </c>
@@ -8629,7 +9263,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="368" spans="1:3">
       <c r="A368">
         <v>378</v>
       </c>
@@ -8640,7 +9274,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="369" spans="1:3">
       <c r="A369">
         <v>379</v>
       </c>
@@ -8651,7 +9285,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="370" spans="1:3">
       <c r="A370">
         <v>380</v>
       </c>
@@ -8662,7 +9296,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="371" spans="1:3">
       <c r="A371">
         <v>381</v>
       </c>
@@ -8673,7 +9307,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="372" spans="1:3">
       <c r="A372">
         <v>382</v>
       </c>
@@ -8684,7 +9318,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="373" spans="1:3">
       <c r="A373">
         <v>383</v>
       </c>
@@ -8695,7 +9329,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="374" spans="1:3">
       <c r="A374">
         <v>384</v>
       </c>
@@ -8706,7 +9340,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="375" spans="1:3">
       <c r="A375">
         <v>385</v>
       </c>
@@ -8717,7 +9351,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="376" spans="1:3">
       <c r="A376">
         <v>386</v>
       </c>
@@ -8728,7 +9362,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="377" spans="1:3">
       <c r="A377">
         <v>387</v>
       </c>
@@ -8739,7 +9373,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="378" spans="1:3">
       <c r="A378">
         <v>388</v>
       </c>
@@ -8750,7 +9384,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="379" spans="1:3">
       <c r="A379">
         <v>389</v>
       </c>
@@ -8761,7 +9395,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="380" spans="1:3">
       <c r="A380">
         <v>390</v>
       </c>
@@ -8772,7 +9406,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="381" spans="1:3">
       <c r="A381">
         <v>391</v>
       </c>
@@ -8783,7 +9417,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="382" spans="1:3">
       <c r="A382">
         <v>392</v>
       </c>
@@ -8794,7 +9428,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="383" spans="1:3">
       <c r="A383">
         <v>393</v>
       </c>
@@ -8805,7 +9439,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="384" spans="1:3">
       <c r="A384">
         <v>394</v>
       </c>
@@ -8816,7 +9450,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="385" spans="1:3">
       <c r="A385">
         <v>395</v>
       </c>
@@ -8827,7 +9461,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="386" spans="1:3">
       <c r="A386">
         <v>396</v>
       </c>
@@ -8838,7 +9472,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="387" spans="1:3">
       <c r="A387">
         <v>397</v>
       </c>
@@ -8849,7 +9483,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="388" spans="1:3">
       <c r="A388">
         <v>398</v>
       </c>
@@ -8860,7 +9494,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="389" spans="1:3">
       <c r="A389">
         <v>399</v>
       </c>
@@ -8871,7 +9505,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="390" spans="1:3">
       <c r="A390">
         <v>400</v>
       </c>
@@ -8882,7 +9516,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="391" spans="1:3">
       <c r="A391">
         <v>401</v>
       </c>
@@ -8893,7 +9527,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="392" ht="17.25" spans="1:3">
       <c r="A392">
         <v>402</v>
       </c>
@@ -8904,7 +9538,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="393" spans="1:3">
       <c r="A393">
         <v>403</v>
       </c>
@@ -8915,7 +9549,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="394" spans="1:3">
       <c r="A394">
         <v>404</v>
       </c>
@@ -8926,7 +9560,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="395" spans="1:3">
       <c r="A395">
         <v>405</v>
       </c>
@@ -8937,7 +9571,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="396" spans="1:3">
       <c r="A396">
         <v>406</v>
       </c>
@@ -8948,7 +9582,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="397" spans="1:3">
       <c r="A397">
         <v>407</v>
       </c>
@@ -8959,7 +9593,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="398" spans="1:3">
       <c r="A398">
         <v>408</v>
       </c>
@@ -8970,7 +9604,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="399" spans="1:3">
       <c r="A399">
         <v>409</v>
       </c>
@@ -8981,7 +9615,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="400" spans="1:3">
       <c r="A400">
         <v>410</v>
       </c>
@@ -8992,7 +9626,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="401" spans="1:3">
       <c r="A401">
         <v>411</v>
       </c>
@@ -9003,7 +9637,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="402" spans="1:3">
       <c r="A402">
         <v>412</v>
       </c>
@@ -9014,7 +9648,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="403" spans="1:3">
       <c r="A403">
         <v>413</v>
       </c>
@@ -9025,7 +9659,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="404" spans="1:3">
       <c r="A404">
         <v>414</v>
       </c>
@@ -9036,7 +9670,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="405" spans="1:3">
       <c r="A405">
         <v>415</v>
       </c>
@@ -9047,7 +9681,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="406" spans="1:3">
       <c r="A406">
         <v>416</v>
       </c>
@@ -9058,7 +9692,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="407" spans="1:3">
       <c r="A407">
         <v>417</v>
       </c>
@@ -9069,7 +9703,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="408" spans="1:3">
       <c r="A408">
         <v>418</v>
       </c>
@@ -9080,7 +9714,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="409" spans="1:3">
       <c r="A409">
         <v>419</v>
       </c>
@@ -9091,7 +9725,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="410" spans="1:3">
       <c r="A410">
         <v>420</v>
       </c>
@@ -9102,7 +9736,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="411" spans="1:3">
       <c r="A411">
         <v>421</v>
       </c>
@@ -9113,7 +9747,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="412" spans="1:3">
       <c r="A412">
         <v>422</v>
       </c>
@@ -9124,7 +9758,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="413" spans="1:3">
       <c r="A413">
         <v>423</v>
       </c>
@@ -9135,7 +9769,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="414" spans="1:3">
       <c r="A414">
         <v>424</v>
       </c>
@@ -9146,7 +9780,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="415" spans="1:3">
       <c r="A415">
         <v>425</v>
       </c>
@@ -9157,7 +9791,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="416" spans="1:3">
       <c r="A416">
         <v>426</v>
       </c>
@@ -9168,7 +9802,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="417" spans="1:3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -9179,7 +9813,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="418" spans="1:3">
       <c r="A418">
         <v>428</v>
       </c>
@@ -9190,7 +9824,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="419" spans="1:3">
       <c r="A419">
         <v>429</v>
       </c>
@@ -9201,7 +9835,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="420" spans="1:3">
       <c r="A420">
         <v>430</v>
       </c>
@@ -9212,7 +9846,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="421" spans="1:3">
       <c r="A421">
         <v>431</v>
       </c>
@@ -9223,7 +9857,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="422" spans="1:3">
       <c r="A422">
         <v>432</v>
       </c>
@@ -9234,7 +9868,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="423" spans="1:3">
       <c r="A423">
         <v>433</v>
       </c>
@@ -9245,7 +9879,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="424" spans="1:3">
       <c r="A424">
         <v>434</v>
       </c>
@@ -9256,7 +9890,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="425" spans="1:3">
       <c r="A425">
         <v>435</v>
       </c>
@@ -9267,7 +9901,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="426" spans="1:3">
       <c r="A426">
         <v>436</v>
       </c>
@@ -9278,7 +9912,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="427" spans="1:3">
       <c r="A427">
         <v>437</v>
       </c>
@@ -9289,7 +9923,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="428" spans="1:3">
       <c r="A428">
         <v>438</v>
       </c>
@@ -9300,7 +9934,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="429" spans="1:3">
       <c r="A429">
         <v>439</v>
       </c>
@@ -9311,7 +9945,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="430" spans="1:3">
       <c r="A430">
         <v>440</v>
       </c>
@@ -9322,7 +9956,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="431" spans="1:3">
       <c r="A431">
         <v>441</v>
       </c>
@@ -9333,7 +9967,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="432" spans="1:3">
       <c r="A432">
         <v>442</v>
       </c>
@@ -9344,7 +9978,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="433" spans="1:3">
       <c r="A433">
         <v>443</v>
       </c>
@@ -9355,7 +9989,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="434" spans="1:3">
       <c r="A434">
         <v>444</v>
       </c>
@@ -9366,7 +10000,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="435" spans="1:3">
       <c r="A435">
         <v>445</v>
       </c>
@@ -9377,7 +10011,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="436" spans="1:3">
       <c r="A436">
         <v>446</v>
       </c>
@@ -9388,7 +10022,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="437" spans="1:3">
       <c r="A437">
         <v>447</v>
       </c>
@@ -9399,7 +10033,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="438" spans="1:3">
       <c r="A438">
         <v>448</v>
       </c>
@@ -9410,7 +10044,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="439" spans="1:3">
       <c r="A439">
         <v>449</v>
       </c>
@@ -9421,7 +10055,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="440" spans="1:3">
       <c r="A440">
         <v>450</v>
       </c>
@@ -9432,7 +10066,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="441" spans="1:3">
       <c r="A441">
         <v>451</v>
       </c>
@@ -9443,7 +10077,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="442" spans="1:3">
       <c r="A442">
         <v>452</v>
       </c>
@@ -9454,7 +10088,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="443" spans="1:3">
       <c r="A443">
         <v>453</v>
       </c>
@@ -9465,7 +10099,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="444" spans="1:3">
       <c r="A444">
         <v>455</v>
       </c>
@@ -9476,7 +10110,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="445" spans="1:3">
       <c r="A445">
         <v>456</v>
       </c>
@@ -9487,7 +10121,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="446" spans="1:3">
       <c r="A446">
         <v>457</v>
       </c>
@@ -9498,7 +10132,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="447" spans="1:3">
       <c r="A447">
         <v>458</v>
       </c>
@@ -9509,7 +10143,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="448" spans="1:3">
       <c r="A448">
         <v>459</v>
       </c>
@@ -9520,7 +10154,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="449" spans="1:3">
       <c r="A449">
         <v>460</v>
       </c>
@@ -9531,7 +10165,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="450" spans="1:3">
       <c r="A450">
         <v>461</v>
       </c>
@@ -9542,7 +10176,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="451" spans="1:3">
       <c r="A451">
         <v>462</v>
       </c>
@@ -9553,7 +10187,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="452" spans="1:3">
       <c r="A452">
         <v>463</v>
       </c>
@@ -9564,7 +10198,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="453" spans="1:3">
       <c r="A453">
         <v>464</v>
       </c>
@@ -9575,7 +10209,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="454" spans="1:3">
       <c r="A454">
         <v>465</v>
       </c>
@@ -9586,7 +10220,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="455" spans="1:3">
       <c r="A455">
         <v>466</v>
       </c>
@@ -9597,7 +10231,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="456" spans="1:3">
       <c r="A456">
         <v>467</v>
       </c>
@@ -9608,7 +10242,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="457" spans="1:3">
       <c r="A457">
         <v>468</v>
       </c>
@@ -9619,7 +10253,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="458" spans="1:3">
       <c r="A458">
         <v>469</v>
       </c>
@@ -9630,7 +10264,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="459" spans="1:3">
       <c r="A459">
         <v>470</v>
       </c>
@@ -9641,7 +10275,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="460" spans="1:3">
       <c r="A460">
         <v>471</v>
       </c>
@@ -9649,7 +10283,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="461" spans="1:3">
       <c r="A461">
         <v>472</v>
       </c>
@@ -9660,7 +10294,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="462" spans="1:3">
       <c r="A462">
         <v>473</v>
       </c>
@@ -9671,7 +10305,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="463" spans="1:3">
       <c r="A463">
         <v>474</v>
       </c>
@@ -9682,7 +10316,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="464" spans="1:3">
       <c r="A464">
         <v>475</v>
       </c>
@@ -9693,7 +10327,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="465" spans="1:3">
       <c r="A465">
         <v>476</v>
       </c>
@@ -9704,7 +10338,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="466" spans="1:3">
       <c r="A466">
         <v>477</v>
       </c>
@@ -9715,7 +10349,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="467" spans="1:3">
       <c r="A467">
         <v>478</v>
       </c>
@@ -9726,7 +10360,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="468" spans="1:3">
       <c r="A468">
         <v>479</v>
       </c>
@@ -9737,7 +10371,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="469" spans="1:3">
       <c r="A469">
         <v>480</v>
       </c>
@@ -9748,7 +10382,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="470" spans="1:3">
       <c r="A470">
         <v>481</v>
       </c>
@@ -9759,7 +10393,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="471" spans="1:3">
       <c r="A471">
         <v>482</v>
       </c>
@@ -9770,7 +10404,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="472" spans="1:3">
       <c r="A472">
         <v>483</v>
       </c>
@@ -9781,7 +10415,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="473" ht="17.25" spans="1:3">
       <c r="A473">
         <v>484</v>
       </c>
@@ -9792,7 +10426,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="474" spans="1:3">
       <c r="A474">
         <v>485</v>
       </c>
@@ -9803,7 +10437,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="475" spans="1:3">
       <c r="A475">
         <v>486</v>
       </c>
@@ -9814,7 +10448,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="476" spans="1:3">
       <c r="A476">
         <v>487</v>
       </c>
@@ -9825,7 +10459,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="477" spans="1:3">
       <c r="A477">
         <v>488</v>
       </c>
@@ -9836,7 +10470,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="478" spans="1:3">
       <c r="A478">
         <v>489</v>
       </c>
@@ -9847,7 +10481,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="479" spans="1:3">
       <c r="A479">
         <v>490</v>
       </c>
@@ -9858,7 +10492,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="480" spans="1:3">
       <c r="A480">
         <v>491</v>
       </c>
@@ -9869,7 +10503,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="481" spans="1:3">
       <c r="A481">
         <v>492</v>
       </c>
@@ -9880,7 +10514,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="482" spans="1:3">
       <c r="A482">
         <v>493</v>
       </c>
@@ -9891,7 +10525,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="483" spans="1:3">
       <c r="A483">
         <v>494</v>
       </c>
@@ -9902,7 +10536,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="484" spans="1:3">
       <c r="A484">
         <v>496</v>
       </c>
@@ -9913,7 +10547,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="485" spans="1:3">
       <c r="A485">
         <v>497</v>
       </c>
@@ -9924,7 +10558,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="486" spans="1:3">
       <c r="A486">
         <v>498</v>
       </c>
@@ -9935,7 +10569,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="487" spans="1:3">
       <c r="A487">
         <v>499</v>
       </c>
@@ -9946,7 +10580,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="488" spans="1:3">
       <c r="A488">
         <v>500</v>
       </c>
@@ -9957,7 +10591,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="489" spans="1:3">
       <c r="A489">
         <v>501</v>
       </c>
@@ -9968,7 +10602,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="490" spans="1:3">
       <c r="A490">
         <v>502</v>
       </c>
@@ -9979,7 +10613,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="491" spans="1:3">
       <c r="A491">
         <v>503</v>
       </c>
@@ -9990,7 +10624,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="492" spans="1:3">
       <c r="A492">
         <v>504</v>
       </c>
@@ -10001,7 +10635,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="493" spans="1:3">
       <c r="A493">
         <v>505</v>
       </c>
@@ -10012,7 +10646,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="494" spans="1:3">
       <c r="A494">
         <v>506</v>
       </c>
@@ -10023,7 +10657,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="495" spans="1:3">
       <c r="A495">
         <v>507</v>
       </c>
@@ -10034,7 +10668,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="496" spans="1:3">
       <c r="A496">
         <v>508</v>
       </c>
@@ -10045,7 +10679,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="497" spans="1:3">
       <c r="A497">
         <v>509</v>
       </c>
@@ -10056,7 +10690,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="498" spans="1:3">
       <c r="A498">
         <v>510</v>
       </c>
@@ -10067,7 +10701,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="499" spans="1:3">
       <c r="A499">
         <v>511</v>
       </c>
@@ -10075,7 +10709,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="500" spans="1:3">
       <c r="A500">
         <v>512</v>
       </c>
@@ -10086,7 +10720,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="501" spans="1:3">
       <c r="A501">
         <v>513</v>
       </c>
@@ -10097,7 +10731,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="502" spans="1:3">
       <c r="A502">
         <v>514</v>
       </c>
@@ -10108,7 +10742,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="503" spans="1:3">
       <c r="A503">
         <v>515</v>
       </c>
@@ -10119,7 +10753,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="504" spans="1:3">
       <c r="A504">
         <v>516</v>
       </c>
@@ -10130,7 +10764,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="505" spans="1:3">
       <c r="A505">
         <v>517</v>
       </c>
@@ -10141,7 +10775,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="506" spans="1:3">
       <c r="A506">
         <v>518</v>
       </c>
@@ -10152,7 +10786,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="507" spans="1:3">
       <c r="A507">
         <v>519</v>
       </c>
@@ -10163,7 +10797,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="508" spans="1:3">
       <c r="A508">
         <v>520</v>
       </c>
@@ -10174,7 +10808,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="509" spans="1:3">
       <c r="A509">
         <v>521</v>
       </c>
@@ -10185,7 +10819,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="510" spans="1:3">
       <c r="A510">
         <v>522</v>
       </c>
@@ -10196,7 +10830,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="511" spans="1:3">
       <c r="A511">
         <v>523</v>
       </c>
@@ -10207,7 +10841,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="512" spans="1:3">
       <c r="A512">
         <v>524</v>
       </c>
@@ -10218,7 +10852,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="513" spans="1:3">
       <c r="A513">
         <v>525</v>
       </c>
@@ -10229,7 +10863,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="514" spans="1:3">
       <c r="A514">
         <v>526</v>
       </c>
@@ -10240,7 +10874,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="515" spans="1:3">
       <c r="A515">
         <v>527</v>
       </c>
@@ -10251,7 +10885,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="516" spans="1:3">
       <c r="A516">
         <v>528</v>
       </c>
@@ -10262,7 +10896,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="517" spans="1:3">
       <c r="A517">
         <v>529</v>
       </c>
@@ -10273,7 +10907,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="518" spans="1:3">
       <c r="A518">
         <v>530</v>
       </c>
@@ -10281,7 +10915,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="519" spans="1:3">
       <c r="A519">
         <v>531</v>
       </c>
@@ -10292,7 +10926,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="520" spans="1:3">
       <c r="A520">
         <v>532</v>
       </c>
@@ -10303,7 +10937,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="521" spans="1:3">
       <c r="A521">
         <v>533</v>
       </c>
@@ -10314,7 +10948,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="522" spans="1:3">
       <c r="A522">
         <v>534</v>
       </c>
@@ -10325,7 +10959,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="523" spans="1:3">
       <c r="A523">
         <v>535</v>
       </c>
@@ -10336,7 +10970,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="524" spans="1:3">
       <c r="A524">
         <v>536</v>
       </c>
@@ -10347,7 +10981,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="525" spans="1:3">
       <c r="A525">
         <v>537</v>
       </c>
@@ -10358,7 +10992,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="526" spans="1:3">
       <c r="A526">
         <v>538</v>
       </c>
@@ -10369,7 +11003,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="527" spans="1:3">
       <c r="A527">
         <v>539</v>
       </c>
@@ -10380,7 +11014,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="528" spans="1:3">
       <c r="A528">
         <v>540</v>
       </c>
@@ -10391,7 +11025,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="529" spans="1:3">
       <c r="A529">
         <v>542</v>
       </c>
@@ -10402,7 +11036,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="530" spans="1:3">
       <c r="A530">
         <v>543</v>
       </c>
@@ -10413,7 +11047,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="531" spans="1:3">
       <c r="A531">
         <v>545</v>
       </c>
@@ -10424,7 +11058,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="532" spans="1:3">
       <c r="A532">
         <v>546</v>
       </c>
@@ -10435,7 +11069,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="533" spans="1:3">
       <c r="A533">
         <v>547</v>
       </c>
@@ -10446,7 +11080,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="534" spans="1:3">
       <c r="A534">
         <v>548</v>
       </c>
@@ -10457,7 +11091,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="535" spans="1:3">
       <c r="A535">
         <v>549</v>
       </c>
@@ -10468,7 +11102,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="536" spans="1:3">
       <c r="A536">
         <v>550</v>
       </c>
@@ -10479,7 +11113,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="537" spans="1:3">
       <c r="A537">
         <v>551</v>
       </c>
@@ -10490,7 +11124,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="538" spans="1:3">
       <c r="A538">
         <v>552</v>
       </c>
@@ -10501,7 +11135,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="539" spans="1:3">
       <c r="A539">
         <v>553</v>
       </c>
@@ -10512,7 +11146,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="540" spans="1:3">
       <c r="A540">
         <v>554</v>
       </c>
@@ -10523,7 +11157,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="541" spans="1:3">
       <c r="A541">
         <v>555</v>
       </c>
@@ -10534,7 +11168,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="542" spans="1:3">
       <c r="A542">
         <v>556</v>
       </c>
@@ -10545,7 +11179,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="543" spans="1:3">
       <c r="A543">
         <v>557</v>
       </c>
@@ -10556,7 +11190,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="544" spans="1:3">
       <c r="A544">
         <v>558</v>
       </c>
@@ -10567,7 +11201,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="545" spans="1:3">
       <c r="A545">
         <v>559</v>
       </c>
@@ -10578,7 +11212,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="546" spans="1:3">
       <c r="A546">
         <v>562</v>
       </c>
@@ -10589,7 +11223,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="547" spans="1:3">
       <c r="A547">
         <v>563</v>
       </c>
@@ -10597,7 +11231,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="548" spans="1:3">
       <c r="A548">
         <v>564</v>
       </c>
@@ -10608,7 +11242,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="549" spans="1:3">
       <c r="A549">
         <v>565</v>
       </c>
@@ -10619,7 +11253,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="550" spans="1:3">
       <c r="A550">
         <v>566</v>
       </c>
@@ -10630,7 +11264,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="551" spans="1:3">
       <c r="A551">
         <v>567</v>
       </c>
@@ -10641,7 +11275,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="552" spans="1:3">
       <c r="A552">
         <v>568</v>
       </c>
@@ -10652,7 +11286,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="553" spans="1:3">
       <c r="A553">
         <v>569</v>
       </c>
@@ -10663,7 +11297,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="554" spans="1:3">
       <c r="A554">
         <v>570</v>
       </c>
@@ -10674,7 +11308,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="555" spans="1:3">
       <c r="A555">
         <v>571</v>
       </c>
@@ -10685,7 +11319,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="556" spans="1:3">
       <c r="A556">
         <v>572</v>
       </c>
@@ -10696,7 +11330,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="557" spans="1:3">
       <c r="A557">
         <v>577</v>
       </c>
@@ -10707,7 +11341,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="558" spans="1:3">
       <c r="A558">
         <v>578</v>
       </c>
@@ -10718,7 +11352,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="559" spans="1:3">
       <c r="A559">
         <v>579</v>
       </c>
@@ -10726,7 +11360,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="560" spans="1:3">
       <c r="A560">
         <v>580</v>
       </c>
@@ -10737,7 +11371,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="561" spans="1:3">
       <c r="A561">
         <v>581</v>
       </c>
@@ -10748,7 +11382,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="562" spans="1:3">
       <c r="A562">
         <v>582</v>
       </c>
@@ -10759,7 +11393,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="563" spans="1:3">
       <c r="A563">
         <v>583</v>
       </c>
@@ -10770,7 +11404,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="564" spans="1:3">
       <c r="A564">
         <v>584</v>
       </c>
@@ -10781,7 +11415,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="565" spans="1:3">
       <c r="A565">
         <v>585</v>
       </c>
@@ -10792,7 +11426,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="566" spans="1:3">
       <c r="A566">
         <v>586</v>
       </c>
@@ -10803,7 +11437,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="567" spans="1:3">
       <c r="A567">
         <v>587</v>
       </c>
@@ -10814,7 +11448,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="568" spans="1:3">
       <c r="A568">
         <v>588</v>
       </c>
@@ -10825,7 +11459,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="569" spans="1:3">
       <c r="A569">
         <v>589</v>
       </c>
@@ -10836,7 +11470,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="570" spans="1:3">
       <c r="A570">
         <v>590</v>
       </c>
@@ -10847,7 +11481,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="571" spans="1:3">
       <c r="A571">
         <v>591</v>
       </c>
@@ -10858,7 +11492,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="572" spans="1:3">
       <c r="A572">
         <v>592</v>
       </c>
@@ -10869,7 +11503,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="573" spans="1:3">
       <c r="A573">
         <v>593</v>
       </c>
@@ -10880,7 +11514,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="574" spans="1:3">
       <c r="A574">
         <v>594</v>
       </c>
@@ -10891,7 +11525,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="575" spans="1:3">
       <c r="A575">
         <v>595</v>
       </c>
@@ -10902,7 +11536,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="576" spans="1:3">
       <c r="A576">
         <v>596</v>
       </c>
@@ -10913,7 +11547,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="577" spans="1:3">
       <c r="A577">
         <v>597</v>
       </c>
@@ -10924,7 +11558,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="578" spans="1:3">
       <c r="A578">
         <v>598</v>
       </c>
@@ -10935,7 +11569,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="579" spans="1:3">
       <c r="A579">
         <v>599</v>
       </c>
@@ -10946,7 +11580,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="580" spans="1:3">
       <c r="A580">
         <v>601</v>
       </c>
@@ -10957,7 +11591,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="581" spans="1:3">
       <c r="A581">
         <v>602</v>
       </c>
@@ -10968,7 +11602,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="582" spans="1:3">
       <c r="A582">
         <v>604</v>
       </c>
@@ -10979,1012 +11613,1047 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.1">
+    <row r="583" spans="1:3">
       <c r="A583">
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1331</v>
+        <v>1151</v>
       </c>
       <c r="C583" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3">
       <c r="A584">
         <v>612</v>
       </c>
       <c r="B584" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C584" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3">
       <c r="A585">
         <v>615</v>
       </c>
       <c r="B585" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C585" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3">
       <c r="A586">
         <v>617</v>
       </c>
       <c r="B586" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C586" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3">
       <c r="A587">
         <v>618</v>
       </c>
       <c r="B587" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C587" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3">
       <c r="A588">
         <v>625</v>
       </c>
       <c r="B588" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="C588" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3">
       <c r="A589">
         <v>624</v>
       </c>
       <c r="B589" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C589" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3">
       <c r="A590">
         <v>626</v>
       </c>
       <c r="B590" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C590" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3">
       <c r="A591">
         <v>629</v>
       </c>
       <c r="B591" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="C591" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3">
       <c r="A592">
         <v>630</v>
       </c>
       <c r="B592" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="C592" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3">
       <c r="A593">
         <v>633</v>
       </c>
       <c r="B593" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C593" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3">
       <c r="A594">
         <v>635</v>
       </c>
       <c r="B594" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C594" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3">
       <c r="A595">
         <v>636</v>
       </c>
       <c r="B595" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C595" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3">
       <c r="A596">
         <v>642</v>
       </c>
       <c r="B596" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C596" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3">
       <c r="A597">
         <v>644</v>
       </c>
       <c r="B597" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C597" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3">
       <c r="A598">
         <v>646</v>
       </c>
       <c r="B598" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C598" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3">
       <c r="A599">
         <v>649</v>
       </c>
       <c r="B599" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C599" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3">
       <c r="A600">
         <v>650</v>
       </c>
       <c r="B600" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C600" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3">
       <c r="A601">
         <v>651</v>
       </c>
       <c r="B601" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C601" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3">
       <c r="A602">
         <v>653</v>
       </c>
       <c r="B602" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C602" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3">
       <c r="A603">
         <v>654</v>
       </c>
       <c r="B603" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C603" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3">
       <c r="A604">
         <v>655</v>
       </c>
       <c r="B604" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="C604" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3">
       <c r="A605">
         <v>659</v>
       </c>
       <c r="B605" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="C605" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3">
       <c r="A606">
         <v>660</v>
       </c>
       <c r="B606" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C606" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3">
       <c r="A607">
         <v>661</v>
       </c>
       <c r="B607" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="C607" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3">
       <c r="A608">
         <v>663</v>
       </c>
       <c r="B608" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C608" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3">
       <c r="A609">
         <v>667</v>
       </c>
       <c r="B609" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C609" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3">
       <c r="A610">
         <v>670</v>
       </c>
       <c r="B610" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="C610" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3">
       <c r="A611">
         <v>673</v>
       </c>
       <c r="B611" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C611" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3">
       <c r="A612">
         <v>674</v>
       </c>
       <c r="B612" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C612" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3">
       <c r="A613">
         <v>675</v>
       </c>
       <c r="B613" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C613" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3">
       <c r="A614">
         <v>680</v>
       </c>
       <c r="B614" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="C614" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3">
       <c r="A615">
         <v>681</v>
       </c>
       <c r="B615" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C615" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3">
       <c r="A616">
         <v>682</v>
       </c>
       <c r="B616" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="C616" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3">
       <c r="A617">
         <v>683</v>
       </c>
       <c r="B617" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="C617" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3">
       <c r="A618">
         <v>684</v>
       </c>
       <c r="B618" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C618" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3">
       <c r="A619">
         <v>685</v>
       </c>
       <c r="B619" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="C619" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3">
       <c r="A620">
         <v>686</v>
       </c>
       <c r="B620" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="C620" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3">
       <c r="A621">
         <v>689</v>
       </c>
       <c r="B621" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C621" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3">
       <c r="A622">
         <v>697</v>
       </c>
       <c r="B622" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="C622" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3">
       <c r="A623">
         <v>701</v>
       </c>
       <c r="B623" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="C623" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3">
       <c r="A624">
         <v>702</v>
       </c>
       <c r="B624" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C624" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3">
       <c r="A625">
         <v>704</v>
       </c>
       <c r="B625" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C625" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3">
       <c r="A626">
         <v>705</v>
       </c>
       <c r="B626" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="C626" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3">
       <c r="A627">
         <v>710</v>
       </c>
       <c r="B627" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C627" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3">
       <c r="A628">
         <v>711</v>
       </c>
       <c r="B628" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="C628" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3">
       <c r="A629">
         <v>712</v>
       </c>
       <c r="B629" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="C629" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3">
       <c r="A630">
         <v>714</v>
       </c>
       <c r="B630" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="C630" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3">
       <c r="A631">
         <v>717</v>
       </c>
       <c r="B631" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C631" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3">
       <c r="A632">
         <v>718</v>
       </c>
       <c r="B632" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="C632" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3">
       <c r="A633">
         <v>719</v>
       </c>
       <c r="B633" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="C633" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="634" ht="19.5" spans="1:3">
       <c r="A634">
         <v>721</v>
       </c>
       <c r="B634" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="C634" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3">
       <c r="A635">
         <v>722</v>
       </c>
       <c r="B635" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="C635" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3">
       <c r="A636">
         <v>723</v>
       </c>
       <c r="B636" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C636" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3">
       <c r="A637">
         <v>725</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="C637" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3">
       <c r="A638">
         <v>726</v>
       </c>
       <c r="B638" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C638" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3">
       <c r="A639">
         <v>727</v>
       </c>
       <c r="B639" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="C639" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="640" ht="19.5" spans="1:3">
       <c r="A640">
         <v>728</v>
       </c>
       <c r="B640" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C640" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="641" ht="19.5" spans="1:3">
       <c r="A641">
         <v>729</v>
       </c>
       <c r="B641" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C641" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3">
       <c r="A642">
         <v>730</v>
       </c>
       <c r="B642" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="C642" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3">
       <c r="A643">
         <v>731</v>
       </c>
       <c r="B643" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="C643" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3">
       <c r="A644">
         <v>733</v>
       </c>
       <c r="B644" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C644" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3">
       <c r="A645">
         <v>735</v>
       </c>
       <c r="B645" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C645" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3">
       <c r="A646">
         <v>736</v>
       </c>
       <c r="B646" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C646" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3">
       <c r="A647">
         <v>737</v>
       </c>
       <c r="B647" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C647" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3">
       <c r="A648">
         <v>738</v>
       </c>
       <c r="B648" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C648" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3">
       <c r="A649">
         <v>739</v>
       </c>
       <c r="B649" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C649" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3">
       <c r="A650">
         <v>740</v>
       </c>
       <c r="B650" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="C650" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3">
       <c r="A651">
         <v>741</v>
       </c>
       <c r="B651" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="C651" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3">
       <c r="A652">
         <v>742</v>
       </c>
       <c r="B652" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C652" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3">
       <c r="A653">
         <v>743</v>
       </c>
       <c r="B653" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C653" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3">
       <c r="A654">
         <v>744</v>
       </c>
       <c r="B654" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="C654" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="655" ht="19.5" spans="1:3">
       <c r="A655">
         <v>745</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C655" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3">
       <c r="A656">
         <v>746</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="C656" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3">
       <c r="A657">
         <v>747</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C657" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3">
       <c r="A658">
         <v>748</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C658" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3">
       <c r="A659">
         <v>749</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="C659" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3">
       <c r="A660">
         <v>753</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="C660" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3">
       <c r="A661">
         <v>755</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C661" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3">
       <c r="A662">
         <v>756</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C662" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3">
       <c r="A663">
         <v>757</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C663" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3">
       <c r="A664">
         <v>758</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C664" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3">
       <c r="A665">
         <v>759</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C665" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3">
       <c r="A666">
         <v>760</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C666" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3">
       <c r="A667">
         <v>761</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="C667" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3">
       <c r="A668">
         <v>762</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="C668" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3">
       <c r="A669">
         <v>763</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C669" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3">
       <c r="A670">
         <v>764</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C670" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3">
       <c r="A671">
         <v>765</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C671" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.1">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3">
       <c r="A672">
-        <v>10001</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.1">
+        <v>766</v>
+      </c>
+      <c r="B672" s="1"/>
+    </row>
+    <row r="673" spans="1:3">
       <c r="A673">
-        <v>10003</v>
-      </c>
-      <c r="B673" t="s">
+        <v>767</v>
+      </c>
+      <c r="B673" s="1" t="s">
         <v>1329</v>
       </c>
       <c r="C673" t="s">
         <v>1330</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3">
+      <c r="A674">
+        <v>768</v>
+      </c>
+      <c r="B674" s="1"/>
+    </row>
+    <row r="675" spans="1:3">
+      <c r="A675">
+        <v>769</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3">
+      <c r="A676">
+        <v>10001</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C676" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3">
+      <c r="A677">
+        <v>10003</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1332</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A611:B612 A392 A393:C401 A390:B390 A391:C391 A167:B167 A168:C169 A285:B286 A487:B487 A488:C498 A421:B423 A208:B208 A209:C228 A313:B313 A314:C314 A133:B133 A134:C144 A591:B591 A609:B609 A474:B474 A536:B538 A279:B280 A374:B374 A375:C376 A406 C412:C413 A412:A413 A414:C417 A499:B500 A23:B23 A24:C27 A569:B572 A584:B584 A586:C587 A604:C604 A170:B170 A171:C207 A38:B39 A30:B31 A85:B85 A86:C92 A473 A475:C476 A349:B349 A350:C350 A464:B465 A353:B353 A354:C373 A593:B593 A598:B598 A600:C602 A43:B43 A44:C50 A295:B295 A296:C306 A327 A328:C344 A386:B386 A387:C389 A407:B407 A408:C411 A477:B477 A478:C479 A556:B557 A565:B565 A15:B15 A16:C19 A40:C42 A99:B99 A100:C106 A455:B456 A469:B469 A470:C472 A505:B505 A506:C506 A521:B522 A523:C530 A451:B452 A379:B379 A384:C385 A383:B383 A380:C382 A594:C596 A8:B8 A9:C12 A71 A128:B128 A129:C132 A154:B154 A155:C161 A58:B58 A59:C69 A107:B107 A108:C113 A229:B230 A231:C233 A250:B251 A252:C256 A260:B260 A261:C267 A268:B268 A269:C278 A281:C284 A402:B402 A403:C405 A425:B425 A426:C431 A432:B432 A433:C446 A447:B447 A448:C448 A466:C468 A507:B507 A510:C512 A509:B509 A508:C508 A517:B517 A518:C518 A539:C539 A550:B550 A551:C552 A449:B449 A450:C450 A580:B580 A582:C582 A2:B5 A13:B13 A14:C14 A424:C424 A453:C454 A501:C502 A513:B515 A576:B578 A614:B614 A531:B531 A532:C535 A519:B519 A520:C520 A480:B480 A481:C486 A150:B150 A151:C153 A503 A504:C504 A79:B79 A80:C84 A418:B419 A287:C294 A114:B114 A115:C119 A420:C420 A20:B20 A21:C22 A607:C607 A566 A567:C568 A573:C573 A6:C7 A257:B257 A258:C259 A619:C621 A377:B377 A378:C378 A162:B162 A163:C166 A70:B70 A72:C78 A51:B51 A52:C52 A345:B345 A346:C348 A553:B553 A554:C555 A93:B94 A516:C516 A457:C458 A53:B54 A307:B307 A308:C312 A579:C579 A28:B28 A29:C29 A558:C564 A55:C57 A540:B540 A541:C549 A145:B145 A146:C149 A95:C98 A234:B234 A235:C249 A616:C616 A459:B459 A460:C463 A574:B574 A575 A590:C590 A351:B351 A352:C352 A316:C326 A315:B315 A672:C672 A120:B120 A121:C127 A1:C1 A37:C37 A36:B36 A32:C35" numberStoredAsText="1"/>
+    <ignoredError sqref="A426:C431 A611:B612 A392 A393:C401 A390:B390 A391:C391 A167:B167 A168:C169 A285:B286 A487:B487 A488:C498 A421:B423 A208:B208 A209:C228 A313:B313 A314:C314 A133:B133 A134:C144 A591:B591 A609:B609 A474:B474 A536:B538 A279:B280 A374:B374 A375:C376 A406 C412:C413 A412:A413 A414:C417 A499:B500 A23:B23 A24:C27 A569:B572 A584:B584 A586:C587 A604:C604 A170:B170 A171:C207 A38:B39 A30:B31 A85:B85 A86:C92 A473 A475:C476 A349:B349 A350:C350 A464:B465 A353:B353 A354:C373 A593:B593 A598:B598 A600:C602 A43:B43 A44:C50 A295:B295 A296:C306 A327 A328:C344 A386:B386 A387:C389 A407:B407 A408:C411 A477:B477 A478:C479 A556:B557 A565:B565 A15:B15 A16:C19 A40:C42 A99:B99 A100:C106 A455:B456 A469:B469 A470:C472 A505:B505 A506:C506 A521:B522 A523:C530 A451:B452 A379:B379 A384:C385 A383:B383 A380:C382 A594:C596 A8:B8 A9:C12 A71 A128:B128 A129:C132 A154:B154 A155:C161 A58:B58 A59:C69 A107:B107 A108:C113 A229:B230 A231:C233 A250:B251 A252:C256 A260:B260 A261:C267 A268:B268 A269:C278 A281:C284 A402:B402 A403:C405 A425:B425 A432:B432 A433:C446 A447:B447 A448:C448 A466:C468 A507:B507 A510:C512 A509:B509 A508:C508 A517:B517 A518:C518 A539:C539 A550:B550 A551:C552 A449:B449 A450:C450 A580:B580 A582:C582 A2:B5 A13:B13 A14:C14 A424:C424 A453:C454 A501:C502 A513:B515 A576:B578 A614:B614 A531:B531 A532:C535 A519:B519 A520:C520 A480:B480 A481:C486 A150:B150 A151:C153 A503 A504:C504 A79:B79 A80:C84 A418:B419 A287:C294 A114:B114 A115:C119 A420:C420 A20:B20 A21:C22 A607:C607 A566 A567:C568 A573:C573 A6:C7 A257:B257 A258:C259 A619:C621 A377:B377 A378:C378 A162:B162 A163:C166 A70:B70 A72:C78 A51:B51 A52:C52 A345:B345 A346:C348 A553:B553 A554:C555 A93:B94 A516:C516 A457:C458 A53:B54 A307:B307 A308:C312 A579:C579 A28:B28 A29:C29 A558:C564 A55:C57 A540:B540 A541:C549 A145:B145 A146:C149 A95:C98 A234:B234 A235:C249 A616:C616 A459:B459 A460:C463 A574:B574 A575 A590:C590 A351:B351 A352:C352 A316:C326 A315:B315 A676:C676 A120:B120 A121:C127 A1:C1 A37:C37 A36:B36 A32:C35" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="1335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="1336">
   <si>
     <t>Id</t>
   </si>
@@ -4174,6 +4174,9 @@
   </si>
   <si>
     <t>台风</t>
+  </si>
+  <si>
+    <t>dokidoki,dkdk,ksar约会曲,演都不演了</t>
   </si>
   <si>
     <t>Mystic Light Quest</t>
@@ -4366,8 +4369,8 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <charset val="128"/>
+      <name val="Segoe UI Symbol"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -4378,8 +4381,8 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <charset val="134"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="33">
@@ -12614,16 +12617,19 @@
         <v>768</v>
       </c>
       <c r="B674" s="1"/>
+      <c r="C674" t="s">
+        <v>1331</v>
+      </c>
     </row>
     <row r="675" spans="1:3">
       <c r="A675">
         <v>769</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C675" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -12631,10 +12637,10 @@
         <v>10001</v>
       </c>
       <c r="B676" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C676" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -12642,10 +12648,10 @@
         <v>10003</v>
       </c>
       <c r="B677" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C677" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
   </sheetData>

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1347" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="1337">
   <si>
     <t>Id</t>
   </si>
@@ -1539,7 +1539,7 @@
     <t>金色へのプレリュード</t>
   </si>
   <si>
-    <t>金色雨,金色,向着金色的序曲</t>
+    <t>金色雨,金色,向着金色的序曲,走向金色的序曲,金色序曲</t>
   </si>
   <si>
     <t>メリッサ</t>
@@ -3614,6 +3614,9 @@
   </si>
   <si>
     <t>kurakura,kura kura</t>
+  </si>
+  <si>
+    <t>阳炎</t>
   </si>
   <si>
     <t>雑踏、僕らの街</t>
@@ -4375,14 +4378,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Segoe UI Emoji"/>
-      <charset val="134"/>
+      <name val="Yu Gothic"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <charset val="128"/>
+      <name val="Segoe UI Emoji"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -5220,7 +5223,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C677"/>
+  <dimension ref="A1:C678"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10.85" customWidth="1"/>
@@ -11728,930 +11731,938 @@
     </row>
     <row r="593" spans="1:3">
       <c r="A593">
-        <v>633</v>
-      </c>
-      <c r="B593" t="s">
+        <v>632</v>
+      </c>
+      <c r="C593" t="s">
         <v>1171</v>
-      </c>
-      <c r="C593" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="594" spans="1:3">
       <c r="A594">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B594" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C594" t="s">
         <v>1173</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="595" spans="1:3">
       <c r="A595">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B595" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C595" t="s">
         <v>1175</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="596" spans="1:3">
       <c r="A596">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B596" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C596" t="s">
         <v>1177</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="597" spans="1:3">
       <c r="A597">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B597" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C597" t="s">
         <v>1179</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="598" spans="1:3">
       <c r="A598">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B598" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C598" t="s">
         <v>1181</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="599" spans="1:3">
       <c r="A599">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B599" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C599" t="s">
         <v>1183</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="600" spans="1:3">
       <c r="A600">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B600" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C600" t="s">
         <v>1185</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="601" spans="1:3">
       <c r="A601">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B601" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C601" t="s">
         <v>1187</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="602" spans="1:3">
       <c r="A602">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B602" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C602" t="s">
         <v>1189</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="603" spans="1:3">
       <c r="A603">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B603" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C603" t="s">
         <v>1191</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="604" spans="1:3">
       <c r="A604">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B604" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C604" t="s">
         <v>1193</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="605" spans="1:3">
       <c r="A605">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B605" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C605" t="s">
         <v>1195</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="606" spans="1:3">
       <c r="A606">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B606" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C606" t="s">
         <v>1197</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="607" spans="1:3">
       <c r="A607">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B607" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C607" t="s">
         <v>1199</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="608" spans="1:3">
       <c r="A608">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B608" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C608" t="s">
         <v>1201</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="609" spans="1:3">
       <c r="A609">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B609" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C609" t="s">
         <v>1203</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="610" spans="1:3">
       <c r="A610">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B610" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C610" t="s">
         <v>1205</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="611" spans="1:3">
       <c r="A611">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B611" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C611" t="s">
         <v>1207</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="612" spans="1:3">
       <c r="A612">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B612" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C612" t="s">
         <v>1209</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="613" spans="1:3">
       <c r="A613">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B613" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C613" t="s">
         <v>1211</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="614" spans="1:3">
       <c r="A614">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B614" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C614" t="s">
         <v>1213</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="615" spans="1:3">
       <c r="A615">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B615" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C615" t="s">
         <v>1215</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="616" spans="1:3">
       <c r="A616">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B616" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C616" t="s">
         <v>1217</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="617" spans="1:3">
       <c r="A617">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B617" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C617" t="s">
         <v>1219</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="618" spans="1:3">
       <c r="A618">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B618" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C618" t="s">
         <v>1221</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="619" spans="1:3">
       <c r="A619">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B619" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C619" t="s">
         <v>1223</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="620" spans="1:3">
       <c r="A620">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B620" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C620" t="s">
         <v>1225</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="621" spans="1:3">
       <c r="A621">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B621" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C621" t="s">
         <v>1227</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="622" spans="1:3">
       <c r="A622">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="B622" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C622" t="s">
         <v>1229</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="623" spans="1:3">
       <c r="A623">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B623" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C623" t="s">
         <v>1231</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="624" spans="1:3">
       <c r="A624">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B624" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C624" t="s">
         <v>1233</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="625" spans="1:3">
       <c r="A625">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B625" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C625" t="s">
         <v>1235</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="626" spans="1:3">
       <c r="A626">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B626" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C626" t="s">
         <v>1237</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="627" spans="1:3">
       <c r="A627">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B627" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C627" t="s">
         <v>1239</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="628" spans="1:3">
       <c r="A628">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B628" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C628" t="s">
         <v>1241</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="629" spans="1:3">
       <c r="A629">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B629" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C629" t="s">
         <v>1243</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="630" spans="1:3">
       <c r="A630">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B630" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C630" t="s">
         <v>1245</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="631" spans="1:3">
       <c r="A631">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B631" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C631" t="s">
         <v>1247</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="632" spans="1:3">
       <c r="A632">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B632" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C632" t="s">
         <v>1249</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="633" spans="1:3">
       <c r="A633">
+        <v>718</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C633" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3">
+      <c r="A634">
         <v>719</v>
       </c>
-      <c r="B633" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C633" t="s">
+      <c r="B634" t="s">
         <v>1252</v>
       </c>
-    </row>
-    <row r="634" ht="19.5" spans="1:3">
-      <c r="A634">
+      <c r="C634" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="635" ht="19.5" spans="1:3">
+      <c r="A635">
         <v>721</v>
       </c>
-      <c r="B634" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C634" t="s">
+      <c r="B635" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="635" spans="1:3">
-      <c r="A635">
-        <v>722</v>
-      </c>
-      <c r="B635" t="s">
+      <c r="C635" t="s">
         <v>1255</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="636" spans="1:3">
       <c r="A636">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B636" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C636" t="s">
         <v>1257</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="637" spans="1:3">
       <c r="A637">
-        <v>725</v>
-      </c>
-      <c r="B637" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C637" t="s">
         <v>1259</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="638" spans="1:3">
       <c r="A638">
-        <v>726</v>
-      </c>
-      <c r="B638" t="s">
+        <v>725</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C638" t="s">
         <v>1261</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="639" spans="1:3">
       <c r="A639">
+        <v>726</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C639" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3">
+      <c r="A640">
         <v>727</v>
       </c>
-      <c r="B639" t="s">
-        <v>1263</v>
-      </c>
-      <c r="C639" t="s">
+      <c r="B640" t="s">
         <v>1264</v>
       </c>
-    </row>
-    <row r="640" ht="19.5" spans="1:3">
-      <c r="A640">
-        <v>728</v>
-      </c>
-      <c r="B640" t="s">
+      <c r="C640" t="s">
         <v>1265</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="641" ht="19.5" spans="1:3">
       <c r="A641">
+        <v>728</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C641" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="642" ht="19.5" spans="1:3">
+      <c r="A642">
         <v>729</v>
       </c>
-      <c r="B641" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C641" t="s">
+      <c r="B642" t="s">
         <v>1268</v>
       </c>
-    </row>
-    <row r="642" spans="1:3">
-      <c r="A642">
-        <v>730</v>
-      </c>
-      <c r="B642" t="s">
+      <c r="C642" t="s">
         <v>1269</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="643" spans="1:3">
       <c r="A643">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B643" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C643" t="s">
         <v>1271</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="644" spans="1:3">
       <c r="A644">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B644" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C644" t="s">
         <v>1273</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="645" spans="1:3">
       <c r="A645">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B645" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C645" t="s">
         <v>1275</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="646" spans="1:3">
       <c r="A646">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B646" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C646" t="s">
         <v>1277</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="647" spans="1:3">
       <c r="A647">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B647" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C647" t="s">
         <v>1279</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="648" spans="1:3">
       <c r="A648">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B648" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C648" t="s">
         <v>1281</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="649" spans="1:3">
       <c r="A649">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B649" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C649" t="s">
         <v>1283</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="650" spans="1:3">
       <c r="A650">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B650" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C650" t="s">
         <v>1285</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="651" spans="1:3">
       <c r="A651">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B651" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C651" t="s">
         <v>1287</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="652" spans="1:3">
       <c r="A652">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B652" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C652" t="s">
         <v>1289</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="653" spans="1:3">
       <c r="A653">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B653" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C653" t="s">
         <v>1291</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="654" spans="1:3">
       <c r="A654">
+        <v>743</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3">
+      <c r="A655">
         <v>744</v>
       </c>
-      <c r="B654" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C654" t="s">
+      <c r="B655" t="s">
         <v>1294</v>
       </c>
-    </row>
-    <row r="655" ht="19.5" spans="1:3">
-      <c r="A655">
+      <c r="C655" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="656" ht="19.5" spans="1:3">
+      <c r="A656">
         <v>745</v>
       </c>
-      <c r="B655" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C655" t="s">
+      <c r="B656" s="1" t="s">
         <v>1296</v>
       </c>
-    </row>
-    <row r="656" spans="1:3">
-      <c r="A656">
-        <v>746</v>
-      </c>
-      <c r="B656" s="1" t="s">
+      <c r="C656" t="s">
         <v>1297</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="657" spans="1:3">
       <c r="A657">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C657" t="s">
         <v>1299</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="658" spans="1:3">
       <c r="A658">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C658" t="s">
         <v>1301</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="659" spans="1:3">
       <c r="A659">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C659" t="s">
         <v>1303</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="660" spans="1:3">
       <c r="A660">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C660" t="s">
         <v>1305</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="661" spans="1:3">
       <c r="A661">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C661" t="s">
         <v>1307</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="662" spans="1:3">
       <c r="A662">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C662" t="s">
         <v>1309</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="663" spans="1:3">
       <c r="A663">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C663" t="s">
         <v>1311</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="664" spans="1:3">
       <c r="A664">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C664" t="s">
         <v>1313</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="665" spans="1:3">
       <c r="A665">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C665" t="s">
         <v>1315</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="666" spans="1:3">
       <c r="A666">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C666" t="s">
         <v>1317</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="667" spans="1:3">
       <c r="A667">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C667" t="s">
         <v>1319</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="668" spans="1:3">
       <c r="A668">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C668" t="s">
         <v>1321</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="669" spans="1:3">
       <c r="A669">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C669" t="s">
         <v>1323</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="670" spans="1:3">
       <c r="A670">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C670" t="s">
         <v>1325</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="671" spans="1:3">
       <c r="A671">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C671" t="s">
         <v>1327</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="672" spans="1:3">
       <c r="A672">
-        <v>766</v>
-      </c>
-      <c r="B672" s="1"/>
+        <v>765</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C672" t="s">
+        <v>1329</v>
+      </c>
     </row>
     <row r="673" spans="1:3">
       <c r="A673">
-        <v>767</v>
-      </c>
-      <c r="B673" s="1" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C673" t="s">
-        <v>1330</v>
-      </c>
+        <v>766</v>
+      </c>
+      <c r="B673" s="1"/>
     </row>
     <row r="674" spans="1:3">
       <c r="A674">
-        <v>768</v>
-      </c>
-      <c r="B674" s="1"/>
+        <v>767</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>1330</v>
+      </c>
       <c r="C674" t="s">
         <v>1331</v>
       </c>
     </row>
     <row r="675" spans="1:3">
       <c r="A675">
-        <v>769</v>
-      </c>
-      <c r="B675" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B675" s="1"/>
+      <c r="C675" t="s">
         <v>1332</v>
-      </c>
-      <c r="C675" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="676" spans="1:3">
       <c r="A676">
-        <v>10001</v>
-      </c>
-      <c r="B676" t="s">
+        <v>769</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C676" t="s">
         <v>1334</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="677" spans="1:3">
       <c r="A677">
+        <v>10001</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3">
+      <c r="A678">
         <v>10003</v>
       </c>
-      <c r="B677" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C677" t="s">
+      <c r="B678" t="s">
         <v>1333</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1334</v>
       </c>
     </row>
   </sheetData>
@@ -12659,7 +12670,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A426:C431 A611:B612 A392 A393:C401 A390:B390 A391:C391 A167:B167 A168:C169 A285:B286 A487:B487 A488:C498 A421:B423 A208:B208 A209:C228 A313:B313 A314:C314 A133:B133 A134:C144 A591:B591 A609:B609 A474:B474 A536:B538 A279:B280 A374:B374 A375:C376 A406 C412:C413 A412:A413 A414:C417 A499:B500 A23:B23 A24:C27 A569:B572 A584:B584 A586:C587 A604:C604 A170:B170 A171:C207 A38:B39 A30:B31 A85:B85 A86:C92 A473 A475:C476 A349:B349 A350:C350 A464:B465 A353:B353 A354:C373 A593:B593 A598:B598 A600:C602 A43:B43 A44:C50 A295:B295 A296:C306 A327 A328:C344 A386:B386 A387:C389 A407:B407 A408:C411 A477:B477 A478:C479 A556:B557 A565:B565 A15:B15 A16:C19 A40:C42 A99:B99 A100:C106 A455:B456 A469:B469 A470:C472 A505:B505 A506:C506 A521:B522 A523:C530 A451:B452 A379:B379 A384:C385 A383:B383 A380:C382 A594:C596 A8:B8 A9:C12 A71 A128:B128 A129:C132 A154:B154 A155:C161 A58:B58 A59:C69 A107:B107 A108:C113 A229:B230 A231:C233 A250:B251 A252:C256 A260:B260 A261:C267 A268:B268 A269:C278 A281:C284 A402:B402 A403:C405 A425:B425 A432:B432 A433:C446 A447:B447 A448:C448 A466:C468 A507:B507 A510:C512 A509:B509 A508:C508 A517:B517 A518:C518 A539:C539 A550:B550 A551:C552 A449:B449 A450:C450 A580:B580 A582:C582 A2:B5 A13:B13 A14:C14 A424:C424 A453:C454 A501:C502 A513:B515 A576:B578 A614:B614 A531:B531 A532:C535 A519:B519 A520:C520 A480:B480 A481:C486 A150:B150 A151:C153 A503 A504:C504 A79:B79 A80:C84 A418:B419 A287:C294 A114:B114 A115:C119 A420:C420 A20:B20 A21:C22 A607:C607 A566 A567:C568 A573:C573 A6:C7 A257:B257 A258:C259 A619:C621 A377:B377 A378:C378 A162:B162 A163:C166 A70:B70 A72:C78 A51:B51 A52:C52 A345:B345 A346:C348 A553:B553 A554:C555 A93:B94 A516:C516 A457:C458 A53:B54 A307:B307 A308:C312 A579:C579 A28:B28 A29:C29 A558:C564 A55:C57 A540:B540 A541:C549 A145:B145 A146:C149 A95:C98 A234:B234 A235:C249 A616:C616 A459:B459 A460:C463 A574:B574 A575 A590:C590 A351:B351 A352:C352 A316:C326 A315:B315 A676:C676 A120:B120 A121:C127 A1:C1 A37:C37 A36:B36 A32:C35" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A677:C677 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A601:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3221FD7-93A5-42C9-BC9E-6521B02680AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -154,6 +160,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -164,7 +171,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Segoe UI Emoji"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>🍬</t>
     </r>
@@ -173,6 +180,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -2408,6 +2416,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -2418,7 +2427,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>♪</t>
     </r>
@@ -2897,6 +2906,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -2907,7 +2917,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>♪</t>
     </r>
@@ -2916,6 +2926,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -3559,9 +3570,6 @@
     <t>V.I.P MONSTER</t>
   </si>
   <si>
-    <t>vipm,vip m,千客万来</t>
-  </si>
-  <si>
     <t>Wreath of Brave</t>
   </si>
   <si>
@@ -3870,6 +3878,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -3880,6 +3889,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Yu Gothic"/>
+        <family val="2"/>
         <charset val="128"/>
       </rPr>
       <t>・とーくとぅゆー</t>
@@ -3924,6 +3934,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -3934,6 +3945,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Yu Gothic"/>
+        <family val="2"/>
         <charset val="128"/>
       </rPr>
       <t>・フォー</t>
@@ -3948,6 +3960,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -3958,6 +3971,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Yu Gothic"/>
+        <family val="2"/>
         <charset val="128"/>
       </rPr>
       <t>・ザ・フロントライン</t>
@@ -4050,7 +4064,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>♡</t>
     </r>
@@ -4059,6 +4073,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Yu Gothic"/>
+        <family val="2"/>
         <charset val="128"/>
       </rPr>
       <t>桃色片想い</t>
@@ -4068,7 +4083,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>♡</t>
     </r>
@@ -4192,19 +4207,17 @@
   </si>
   <si>
     <t>彩虹答辩</t>
+  </si>
+  <si>
+    <t>vipm,vip m,千客万来,千克万来</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4216,373 +4229,53 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -4590,312 +4283,27 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5217,22 +4625,22 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C678"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85" customWidth="1"/>
-    <col min="2" max="2" width="50.8083333333333" customWidth="1"/>
-    <col min="3" max="3" width="65.85" customWidth="1"/>
-    <col min="4" max="4" width="55.7333333333333" customWidth="1"/>
+    <col min="1" max="1" width="10.796875" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" customWidth="1"/>
+    <col min="3" max="3" width="65.796875" customWidth="1"/>
+    <col min="4" max="4" width="55.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5243,7 +4651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5254,7 +4662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5265,7 +4673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5276,7 +4684,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5287,7 +4695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5298,7 +4706,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -5309,7 +4717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -5320,7 +4728,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -5331,7 +4739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -5342,7 +4750,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -5353,7 +4761,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -5364,7 +4772,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -5375,7 +4783,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -5386,7 +4794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -5397,7 +4805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -5408,7 +4816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -5419,7 +4827,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -5430,7 +4838,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -5441,7 +4849,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" spans="1:3">
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>20</v>
       </c>
@@ -5452,7 +4860,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -5463,7 +4871,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -5474,7 +4882,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>24</v>
       </c>
@@ -5485,7 +4893,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25</v>
       </c>
@@ -5496,7 +4904,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26</v>
       </c>
@@ -5507,7 +4915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>27</v>
       </c>
@@ -5518,7 +4926,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
@@ -5529,7 +4937,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5540,7 +4948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5551,7 +4959,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5562,7 +4970,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5573,7 +4981,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5584,7 +4992,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5595,7 +5003,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5606,7 +5014,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5617,7 +5025,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5628,7 +5036,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5639,7 +5047,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5650,7 +5058,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5661,7 +5069,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5672,7 +5080,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5683,7 +5091,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5694,7 +5102,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5705,7 +5113,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5716,7 +5124,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5727,7 +5135,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5738,7 +5146,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5749,7 +5157,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5760,7 +5168,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5771,7 +5179,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5782,7 +5190,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5793,7 +5201,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5804,7 +5212,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5815,7 +5223,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5826,7 +5234,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5837,7 +5245,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5848,7 +5256,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5859,7 +5267,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5870,7 +5278,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5881,7 +5289,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5892,7 +5300,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5903,7 +5311,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5914,7 +5322,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5925,7 +5333,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5936,7 +5344,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5947,7 +5355,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5958,7 +5366,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5969,7 +5377,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5980,7 +5388,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5991,7 +5399,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>73</v>
       </c>
@@ -6002,7 +5410,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>74</v>
       </c>
@@ -6013,7 +5421,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>75</v>
       </c>
@@ -6024,7 +5432,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>76</v>
       </c>
@@ -6035,7 +5443,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>77</v>
       </c>
@@ -6046,7 +5454,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>78</v>
       </c>
@@ -6057,7 +5465,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>79</v>
       </c>
@@ -6068,7 +5476,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>80</v>
       </c>
@@ -6079,7 +5487,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>81</v>
       </c>
@@ -6090,7 +5498,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>82</v>
       </c>
@@ -6101,7 +5509,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>83</v>
       </c>
@@ -6112,7 +5520,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>84</v>
       </c>
@@ -6123,7 +5531,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>85</v>
       </c>
@@ -6134,7 +5542,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>86</v>
       </c>
@@ -6145,7 +5553,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>87</v>
       </c>
@@ -6156,7 +5564,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>88</v>
       </c>
@@ -6167,7 +5575,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>89</v>
       </c>
@@ -6178,7 +5586,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>90</v>
       </c>
@@ -6189,7 +5597,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>91</v>
       </c>
@@ -6200,7 +5608,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>92</v>
       </c>
@@ -6211,7 +5619,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>93</v>
       </c>
@@ -6222,7 +5630,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>94</v>
       </c>
@@ -6233,7 +5641,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>95</v>
       </c>
@@ -6244,7 +5652,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>96</v>
       </c>
@@ -6255,7 +5663,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>97</v>
       </c>
@@ -6266,7 +5674,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>100</v>
       </c>
@@ -6277,7 +5685,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>101</v>
       </c>
@@ -6288,7 +5696,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>104</v>
       </c>
@@ -6299,7 +5707,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>105</v>
       </c>
@@ -6310,7 +5718,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>106</v>
       </c>
@@ -6321,7 +5729,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>107</v>
       </c>
@@ -6332,7 +5740,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>108</v>
       </c>
@@ -6343,7 +5751,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>109</v>
       </c>
@@ -6354,7 +5762,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>110</v>
       </c>
@@ -6365,7 +5773,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>111</v>
       </c>
@@ -6376,7 +5784,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>112</v>
       </c>
@@ -6387,7 +5795,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>113</v>
       </c>
@@ -6398,7 +5806,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>115</v>
       </c>
@@ -6409,7 +5817,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>116</v>
       </c>
@@ -6420,7 +5828,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>117</v>
       </c>
@@ -6431,7 +5839,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>118</v>
       </c>
@@ -6442,7 +5850,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>119</v>
       </c>
@@ -6453,7 +5861,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>120</v>
       </c>
@@ -6464,7 +5872,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>121</v>
       </c>
@@ -6475,7 +5883,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>122</v>
       </c>
@@ -6486,7 +5894,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>123</v>
       </c>
@@ -6497,7 +5905,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>124</v>
       </c>
@@ -6508,7 +5916,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>125</v>
       </c>
@@ -6519,7 +5927,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126</v>
       </c>
@@ -6530,7 +5938,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6541,7 +5949,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6552,7 +5960,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6563,7 +5971,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6574,7 +5982,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6585,7 +5993,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6596,7 +6004,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6607,7 +6015,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6618,7 +6026,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6629,7 +6037,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6640,7 +6048,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6651,7 +6059,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6662,7 +6070,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6673,7 +6081,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6684,7 +6092,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6695,7 +6103,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6706,7 +6114,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6717,7 +6125,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6728,7 +6136,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6739,7 +6147,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6750,7 +6158,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6761,7 +6169,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6772,7 +6180,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6783,7 +6191,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6794,7 +6202,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6805,7 +6213,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6816,7 +6224,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6827,7 +6235,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6838,7 +6246,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6849,7 +6257,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6860,7 +6268,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6871,7 +6279,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6882,7 +6290,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6893,7 +6301,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6904,7 +6312,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6915,7 +6323,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6926,7 +6334,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6937,7 +6345,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6948,7 +6356,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6959,7 +6367,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6970,7 +6378,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6981,7 +6389,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6992,7 +6400,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>169</v>
       </c>
@@ -7003,7 +6411,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>170</v>
       </c>
@@ -7014,7 +6422,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>171</v>
       </c>
@@ -7025,7 +6433,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>172</v>
       </c>
@@ -7036,7 +6444,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>173</v>
       </c>
@@ -7047,7 +6455,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>174</v>
       </c>
@@ -7058,7 +6466,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>175</v>
       </c>
@@ -7069,7 +6477,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>176</v>
       </c>
@@ -7080,7 +6488,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>177</v>
       </c>
@@ -7091,7 +6499,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>178</v>
       </c>
@@ -7102,7 +6510,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>179</v>
       </c>
@@ -7113,7 +6521,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>180</v>
       </c>
@@ -7124,7 +6532,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>181</v>
       </c>
@@ -7135,7 +6543,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>182</v>
       </c>
@@ -7146,7 +6554,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>183</v>
       </c>
@@ -7157,7 +6565,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>184</v>
       </c>
@@ -7168,7 +6576,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>185</v>
       </c>
@@ -7179,7 +6587,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>186</v>
       </c>
@@ -7190,7 +6598,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>187</v>
       </c>
@@ -7201,7 +6609,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>188</v>
       </c>
@@ -7212,7 +6620,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>189</v>
       </c>
@@ -7223,7 +6631,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>190</v>
       </c>
@@ -7234,7 +6642,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>191</v>
       </c>
@@ -7245,7 +6653,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>192</v>
       </c>
@@ -7256,7 +6664,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>193</v>
       </c>
@@ -7267,7 +6675,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>194</v>
       </c>
@@ -7278,7 +6686,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>195</v>
       </c>
@@ -7289,7 +6697,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>196</v>
       </c>
@@ -7300,7 +6708,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>197</v>
       </c>
@@ -7311,7 +6719,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>198</v>
       </c>
@@ -7322,7 +6730,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>199</v>
       </c>
@@ -7333,7 +6741,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>200</v>
       </c>
@@ -7344,7 +6752,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>201</v>
       </c>
@@ -7355,7 +6763,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>202</v>
       </c>
@@ -7366,7 +6774,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>203</v>
       </c>
@@ -7377,7 +6785,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>204</v>
       </c>
@@ -7388,7 +6796,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>205</v>
       </c>
@@ -7399,7 +6807,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>206</v>
       </c>
@@ -7410,7 +6818,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>207</v>
       </c>
@@ -7421,7 +6829,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>208</v>
       </c>
@@ -7432,7 +6840,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>209</v>
       </c>
@@ -7443,7 +6851,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>210</v>
       </c>
@@ -7454,7 +6862,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="203" spans="1:3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>211</v>
       </c>
@@ -7465,7 +6873,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>212</v>
       </c>
@@ -7476,7 +6884,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>213</v>
       </c>
@@ -7487,7 +6895,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>214</v>
       </c>
@@ -7498,7 +6906,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>215</v>
       </c>
@@ -7509,7 +6917,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="208" spans="1:3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>217</v>
       </c>
@@ -7520,7 +6928,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>218</v>
       </c>
@@ -7531,7 +6939,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7542,7 +6950,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7553,7 +6961,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7564,7 +6972,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7575,7 +6983,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7586,7 +6994,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7597,7 +7005,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7608,7 +7016,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7619,7 +7027,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7630,7 +7038,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7641,7 +7049,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7652,7 +7060,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7663,7 +7071,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7674,7 +7082,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7685,7 +7093,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7696,7 +7104,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7707,7 +7115,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="226" spans="1:3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7718,7 +7126,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="227" spans="1:3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7729,7 +7137,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7740,7 +7148,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="229" spans="1:3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7751,7 +7159,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7762,7 +7170,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7773,7 +7181,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7784,7 +7192,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7795,7 +7203,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7806,7 +7214,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7817,7 +7225,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7828,7 +7236,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="237" spans="1:3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7839,7 +7247,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7850,7 +7258,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7861,7 +7269,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7872,7 +7280,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7883,7 +7291,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7894,7 +7302,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="243" spans="1:3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7905,7 +7313,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="244" spans="1:3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7916,7 +7324,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7927,7 +7335,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="246" spans="1:3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7938,7 +7346,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7949,7 +7357,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7960,7 +7368,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7971,7 +7379,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7982,7 +7390,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="251" spans="1:3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7993,7 +7401,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>261</v>
       </c>
@@ -8004,7 +7412,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>262</v>
       </c>
@@ -8015,7 +7423,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>263</v>
       </c>
@@ -8026,7 +7434,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>264</v>
       </c>
@@ -8037,7 +7445,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>265</v>
       </c>
@@ -8048,7 +7456,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>266</v>
       </c>
@@ -8059,7 +7467,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>267</v>
       </c>
@@ -8070,7 +7478,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>268</v>
       </c>
@@ -8081,7 +7489,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>269</v>
       </c>
@@ -8092,7 +7500,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>270</v>
       </c>
@@ -8103,7 +7511,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>271</v>
       </c>
@@ -8114,7 +7522,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>272</v>
       </c>
@@ -8125,7 +7533,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>274</v>
       </c>
@@ -8136,7 +7544,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="265" spans="1:3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>275</v>
       </c>
@@ -8147,7 +7555,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="266" spans="1:3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>276</v>
       </c>
@@ -8158,7 +7566,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>277</v>
       </c>
@@ -8169,7 +7577,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>278</v>
       </c>
@@ -8180,7 +7588,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>279</v>
       </c>
@@ -8191,7 +7599,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="270" spans="1:3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>280</v>
       </c>
@@ -8202,7 +7610,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>281</v>
       </c>
@@ -8213,7 +7621,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>282</v>
       </c>
@@ -8224,7 +7632,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>283</v>
       </c>
@@ -8235,7 +7643,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="274" spans="1:3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>284</v>
       </c>
@@ -8246,7 +7654,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>285</v>
       </c>
@@ -8257,7 +7665,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>286</v>
       </c>
@@ -8268,7 +7676,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>287</v>
       </c>
@@ -8279,7 +7687,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>288</v>
       </c>
@@ -8290,7 +7698,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>289</v>
       </c>
@@ -8301,7 +7709,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>290</v>
       </c>
@@ -8312,7 +7720,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>291</v>
       </c>
@@ -8323,7 +7731,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>292</v>
       </c>
@@ -8334,7 +7742,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>293</v>
       </c>
@@ -8345,7 +7753,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>294</v>
       </c>
@@ -8356,7 +7764,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>295</v>
       </c>
@@ -8367,7 +7775,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>296</v>
       </c>
@@ -8378,7 +7786,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>297</v>
       </c>
@@ -8389,7 +7797,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>298</v>
       </c>
@@ -8400,7 +7808,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>299</v>
       </c>
@@ -8411,7 +7819,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>300</v>
       </c>
@@ -8422,7 +7830,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>301</v>
       </c>
@@ -8433,7 +7841,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>302</v>
       </c>
@@ -8444,7 +7852,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="293" spans="1:3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>303</v>
       </c>
@@ -8455,7 +7863,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>304</v>
       </c>
@@ -8466,7 +7874,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="295" spans="1:3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>305</v>
       </c>
@@ -8477,7 +7885,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>306</v>
       </c>
@@ -8488,7 +7896,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>307</v>
       </c>
@@ -8499,7 +7907,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>308</v>
       </c>
@@ -8510,7 +7918,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>309</v>
       </c>
@@ -8521,7 +7929,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="300" spans="1:3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>310</v>
       </c>
@@ -8532,7 +7940,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="301" spans="1:3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>311</v>
       </c>
@@ -8543,7 +7951,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>312</v>
       </c>
@@ -8554,7 +7962,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>313</v>
       </c>
@@ -8565,7 +7973,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>314</v>
       </c>
@@ -8576,7 +7984,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>315</v>
       </c>
@@ -8587,7 +7995,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>316</v>
       </c>
@@ -8598,7 +8006,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>317</v>
       </c>
@@ -8609,7 +8017,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>318</v>
       </c>
@@ -8620,7 +8028,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="309" spans="1:3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>319</v>
       </c>
@@ -8631,7 +8039,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="310" spans="1:3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>320</v>
       </c>
@@ -8642,7 +8050,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>321</v>
       </c>
@@ -8653,7 +8061,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="312" spans="1:3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>322</v>
       </c>
@@ -8664,7 +8072,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="313" spans="1:3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>323</v>
       </c>
@@ -8675,7 +8083,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>324</v>
       </c>
@@ -8686,7 +8094,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>325</v>
       </c>
@@ -8697,7 +8105,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="316" spans="1:3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>326</v>
       </c>
@@ -8708,7 +8116,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="317" spans="1:3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>327</v>
       </c>
@@ -8719,7 +8127,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="318" spans="1:3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>328</v>
       </c>
@@ -8730,7 +8138,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="319" spans="1:3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>329</v>
       </c>
@@ -8741,7 +8149,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>330</v>
       </c>
@@ -8752,7 +8160,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>331</v>
       </c>
@@ -8763,7 +8171,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>332</v>
       </c>
@@ -8774,7 +8182,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>333</v>
       </c>
@@ -8785,7 +8193,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>334</v>
       </c>
@@ -8796,7 +8204,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>335</v>
       </c>
@@ -8807,7 +8215,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>336</v>
       </c>
@@ -8818,7 +8226,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>337</v>
       </c>
@@ -8829,7 +8237,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="328" spans="1:3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>338</v>
       </c>
@@ -8840,7 +8248,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>339</v>
       </c>
@@ -8851,7 +8259,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>340</v>
       </c>
@@ -8862,7 +8270,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>341</v>
       </c>
@@ -8873,7 +8281,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>342</v>
       </c>
@@ -8884,7 +8292,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>343</v>
       </c>
@@ -8895,7 +8303,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>344</v>
       </c>
@@ -8906,7 +8314,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>345</v>
       </c>
@@ -8917,7 +8325,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="336" spans="1:3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>346</v>
       </c>
@@ -8928,7 +8336,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>347</v>
       </c>
@@ -8939,7 +8347,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>348</v>
       </c>
@@ -8950,7 +8358,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>349</v>
       </c>
@@ -8961,7 +8369,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>350</v>
       </c>
@@ -8972,7 +8380,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>351</v>
       </c>
@@ -8983,7 +8391,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>352</v>
       </c>
@@ -8994,7 +8402,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>353</v>
       </c>
@@ -9005,7 +8413,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>354</v>
       </c>
@@ -9016,7 +8424,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>355</v>
       </c>
@@ -9027,7 +8435,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>356</v>
       </c>
@@ -9038,7 +8446,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>357</v>
       </c>
@@ -9049,7 +8457,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="348" spans="1:3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>358</v>
       </c>
@@ -9060,7 +8468,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>359</v>
       </c>
@@ -9071,7 +8479,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>360</v>
       </c>
@@ -9082,7 +8490,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>361</v>
       </c>
@@ -9093,7 +8501,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>362</v>
       </c>
@@ -9104,7 +8512,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="353" spans="1:3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>363</v>
       </c>
@@ -9115,7 +8523,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="354" spans="1:3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>364</v>
       </c>
@@ -9126,7 +8534,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>365</v>
       </c>
@@ -9137,7 +8545,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="356" spans="1:3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>366</v>
       </c>
@@ -9148,7 +8556,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>367</v>
       </c>
@@ -9159,7 +8567,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="358" spans="1:3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>368</v>
       </c>
@@ -9170,7 +8578,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="359" spans="1:3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>369</v>
       </c>
@@ -9181,7 +8589,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="360" spans="1:3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>370</v>
       </c>
@@ -9192,7 +8600,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="361" spans="1:3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>371</v>
       </c>
@@ -9203,7 +8611,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="362" spans="1:3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>372</v>
       </c>
@@ -9214,7 +8622,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="363" spans="1:3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>373</v>
       </c>
@@ -9225,7 +8633,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="364" spans="1:3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>374</v>
       </c>
@@ -9236,7 +8644,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="365" spans="1:3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>375</v>
       </c>
@@ -9247,7 +8655,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="366" spans="1:3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>376</v>
       </c>
@@ -9258,7 +8666,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>377</v>
       </c>
@@ -9269,7 +8677,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="368" spans="1:3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>378</v>
       </c>
@@ -9280,7 +8688,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>379</v>
       </c>
@@ -9291,7 +8699,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="370" spans="1:3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>380</v>
       </c>
@@ -9302,7 +8710,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>381</v>
       </c>
@@ -9313,7 +8721,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="372" spans="1:3">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>382</v>
       </c>
@@ -9324,7 +8732,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="373" spans="1:3">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>383</v>
       </c>
@@ -9335,7 +8743,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="374" spans="1:3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>384</v>
       </c>
@@ -9346,7 +8754,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="375" spans="1:3">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>385</v>
       </c>
@@ -9357,7 +8765,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="376" spans="1:3">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>386</v>
       </c>
@@ -9368,7 +8776,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="377" spans="1:3">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>387</v>
       </c>
@@ -9379,7 +8787,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>388</v>
       </c>
@@ -9390,7 +8798,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="379" spans="1:3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>389</v>
       </c>
@@ -9401,7 +8809,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="380" spans="1:3">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>390</v>
       </c>
@@ -9412,7 +8820,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="381" spans="1:3">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>391</v>
       </c>
@@ -9423,7 +8831,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="382" spans="1:3">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>392</v>
       </c>
@@ -9434,7 +8842,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="383" spans="1:3">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>393</v>
       </c>
@@ -9445,7 +8853,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="384" spans="1:3">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>394</v>
       </c>
@@ -9456,7 +8864,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="385" spans="1:3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>395</v>
       </c>
@@ -9467,7 +8875,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="386" spans="1:3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>396</v>
       </c>
@@ -9478,7 +8886,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="387" spans="1:3">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>397</v>
       </c>
@@ -9489,7 +8897,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="388" spans="1:3">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>398</v>
       </c>
@@ -9500,7 +8908,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="389" spans="1:3">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>399</v>
       </c>
@@ -9511,7 +8919,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="390" spans="1:3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>400</v>
       </c>
@@ -9522,7 +8930,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="391" spans="1:3">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>401</v>
       </c>
@@ -9533,7 +8941,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="392" ht="17.25" spans="1:3">
+    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>402</v>
       </c>
@@ -9544,7 +8952,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>403</v>
       </c>
@@ -9555,7 +8963,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="394" spans="1:3">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>404</v>
       </c>
@@ -9566,7 +8974,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="395" spans="1:3">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>405</v>
       </c>
@@ -9577,7 +8985,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="396" spans="1:3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>406</v>
       </c>
@@ -9588,7 +8996,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="397" spans="1:3">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>407</v>
       </c>
@@ -9599,7 +9007,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="398" spans="1:3">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>408</v>
       </c>
@@ -9610,7 +9018,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="399" spans="1:3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>409</v>
       </c>
@@ -9621,7 +9029,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="400" spans="1:3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>410</v>
       </c>
@@ -9632,7 +9040,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>411</v>
       </c>
@@ -9643,7 +9051,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>412</v>
       </c>
@@ -9654,7 +9062,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>413</v>
       </c>
@@ -9665,7 +9073,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="404" spans="1:3">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>414</v>
       </c>
@@ -9676,7 +9084,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>415</v>
       </c>
@@ -9687,7 +9095,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="406" spans="1:3">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>416</v>
       </c>
@@ -9698,7 +9106,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>417</v>
       </c>
@@ -9709,7 +9117,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>418</v>
       </c>
@@ -9720,7 +9128,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="409" spans="1:3">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>419</v>
       </c>
@@ -9731,7 +9139,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>420</v>
       </c>
@@ -9742,7 +9150,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="411" spans="1:3">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>421</v>
       </c>
@@ -9753,7 +9161,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="412" spans="1:3">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>422</v>
       </c>
@@ -9764,7 +9172,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>423</v>
       </c>
@@ -9775,7 +9183,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="414" spans="1:3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>424</v>
       </c>
@@ -9786,7 +9194,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="415" spans="1:3">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>425</v>
       </c>
@@ -9797,7 +9205,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="416" spans="1:3">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>426</v>
       </c>
@@ -9808,7 +9216,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="417" spans="1:3">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>427</v>
       </c>
@@ -9819,7 +9227,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="418" spans="1:3">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>428</v>
       </c>
@@ -9830,7 +9238,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="419" spans="1:3">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>429</v>
       </c>
@@ -9841,7 +9249,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="420" spans="1:3">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>430</v>
       </c>
@@ -9852,7 +9260,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="421" spans="1:3">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>431</v>
       </c>
@@ -9863,7 +9271,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="422" spans="1:3">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>432</v>
       </c>
@@ -9874,7 +9282,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="423" spans="1:3">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>433</v>
       </c>
@@ -9885,7 +9293,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="424" spans="1:3">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>434</v>
       </c>
@@ -9896,7 +9304,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="425" spans="1:3">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>435</v>
       </c>
@@ -9907,7 +9315,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="426" spans="1:3">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>436</v>
       </c>
@@ -9918,7 +9326,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="427" spans="1:3">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>437</v>
       </c>
@@ -9929,7 +9337,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="428" spans="1:3">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>438</v>
       </c>
@@ -9940,7 +9348,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="429" spans="1:3">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>439</v>
       </c>
@@ -9951,7 +9359,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="430" spans="1:3">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>440</v>
       </c>
@@ -9962,7 +9370,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="431" spans="1:3">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>441</v>
       </c>
@@ -9973,7 +9381,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="432" spans="1:3">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>442</v>
       </c>
@@ -9984,7 +9392,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="433" spans="1:3">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>443</v>
       </c>
@@ -9995,7 +9403,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="434" spans="1:3">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>444</v>
       </c>
@@ -10006,7 +9414,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="435" spans="1:3">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>445</v>
       </c>
@@ -10017,7 +9425,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="436" spans="1:3">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>446</v>
       </c>
@@ -10028,7 +9436,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="437" spans="1:3">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>447</v>
       </c>
@@ -10039,7 +9447,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="438" spans="1:3">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>448</v>
       </c>
@@ -10050,7 +9458,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="439" spans="1:3">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>449</v>
       </c>
@@ -10061,7 +9469,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="440" spans="1:3">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>450</v>
       </c>
@@ -10072,7 +9480,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="441" spans="1:3">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>451</v>
       </c>
@@ -10083,7 +9491,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="442" spans="1:3">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>452</v>
       </c>
@@ -10094,7 +9502,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="443" spans="1:3">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>453</v>
       </c>
@@ -10105,7 +9513,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="444" spans="1:3">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>455</v>
       </c>
@@ -10116,7 +9524,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="445" spans="1:3">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>456</v>
       </c>
@@ -10127,7 +9535,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="446" spans="1:3">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>457</v>
       </c>
@@ -10138,7 +9546,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="447" spans="1:3">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>458</v>
       </c>
@@ -10149,7 +9557,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="448" spans="1:3">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>459</v>
       </c>
@@ -10160,7 +9568,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>460</v>
       </c>
@@ -10171,7 +9579,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="450" spans="1:3">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>461</v>
       </c>
@@ -10182,7 +9590,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>462</v>
       </c>
@@ -10193,7 +9601,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>463</v>
       </c>
@@ -10204,7 +9612,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>464</v>
       </c>
@@ -10215,7 +9623,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="454" spans="1:3">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>465</v>
       </c>
@@ -10226,7 +9634,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="455" spans="1:3">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>466</v>
       </c>
@@ -10237,7 +9645,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="456" spans="1:3">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>467</v>
       </c>
@@ -10248,7 +9656,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="457" spans="1:3">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>468</v>
       </c>
@@ -10259,7 +9667,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="458" spans="1:3">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>469</v>
       </c>
@@ -10270,7 +9678,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="459" spans="1:3">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>470</v>
       </c>
@@ -10281,7 +9689,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="460" spans="1:3">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>471</v>
       </c>
@@ -10289,7 +9697,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="461" spans="1:3">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>472</v>
       </c>
@@ -10300,7 +9708,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="462" spans="1:3">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>473</v>
       </c>
@@ -10311,7 +9719,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="463" spans="1:3">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>474</v>
       </c>
@@ -10322,7 +9730,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="464" spans="1:3">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>475</v>
       </c>
@@ -10333,7 +9741,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="465" spans="1:3">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>476</v>
       </c>
@@ -10344,7 +9752,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="466" spans="1:3">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>477</v>
       </c>
@@ -10355,7 +9763,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="467" spans="1:3">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>478</v>
       </c>
@@ -10366,7 +9774,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="468" spans="1:3">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>479</v>
       </c>
@@ -10377,7 +9785,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="469" spans="1:3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>480</v>
       </c>
@@ -10388,7 +9796,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="470" spans="1:3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>481</v>
       </c>
@@ -10399,7 +9807,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="471" spans="1:3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>482</v>
       </c>
@@ -10410,7 +9818,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="472" spans="1:3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>483</v>
       </c>
@@ -10421,7 +9829,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="473" ht="17.25" spans="1:3">
+    <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A473">
         <v>484</v>
       </c>
@@ -10432,7 +9840,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>485</v>
       </c>
@@ -10443,7 +9851,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="475" spans="1:3">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>486</v>
       </c>
@@ -10454,7 +9862,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="476" spans="1:3">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>487</v>
       </c>
@@ -10465,7 +9873,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="477" spans="1:3">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>488</v>
       </c>
@@ -10476,7 +9884,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="478" spans="1:3">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>489</v>
       </c>
@@ -10487,7 +9895,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="479" spans="1:3">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>490</v>
       </c>
@@ -10498,7 +9906,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="480" spans="1:3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>491</v>
       </c>
@@ -10509,7 +9917,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="481" spans="1:3">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>492</v>
       </c>
@@ -10520,7 +9928,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="482" spans="1:3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>493</v>
       </c>
@@ -10531,7 +9939,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="483" spans="1:3">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>494</v>
       </c>
@@ -10542,7 +9950,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="484" spans="1:3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>496</v>
       </c>
@@ -10553,7 +9961,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="485" spans="1:3">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>497</v>
       </c>
@@ -10564,7 +9972,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="486" spans="1:3">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>498</v>
       </c>
@@ -10575,7 +9983,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>499</v>
       </c>
@@ -10586,7 +9994,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="488" spans="1:3">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>500</v>
       </c>
@@ -10597,7 +10005,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="489" spans="1:3">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>501</v>
       </c>
@@ -10608,7 +10016,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="490" spans="1:3">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>502</v>
       </c>
@@ -10619,7 +10027,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="491" spans="1:3">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>503</v>
       </c>
@@ -10630,7 +10038,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="492" spans="1:3">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>504</v>
       </c>
@@ -10641,7 +10049,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="493" spans="1:3">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>505</v>
       </c>
@@ -10652,7 +10060,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="494" spans="1:3">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>506</v>
       </c>
@@ -10663,7 +10071,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="495" spans="1:3">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>507</v>
       </c>
@@ -10674,7 +10082,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="496" spans="1:3">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>508</v>
       </c>
@@ -10685,7 +10093,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="497" spans="1:3">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>509</v>
       </c>
@@ -10696,7 +10104,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="498" spans="1:3">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>510</v>
       </c>
@@ -10707,7 +10115,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="499" spans="1:3">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>511</v>
       </c>
@@ -10715,7 +10123,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="500" spans="1:3">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>512</v>
       </c>
@@ -10726,7 +10134,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="501" spans="1:3">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>513</v>
       </c>
@@ -10737,7 +10145,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="502" spans="1:3">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>514</v>
       </c>
@@ -10748,7 +10156,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="503" spans="1:3">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>515</v>
       </c>
@@ -10759,7 +10167,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="504" spans="1:3">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>516</v>
       </c>
@@ -10770,7 +10178,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="505" spans="1:3">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>517</v>
       </c>
@@ -10781,7 +10189,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="506" spans="1:3">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>518</v>
       </c>
@@ -10792,7 +10200,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="507" spans="1:3">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>519</v>
       </c>
@@ -10803,7 +10211,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="508" spans="1:3">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>520</v>
       </c>
@@ -10814,7 +10222,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="509" spans="1:3">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>521</v>
       </c>
@@ -10825,7 +10233,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="510" spans="1:3">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>522</v>
       </c>
@@ -10836,7 +10244,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="511" spans="1:3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>523</v>
       </c>
@@ -10847,7 +10255,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="512" spans="1:3">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>524</v>
       </c>
@@ -10858,7 +10266,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="513" spans="1:3">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>525</v>
       </c>
@@ -10869,7 +10277,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="514" spans="1:3">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>526</v>
       </c>
@@ -10880,7 +10288,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="515" spans="1:3">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>527</v>
       </c>
@@ -10891,7 +10299,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="516" spans="1:3">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>528</v>
       </c>
@@ -10902,7 +10310,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="517" spans="1:3">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>529</v>
       </c>
@@ -10913,7 +10321,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="518" spans="1:3">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>530</v>
       </c>
@@ -10921,7 +10329,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="519" spans="1:3">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>531</v>
       </c>
@@ -10932,7 +10340,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="520" spans="1:3">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>532</v>
       </c>
@@ -10943,7 +10351,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="521" spans="1:3">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>533</v>
       </c>
@@ -10954,7 +10362,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="522" spans="1:3">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>534</v>
       </c>
@@ -10965,7 +10373,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="523" spans="1:3">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>535</v>
       </c>
@@ -10976,7 +10384,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="524" spans="1:3">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>536</v>
       </c>
@@ -10987,7 +10395,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="525" spans="1:3">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>537</v>
       </c>
@@ -10998,7 +10406,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="526" spans="1:3">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>538</v>
       </c>
@@ -11009,7 +10417,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="527" spans="1:3">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>539</v>
       </c>
@@ -11020,7 +10428,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="528" spans="1:3">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>540</v>
       </c>
@@ -11031,7 +10439,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="529" spans="1:3">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>542</v>
       </c>
@@ -11042,7 +10450,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="530" spans="1:3">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>543</v>
       </c>
@@ -11053,7 +10461,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="531" spans="1:3">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>545</v>
       </c>
@@ -11064,7 +10472,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="532" spans="1:3">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>546</v>
       </c>
@@ -11075,7 +10483,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="533" spans="1:3">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>547</v>
       </c>
@@ -11086,7 +10494,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="534" spans="1:3">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>548</v>
       </c>
@@ -11097,7 +10505,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="535" spans="1:3">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>549</v>
       </c>
@@ -11108,7 +10516,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="536" spans="1:3">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>550</v>
       </c>
@@ -11119,7 +10527,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="537" spans="1:3">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>551</v>
       </c>
@@ -11130,7 +10538,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="538" spans="1:3">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>552</v>
       </c>
@@ -11141,7 +10549,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="539" spans="1:3">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>553</v>
       </c>
@@ -11152,7 +10560,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="540" spans="1:3">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>554</v>
       </c>
@@ -11163,7 +10571,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="541" spans="1:3">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>555</v>
       </c>
@@ -11174,7 +10582,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="542" spans="1:3">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>556</v>
       </c>
@@ -11185,7 +10593,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="543" spans="1:3">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>557</v>
       </c>
@@ -11196,7 +10604,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="544" spans="1:3">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>558</v>
       </c>
@@ -11207,7 +10615,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="545" spans="1:3">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>559</v>
       </c>
@@ -11218,7 +10626,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="546" spans="1:3">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>562</v>
       </c>
@@ -11229,7 +10637,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="547" spans="1:3">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>563</v>
       </c>
@@ -11237,7 +10645,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="548" spans="1:3">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>564</v>
       </c>
@@ -11248,7 +10656,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="549" spans="1:3">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>565</v>
       </c>
@@ -11259,7 +10667,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="550" spans="1:3">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>566</v>
       </c>
@@ -11270,7 +10678,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="551" spans="1:3">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>567</v>
       </c>
@@ -11281,7 +10689,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="552" spans="1:3">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>568</v>
       </c>
@@ -11292,7 +10700,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="553" spans="1:3">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>569</v>
       </c>
@@ -11303,7 +10711,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="554" spans="1:3">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>570</v>
       </c>
@@ -11314,7 +10722,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="555" spans="1:3">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>571</v>
       </c>
@@ -11325,7 +10733,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="556" spans="1:3">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>572</v>
       </c>
@@ -11336,7 +10744,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="557" spans="1:3">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>577</v>
       </c>
@@ -11347,7 +10755,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="558" spans="1:3">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>578</v>
       </c>
@@ -11358,7 +10766,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="559" spans="1:3">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>579</v>
       </c>
@@ -11366,7 +10774,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="560" spans="1:3">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>580</v>
       </c>
@@ -11377,7 +10785,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="561" spans="1:3">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>581</v>
       </c>
@@ -11388,7 +10796,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="562" spans="1:3">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>582</v>
       </c>
@@ -11399,7 +10807,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="563" spans="1:3">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>583</v>
       </c>
@@ -11410,7 +10818,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="564" spans="1:3">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>584</v>
       </c>
@@ -11421,7 +10829,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="565" spans="1:3">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>585</v>
       </c>
@@ -11432,7 +10840,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="566" spans="1:3">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>586</v>
       </c>
@@ -11443,7 +10851,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="567" spans="1:3">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>587</v>
       </c>
@@ -11454,7 +10862,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="568" spans="1:3">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>588</v>
       </c>
@@ -11465,7 +10873,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="569" spans="1:3">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>589</v>
       </c>
@@ -11476,7 +10884,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="570" spans="1:3">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>590</v>
       </c>
@@ -11487,7 +10895,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="571" spans="1:3">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>591</v>
       </c>
@@ -11498,7 +10906,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="572" spans="1:3">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>592</v>
       </c>
@@ -11509,7 +10917,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="573" spans="1:3">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>593</v>
       </c>
@@ -11520,7 +10928,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="574" spans="1:3">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>594</v>
       </c>
@@ -11531,7 +10939,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="575" spans="1:3">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>595</v>
       </c>
@@ -11542,7 +10950,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="576" spans="1:3">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>596</v>
       </c>
@@ -11553,7 +10961,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="577" spans="1:3">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>597</v>
       </c>
@@ -11564,7 +10972,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="578" spans="1:3">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>598</v>
       </c>
@@ -11575,7 +10983,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="579" spans="1:3">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>599</v>
       </c>
@@ -11586,7 +10994,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="580" spans="1:3">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>601</v>
       </c>
@@ -11597,7 +11005,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="581" spans="1:3">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>602</v>
       </c>
@@ -11608,7 +11016,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="582" spans="1:3">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>604</v>
       </c>
@@ -11619,1056 +11027,1056 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="583" spans="1:3">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>606</v>
       </c>
       <c r="B583" t="s">
         <v>1151</v>
       </c>
-      <c r="C583" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3">
+      <c r="C583" s="3" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>612</v>
       </c>
       <c r="B584" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C584" t="s">
         <v>1153</v>
       </c>
-      <c r="C584" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3">
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>615</v>
       </c>
       <c r="B585" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C585" t="s">
         <v>1155</v>
       </c>
-      <c r="C585" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3">
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>617</v>
       </c>
       <c r="B586" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C586" t="s">
         <v>1157</v>
       </c>
-      <c r="C586" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3">
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>618</v>
       </c>
       <c r="B587" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C587" t="s">
         <v>1159</v>
       </c>
-      <c r="C587" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3">
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>625</v>
       </c>
       <c r="B588" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C588" t="s">
         <v>1161</v>
       </c>
-      <c r="C588" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3">
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>624</v>
       </c>
       <c r="B589" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C589" t="s">
         <v>1163</v>
       </c>
-      <c r="C589" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3">
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>626</v>
       </c>
       <c r="B590" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C590" t="s">
         <v>1165</v>
       </c>
-      <c r="C590" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3">
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>629</v>
       </c>
       <c r="B591" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C591" t="s">
         <v>1167</v>
       </c>
-      <c r="C591" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3">
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>630</v>
       </c>
       <c r="B592" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C592" t="s">
         <v>1169</v>
       </c>
-      <c r="C592" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3">
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>633</v>
       </c>
       <c r="B594" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C594" t="s">
         <v>1172</v>
       </c>
-      <c r="C594" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3">
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>635</v>
       </c>
       <c r="B595" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C595" t="s">
         <v>1174</v>
       </c>
-      <c r="C595" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3">
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>636</v>
       </c>
       <c r="B596" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C596" t="s">
         <v>1176</v>
       </c>
-      <c r="C596" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3">
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>642</v>
       </c>
       <c r="B597" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C597" t="s">
         <v>1178</v>
       </c>
-      <c r="C597" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3">
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>644</v>
       </c>
       <c r="B598" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C598" t="s">
         <v>1180</v>
       </c>
-      <c r="C598" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3">
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>646</v>
       </c>
       <c r="B599" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C599" t="s">
         <v>1182</v>
       </c>
-      <c r="C599" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3">
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>649</v>
       </c>
       <c r="B600" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C600" t="s">
         <v>1184</v>
       </c>
-      <c r="C600" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3">
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>650</v>
       </c>
       <c r="B601" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C601" t="s">
         <v>1186</v>
       </c>
-      <c r="C601" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3">
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>651</v>
       </c>
       <c r="B602" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C602" t="s">
         <v>1188</v>
       </c>
-      <c r="C602" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3">
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>653</v>
       </c>
       <c r="B603" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C603" t="s">
         <v>1190</v>
       </c>
-      <c r="C603" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3">
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>654</v>
       </c>
       <c r="B604" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C604" t="s">
         <v>1192</v>
       </c>
-      <c r="C604" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3">
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>655</v>
       </c>
       <c r="B605" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C605" t="s">
         <v>1194</v>
       </c>
-      <c r="C605" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3">
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>659</v>
       </c>
       <c r="B606" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C606" t="s">
         <v>1196</v>
       </c>
-      <c r="C606" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3">
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>660</v>
       </c>
       <c r="B607" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C607" t="s">
         <v>1198</v>
       </c>
-      <c r="C607" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3">
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>661</v>
       </c>
       <c r="B608" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C608" t="s">
         <v>1200</v>
       </c>
-      <c r="C608" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3">
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>663</v>
       </c>
       <c r="B609" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C609" t="s">
         <v>1202</v>
       </c>
-      <c r="C609" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3">
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>667</v>
       </c>
       <c r="B610" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C610" t="s">
         <v>1204</v>
       </c>
-      <c r="C610" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3">
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>670</v>
       </c>
       <c r="B611" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C611" t="s">
         <v>1206</v>
       </c>
-      <c r="C611" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3">
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>673</v>
       </c>
       <c r="B612" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C612" t="s">
         <v>1208</v>
       </c>
-      <c r="C612" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3">
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>674</v>
       </c>
       <c r="B613" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C613" t="s">
         <v>1210</v>
       </c>
-      <c r="C613" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3">
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>675</v>
       </c>
       <c r="B614" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C614" t="s">
         <v>1212</v>
       </c>
-      <c r="C614" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3">
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>680</v>
       </c>
       <c r="B615" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C615" t="s">
         <v>1214</v>
       </c>
-      <c r="C615" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3">
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>681</v>
       </c>
       <c r="B616" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C616" t="s">
         <v>1216</v>
       </c>
-      <c r="C616" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3">
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>682</v>
       </c>
       <c r="B617" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C617" t="s">
         <v>1218</v>
       </c>
-      <c r="C617" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3">
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>683</v>
       </c>
       <c r="B618" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C618" t="s">
         <v>1220</v>
       </c>
-      <c r="C618" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3">
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>684</v>
       </c>
       <c r="B619" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C619" t="s">
         <v>1222</v>
       </c>
-      <c r="C619" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3">
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>685</v>
       </c>
       <c r="B620" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C620" t="s">
         <v>1224</v>
       </c>
-      <c r="C620" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3">
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>686</v>
       </c>
       <c r="B621" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C621" t="s">
         <v>1226</v>
       </c>
-      <c r="C621" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3">
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>689</v>
       </c>
       <c r="B622" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C622" t="s">
         <v>1228</v>
       </c>
-      <c r="C622" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3">
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>697</v>
       </c>
       <c r="B623" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C623" t="s">
         <v>1230</v>
       </c>
-      <c r="C623" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3">
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>701</v>
       </c>
       <c r="B624" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C624" t="s">
         <v>1232</v>
       </c>
-      <c r="C624" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3">
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>702</v>
       </c>
       <c r="B625" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C625" t="s">
         <v>1234</v>
       </c>
-      <c r="C625" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3">
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>704</v>
       </c>
       <c r="B626" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C626" t="s">
         <v>1236</v>
       </c>
-      <c r="C626" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3">
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>705</v>
       </c>
       <c r="B627" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C627" t="s">
         <v>1238</v>
       </c>
-      <c r="C627" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3">
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>710</v>
       </c>
       <c r="B628" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C628" t="s">
         <v>1240</v>
       </c>
-      <c r="C628" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3">
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>711</v>
       </c>
       <c r="B629" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C629" t="s">
         <v>1242</v>
       </c>
-      <c r="C629" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3">
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>712</v>
       </c>
       <c r="B630" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C630" t="s">
         <v>1244</v>
       </c>
-      <c r="C630" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3">
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>714</v>
       </c>
       <c r="B631" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C631" t="s">
         <v>1246</v>
       </c>
-      <c r="C631" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3">
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>717</v>
       </c>
       <c r="B632" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C632" t="s">
         <v>1248</v>
       </c>
-      <c r="C632" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3">
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>718</v>
       </c>
       <c r="B633" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C633" t="s">
         <v>1250</v>
       </c>
-      <c r="C633" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3">
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>719</v>
       </c>
       <c r="B634" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C634" t="s">
         <v>1252</v>
       </c>
-      <c r="C634" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="635" ht="19.5" spans="1:3">
+    </row>
+    <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A635">
         <v>721</v>
       </c>
       <c r="B635" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C635" t="s">
         <v>1254</v>
       </c>
-      <c r="C635" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3">
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>722</v>
       </c>
       <c r="B636" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C636" t="s">
         <v>1256</v>
       </c>
-      <c r="C636" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3">
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>723</v>
       </c>
       <c r="B637" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C637" t="s">
         <v>1258</v>
       </c>
-      <c r="C637" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3">
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>725</v>
       </c>
       <c r="B638" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C638" t="s">
         <v>1260</v>
       </c>
-      <c r="C638" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3">
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>726</v>
       </c>
       <c r="B639" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C639" t="s">
         <v>1262</v>
       </c>
-      <c r="C639" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3">
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>727</v>
       </c>
       <c r="B640" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C640" t="s">
         <v>1264</v>
       </c>
-      <c r="C640" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="641" ht="19.5" spans="1:3">
+    </row>
+    <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A641">
         <v>728</v>
       </c>
       <c r="B641" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C641" t="s">
         <v>1266</v>
       </c>
-      <c r="C641" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="642" ht="19.5" spans="1:3">
+    </row>
+    <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A642">
         <v>729</v>
       </c>
       <c r="B642" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C642" t="s">
         <v>1268</v>
       </c>
-      <c r="C642" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3">
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>730</v>
       </c>
       <c r="B643" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C643" t="s">
         <v>1270</v>
       </c>
-      <c r="C643" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3">
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>731</v>
       </c>
       <c r="B644" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C644" t="s">
         <v>1272</v>
       </c>
-      <c r="C644" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3">
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>733</v>
       </c>
       <c r="B645" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C645" t="s">
         <v>1274</v>
       </c>
-      <c r="C645" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3">
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>735</v>
       </c>
       <c r="B646" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C646" t="s">
         <v>1276</v>
       </c>
-      <c r="C646" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3">
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>736</v>
       </c>
       <c r="B647" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C647" t="s">
         <v>1278</v>
       </c>
-      <c r="C647" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3">
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>737</v>
       </c>
       <c r="B648" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C648" t="s">
         <v>1280</v>
       </c>
-      <c r="C648" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3">
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>738</v>
       </c>
       <c r="B649" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C649" t="s">
         <v>1282</v>
       </c>
-      <c r="C649" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3">
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>739</v>
       </c>
       <c r="B650" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C650" t="s">
         <v>1284</v>
       </c>
-      <c r="C650" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3">
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>740</v>
       </c>
       <c r="B651" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C651" t="s">
         <v>1286</v>
       </c>
-      <c r="C651" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3">
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>741</v>
       </c>
       <c r="B652" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C652" t="s">
         <v>1288</v>
       </c>
-      <c r="C652" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3">
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>742</v>
       </c>
       <c r="B653" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C653" t="s">
         <v>1290</v>
       </c>
-      <c r="C653" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3">
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>743</v>
       </c>
       <c r="B654" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C654" t="s">
         <v>1292</v>
       </c>
-      <c r="C654" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3">
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>744</v>
       </c>
       <c r="B655" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C655" t="s">
         <v>1294</v>
       </c>
-      <c r="C655" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="656" ht="19.5" spans="1:3">
+    </row>
+    <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
       <c r="A656">
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C656" t="s">
         <v>1296</v>
       </c>
-      <c r="C656" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3">
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C657" t="s">
         <v>1298</v>
       </c>
-      <c r="C657" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3">
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C658" t="s">
         <v>1300</v>
       </c>
-      <c r="C658" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3">
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C659" t="s">
         <v>1302</v>
       </c>
-      <c r="C659" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3">
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C660" t="s">
         <v>1304</v>
       </c>
-      <c r="C660" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3">
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C661" t="s">
         <v>1306</v>
       </c>
-      <c r="C661" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3">
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C662" t="s">
         <v>1308</v>
       </c>
-      <c r="C662" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3">
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C663" t="s">
         <v>1310</v>
       </c>
-      <c r="C663" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3">
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C664" t="s">
         <v>1312</v>
       </c>
-      <c r="C664" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3">
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C665" t="s">
         <v>1314</v>
       </c>
-      <c r="C665" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3">
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C666" t="s">
         <v>1316</v>
       </c>
-      <c r="C666" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3">
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C667" t="s">
         <v>1318</v>
       </c>
-      <c r="C667" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3">
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C668" t="s">
         <v>1320</v>
       </c>
-      <c r="C668" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3">
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C669" t="s">
         <v>1322</v>
       </c>
-      <c r="C669" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3">
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C670" t="s">
         <v>1324</v>
       </c>
-      <c r="C670" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3">
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671">
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C671" t="s">
         <v>1326</v>
       </c>
-      <c r="C671" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3">
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672">
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C672" t="s">
         <v>1328</v>
       </c>
-      <c r="C672" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3">
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673">
         <v>766</v>
       </c>
       <c r="B673" s="1"/>
     </row>
-    <row r="674" spans="1:3">
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674">
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C674" t="s">
         <v>1330</v>
       </c>
-      <c r="C674" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="675" spans="1:3">
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675">
         <v>768</v>
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="676" spans="1:3">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676">
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C676" t="s">
         <v>1333</v>
       </c>
-      <c r="C676" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="677" spans="1:3">
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677">
         <v>10001</v>
       </c>
       <c r="B677" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C677" t="s">
         <v>1335</v>
       </c>
-      <c r="C677" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="678" spans="1:3">
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678">
         <v>10003</v>
       </c>
       <c r="B678" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C678" t="s">
         <v>1333</v>
       </c>
-      <c r="C678" t="s">
-        <v>1334</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
   <ignoredErrors>
     <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A677:C677 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A601:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431" numberStoredAsText="1"/>
   </ignoredErrors>

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3221FD7-93A5-42C9-BC9E-6521B02680AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0456590A-F04F-480C-AF48-3C0D1A3A3457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3528,9 +3528,6 @@
     <t>「僕は...」</t>
   </si>
   <si>
-    <t>剥裤袜,僕は,bkw,bokuwa,我心危,我里危险</t>
-  </si>
-  <si>
     <t>[超高難易度 新SPECIAL] SENSENFUKOKU</t>
   </si>
   <si>
@@ -4210,6 +4207,10 @@
   </si>
   <si>
     <t>vipm,vip m,千客万来,千克万来</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>剥裤袜,僕は,bkw,bokuwa,我心危,我里危险,扎聋耳朵</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -10946,8 +10947,8 @@
       <c r="B575" t="s">
         <v>1137</v>
       </c>
-      <c r="C575" t="s">
-        <v>1138</v>
+      <c r="C575" s="3" t="s">
+        <v>1336</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -10955,10 +10956,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C576" t="s">
         <v>1139</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -10969,7 +10970,7 @@
         <v>943</v>
       </c>
       <c r="C577" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -10980,7 +10981,7 @@
         <v>945</v>
       </c>
       <c r="C578" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -10988,10 +10989,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C579" t="s">
         <v>1143</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -10999,10 +11000,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C580" t="s">
         <v>1145</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11010,10 +11011,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C581" t="s">
         <v>1147</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11021,10 +11022,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C582" t="s">
         <v>1149</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11032,10 +11033,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11043,10 +11044,10 @@
         <v>612</v>
       </c>
       <c r="B584" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C584" t="s">
         <v>1152</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11054,10 +11055,10 @@
         <v>615</v>
       </c>
       <c r="B585" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C585" t="s">
         <v>1154</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11065,10 +11066,10 @@
         <v>617</v>
       </c>
       <c r="B586" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C586" t="s">
         <v>1156</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11076,10 +11077,10 @@
         <v>618</v>
       </c>
       <c r="B587" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C587" t="s">
         <v>1158</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11087,10 +11088,10 @@
         <v>625</v>
       </c>
       <c r="B588" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C588" t="s">
         <v>1160</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11098,10 +11099,10 @@
         <v>624</v>
       </c>
       <c r="B589" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C589" t="s">
         <v>1162</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11109,10 +11110,10 @@
         <v>626</v>
       </c>
       <c r="B590" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C590" t="s">
         <v>1164</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11120,10 +11121,10 @@
         <v>629</v>
       </c>
       <c r="B591" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C591" t="s">
         <v>1166</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11131,10 +11132,10 @@
         <v>630</v>
       </c>
       <c r="B592" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C592" t="s">
         <v>1168</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11142,7 +11143,7 @@
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11150,10 +11151,10 @@
         <v>633</v>
       </c>
       <c r="B594" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C594" t="s">
         <v>1171</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11161,10 +11162,10 @@
         <v>635</v>
       </c>
       <c r="B595" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C595" t="s">
         <v>1173</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11172,10 +11173,10 @@
         <v>636</v>
       </c>
       <c r="B596" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C596" t="s">
         <v>1175</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11183,10 +11184,10 @@
         <v>642</v>
       </c>
       <c r="B597" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C597" t="s">
         <v>1177</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11194,10 +11195,10 @@
         <v>644</v>
       </c>
       <c r="B598" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C598" t="s">
         <v>1179</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11205,10 +11206,10 @@
         <v>646</v>
       </c>
       <c r="B599" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C599" t="s">
         <v>1181</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11216,10 +11217,10 @@
         <v>649</v>
       </c>
       <c r="B600" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C600" t="s">
         <v>1183</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11227,10 +11228,10 @@
         <v>650</v>
       </c>
       <c r="B601" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C601" t="s">
         <v>1185</v>
-      </c>
-      <c r="C601" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11238,10 +11239,10 @@
         <v>651</v>
       </c>
       <c r="B602" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C602" t="s">
         <v>1187</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11249,10 +11250,10 @@
         <v>653</v>
       </c>
       <c r="B603" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C603" t="s">
         <v>1189</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11260,10 +11261,10 @@
         <v>654</v>
       </c>
       <c r="B604" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C604" t="s">
         <v>1191</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11271,10 +11272,10 @@
         <v>655</v>
       </c>
       <c r="B605" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C605" t="s">
         <v>1193</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11282,10 +11283,10 @@
         <v>659</v>
       </c>
       <c r="B606" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C606" t="s">
         <v>1195</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11293,10 +11294,10 @@
         <v>660</v>
       </c>
       <c r="B607" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C607" t="s">
         <v>1197</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11304,10 +11305,10 @@
         <v>661</v>
       </c>
       <c r="B608" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C608" t="s">
         <v>1199</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11315,10 +11316,10 @@
         <v>663</v>
       </c>
       <c r="B609" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C609" t="s">
         <v>1201</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11326,10 +11327,10 @@
         <v>667</v>
       </c>
       <c r="B610" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C610" t="s">
         <v>1203</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11337,10 +11338,10 @@
         <v>670</v>
       </c>
       <c r="B611" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C611" t="s">
         <v>1205</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11348,10 +11349,10 @@
         <v>673</v>
       </c>
       <c r="B612" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C612" t="s">
         <v>1207</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11359,10 +11360,10 @@
         <v>674</v>
       </c>
       <c r="B613" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C613" t="s">
         <v>1209</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11370,10 +11371,10 @@
         <v>675</v>
       </c>
       <c r="B614" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C614" t="s">
         <v>1211</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11381,10 +11382,10 @@
         <v>680</v>
       </c>
       <c r="B615" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C615" t="s">
         <v>1213</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11392,10 +11393,10 @@
         <v>681</v>
       </c>
       <c r="B616" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C616" t="s">
         <v>1215</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11403,10 +11404,10 @@
         <v>682</v>
       </c>
       <c r="B617" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C617" t="s">
         <v>1217</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11414,10 +11415,10 @@
         <v>683</v>
       </c>
       <c r="B618" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C618" t="s">
         <v>1219</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11425,10 +11426,10 @@
         <v>684</v>
       </c>
       <c r="B619" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C619" t="s">
         <v>1221</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11436,10 +11437,10 @@
         <v>685</v>
       </c>
       <c r="B620" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C620" t="s">
         <v>1223</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11447,10 +11448,10 @@
         <v>686</v>
       </c>
       <c r="B621" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C621" t="s">
         <v>1225</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11458,10 +11459,10 @@
         <v>689</v>
       </c>
       <c r="B622" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C622" t="s">
         <v>1227</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11469,10 +11470,10 @@
         <v>697</v>
       </c>
       <c r="B623" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C623" t="s">
         <v>1229</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11480,10 +11481,10 @@
         <v>701</v>
       </c>
       <c r="B624" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C624" t="s">
         <v>1231</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11491,10 +11492,10 @@
         <v>702</v>
       </c>
       <c r="B625" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C625" t="s">
         <v>1233</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11502,10 +11503,10 @@
         <v>704</v>
       </c>
       <c r="B626" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C626" t="s">
         <v>1235</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11513,10 +11514,10 @@
         <v>705</v>
       </c>
       <c r="B627" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C627" t="s">
         <v>1237</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11524,10 +11525,10 @@
         <v>710</v>
       </c>
       <c r="B628" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C628" t="s">
         <v>1239</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11535,10 +11536,10 @@
         <v>711</v>
       </c>
       <c r="B629" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C629" t="s">
         <v>1241</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11546,10 +11547,10 @@
         <v>712</v>
       </c>
       <c r="B630" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C630" t="s">
         <v>1243</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11557,10 +11558,10 @@
         <v>714</v>
       </c>
       <c r="B631" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C631" t="s">
         <v>1245</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11568,10 +11569,10 @@
         <v>717</v>
       </c>
       <c r="B632" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C632" t="s">
         <v>1247</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11579,10 +11580,10 @@
         <v>718</v>
       </c>
       <c r="B633" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C633" t="s">
         <v>1249</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11590,10 +11591,10 @@
         <v>719</v>
       </c>
       <c r="B634" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C634" t="s">
         <v>1251</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11601,10 +11602,10 @@
         <v>721</v>
       </c>
       <c r="B635" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C635" t="s">
         <v>1253</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11612,10 +11613,10 @@
         <v>722</v>
       </c>
       <c r="B636" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C636" t="s">
         <v>1255</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11623,10 +11624,10 @@
         <v>723</v>
       </c>
       <c r="B637" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C637" t="s">
         <v>1257</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11634,10 +11635,10 @@
         <v>725</v>
       </c>
       <c r="B638" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C638" t="s">
         <v>1259</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11645,10 +11646,10 @@
         <v>726</v>
       </c>
       <c r="B639" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C639" t="s">
         <v>1261</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11656,10 +11657,10 @@
         <v>727</v>
       </c>
       <c r="B640" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C640" t="s">
         <v>1263</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11667,10 +11668,10 @@
         <v>728</v>
       </c>
       <c r="B641" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C641" t="s">
         <v>1265</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11678,10 +11679,10 @@
         <v>729</v>
       </c>
       <c r="B642" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C642" t="s">
         <v>1267</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11689,10 +11690,10 @@
         <v>730</v>
       </c>
       <c r="B643" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C643" t="s">
         <v>1269</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11700,10 +11701,10 @@
         <v>731</v>
       </c>
       <c r="B644" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C644" t="s">
         <v>1271</v>
-      </c>
-      <c r="C644" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11711,10 +11712,10 @@
         <v>733</v>
       </c>
       <c r="B645" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C645" t="s">
         <v>1273</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11722,10 +11723,10 @@
         <v>735</v>
       </c>
       <c r="B646" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C646" t="s">
         <v>1275</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11733,10 +11734,10 @@
         <v>736</v>
       </c>
       <c r="B647" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C647" t="s">
         <v>1277</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11744,10 +11745,10 @@
         <v>737</v>
       </c>
       <c r="B648" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C648" t="s">
         <v>1279</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11755,10 +11756,10 @@
         <v>738</v>
       </c>
       <c r="B649" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C649" t="s">
         <v>1281</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11766,10 +11767,10 @@
         <v>739</v>
       </c>
       <c r="B650" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C650" t="s">
         <v>1283</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11777,10 +11778,10 @@
         <v>740</v>
       </c>
       <c r="B651" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C651" t="s">
         <v>1285</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11788,10 +11789,10 @@
         <v>741</v>
       </c>
       <c r="B652" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C652" t="s">
         <v>1287</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11799,10 +11800,10 @@
         <v>742</v>
       </c>
       <c r="B653" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C653" t="s">
         <v>1289</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11810,10 +11811,10 @@
         <v>743</v>
       </c>
       <c r="B654" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C654" t="s">
         <v>1291</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11821,10 +11822,10 @@
         <v>744</v>
       </c>
       <c r="B655" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C655" t="s">
         <v>1293</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11832,10 +11833,10 @@
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C656" t="s">
         <v>1295</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11843,10 +11844,10 @@
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C657" t="s">
         <v>1297</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11854,10 +11855,10 @@
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C658" t="s">
         <v>1299</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11865,10 +11866,10 @@
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C659" t="s">
         <v>1301</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11876,10 +11877,10 @@
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C660" t="s">
         <v>1303</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11887,10 +11888,10 @@
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C661" t="s">
         <v>1305</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11898,10 +11899,10 @@
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C662" t="s">
         <v>1307</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11909,10 +11910,10 @@
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C663" t="s">
         <v>1309</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11920,10 +11921,10 @@
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C664" t="s">
         <v>1311</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11931,10 +11932,10 @@
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C665" t="s">
         <v>1313</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -11942,10 +11943,10 @@
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C666" t="s">
         <v>1315</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -11953,10 +11954,10 @@
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C667" t="s">
         <v>1317</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -11964,10 +11965,10 @@
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C668" t="s">
         <v>1319</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -11975,10 +11976,10 @@
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C669" t="s">
         <v>1321</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -11986,10 +11987,10 @@
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C670" t="s">
         <v>1323</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -11997,10 +11998,10 @@
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C671" t="s">
         <v>1325</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12008,10 +12009,10 @@
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C672" t="s">
         <v>1327</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12025,10 +12026,10 @@
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C674" t="s">
         <v>1329</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12037,7 +12038,7 @@
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12045,10 +12046,10 @@
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C676" t="s">
         <v>1332</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12056,10 +12057,10 @@
         <v>10001</v>
       </c>
       <c r="B677" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C677" t="s">
         <v>1334</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12067,10 +12068,10 @@
         <v>10003</v>
       </c>
       <c r="B678" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C678" t="s">
         <v>1332</v>
-      </c>
-      <c r="C678" t="s">
-        <v>1333</v>
       </c>
     </row>
   </sheetData>

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0456590A-F04F-480C-AF48-3C0D1A3A3457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C2997A-FA32-45FF-8954-49BA072995D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="3012" windowWidth="13176" windowHeight="22536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="1339">
   <si>
     <t>Id</t>
   </si>
@@ -3987,9 +3987,6 @@
     <t>恋愛サーキュレーション</t>
   </si>
   <si>
-    <t>恋爱</t>
-  </si>
-  <si>
     <t>怪獣</t>
   </si>
   <si>
@@ -4211,6 +4208,18 @@
   </si>
   <si>
     <t>剥裤袜,僕は,bkw,bokuwa,我心危,我里危险,扎聋耳朵</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>恋爱,恋爱循环</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thanks to you.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢你</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4632,7 +4641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C678"/>
+  <dimension ref="A1:C679"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -10948,7 +10957,7 @@
         <v>1137</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11036,7 +11045,7 @@
         <v>1150</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11703,8 +11712,8 @@
       <c r="B644" t="s">
         <v>1270</v>
       </c>
-      <c r="C644" t="s">
-        <v>1271</v>
+      <c r="C644" s="3" t="s">
+        <v>1336</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11712,10 +11721,10 @@
         <v>733</v>
       </c>
       <c r="B645" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C645" t="s">
         <v>1272</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11723,10 +11732,10 @@
         <v>735</v>
       </c>
       <c r="B646" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C646" t="s">
         <v>1274</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11734,10 +11743,10 @@
         <v>736</v>
       </c>
       <c r="B647" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C647" t="s">
         <v>1276</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11745,10 +11754,10 @@
         <v>737</v>
       </c>
       <c r="B648" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C648" t="s">
         <v>1278</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11756,10 +11765,10 @@
         <v>738</v>
       </c>
       <c r="B649" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C649" t="s">
         <v>1280</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11767,10 +11776,10 @@
         <v>739</v>
       </c>
       <c r="B650" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C650" t="s">
         <v>1282</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11778,10 +11787,10 @@
         <v>740</v>
       </c>
       <c r="B651" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C651" t="s">
         <v>1284</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11789,10 +11798,10 @@
         <v>741</v>
       </c>
       <c r="B652" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C652" t="s">
         <v>1286</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11800,10 +11809,10 @@
         <v>742</v>
       </c>
       <c r="B653" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C653" t="s">
         <v>1288</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11811,10 +11820,10 @@
         <v>743</v>
       </c>
       <c r="B654" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C654" t="s">
         <v>1290</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11822,10 +11831,10 @@
         <v>744</v>
       </c>
       <c r="B655" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C655" t="s">
         <v>1292</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11833,10 +11842,10 @@
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C656" t="s">
         <v>1294</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11844,10 +11853,10 @@
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C657" t="s">
         <v>1296</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11855,10 +11864,10 @@
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C658" t="s">
         <v>1298</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11866,10 +11875,10 @@
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C659" t="s">
         <v>1300</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11877,10 +11886,10 @@
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C660" t="s">
         <v>1302</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11888,10 +11897,10 @@
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C661" t="s">
         <v>1304</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11899,10 +11908,10 @@
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C662" t="s">
         <v>1306</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11910,10 +11919,10 @@
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C663" t="s">
         <v>1308</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11921,10 +11930,10 @@
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C664" t="s">
         <v>1310</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11932,10 +11941,10 @@
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C665" t="s">
         <v>1312</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -11943,10 +11952,10 @@
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C666" t="s">
         <v>1314</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -11954,10 +11963,10 @@
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C667" t="s">
         <v>1316</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -11965,10 +11974,10 @@
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C668" t="s">
         <v>1318</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -11976,10 +11985,10 @@
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C669" t="s">
         <v>1320</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -11987,10 +11996,10 @@
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C670" t="s">
         <v>1322</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -11998,10 +12007,10 @@
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C671" t="s">
         <v>1324</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12009,10 +12018,10 @@
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C672" t="s">
         <v>1326</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12026,10 +12035,10 @@
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C674" t="s">
         <v>1328</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12038,7 +12047,7 @@
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12046,32 +12055,43 @@
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C676" t="s">
         <v>1331</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677">
-        <v>10001</v>
-      </c>
-      <c r="B677" t="s">
-        <v>1333</v>
-      </c>
-      <c r="C677" t="s">
-        <v>1334</v>
+        <v>772</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678">
+        <v>10001</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A679">
         <v>10003</v>
       </c>
-      <c r="B678" t="s">
+      <c r="B679" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C679" t="s">
         <v>1331</v>
-      </c>
-      <c r="C678" t="s">
-        <v>1332</v>
       </c>
     </row>
   </sheetData>
@@ -12079,7 +12099,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A677:C677 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A601:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A678:C678 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A601:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C2997A-FA32-45FF-8954-49BA072995D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278826F3-AC87-435C-AAE1-2D1BCDC3B93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="3012" windowWidth="13176" windowHeight="22536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3669,9 +3669,6 @@
     <t>TARINAI</t>
   </si>
   <si>
-    <t>还不够</t>
-  </si>
-  <si>
     <t>愛包ダンスホール</t>
   </si>
   <si>
@@ -3847,9 +3844,6 @@
   </si>
   <si>
     <t>Steadfast Spirits</t>
-  </si>
-  <si>
-    <t>坚忍不拔</t>
   </si>
   <si>
     <t>Requiem for Fate</t>
@@ -4220,6 +4214,14 @@
   </si>
   <si>
     <t>谢谢你</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>还不够,tarinal,trainal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚忍不拔,sfs</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -10957,7 +10959,7 @@
         <v>1137</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11045,7 +11047,7 @@
         <v>1150</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11239,8 +11241,8 @@
       <c r="B601" t="s">
         <v>1184</v>
       </c>
-      <c r="C601" t="s">
-        <v>1185</v>
+      <c r="C601" s="3" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11248,10 +11250,10 @@
         <v>651</v>
       </c>
       <c r="B602" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C602" t="s">
         <v>1186</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11259,10 +11261,10 @@
         <v>653</v>
       </c>
       <c r="B603" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C603" t="s">
         <v>1188</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11270,10 +11272,10 @@
         <v>654</v>
       </c>
       <c r="B604" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C604" t="s">
         <v>1190</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11281,10 +11283,10 @@
         <v>655</v>
       </c>
       <c r="B605" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C605" t="s">
         <v>1192</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11292,10 +11294,10 @@
         <v>659</v>
       </c>
       <c r="B606" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C606" t="s">
         <v>1194</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11303,10 +11305,10 @@
         <v>660</v>
       </c>
       <c r="B607" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C607" t="s">
         <v>1196</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11314,10 +11316,10 @@
         <v>661</v>
       </c>
       <c r="B608" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C608" t="s">
         <v>1198</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11325,10 +11327,10 @@
         <v>663</v>
       </c>
       <c r="B609" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C609" t="s">
         <v>1200</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11336,10 +11338,10 @@
         <v>667</v>
       </c>
       <c r="B610" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C610" t="s">
         <v>1202</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11347,10 +11349,10 @@
         <v>670</v>
       </c>
       <c r="B611" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C611" t="s">
         <v>1204</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11358,10 +11360,10 @@
         <v>673</v>
       </c>
       <c r="B612" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C612" t="s">
         <v>1206</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11369,10 +11371,10 @@
         <v>674</v>
       </c>
       <c r="B613" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C613" t="s">
         <v>1208</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11380,10 +11382,10 @@
         <v>675</v>
       </c>
       <c r="B614" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C614" t="s">
         <v>1210</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11391,10 +11393,10 @@
         <v>680</v>
       </c>
       <c r="B615" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C615" t="s">
         <v>1212</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11402,10 +11404,10 @@
         <v>681</v>
       </c>
       <c r="B616" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C616" t="s">
         <v>1214</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11413,10 +11415,10 @@
         <v>682</v>
       </c>
       <c r="B617" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C617" t="s">
         <v>1216</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11424,10 +11426,10 @@
         <v>683</v>
       </c>
       <c r="B618" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C618" t="s">
         <v>1218</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11435,10 +11437,10 @@
         <v>684</v>
       </c>
       <c r="B619" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C619" t="s">
         <v>1220</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11446,10 +11448,10 @@
         <v>685</v>
       </c>
       <c r="B620" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C620" t="s">
         <v>1222</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11457,10 +11459,10 @@
         <v>686</v>
       </c>
       <c r="B621" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C621" t="s">
         <v>1224</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11468,10 +11470,10 @@
         <v>689</v>
       </c>
       <c r="B622" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C622" t="s">
         <v>1226</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11479,10 +11481,10 @@
         <v>697</v>
       </c>
       <c r="B623" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C623" t="s">
         <v>1228</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11490,10 +11492,10 @@
         <v>701</v>
       </c>
       <c r="B624" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C624" t="s">
         <v>1230</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11501,10 +11503,10 @@
         <v>702</v>
       </c>
       <c r="B625" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C625" t="s">
         <v>1232</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11512,10 +11514,10 @@
         <v>704</v>
       </c>
       <c r="B626" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C626" t="s">
         <v>1234</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11523,10 +11525,10 @@
         <v>705</v>
       </c>
       <c r="B627" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C627" t="s">
         <v>1236</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11534,10 +11536,10 @@
         <v>710</v>
       </c>
       <c r="B628" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C628" t="s">
         <v>1238</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11545,10 +11547,10 @@
         <v>711</v>
       </c>
       <c r="B629" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C629" t="s">
         <v>1240</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11556,10 +11558,10 @@
         <v>712</v>
       </c>
       <c r="B630" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C630" t="s">
         <v>1242</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11567,10 +11569,10 @@
         <v>714</v>
       </c>
       <c r="B631" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C631" t="s">
-        <v>1245</v>
+        <v>1243</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11578,10 +11580,10 @@
         <v>717</v>
       </c>
       <c r="B632" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C632" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11589,10 +11591,10 @@
         <v>718</v>
       </c>
       <c r="B633" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C633" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11600,10 +11602,10 @@
         <v>719</v>
       </c>
       <c r="B634" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C634" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11611,10 +11613,10 @@
         <v>721</v>
       </c>
       <c r="B635" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C635" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11622,10 +11624,10 @@
         <v>722</v>
       </c>
       <c r="B636" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C636" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11633,10 +11635,10 @@
         <v>723</v>
       </c>
       <c r="B637" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C637" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11644,10 +11646,10 @@
         <v>725</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C638" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11655,10 +11657,10 @@
         <v>726</v>
       </c>
       <c r="B639" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C639" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11666,10 +11668,10 @@
         <v>727</v>
       </c>
       <c r="B640" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C640" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11677,10 +11679,10 @@
         <v>728</v>
       </c>
       <c r="B641" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C641" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11688,10 +11690,10 @@
         <v>729</v>
       </c>
       <c r="B642" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C642" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11699,10 +11701,10 @@
         <v>730</v>
       </c>
       <c r="B643" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C643" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11710,10 +11712,10 @@
         <v>731</v>
       </c>
       <c r="B644" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11721,10 +11723,10 @@
         <v>733</v>
       </c>
       <c r="B645" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C645" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11732,10 +11734,10 @@
         <v>735</v>
       </c>
       <c r="B646" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C646" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11743,10 +11745,10 @@
         <v>736</v>
       </c>
       <c r="B647" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C647" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11754,10 +11756,10 @@
         <v>737</v>
       </c>
       <c r="B648" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C648" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11765,10 +11767,10 @@
         <v>738</v>
       </c>
       <c r="B649" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C649" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11776,10 +11778,10 @@
         <v>739</v>
       </c>
       <c r="B650" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="C650" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11787,10 +11789,10 @@
         <v>740</v>
       </c>
       <c r="B651" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C651" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11798,10 +11800,10 @@
         <v>741</v>
       </c>
       <c r="B652" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C652" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11809,10 +11811,10 @@
         <v>742</v>
       </c>
       <c r="B653" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C653" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11820,10 +11822,10 @@
         <v>743</v>
       </c>
       <c r="B654" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C654" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11831,10 +11833,10 @@
         <v>744</v>
       </c>
       <c r="B655" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C655" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11842,10 +11844,10 @@
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C656" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11853,10 +11855,10 @@
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C657" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11864,10 +11866,10 @@
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C658" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11875,10 +11877,10 @@
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C659" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11886,10 +11888,10 @@
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C660" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11897,10 +11899,10 @@
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="C661" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11908,10 +11910,10 @@
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="C662" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11919,10 +11921,10 @@
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="C663" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11930,10 +11932,10 @@
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C664" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11941,10 +11943,10 @@
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="C665" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -11952,10 +11954,10 @@
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C666" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -11963,10 +11965,10 @@
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="C667" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -11974,10 +11976,10 @@
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="C668" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -11985,10 +11987,10 @@
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C669" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -11996,10 +11998,10 @@
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C670" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12007,10 +12009,10 @@
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C671" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12018,10 +12020,10 @@
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C672" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12035,10 +12037,10 @@
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C674" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12047,7 +12049,7 @@
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12055,10 +12057,10 @@
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C676" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12066,10 +12068,10 @@
         <v>772</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C677" s="3" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12077,10 +12079,10 @@
         <v>10001</v>
       </c>
       <c r="B678" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C678" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12088,10 +12090,10 @@
         <v>10003</v>
       </c>
       <c r="B679" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="C679" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
   </sheetData>
@@ -12099,7 +12101,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A678:C678 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A601:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A678:C678 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278826F3-AC87-435C-AAE1-2D1BCDC3B93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23785C07-7851-4A3E-A5D1-D237AE435EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="1347">
   <si>
     <t>Id</t>
   </si>
@@ -743,9 +743,6 @@
     <t>COMIC PANIC!!!</t>
   </si>
   <si>
-    <t>漫画,cp</t>
-  </si>
-  <si>
     <t>二重の虹(ダブル レインボウ)</t>
   </si>
   <si>
@@ -2090,13 +2087,7 @@
     <t>灼熱 Bonfire!</t>
   </si>
   <si>
-    <t>灼热小太阳,灼热,火焰弹</t>
-  </si>
-  <si>
     <t>ここから先は歌にならない</t>
-  </si>
-  <si>
-    <t>我们的重制人生,先歌</t>
   </si>
   <si>
     <t>Singing “OURS”</t>
@@ -4222,6 +4213,50 @@
   </si>
   <si>
     <t>坚忍不拔,sfs</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>极乐汤</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>mb</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>day2,day x day,dayday,dayxday</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>金曜日,星期日的早安,星期天的早安,星期日早安,星期天早安</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>许婚</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>过去,过去食,过去喰</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>漫画,cp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>漫画平行,cp平行,平行世界</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>灼热小太阳平行,灼热平行,火焰弹平行,炽热平行</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>灼热小太阳,灼热,火焰弹,炽热</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们的重制人生,先歌,我们重制人生</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4643,7 +4678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C679"/>
+  <dimension ref="A1:C687"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -5891,8 +5926,8 @@
       <c r="B113" t="s">
         <v>225</v>
       </c>
-      <c r="C113" t="s">
-        <v>226</v>
+      <c r="C113" s="3" t="s">
+        <v>1342</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -5900,10 +5935,10 @@
         <v>122</v>
       </c>
       <c r="B114" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" t="s">
         <v>227</v>
-      </c>
-      <c r="C114" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -5911,10 +5946,10 @@
         <v>123</v>
       </c>
       <c r="B115" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" t="s">
         <v>229</v>
-      </c>
-      <c r="C115" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -5922,10 +5957,10 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
+        <v>230</v>
+      </c>
+      <c r="C116" t="s">
         <v>231</v>
-      </c>
-      <c r="C116" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -5933,10 +5968,10 @@
         <v>125</v>
       </c>
       <c r="B117" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" t="s">
         <v>233</v>
-      </c>
-      <c r="C117" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -5944,10 +5979,10 @@
         <v>126</v>
       </c>
       <c r="B118" t="s">
+        <v>234</v>
+      </c>
+      <c r="C118" t="s">
         <v>235</v>
-      </c>
-      <c r="C118" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -5955,10 +5990,10 @@
         <v>127</v>
       </c>
       <c r="B119" t="s">
+        <v>236</v>
+      </c>
+      <c r="C119" t="s">
         <v>237</v>
-      </c>
-      <c r="C119" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -5966,10 +6001,10 @@
         <v>128</v>
       </c>
       <c r="B120" t="s">
+        <v>238</v>
+      </c>
+      <c r="C120" t="s">
         <v>239</v>
-      </c>
-      <c r="C120" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -5977,10 +6012,10 @@
         <v>129</v>
       </c>
       <c r="B121" t="s">
+        <v>240</v>
+      </c>
+      <c r="C121" t="s">
         <v>241</v>
-      </c>
-      <c r="C121" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -5988,10 +6023,10 @@
         <v>130</v>
       </c>
       <c r="B122" t="s">
+        <v>242</v>
+      </c>
+      <c r="C122" t="s">
         <v>243</v>
-      </c>
-      <c r="C122" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -5999,10 +6034,10 @@
         <v>131</v>
       </c>
       <c r="B123" t="s">
+        <v>244</v>
+      </c>
+      <c r="C123" t="s">
         <v>245</v>
-      </c>
-      <c r="C123" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -6010,10 +6045,10 @@
         <v>132</v>
       </c>
       <c r="B124" t="s">
+        <v>246</v>
+      </c>
+      <c r="C124" t="s">
         <v>247</v>
-      </c>
-      <c r="C124" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -6021,10 +6056,10 @@
         <v>133</v>
       </c>
       <c r="B125" t="s">
+        <v>248</v>
+      </c>
+      <c r="C125" t="s">
         <v>249</v>
-      </c>
-      <c r="C125" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -6032,10 +6067,10 @@
         <v>134</v>
       </c>
       <c r="B126" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" t="s">
         <v>251</v>
-      </c>
-      <c r="C126" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -6043,10 +6078,10 @@
         <v>135</v>
       </c>
       <c r="B127" t="s">
+        <v>252</v>
+      </c>
+      <c r="C127" t="s">
         <v>253</v>
-      </c>
-      <c r="C127" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -6054,10 +6089,10 @@
         <v>136</v>
       </c>
       <c r="B128" t="s">
+        <v>254</v>
+      </c>
+      <c r="C128" t="s">
         <v>255</v>
-      </c>
-      <c r="C128" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -6065,10 +6100,10 @@
         <v>137</v>
       </c>
       <c r="B129" t="s">
+        <v>256</v>
+      </c>
+      <c r="C129" t="s">
         <v>257</v>
-      </c>
-      <c r="C129" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -6076,10 +6111,10 @@
         <v>138</v>
       </c>
       <c r="B130" t="s">
+        <v>258</v>
+      </c>
+      <c r="C130" t="s">
         <v>259</v>
-      </c>
-      <c r="C130" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -6087,10 +6122,10 @@
         <v>139</v>
       </c>
       <c r="B131" t="s">
+        <v>260</v>
+      </c>
+      <c r="C131" t="s">
         <v>261</v>
-      </c>
-      <c r="C131" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -6098,10 +6133,10 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
+        <v>262</v>
+      </c>
+      <c r="C132" t="s">
         <v>263</v>
-      </c>
-      <c r="C132" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -6109,10 +6144,10 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
+        <v>264</v>
+      </c>
+      <c r="C133" t="s">
         <v>265</v>
-      </c>
-      <c r="C133" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -6120,10 +6155,10 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134" t="s">
         <v>267</v>
-      </c>
-      <c r="C134" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -6131,10 +6166,10 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
+        <v>268</v>
+      </c>
+      <c r="C135" t="s">
         <v>269</v>
-      </c>
-      <c r="C135" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -6142,10 +6177,10 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
+        <v>270</v>
+      </c>
+      <c r="C136" t="s">
         <v>271</v>
-      </c>
-      <c r="C136" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -6153,10 +6188,10 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
+        <v>272</v>
+      </c>
+      <c r="C137" t="s">
         <v>273</v>
-      </c>
-      <c r="C137" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -6164,10 +6199,10 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
+        <v>274</v>
+      </c>
+      <c r="C138" t="s">
         <v>275</v>
-      </c>
-      <c r="C138" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -6175,10 +6210,10 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
+        <v>276</v>
+      </c>
+      <c r="C139" t="s">
         <v>277</v>
-      </c>
-      <c r="C139" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -6186,10 +6221,10 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
+        <v>278</v>
+      </c>
+      <c r="C140" t="s">
         <v>279</v>
-      </c>
-      <c r="C140" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -6197,10 +6232,10 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
+        <v>280</v>
+      </c>
+      <c r="C141" t="s">
         <v>281</v>
-      </c>
-      <c r="C141" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -6208,10 +6243,10 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
+        <v>282</v>
+      </c>
+      <c r="C142" t="s">
         <v>283</v>
-      </c>
-      <c r="C142" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -6219,10 +6254,10 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
+        <v>284</v>
+      </c>
+      <c r="C143" t="s">
         <v>285</v>
-      </c>
-      <c r="C143" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -6230,10 +6265,10 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
+        <v>286</v>
+      </c>
+      <c r="C144" t="s">
         <v>287</v>
-      </c>
-      <c r="C144" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -6241,10 +6276,10 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
+        <v>288</v>
+      </c>
+      <c r="C145" t="s">
         <v>289</v>
-      </c>
-      <c r="C145" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -6252,10 +6287,10 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
+        <v>290</v>
+      </c>
+      <c r="C146" t="s">
         <v>291</v>
-      </c>
-      <c r="C146" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -6263,10 +6298,10 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
+        <v>292</v>
+      </c>
+      <c r="C147" t="s">
         <v>293</v>
-      </c>
-      <c r="C147" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -6274,10 +6309,10 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
+        <v>294</v>
+      </c>
+      <c r="C148" t="s">
         <v>295</v>
-      </c>
-      <c r="C148" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -6285,10 +6320,10 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
+        <v>296</v>
+      </c>
+      <c r="C149" t="s">
         <v>297</v>
-      </c>
-      <c r="C149" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -6296,10 +6331,10 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" t="s">
         <v>299</v>
-      </c>
-      <c r="C150" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -6307,10 +6342,10 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
+        <v>300</v>
+      </c>
+      <c r="C151" t="s">
         <v>301</v>
-      </c>
-      <c r="C151" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -6318,10 +6353,10 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
+        <v>302</v>
+      </c>
+      <c r="C152" t="s">
         <v>303</v>
-      </c>
-      <c r="C152" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -6329,10 +6364,10 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
+        <v>304</v>
+      </c>
+      <c r="C153" t="s">
         <v>305</v>
-      </c>
-      <c r="C153" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -6340,10 +6375,10 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
+        <v>306</v>
+      </c>
+      <c r="C154" t="s">
         <v>307</v>
-      </c>
-      <c r="C154" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -6351,10 +6386,10 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
+        <v>308</v>
+      </c>
+      <c r="C155" t="s">
         <v>309</v>
-      </c>
-      <c r="C155" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -6362,10 +6397,10 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
+        <v>310</v>
+      </c>
+      <c r="C156" t="s">
         <v>311</v>
-      </c>
-      <c r="C156" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -6373,10 +6408,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
+        <v>312</v>
+      </c>
+      <c r="C157" t="s">
         <v>313</v>
-      </c>
-      <c r="C157" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -6384,10 +6419,10 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
+        <v>314</v>
+      </c>
+      <c r="C158" t="s">
         <v>315</v>
-      </c>
-      <c r="C158" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -6395,10 +6430,10 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
+        <v>316</v>
+      </c>
+      <c r="C159" t="s">
         <v>317</v>
-      </c>
-      <c r="C159" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -6406,10 +6441,10 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
+        <v>318</v>
+      </c>
+      <c r="C160" t="s">
         <v>319</v>
-      </c>
-      <c r="C160" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -6417,10 +6452,10 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
+        <v>320</v>
+      </c>
+      <c r="C161" t="s">
         <v>321</v>
-      </c>
-      <c r="C161" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -6428,10 +6463,10 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
+        <v>322</v>
+      </c>
+      <c r="C162" t="s">
         <v>323</v>
-      </c>
-      <c r="C162" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -6439,10 +6474,10 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
+        <v>324</v>
+      </c>
+      <c r="C163" t="s">
         <v>325</v>
-      </c>
-      <c r="C163" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -6450,10 +6485,10 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
+        <v>326</v>
+      </c>
+      <c r="C164" t="s">
         <v>327</v>
-      </c>
-      <c r="C164" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -6461,10 +6496,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
+        <v>328</v>
+      </c>
+      <c r="C165" t="s">
         <v>329</v>
-      </c>
-      <c r="C165" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -6472,10 +6507,10 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
+        <v>330</v>
+      </c>
+      <c r="C166" t="s">
         <v>331</v>
-      </c>
-      <c r="C166" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -6483,10 +6518,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
+        <v>332</v>
+      </c>
+      <c r="C167" t="s">
         <v>333</v>
-      </c>
-      <c r="C167" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -6494,10 +6529,10 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
+        <v>334</v>
+      </c>
+      <c r="C168" t="s">
         <v>335</v>
-      </c>
-      <c r="C168" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -6505,10 +6540,10 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
+        <v>336</v>
+      </c>
+      <c r="C169" t="s">
         <v>337</v>
-      </c>
-      <c r="C169" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -6516,10 +6551,10 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
+        <v>338</v>
+      </c>
+      <c r="C170" t="s">
         <v>339</v>
-      </c>
-      <c r="C170" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -6527,10 +6562,10 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
+        <v>340</v>
+      </c>
+      <c r="C171" t="s">
         <v>341</v>
-      </c>
-      <c r="C171" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -6538,10 +6573,10 @@
         <v>180</v>
       </c>
       <c r="B172" t="s">
+        <v>342</v>
+      </c>
+      <c r="C172" t="s">
         <v>343</v>
-      </c>
-      <c r="C172" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -6549,10 +6584,10 @@
         <v>181</v>
       </c>
       <c r="B173" t="s">
+        <v>344</v>
+      </c>
+      <c r="C173" t="s">
         <v>345</v>
-      </c>
-      <c r="C173" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -6560,10 +6595,10 @@
         <v>182</v>
       </c>
       <c r="B174" t="s">
+        <v>346</v>
+      </c>
+      <c r="C174" t="s">
         <v>347</v>
-      </c>
-      <c r="C174" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -6571,10 +6606,10 @@
         <v>183</v>
       </c>
       <c r="B175" t="s">
+        <v>348</v>
+      </c>
+      <c r="C175" t="s">
         <v>349</v>
-      </c>
-      <c r="C175" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -6582,10 +6617,10 @@
         <v>184</v>
       </c>
       <c r="B176" t="s">
+        <v>350</v>
+      </c>
+      <c r="C176" t="s">
         <v>351</v>
-      </c>
-      <c r="C176" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -6593,10 +6628,10 @@
         <v>185</v>
       </c>
       <c r="B177" t="s">
+        <v>352</v>
+      </c>
+      <c r="C177" t="s">
         <v>353</v>
-      </c>
-      <c r="C177" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -6604,10 +6639,10 @@
         <v>186</v>
       </c>
       <c r="B178" t="s">
+        <v>354</v>
+      </c>
+      <c r="C178" t="s">
         <v>355</v>
-      </c>
-      <c r="C178" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -6615,10 +6650,10 @@
         <v>187</v>
       </c>
       <c r="B179" t="s">
+        <v>356</v>
+      </c>
+      <c r="C179" t="s">
         <v>357</v>
-      </c>
-      <c r="C179" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -6626,10 +6661,10 @@
         <v>188</v>
       </c>
       <c r="B180" t="s">
+        <v>358</v>
+      </c>
+      <c r="C180" t="s">
         <v>359</v>
-      </c>
-      <c r="C180" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -6637,10 +6672,10 @@
         <v>189</v>
       </c>
       <c r="B181" t="s">
+        <v>360</v>
+      </c>
+      <c r="C181" t="s">
         <v>361</v>
-      </c>
-      <c r="C181" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -6648,10 +6683,10 @@
         <v>190</v>
       </c>
       <c r="B182" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" t="s">
         <v>363</v>
-      </c>
-      <c r="C182" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -6659,10 +6694,10 @@
         <v>191</v>
       </c>
       <c r="B183" t="s">
+        <v>364</v>
+      </c>
+      <c r="C183" t="s">
         <v>365</v>
-      </c>
-      <c r="C183" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -6670,10 +6705,10 @@
         <v>192</v>
       </c>
       <c r="B184" t="s">
+        <v>366</v>
+      </c>
+      <c r="C184" t="s">
         <v>367</v>
-      </c>
-      <c r="C184" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -6681,10 +6716,10 @@
         <v>193</v>
       </c>
       <c r="B185" t="s">
+        <v>368</v>
+      </c>
+      <c r="C185" t="s">
         <v>369</v>
-      </c>
-      <c r="C185" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -6692,10 +6727,10 @@
         <v>194</v>
       </c>
       <c r="B186" t="s">
+        <v>370</v>
+      </c>
+      <c r="C186" t="s">
         <v>371</v>
-      </c>
-      <c r="C186" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -6703,10 +6738,10 @@
         <v>195</v>
       </c>
       <c r="B187" t="s">
+        <v>372</v>
+      </c>
+      <c r="C187" t="s">
         <v>373</v>
-      </c>
-      <c r="C187" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -6714,10 +6749,10 @@
         <v>196</v>
       </c>
       <c r="B188" t="s">
+        <v>374</v>
+      </c>
+      <c r="C188" t="s">
         <v>375</v>
-      </c>
-      <c r="C188" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -6725,10 +6760,10 @@
         <v>197</v>
       </c>
       <c r="B189" t="s">
+        <v>376</v>
+      </c>
+      <c r="C189" t="s">
         <v>377</v>
-      </c>
-      <c r="C189" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -6736,10 +6771,10 @@
         <v>198</v>
       </c>
       <c r="B190" t="s">
+        <v>378</v>
+      </c>
+      <c r="C190" t="s">
         <v>379</v>
-      </c>
-      <c r="C190" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -6747,10 +6782,10 @@
         <v>199</v>
       </c>
       <c r="B191" t="s">
+        <v>380</v>
+      </c>
+      <c r="C191" t="s">
         <v>381</v>
-      </c>
-      <c r="C191" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -6758,10 +6793,10 @@
         <v>200</v>
       </c>
       <c r="B192" t="s">
+        <v>382</v>
+      </c>
+      <c r="C192" t="s">
         <v>383</v>
-      </c>
-      <c r="C192" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -6769,10 +6804,10 @@
         <v>201</v>
       </c>
       <c r="B193" t="s">
+        <v>384</v>
+      </c>
+      <c r="C193" t="s">
         <v>385</v>
-      </c>
-      <c r="C193" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -6780,10 +6815,10 @@
         <v>202</v>
       </c>
       <c r="B194" t="s">
+        <v>386</v>
+      </c>
+      <c r="C194" t="s">
         <v>387</v>
-      </c>
-      <c r="C194" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -6791,10 +6826,10 @@
         <v>203</v>
       </c>
       <c r="B195" t="s">
+        <v>388</v>
+      </c>
+      <c r="C195" t="s">
         <v>389</v>
-      </c>
-      <c r="C195" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -6802,10 +6837,10 @@
         <v>204</v>
       </c>
       <c r="B196" t="s">
+        <v>390</v>
+      </c>
+      <c r="C196" t="s">
         <v>391</v>
-      </c>
-      <c r="C196" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -6813,10 +6848,10 @@
         <v>205</v>
       </c>
       <c r="B197" t="s">
+        <v>392</v>
+      </c>
+      <c r="C197" t="s">
         <v>393</v>
-      </c>
-      <c r="C197" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -6824,10 +6859,10 @@
         <v>206</v>
       </c>
       <c r="B198" t="s">
+        <v>394</v>
+      </c>
+      <c r="C198" t="s">
         <v>395</v>
-      </c>
-      <c r="C198" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -6835,10 +6870,10 @@
         <v>207</v>
       </c>
       <c r="B199" t="s">
+        <v>396</v>
+      </c>
+      <c r="C199" t="s">
         <v>397</v>
-      </c>
-      <c r="C199" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -6846,10 +6881,10 @@
         <v>208</v>
       </c>
       <c r="B200" t="s">
+        <v>398</v>
+      </c>
+      <c r="C200" t="s">
         <v>399</v>
-      </c>
-      <c r="C200" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -6857,10 +6892,10 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
+        <v>400</v>
+      </c>
+      <c r="C201" t="s">
         <v>401</v>
-      </c>
-      <c r="C201" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -6868,10 +6903,10 @@
         <v>210</v>
       </c>
       <c r="B202" t="s">
+        <v>402</v>
+      </c>
+      <c r="C202" t="s">
         <v>403</v>
-      </c>
-      <c r="C202" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -6879,10 +6914,10 @@
         <v>211</v>
       </c>
       <c r="B203" t="s">
+        <v>404</v>
+      </c>
+      <c r="C203" t="s">
         <v>405</v>
-      </c>
-      <c r="C203" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -6890,10 +6925,10 @@
         <v>212</v>
       </c>
       <c r="B204" t="s">
+        <v>406</v>
+      </c>
+      <c r="C204" t="s">
         <v>407</v>
-      </c>
-      <c r="C204" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -6901,10 +6936,10 @@
         <v>213</v>
       </c>
       <c r="B205" t="s">
+        <v>408</v>
+      </c>
+      <c r="C205" t="s">
         <v>409</v>
-      </c>
-      <c r="C205" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -6912,10 +6947,10 @@
         <v>214</v>
       </c>
       <c r="B206" t="s">
+        <v>410</v>
+      </c>
+      <c r="C206" t="s">
         <v>411</v>
-      </c>
-      <c r="C206" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -6923,10 +6958,10 @@
         <v>215</v>
       </c>
       <c r="B207" t="s">
+        <v>412</v>
+      </c>
+      <c r="C207" t="s">
         <v>413</v>
-      </c>
-      <c r="C207" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -6934,10 +6969,10 @@
         <v>217</v>
       </c>
       <c r="B208" t="s">
+        <v>414</v>
+      </c>
+      <c r="C208" t="s">
         <v>415</v>
-      </c>
-      <c r="C208" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -6945,10 +6980,10 @@
         <v>218</v>
       </c>
       <c r="B209" t="s">
+        <v>416</v>
+      </c>
+      <c r="C209" t="s">
         <v>417</v>
-      </c>
-      <c r="C209" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -6956,10 +6991,10 @@
         <v>219</v>
       </c>
       <c r="B210" t="s">
+        <v>418</v>
+      </c>
+      <c r="C210" t="s">
         <v>419</v>
-      </c>
-      <c r="C210" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -6967,10 +7002,10 @@
         <v>220</v>
       </c>
       <c r="B211" t="s">
+        <v>420</v>
+      </c>
+      <c r="C211" t="s">
         <v>421</v>
-      </c>
-      <c r="C211" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -6978,10 +7013,10 @@
         <v>221</v>
       </c>
       <c r="B212" t="s">
+        <v>422</v>
+      </c>
+      <c r="C212" t="s">
         <v>423</v>
-      </c>
-      <c r="C212" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -6989,10 +7024,10 @@
         <v>222</v>
       </c>
       <c r="B213" t="s">
+        <v>424</v>
+      </c>
+      <c r="C213" t="s">
         <v>425</v>
-      </c>
-      <c r="C213" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -7000,10 +7035,10 @@
         <v>223</v>
       </c>
       <c r="B214" t="s">
+        <v>426</v>
+      </c>
+      <c r="C214" t="s">
         <v>427</v>
-      </c>
-      <c r="C214" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -7011,10 +7046,10 @@
         <v>224</v>
       </c>
       <c r="B215" t="s">
+        <v>428</v>
+      </c>
+      <c r="C215" t="s">
         <v>429</v>
-      </c>
-      <c r="C215" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -7022,10 +7057,10 @@
         <v>225</v>
       </c>
       <c r="B216" t="s">
+        <v>430</v>
+      </c>
+      <c r="C216" t="s">
         <v>431</v>
-      </c>
-      <c r="C216" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -7033,10 +7068,10 @@
         <v>226</v>
       </c>
       <c r="B217" t="s">
+        <v>432</v>
+      </c>
+      <c r="C217" t="s">
         <v>433</v>
-      </c>
-      <c r="C217" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -7044,10 +7079,10 @@
         <v>227</v>
       </c>
       <c r="B218" t="s">
+        <v>434</v>
+      </c>
+      <c r="C218" t="s">
         <v>435</v>
-      </c>
-      <c r="C218" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -7055,10 +7090,10 @@
         <v>228</v>
       </c>
       <c r="B219" t="s">
+        <v>436</v>
+      </c>
+      <c r="C219" t="s">
         <v>437</v>
-      </c>
-      <c r="C219" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -7066,10 +7101,10 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
+        <v>438</v>
+      </c>
+      <c r="C220" t="s">
         <v>439</v>
-      </c>
-      <c r="C220" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -7077,10 +7112,10 @@
         <v>230</v>
       </c>
       <c r="B221" t="s">
+        <v>440</v>
+      </c>
+      <c r="C221" t="s">
         <v>441</v>
-      </c>
-      <c r="C221" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -7088,10 +7123,10 @@
         <v>231</v>
       </c>
       <c r="B222" t="s">
+        <v>442</v>
+      </c>
+      <c r="C222" t="s">
         <v>443</v>
-      </c>
-      <c r="C222" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -7099,10 +7134,10 @@
         <v>232</v>
       </c>
       <c r="B223" t="s">
+        <v>444</v>
+      </c>
+      <c r="C223" t="s">
         <v>445</v>
-      </c>
-      <c r="C223" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -7110,10 +7145,10 @@
         <v>233</v>
       </c>
       <c r="B224" t="s">
+        <v>446</v>
+      </c>
+      <c r="C224" t="s">
         <v>447</v>
-      </c>
-      <c r="C224" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -7121,10 +7156,10 @@
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>448</v>
+      </c>
+      <c r="C225" t="s">
         <v>449</v>
-      </c>
-      <c r="C225" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -7132,10 +7167,10 @@
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>450</v>
+      </c>
+      <c r="C226" t="s">
         <v>451</v>
-      </c>
-      <c r="C226" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -7143,10 +7178,10 @@
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>452</v>
+      </c>
+      <c r="C227" t="s">
         <v>453</v>
-      </c>
-      <c r="C227" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -7154,10 +7189,10 @@
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>454</v>
+      </c>
+      <c r="C228" t="s">
         <v>455</v>
-      </c>
-      <c r="C228" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -7165,10 +7200,10 @@
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>456</v>
+      </c>
+      <c r="C229" t="s">
         <v>457</v>
-      </c>
-      <c r="C229" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -7176,10 +7211,10 @@
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>458</v>
+      </c>
+      <c r="C230" t="s">
         <v>459</v>
-      </c>
-      <c r="C230" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -7187,10 +7222,10 @@
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>460</v>
+      </c>
+      <c r="C231" t="s">
         <v>461</v>
-      </c>
-      <c r="C231" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -7198,10 +7233,10 @@
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>462</v>
+      </c>
+      <c r="C232" t="s">
         <v>463</v>
-      </c>
-      <c r="C232" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -7209,10 +7244,10 @@
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>464</v>
+      </c>
+      <c r="C233" t="s">
         <v>465</v>
-      </c>
-      <c r="C233" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -7220,10 +7255,10 @@
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>466</v>
+      </c>
+      <c r="C234" t="s">
         <v>467</v>
-      </c>
-      <c r="C234" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -7231,10 +7266,10 @@
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>468</v>
+      </c>
+      <c r="C235" t="s">
         <v>469</v>
-      </c>
-      <c r="C235" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -7242,10 +7277,10 @@
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>470</v>
+      </c>
+      <c r="C236" t="s">
         <v>471</v>
-      </c>
-      <c r="C236" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -7253,10 +7288,10 @@
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>472</v>
+      </c>
+      <c r="C237" t="s">
         <v>473</v>
-      </c>
-      <c r="C237" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -7264,10 +7299,10 @@
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>474</v>
+      </c>
+      <c r="C238" t="s">
         <v>475</v>
-      </c>
-      <c r="C238" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -7275,10 +7310,10 @@
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>476</v>
+      </c>
+      <c r="C239" t="s">
         <v>477</v>
-      </c>
-      <c r="C239" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -7286,10 +7321,10 @@
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>478</v>
+      </c>
+      <c r="C240" t="s">
         <v>479</v>
-      </c>
-      <c r="C240" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -7297,10 +7332,10 @@
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>480</v>
+      </c>
+      <c r="C241" t="s">
         <v>481</v>
-      </c>
-      <c r="C241" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -7308,10 +7343,10 @@
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>482</v>
+      </c>
+      <c r="C242" t="s">
         <v>483</v>
-      </c>
-      <c r="C242" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -7319,10 +7354,10 @@
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>484</v>
+      </c>
+      <c r="C243" t="s">
         <v>485</v>
-      </c>
-      <c r="C243" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -7330,10 +7365,10 @@
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>486</v>
+      </c>
+      <c r="C244" t="s">
         <v>487</v>
-      </c>
-      <c r="C244" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -7341,10 +7376,10 @@
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>488</v>
+      </c>
+      <c r="C245" t="s">
         <v>489</v>
-      </c>
-      <c r="C245" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -7352,10 +7387,10 @@
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>490</v>
+      </c>
+      <c r="C246" t="s">
         <v>491</v>
-      </c>
-      <c r="C246" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -7363,10 +7398,10 @@
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>492</v>
+      </c>
+      <c r="C247" t="s">
         <v>493</v>
-      </c>
-      <c r="C247" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -7374,10 +7409,10 @@
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>494</v>
+      </c>
+      <c r="C248" t="s">
         <v>495</v>
-      </c>
-      <c r="C248" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -7385,10 +7420,10 @@
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>496</v>
+      </c>
+      <c r="C249" t="s">
         <v>497</v>
-      </c>
-      <c r="C249" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -7396,10 +7431,10 @@
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>498</v>
+      </c>
+      <c r="C250" t="s">
         <v>499</v>
-      </c>
-      <c r="C250" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -7407,10 +7442,10 @@
         <v>260</v>
       </c>
       <c r="B251" t="s">
+        <v>500</v>
+      </c>
+      <c r="C251" t="s">
         <v>501</v>
-      </c>
-      <c r="C251" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -7418,10 +7453,10 @@
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C252" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -7429,10 +7464,10 @@
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>503</v>
+      </c>
+      <c r="C253" t="s">
         <v>504</v>
-      </c>
-      <c r="C253" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -7440,10 +7475,10 @@
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>505</v>
+      </c>
+      <c r="C254" t="s">
         <v>506</v>
-      </c>
-      <c r="C254" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -7451,10 +7486,10 @@
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>507</v>
+      </c>
+      <c r="C255" t="s">
         <v>508</v>
-      </c>
-      <c r="C255" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -7462,10 +7497,10 @@
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>509</v>
+      </c>
+      <c r="C256" t="s">
         <v>510</v>
-      </c>
-      <c r="C256" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -7473,10 +7508,10 @@
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>511</v>
+      </c>
+      <c r="C257" t="s">
         <v>512</v>
-      </c>
-      <c r="C257" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -7484,10 +7519,10 @@
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>513</v>
+      </c>
+      <c r="C258" t="s">
         <v>514</v>
-      </c>
-      <c r="C258" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -7495,10 +7530,10 @@
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>515</v>
+      </c>
+      <c r="C259" t="s">
         <v>516</v>
-      </c>
-      <c r="C259" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -7506,10 +7541,10 @@
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>517</v>
+      </c>
+      <c r="C260" t="s">
         <v>518</v>
-      </c>
-      <c r="C260" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -7517,10 +7552,10 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>519</v>
+      </c>
+      <c r="C261" t="s">
         <v>520</v>
-      </c>
-      <c r="C261" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -7528,10 +7563,10 @@
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>521</v>
+      </c>
+      <c r="C262" t="s">
         <v>522</v>
-      </c>
-      <c r="C262" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -7539,10 +7574,10 @@
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>523</v>
+      </c>
+      <c r="C263" t="s">
         <v>524</v>
-      </c>
-      <c r="C263" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -7550,10 +7585,10 @@
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>525</v>
+      </c>
+      <c r="C264" t="s">
         <v>526</v>
-      </c>
-      <c r="C264" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -7561,10 +7596,10 @@
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>527</v>
+      </c>
+      <c r="C265" t="s">
         <v>528</v>
-      </c>
-      <c r="C265" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -7572,10 +7607,10 @@
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>529</v>
+      </c>
+      <c r="C266" t="s">
         <v>530</v>
-      </c>
-      <c r="C266" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -7583,10 +7618,10 @@
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>531</v>
+      </c>
+      <c r="C267" t="s">
         <v>532</v>
-      </c>
-      <c r="C267" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -7594,10 +7629,10 @@
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>533</v>
+      </c>
+      <c r="C268" t="s">
         <v>534</v>
-      </c>
-      <c r="C268" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -7605,10 +7640,10 @@
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>535</v>
+      </c>
+      <c r="C269" t="s">
         <v>536</v>
-      </c>
-      <c r="C269" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -7616,10 +7651,10 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>537</v>
+      </c>
+      <c r="C270" t="s">
         <v>538</v>
-      </c>
-      <c r="C270" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -7627,10 +7662,10 @@
         <v>281</v>
       </c>
       <c r="B271" t="s">
+        <v>539</v>
+      </c>
+      <c r="C271" t="s">
         <v>540</v>
-      </c>
-      <c r="C271" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -7638,10 +7673,10 @@
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>541</v>
+      </c>
+      <c r="C272" t="s">
         <v>542</v>
-      </c>
-      <c r="C272" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -7649,10 +7684,10 @@
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>543</v>
+      </c>
+      <c r="C273" t="s">
         <v>544</v>
-      </c>
-      <c r="C273" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -7660,10 +7695,10 @@
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>545</v>
+      </c>
+      <c r="C274" t="s">
         <v>546</v>
-      </c>
-      <c r="C274" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -7671,10 +7706,10 @@
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>547</v>
+      </c>
+      <c r="C275" t="s">
         <v>548</v>
-      </c>
-      <c r="C275" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -7682,10 +7717,10 @@
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>549</v>
+      </c>
+      <c r="C276" t="s">
         <v>550</v>
-      </c>
-      <c r="C276" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -7693,10 +7728,10 @@
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>551</v>
+      </c>
+      <c r="C277" t="s">
         <v>552</v>
-      </c>
-      <c r="C277" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -7704,10 +7739,10 @@
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>553</v>
+      </c>
+      <c r="C278" t="s">
         <v>554</v>
-      </c>
-      <c r="C278" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -7715,10 +7750,10 @@
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>555</v>
+      </c>
+      <c r="C279" t="s">
         <v>556</v>
-      </c>
-      <c r="C279" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -7726,10 +7761,10 @@
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>557</v>
+      </c>
+      <c r="C280" t="s">
         <v>558</v>
-      </c>
-      <c r="C280" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -7737,10 +7772,10 @@
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>559</v>
+      </c>
+      <c r="C281" t="s">
         <v>560</v>
-      </c>
-      <c r="C281" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -7748,10 +7783,10 @@
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>561</v>
+      </c>
+      <c r="C282" t="s">
         <v>562</v>
-      </c>
-      <c r="C282" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -7759,10 +7794,10 @@
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>563</v>
+      </c>
+      <c r="C283" t="s">
         <v>564</v>
-      </c>
-      <c r="C283" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -7770,10 +7805,10 @@
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>565</v>
+      </c>
+      <c r="C284" t="s">
         <v>566</v>
-      </c>
-      <c r="C284" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -7781,10 +7816,10 @@
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>567</v>
+      </c>
+      <c r="C285" t="s">
         <v>568</v>
-      </c>
-      <c r="C285" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -7792,10 +7827,10 @@
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>569</v>
+      </c>
+      <c r="C286" t="s">
         <v>570</v>
-      </c>
-      <c r="C286" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -7803,10 +7838,10 @@
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>571</v>
+      </c>
+      <c r="C287" t="s">
         <v>572</v>
-      </c>
-      <c r="C287" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -7814,10 +7849,10 @@
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>573</v>
+      </c>
+      <c r="C288" t="s">
         <v>574</v>
-      </c>
-      <c r="C288" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -7825,10 +7860,10 @@
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>575</v>
+      </c>
+      <c r="C289" t="s">
         <v>576</v>
-      </c>
-      <c r="C289" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -7836,10 +7871,10 @@
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>577</v>
+      </c>
+      <c r="C290" t="s">
         <v>578</v>
-      </c>
-      <c r="C290" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -7847,10 +7882,10 @@
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>579</v>
+      </c>
+      <c r="C291" t="s">
         <v>580</v>
-      </c>
-      <c r="C291" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -7858,10 +7893,10 @@
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>581</v>
+      </c>
+      <c r="C292" t="s">
         <v>582</v>
-      </c>
-      <c r="C292" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -7869,10 +7904,10 @@
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>583</v>
+      </c>
+      <c r="C293" t="s">
         <v>584</v>
-      </c>
-      <c r="C293" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -7880,10 +7915,10 @@
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>585</v>
+      </c>
+      <c r="C294" t="s">
         <v>586</v>
-      </c>
-      <c r="C294" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -7891,10 +7926,10 @@
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>587</v>
+      </c>
+      <c r="C295" t="s">
         <v>588</v>
-      </c>
-      <c r="C295" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -7902,10 +7937,10 @@
         <v>306</v>
       </c>
       <c r="B296" t="s">
+        <v>589</v>
+      </c>
+      <c r="C296" t="s">
         <v>590</v>
-      </c>
-      <c r="C296" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7913,10 +7948,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>591</v>
+      </c>
+      <c r="C297" t="s">
         <v>592</v>
-      </c>
-      <c r="C297" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7924,10 +7959,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>593</v>
+      </c>
+      <c r="C298" t="s">
         <v>594</v>
-      </c>
-      <c r="C298" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -7935,10 +7970,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>595</v>
+      </c>
+      <c r="C299" t="s">
         <v>596</v>
-      </c>
-      <c r="C299" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -7946,10 +7981,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>597</v>
+      </c>
+      <c r="C300" t="s">
         <v>598</v>
-      </c>
-      <c r="C300" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -7957,10 +7992,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>599</v>
+      </c>
+      <c r="C301" t="s">
         <v>600</v>
-      </c>
-      <c r="C301" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -7968,10 +8003,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>601</v>
+      </c>
+      <c r="C302" t="s">
         <v>602</v>
-      </c>
-      <c r="C302" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -7979,10 +8014,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>603</v>
+      </c>
+      <c r="C303" t="s">
         <v>604</v>
-      </c>
-      <c r="C303" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -7990,10 +8025,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>605</v>
+      </c>
+      <c r="C304" t="s">
         <v>606</v>
-      </c>
-      <c r="C304" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8001,10 +8036,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>607</v>
+      </c>
+      <c r="C305" t="s">
         <v>608</v>
-      </c>
-      <c r="C305" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8012,10 +8047,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>609</v>
+      </c>
+      <c r="C306" t="s">
         <v>610</v>
-      </c>
-      <c r="C306" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8023,10 +8058,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>611</v>
+      </c>
+      <c r="C307" t="s">
         <v>612</v>
-      </c>
-      <c r="C307" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8034,10 +8069,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>613</v>
+      </c>
+      <c r="C308" t="s">
         <v>614</v>
-      </c>
-      <c r="C308" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8045,10 +8080,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>615</v>
+      </c>
+      <c r="C309" t="s">
         <v>616</v>
-      </c>
-      <c r="C309" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8056,10 +8091,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>617</v>
+      </c>
+      <c r="C310" t="s">
         <v>618</v>
-      </c>
-      <c r="C310" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8067,10 +8102,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>619</v>
+      </c>
+      <c r="C311" t="s">
         <v>620</v>
-      </c>
-      <c r="C311" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8078,10 +8113,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>621</v>
+      </c>
+      <c r="C312" t="s">
         <v>622</v>
-      </c>
-      <c r="C312" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8089,10 +8124,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>623</v>
+      </c>
+      <c r="C313" t="s">
         <v>624</v>
-      </c>
-      <c r="C313" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8100,10 +8135,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>625</v>
+      </c>
+      <c r="C314" t="s">
         <v>626</v>
-      </c>
-      <c r="C314" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8111,10 +8146,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>627</v>
+      </c>
+      <c r="C315" t="s">
         <v>628</v>
-      </c>
-      <c r="C315" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8122,10 +8157,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>629</v>
+      </c>
+      <c r="C316" t="s">
         <v>630</v>
-      </c>
-      <c r="C316" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8133,10 +8168,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>631</v>
+      </c>
+      <c r="C317" t="s">
         <v>632</v>
-      </c>
-      <c r="C317" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8144,10 +8179,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>633</v>
+      </c>
+      <c r="C318" t="s">
         <v>634</v>
-      </c>
-      <c r="C318" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8155,10 +8190,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>635</v>
+      </c>
+      <c r="C319" t="s">
         <v>636</v>
-      </c>
-      <c r="C319" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8166,10 +8201,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>637</v>
+      </c>
+      <c r="C320" t="s">
         <v>638</v>
-      </c>
-      <c r="C320" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8177,10 +8212,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>639</v>
+      </c>
+      <c r="C321" t="s">
         <v>640</v>
-      </c>
-      <c r="C321" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8188,10 +8223,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>641</v>
+      </c>
+      <c r="C322" t="s">
         <v>642</v>
-      </c>
-      <c r="C322" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8199,10 +8234,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>643</v>
+      </c>
+      <c r="C323" t="s">
         <v>644</v>
-      </c>
-      <c r="C323" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8210,10 +8245,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>645</v>
+      </c>
+      <c r="C324" t="s">
         <v>646</v>
-      </c>
-      <c r="C324" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8221,10 +8256,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>647</v>
+      </c>
+      <c r="C325" t="s">
         <v>648</v>
-      </c>
-      <c r="C325" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8232,10 +8267,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>649</v>
+      </c>
+      <c r="C326" t="s">
         <v>650</v>
-      </c>
-      <c r="C326" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8243,10 +8278,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>651</v>
+      </c>
+      <c r="C327" t="s">
         <v>652</v>
-      </c>
-      <c r="C327" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8254,10 +8289,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>653</v>
+      </c>
+      <c r="C328" t="s">
         <v>654</v>
-      </c>
-      <c r="C328" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8265,10 +8300,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>655</v>
+      </c>
+      <c r="C329" t="s">
         <v>656</v>
-      </c>
-      <c r="C329" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8276,10 +8311,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>657</v>
+      </c>
+      <c r="C330" t="s">
         <v>658</v>
-      </c>
-      <c r="C330" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8287,10 +8322,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>659</v>
+      </c>
+      <c r="C331" t="s">
         <v>660</v>
-      </c>
-      <c r="C331" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8298,10 +8333,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>661</v>
+      </c>
+      <c r="C332" t="s">
         <v>662</v>
-      </c>
-      <c r="C332" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8309,10 +8344,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>663</v>
+      </c>
+      <c r="C333" t="s">
         <v>664</v>
-      </c>
-      <c r="C333" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8320,10 +8355,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>665</v>
+      </c>
+      <c r="C334" t="s">
         <v>666</v>
-      </c>
-      <c r="C334" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8331,10 +8366,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>667</v>
+      </c>
+      <c r="C335" t="s">
         <v>668</v>
-      </c>
-      <c r="C335" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8342,10 +8377,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>669</v>
+      </c>
+      <c r="C336" t="s">
         <v>670</v>
-      </c>
-      <c r="C336" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8353,10 +8388,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>671</v>
+      </c>
+      <c r="C337" t="s">
         <v>672</v>
-      </c>
-      <c r="C337" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8364,10 +8399,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>674</v>
-      </c>
-      <c r="C338" t="s">
-        <v>675</v>
+        <v>673</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8375,10 +8410,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>676</v>
-      </c>
-      <c r="C339" t="s">
-        <v>677</v>
+        <v>674</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8386,10 +8421,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C340" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8397,10 +8432,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C341" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8408,10 +8443,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C342" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8419,10 +8454,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C343" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8430,10 +8465,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C344" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8441,10 +8476,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C345" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8452,10 +8487,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C346" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8463,10 +8498,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C347" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8474,10 +8509,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C348" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8485,10 +8520,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C349" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8496,10 +8531,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C350" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8507,10 +8542,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C351" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8518,10 +8553,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C352" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8529,10 +8564,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C353" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8540,10 +8575,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C354" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8551,10 +8586,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C355" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8562,10 +8597,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C356" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8573,10 +8608,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C357" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8584,10 +8619,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C358" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8595,10 +8630,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C359" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8606,10 +8641,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C360" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8617,10 +8652,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C361" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8628,10 +8663,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C362" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8639,10 +8674,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C363" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8650,10 +8685,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C364" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8661,10 +8696,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C365" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8672,10 +8707,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C366" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8683,10 +8718,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C367" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8694,10 +8729,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C368" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8705,10 +8740,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C369" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8716,10 +8751,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C370" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8727,10 +8762,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C371" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8738,10 +8773,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C372" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8749,10 +8784,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C373" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8760,10 +8795,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C374" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8771,10 +8806,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C375" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8782,10 +8817,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C376" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8793,10 +8828,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C377" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8804,10 +8839,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C378" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8815,10 +8850,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C379" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8826,10 +8861,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C380" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8837,10 +8872,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C381" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8848,10 +8883,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C382" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8859,10 +8894,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C383" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8870,10 +8905,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C384" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8881,10 +8916,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C385" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8892,10 +8927,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C386" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8903,10 +8938,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C387" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8914,10 +8949,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C388" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8925,10 +8960,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C389" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -8936,10 +8971,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C390" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -8947,10 +8982,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C391" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -8958,10 +8993,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C392" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -8969,10 +9004,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C393" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -8980,10 +9015,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C394" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -8991,10 +9026,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C395" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9002,10 +9037,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C396" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9013,10 +9048,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C397" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9024,10 +9059,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C398" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9035,10 +9070,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C399" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9046,10 +9081,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C400" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9057,10 +9092,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C401" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9068,10 +9103,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C402" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9079,10 +9114,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C403" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9090,10 +9125,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C404" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9101,10 +9136,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C405" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9112,10 +9147,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C406" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9123,10 +9158,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C407" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9134,10 +9169,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C408" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9145,10 +9180,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C409" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9156,10 +9191,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C410" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9167,10 +9202,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C411" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9178,10 +9213,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C412" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9189,10 +9224,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C413" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9200,10 +9235,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C414" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9211,10 +9246,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C415" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9222,10 +9257,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C416" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9233,10 +9268,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C417" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9244,10 +9279,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C418" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9255,10 +9290,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C419" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9266,10 +9301,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C420" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9277,10 +9312,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C421" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9288,10 +9323,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C422" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9299,10 +9334,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C423" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9310,10 +9345,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C424" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9321,10 +9356,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C425" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9332,10 +9367,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C426" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9343,10 +9378,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C427" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9354,10 +9389,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C428" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9365,10 +9400,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="C429" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9376,10 +9411,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C430" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9387,10 +9422,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C431" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9398,10 +9433,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C432" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9409,10 +9444,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C433" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9420,10 +9455,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C434" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9431,10 +9466,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C435" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9442,10 +9477,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C436" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9453,10 +9488,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C437" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9464,10 +9499,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C438" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9475,10 +9510,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C439" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9486,10 +9521,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C440" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9497,10 +9532,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C441" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9508,10 +9543,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C442" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9519,10 +9554,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C443" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9530,10 +9565,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C444" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9541,10 +9576,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C445" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9552,10 +9587,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C446" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9563,10 +9598,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C447" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9574,10 +9609,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C448" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9585,10 +9620,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="C449" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9596,10 +9631,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C450" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9607,10 +9642,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C451" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9618,10 +9653,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="C452" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9629,10 +9664,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C453" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9640,10 +9675,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C454" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9651,10 +9686,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C455" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9662,10 +9697,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C456" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9673,10 +9708,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="C457" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9684,10 +9719,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="C458" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9695,10 +9730,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C459" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9706,7 +9741,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9714,10 +9749,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="C461" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9725,10 +9760,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="C462" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9736,10 +9771,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C463" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9747,10 +9782,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="C464" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9758,10 +9793,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C465" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9769,10 +9804,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C466" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9780,10 +9815,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="C467" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9791,10 +9826,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C468" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9802,10 +9837,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C469" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9813,10 +9848,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="C470" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9824,10 +9859,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C471" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9835,10 +9870,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="C472" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9846,10 +9881,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="C473" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9857,10 +9892,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C474" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9868,10 +9903,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C475" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9879,10 +9914,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C476" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9890,10 +9925,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C477" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9901,10 +9936,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="C478" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9912,10 +9947,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="C479" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9923,10 +9958,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="C480" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -9934,10 +9969,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="C481" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -9945,10 +9980,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="C482" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -9956,10 +9991,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="C483" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -9967,10 +10002,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="C484" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -9978,10 +10013,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C485" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -9989,10 +10024,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="C486" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10000,10 +10035,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="C487" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10011,10 +10046,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="C488" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10022,10 +10057,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="C489" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10033,10 +10068,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="C490" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10044,10 +10079,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C491" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10055,10 +10090,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C492" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10066,10 +10101,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C493" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10077,10 +10112,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C494" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10088,10 +10123,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C495" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10099,10 +10134,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C496" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10110,10 +10145,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C497" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10121,10 +10156,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C498" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10132,7 +10167,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10140,10 +10175,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="C500" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10151,10 +10186,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C501" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10162,10 +10197,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C502" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10173,10 +10208,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C503" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10184,10 +10219,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C504" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10195,10 +10230,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="C505" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10206,10 +10241,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="C506" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10217,10 +10252,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C507" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10228,10 +10263,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="C508" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10239,10 +10274,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C509" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10250,10 +10285,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="C510" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10261,10 +10296,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="C511" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10272,10 +10307,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="C512" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10283,10 +10318,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C513" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10294,10 +10329,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C514" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10305,10 +10340,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C515" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10316,10 +10351,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C516" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10327,10 +10362,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C517" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10338,7 +10373,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10346,10 +10381,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="C519" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10357,10 +10392,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C520" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10368,10 +10403,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C521" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10379,10 +10414,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="C522" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10390,10 +10425,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C523" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10401,10 +10436,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C524" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10412,10 +10447,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C525" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10423,10 +10458,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C526" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10434,10 +10469,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C527" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10445,10 +10480,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C528" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10456,10 +10491,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C529" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10467,10 +10502,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C530" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10478,10 +10513,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C531" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10489,10 +10524,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C532" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10500,10 +10535,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C533" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10511,10 +10546,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C534" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10522,10 +10557,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="C535" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10533,10 +10568,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="C536" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10544,10 +10579,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C537" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10555,10 +10590,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C538" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10566,10 +10601,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="C539" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10577,10 +10612,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="C540" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10588,10 +10623,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="C541" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10599,10 +10634,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="C542" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10610,10 +10645,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="C543" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10621,10 +10656,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="C544" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10632,10 +10667,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C545" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10643,10 +10678,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="C546" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10654,7 +10689,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10662,10 +10697,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="C548" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10673,10 +10708,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C549" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10684,10 +10719,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C550" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10695,10 +10730,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C551" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10706,10 +10741,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="C552" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10717,10 +10752,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="C553" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10728,10 +10763,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="C554" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10739,10 +10774,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="C555" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10750,10 +10785,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="C556" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10761,10 +10796,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C557" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10772,10 +10807,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C558" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10783,7 +10818,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10791,10 +10826,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="C560" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10802,10 +10837,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="C561" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10813,10 +10848,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C562" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10824,10 +10859,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C563" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10835,10 +10870,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C564" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10846,10 +10881,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C565" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10857,10 +10892,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="C566" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10868,10 +10903,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="C567" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10879,10 +10914,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C568" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10890,10 +10925,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="C569" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10901,10 +10936,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="C570" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10912,10 +10947,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="C571" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10923,10 +10958,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="C572" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10934,10 +10969,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C573" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -10945,10 +10980,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="C574" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -10956,10 +10991,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -10967,10 +11002,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C576" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -10978,10 +11013,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C577" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -10989,10 +11024,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C578" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11000,10 +11035,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="C579" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11011,10 +11046,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="C580" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11022,10 +11057,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="C581" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11033,10 +11068,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C582" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11044,10 +11079,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11055,10 +11090,10 @@
         <v>612</v>
       </c>
       <c r="B584" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C584" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11066,10 +11101,10 @@
         <v>615</v>
       </c>
       <c r="B585" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="C585" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11077,10 +11112,10 @@
         <v>617</v>
       </c>
       <c r="B586" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="C586" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11088,10 +11123,10 @@
         <v>618</v>
       </c>
       <c r="B587" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="C587" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11099,10 +11134,10 @@
         <v>625</v>
       </c>
       <c r="B588" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C588" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11110,10 +11145,10 @@
         <v>624</v>
       </c>
       <c r="B589" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="C589" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11121,10 +11156,10 @@
         <v>626</v>
       </c>
       <c r="B590" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="C590" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11132,10 +11167,10 @@
         <v>629</v>
       </c>
       <c r="B591" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="C591" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11143,10 +11178,10 @@
         <v>630</v>
       </c>
       <c r="B592" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="C592" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11154,7 +11189,7 @@
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11162,10 +11197,10 @@
         <v>633</v>
       </c>
       <c r="B594" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C594" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11173,10 +11208,10 @@
         <v>635</v>
       </c>
       <c r="B595" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C595" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11184,10 +11219,10 @@
         <v>636</v>
       </c>
       <c r="B596" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C596" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11195,10 +11230,10 @@
         <v>642</v>
       </c>
       <c r="B597" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="C597" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11206,10 +11241,10 @@
         <v>644</v>
       </c>
       <c r="B598" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="C598" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11217,10 +11252,10 @@
         <v>646</v>
       </c>
       <c r="B599" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C599" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11228,10 +11263,10 @@
         <v>649</v>
       </c>
       <c r="B600" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C600" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11239,10 +11274,10 @@
         <v>650</v>
       </c>
       <c r="B601" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11250,10 +11285,10 @@
         <v>651</v>
       </c>
       <c r="B602" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="C602" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11261,10 +11296,10 @@
         <v>653</v>
       </c>
       <c r="B603" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="C603" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11272,10 +11307,10 @@
         <v>654</v>
       </c>
       <c r="B604" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C604" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11283,10 +11318,10 @@
         <v>655</v>
       </c>
       <c r="B605" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C605" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11294,10 +11329,10 @@
         <v>659</v>
       </c>
       <c r="B606" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C606" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11305,10 +11340,10 @@
         <v>660</v>
       </c>
       <c r="B607" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="C607" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11316,10 +11351,10 @@
         <v>661</v>
       </c>
       <c r="B608" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C608" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11327,10 +11362,10 @@
         <v>663</v>
       </c>
       <c r="B609" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="C609" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11338,10 +11373,10 @@
         <v>667</v>
       </c>
       <c r="B610" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="C610" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11349,10 +11384,10 @@
         <v>670</v>
       </c>
       <c r="B611" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="C611" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11360,10 +11395,10 @@
         <v>673</v>
       </c>
       <c r="B612" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="C612" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11371,10 +11406,10 @@
         <v>674</v>
       </c>
       <c r="B613" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="C613" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11382,10 +11417,10 @@
         <v>675</v>
       </c>
       <c r="B614" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="C614" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11393,10 +11428,10 @@
         <v>680</v>
       </c>
       <c r="B615" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C615" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11404,10 +11439,10 @@
         <v>681</v>
       </c>
       <c r="B616" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C616" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11415,10 +11450,10 @@
         <v>682</v>
       </c>
       <c r="B617" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C617" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11426,10 +11461,10 @@
         <v>683</v>
       </c>
       <c r="B618" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C618" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11437,10 +11472,10 @@
         <v>684</v>
       </c>
       <c r="B619" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C619" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11448,10 +11483,10 @@
         <v>685</v>
       </c>
       <c r="B620" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="C620" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11459,10 +11494,10 @@
         <v>686</v>
       </c>
       <c r="B621" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C621" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11470,10 +11505,10 @@
         <v>689</v>
       </c>
       <c r="B622" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="C622" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11481,10 +11516,10 @@
         <v>697</v>
       </c>
       <c r="B623" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="C623" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11492,10 +11527,10 @@
         <v>701</v>
       </c>
       <c r="B624" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="C624" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11503,10 +11538,10 @@
         <v>702</v>
       </c>
       <c r="B625" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="C625" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11514,10 +11549,10 @@
         <v>704</v>
       </c>
       <c r="B626" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="C626" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11525,10 +11560,10 @@
         <v>705</v>
       </c>
       <c r="B627" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="C627" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11536,10 +11571,10 @@
         <v>710</v>
       </c>
       <c r="B628" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C628" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11547,10 +11582,10 @@
         <v>711</v>
       </c>
       <c r="B629" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C629" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11558,10 +11593,10 @@
         <v>712</v>
       </c>
       <c r="B630" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="C630" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11569,10 +11604,10 @@
         <v>714</v>
       </c>
       <c r="B631" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11580,10 +11615,10 @@
         <v>717</v>
       </c>
       <c r="B632" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="C632" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11591,10 +11626,10 @@
         <v>718</v>
       </c>
       <c r="B633" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="C633" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11602,10 +11637,10 @@
         <v>719</v>
       </c>
       <c r="B634" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="C634" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11613,10 +11648,10 @@
         <v>721</v>
       </c>
       <c r="B635" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="C635" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11624,10 +11659,10 @@
         <v>722</v>
       </c>
       <c r="B636" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C636" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11635,10 +11670,10 @@
         <v>723</v>
       </c>
       <c r="B637" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C637" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11646,10 +11681,10 @@
         <v>725</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C638" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11657,10 +11692,10 @@
         <v>726</v>
       </c>
       <c r="B639" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C639" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11668,10 +11703,10 @@
         <v>727</v>
       </c>
       <c r="B640" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C640" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11679,10 +11714,10 @@
         <v>728</v>
       </c>
       <c r="B641" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="C641" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11690,10 +11725,10 @@
         <v>729</v>
       </c>
       <c r="B642" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C642" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11701,10 +11736,10 @@
         <v>730</v>
       </c>
       <c r="B643" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="C643" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11712,10 +11747,10 @@
         <v>731</v>
       </c>
       <c r="B644" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11723,10 +11758,10 @@
         <v>733</v>
       </c>
       <c r="B645" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C645" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11734,10 +11769,10 @@
         <v>735</v>
       </c>
       <c r="B646" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C646" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11745,10 +11780,10 @@
         <v>736</v>
       </c>
       <c r="B647" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="C647" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11756,10 +11791,10 @@
         <v>737</v>
       </c>
       <c r="B648" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="C648" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11767,10 +11802,10 @@
         <v>738</v>
       </c>
       <c r="B649" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C649" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11778,10 +11813,10 @@
         <v>739</v>
       </c>
       <c r="B650" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C650" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11789,10 +11824,10 @@
         <v>740</v>
       </c>
       <c r="B651" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C651" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11800,10 +11835,10 @@
         <v>741</v>
       </c>
       <c r="B652" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C652" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11811,10 +11846,10 @@
         <v>742</v>
       </c>
       <c r="B653" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="C653" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11822,10 +11857,10 @@
         <v>743</v>
       </c>
       <c r="B654" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="C654" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11833,10 +11868,10 @@
         <v>744</v>
       </c>
       <c r="B655" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="C655" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11844,10 +11879,10 @@
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="C656" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11855,10 +11890,10 @@
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="C657" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11866,10 +11901,10 @@
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="C658" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11877,10 +11912,10 @@
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="C659" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11888,10 +11923,10 @@
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C660" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11899,10 +11934,10 @@
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="C661" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11910,10 +11945,10 @@
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="C662" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11921,10 +11956,10 @@
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="C663" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11932,10 +11967,10 @@
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="C664" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11943,10 +11978,10 @@
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C665" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -11954,10 +11989,10 @@
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="C666" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -11965,10 +12000,10 @@
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C667" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -11976,10 +12011,10 @@
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="C668" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -11987,10 +12022,10 @@
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="C669" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -11998,10 +12033,10 @@
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C670" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12009,10 +12044,10 @@
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="C671" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12020,10 +12055,10 @@
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="C672" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12037,10 +12072,10 @@
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="C674" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12049,7 +12084,7 @@
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12057,10 +12092,10 @@
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="C676" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12068,40 +12103,112 @@
         <v>772</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="C677" s="3" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678">
-        <v>10001</v>
-      </c>
-      <c r="B678" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C678" t="s">
-        <v>1331</v>
+        <v>773</v>
+      </c>
+      <c r="B678" s="1"/>
+      <c r="C678" s="3" t="s">
+        <v>1336</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679">
+        <v>774</v>
+      </c>
+      <c r="B679" s="1"/>
+      <c r="C679" s="3" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A680">
+        <v>776</v>
+      </c>
+      <c r="B680" s="1"/>
+      <c r="C680" s="3" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A681">
+        <v>779</v>
+      </c>
+      <c r="B681" s="1"/>
+      <c r="C681" s="3" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A682">
+        <v>780</v>
+      </c>
+      <c r="B682" s="1"/>
+      <c r="C682" s="3" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A683">
+        <v>781</v>
+      </c>
+      <c r="B683" s="1"/>
+      <c r="C683" s="3" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A684">
+        <v>783</v>
+      </c>
+      <c r="B684" s="1"/>
+      <c r="C684" s="3" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A685">
+        <v>784</v>
+      </c>
+      <c r="B685" s="1"/>
+      <c r="C685" s="3" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A686">
+        <v>10001</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A687">
         <v>10003</v>
       </c>
-      <c r="B679" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C679" t="s">
-        <v>1329</v>
+      <c r="B687" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1326</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A678:C678 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C113 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C344 A327 A296:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A686:C686 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A296:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23785C07-7851-4A3E-A5D1-D237AE435EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE62E693-0BBB-47D0-A7ED-248F1BDDA20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4188,10 +4188,6 @@
     <t>彩虹答辩</t>
   </si>
   <si>
-    <t>vipm,vip m,千客万来,千克万来</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>剥裤袜,僕は,bkw,bokuwa,我心危,我里危险,扎聋耳朵</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -4257,6 +4253,10 @@
   </si>
   <si>
     <t>我们的重制人生,先歌,我们重制人生</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>vipm,vip m,千客万来,千克万来,vip monster</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5927,7 +5927,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -8402,7 +8402,7 @@
         <v>673</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>674</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -10994,7 +10994,7 @@
         <v>1134</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11082,7 +11082,7 @@
         <v>1147</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1329</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11277,7 +11277,7 @@
         <v>1181</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11607,7 +11607,7 @@
         <v>1240</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11750,7 +11750,7 @@
         <v>1265</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -12103,10 +12103,10 @@
         <v>772</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C677" s="3" t="s">
         <v>1332</v>
-      </c>
-      <c r="C677" s="3" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="B679" s="1"/>
       <c r="C679" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="B680" s="1"/>
       <c r="C680" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE62E693-0BBB-47D0-A7ED-248F1BDDA20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099394C9-AB8F-4A82-B727-1B2DC3F11BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24480" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4224,10 +4224,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>金曜日,星期日的早安,星期天的早安,星期日早安,星期天早安</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>许婚</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -4257,6 +4253,10 @@
   </si>
   <si>
     <t>vipm,vip m,千客万来,千克万来,vip monster</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>金曜日,星期五的早安,星期5的早安,星期5早安,星期五早安,周五的早安,周五早安</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5927,7 +5927,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -8402,7 +8402,7 @@
         <v>673</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>674</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -11082,7 +11082,7 @@
         <v>1147</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{099394C9-AB8F-4A82-B727-1B2DC3F11BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DAC185-1300-4A53-AD2A-D85770411F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4256,7 +4256,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>金曜日,星期五的早安,星期5的早安,星期5早安,星期五早安,周五的早安,周五早安</t>
+    <t>金曜日的早晨,金曜日早安,金曜日的早安,金曜日的早安,星期五的早安,星期5的早安,星期5早安,星期五早安,周五的早安,周五早安,星期五的早晨,星期五早晨,周五早晨</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88DAC185-1300-4A53-AD2A-D85770411F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA22ED44-7BC1-41F0-9915-91E0C7321087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1835,9 +1835,6 @@
     <t>SAVIOR OF SONG</t>
   </si>
   <si>
-    <t>SOS,sos,苍蓝钢铁,效率,救救</t>
-  </si>
-  <si>
     <t>ムーンライト伝説</t>
   </si>
   <si>
@@ -4257,6 +4254,10 @@
   </si>
   <si>
     <t>金曜日的早晨,金曜日早安,金曜日的早安,金曜日的早安,星期五的早安,星期5的早安,星期5早安,星期五早安,周五的早安,周五早安,星期五的早晨,星期五早晨,周五早晨</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOS,sos,苍蓝钢铁,效率,救救,s</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5927,7 +5928,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -7939,8 +7940,8 @@
       <c r="B296" t="s">
         <v>589</v>
       </c>
-      <c r="C296" t="s">
-        <v>590</v>
+      <c r="C296" s="3" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -7948,10 +7949,10 @@
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>590</v>
+      </c>
+      <c r="C297" t="s">
         <v>591</v>
-      </c>
-      <c r="C297" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -7959,10 +7960,10 @@
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>592</v>
+      </c>
+      <c r="C298" t="s">
         <v>593</v>
-      </c>
-      <c r="C298" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -7970,10 +7971,10 @@
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>594</v>
+      </c>
+      <c r="C299" t="s">
         <v>595</v>
-      </c>
-      <c r="C299" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -7981,10 +7982,10 @@
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>596</v>
+      </c>
+      <c r="C300" t="s">
         <v>597</v>
-      </c>
-      <c r="C300" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -7992,10 +7993,10 @@
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>598</v>
+      </c>
+      <c r="C301" t="s">
         <v>599</v>
-      </c>
-      <c r="C301" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -8003,10 +8004,10 @@
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>600</v>
+      </c>
+      <c r="C302" t="s">
         <v>601</v>
-      </c>
-      <c r="C302" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -8014,10 +8015,10 @@
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>602</v>
+      </c>
+      <c r="C303" t="s">
         <v>603</v>
-      </c>
-      <c r="C303" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -8025,10 +8026,10 @@
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>604</v>
+      </c>
+      <c r="C304" t="s">
         <v>605</v>
-      </c>
-      <c r="C304" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -8036,10 +8037,10 @@
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>606</v>
+      </c>
+      <c r="C305" t="s">
         <v>607</v>
-      </c>
-      <c r="C305" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -8047,10 +8048,10 @@
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>608</v>
+      </c>
+      <c r="C306" t="s">
         <v>609</v>
-      </c>
-      <c r="C306" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -8058,10 +8059,10 @@
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>610</v>
+      </c>
+      <c r="C307" t="s">
         <v>611</v>
-      </c>
-      <c r="C307" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -8069,10 +8070,10 @@
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>612</v>
+      </c>
+      <c r="C308" t="s">
         <v>613</v>
-      </c>
-      <c r="C308" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -8080,10 +8081,10 @@
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>614</v>
+      </c>
+      <c r="C309" t="s">
         <v>615</v>
-      </c>
-      <c r="C309" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -8091,10 +8092,10 @@
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>616</v>
+      </c>
+      <c r="C310" t="s">
         <v>617</v>
-      </c>
-      <c r="C310" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -8102,10 +8103,10 @@
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>618</v>
+      </c>
+      <c r="C311" t="s">
         <v>619</v>
-      </c>
-      <c r="C311" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -8113,10 +8114,10 @@
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>620</v>
+      </c>
+      <c r="C312" t="s">
         <v>621</v>
-      </c>
-      <c r="C312" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -8124,10 +8125,10 @@
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>622</v>
+      </c>
+      <c r="C313" t="s">
         <v>623</v>
-      </c>
-      <c r="C313" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -8135,10 +8136,10 @@
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>624</v>
+      </c>
+      <c r="C314" t="s">
         <v>625</v>
-      </c>
-      <c r="C314" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -8146,10 +8147,10 @@
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>626</v>
+      </c>
+      <c r="C315" t="s">
         <v>627</v>
-      </c>
-      <c r="C315" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -8157,10 +8158,10 @@
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>628</v>
+      </c>
+      <c r="C316" t="s">
         <v>629</v>
-      </c>
-      <c r="C316" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -8168,10 +8169,10 @@
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>630</v>
+      </c>
+      <c r="C317" t="s">
         <v>631</v>
-      </c>
-      <c r="C317" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -8179,10 +8180,10 @@
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>632</v>
+      </c>
+      <c r="C318" t="s">
         <v>633</v>
-      </c>
-      <c r="C318" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -8190,10 +8191,10 @@
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>634</v>
+      </c>
+      <c r="C319" t="s">
         <v>635</v>
-      </c>
-      <c r="C319" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -8201,10 +8202,10 @@
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>636</v>
+      </c>
+      <c r="C320" t="s">
         <v>637</v>
-      </c>
-      <c r="C320" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -8212,10 +8213,10 @@
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>638</v>
+      </c>
+      <c r="C321" t="s">
         <v>639</v>
-      </c>
-      <c r="C321" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -8223,10 +8224,10 @@
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>640</v>
+      </c>
+      <c r="C322" t="s">
         <v>641</v>
-      </c>
-      <c r="C322" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -8234,10 +8235,10 @@
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>642</v>
+      </c>
+      <c r="C323" t="s">
         <v>643</v>
-      </c>
-      <c r="C323" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -8245,10 +8246,10 @@
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>644</v>
+      </c>
+      <c r="C324" t="s">
         <v>645</v>
-      </c>
-      <c r="C324" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -8256,10 +8257,10 @@
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>646</v>
+      </c>
+      <c r="C325" t="s">
         <v>647</v>
-      </c>
-      <c r="C325" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -8267,10 +8268,10 @@
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>648</v>
+      </c>
+      <c r="C326" t="s">
         <v>649</v>
-      </c>
-      <c r="C326" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -8278,10 +8279,10 @@
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>650</v>
+      </c>
+      <c r="C327" t="s">
         <v>651</v>
-      </c>
-      <c r="C327" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -8289,10 +8290,10 @@
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>652</v>
+      </c>
+      <c r="C328" t="s">
         <v>653</v>
-      </c>
-      <c r="C328" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -8300,10 +8301,10 @@
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>654</v>
+      </c>
+      <c r="C329" t="s">
         <v>655</v>
-      </c>
-      <c r="C329" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -8311,10 +8312,10 @@
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>656</v>
+      </c>
+      <c r="C330" t="s">
         <v>657</v>
-      </c>
-      <c r="C330" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -8322,10 +8323,10 @@
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>658</v>
+      </c>
+      <c r="C331" t="s">
         <v>659</v>
-      </c>
-      <c r="C331" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -8333,10 +8334,10 @@
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>660</v>
+      </c>
+      <c r="C332" t="s">
         <v>661</v>
-      </c>
-      <c r="C332" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -8344,10 +8345,10 @@
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>662</v>
+      </c>
+      <c r="C333" t="s">
         <v>663</v>
-      </c>
-      <c r="C333" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -8355,10 +8356,10 @@
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>664</v>
+      </c>
+      <c r="C334" t="s">
         <v>665</v>
-      </c>
-      <c r="C334" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -8366,10 +8367,10 @@
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>666</v>
+      </c>
+      <c r="C335" t="s">
         <v>667</v>
-      </c>
-      <c r="C335" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -8377,10 +8378,10 @@
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>668</v>
+      </c>
+      <c r="C336" t="s">
         <v>669</v>
-      </c>
-      <c r="C336" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -8388,10 +8389,10 @@
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>670</v>
+      </c>
+      <c r="C337" t="s">
         <v>671</v>
-      </c>
-      <c r="C337" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -8399,10 +8400,10 @@
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8410,10 +8411,10 @@
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -8421,10 +8422,10 @@
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>674</v>
+      </c>
+      <c r="C340" t="s">
         <v>675</v>
-      </c>
-      <c r="C340" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -8432,10 +8433,10 @@
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>676</v>
+      </c>
+      <c r="C341" t="s">
         <v>677</v>
-      </c>
-      <c r="C341" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -8443,10 +8444,10 @@
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>678</v>
+      </c>
+      <c r="C342" t="s">
         <v>679</v>
-      </c>
-      <c r="C342" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -8454,10 +8455,10 @@
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>680</v>
+      </c>
+      <c r="C343" t="s">
         <v>681</v>
-      </c>
-      <c r="C343" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -8465,10 +8466,10 @@
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>682</v>
+      </c>
+      <c r="C344" t="s">
         <v>683</v>
-      </c>
-      <c r="C344" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -8476,10 +8477,10 @@
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>684</v>
+      </c>
+      <c r="C345" t="s">
         <v>685</v>
-      </c>
-      <c r="C345" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -8487,10 +8488,10 @@
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>686</v>
+      </c>
+      <c r="C346" t="s">
         <v>687</v>
-      </c>
-      <c r="C346" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -8498,10 +8499,10 @@
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>688</v>
+      </c>
+      <c r="C347" t="s">
         <v>689</v>
-      </c>
-      <c r="C347" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -8509,10 +8510,10 @@
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>690</v>
+      </c>
+      <c r="C348" t="s">
         <v>691</v>
-      </c>
-      <c r="C348" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -8520,10 +8521,10 @@
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>692</v>
+      </c>
+      <c r="C349" t="s">
         <v>693</v>
-      </c>
-      <c r="C349" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -8531,10 +8532,10 @@
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>694</v>
+      </c>
+      <c r="C350" t="s">
         <v>695</v>
-      </c>
-      <c r="C350" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -8542,10 +8543,10 @@
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>696</v>
+      </c>
+      <c r="C351" t="s">
         <v>697</v>
-      </c>
-      <c r="C351" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -8553,10 +8554,10 @@
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>698</v>
+      </c>
+      <c r="C352" t="s">
         <v>699</v>
-      </c>
-      <c r="C352" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -8564,10 +8565,10 @@
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>700</v>
+      </c>
+      <c r="C353" t="s">
         <v>701</v>
-      </c>
-      <c r="C353" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -8575,10 +8576,10 @@
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>702</v>
+      </c>
+      <c r="C354" t="s">
         <v>703</v>
-      </c>
-      <c r="C354" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
@@ -8586,10 +8587,10 @@
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>704</v>
+      </c>
+      <c r="C355" t="s">
         <v>705</v>
-      </c>
-      <c r="C355" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -8597,10 +8598,10 @@
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>706</v>
+      </c>
+      <c r="C356" t="s">
         <v>707</v>
-      </c>
-      <c r="C356" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
@@ -8608,10 +8609,10 @@
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>708</v>
+      </c>
+      <c r="C357" t="s">
         <v>709</v>
-      </c>
-      <c r="C357" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -8619,10 +8620,10 @@
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>710</v>
+      </c>
+      <c r="C358" t="s">
         <v>711</v>
-      </c>
-      <c r="C358" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
@@ -8630,10 +8631,10 @@
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>712</v>
+      </c>
+      <c r="C359" t="s">
         <v>713</v>
-      </c>
-      <c r="C359" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -8641,10 +8642,10 @@
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>714</v>
+      </c>
+      <c r="C360" t="s">
         <v>715</v>
-      </c>
-      <c r="C360" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
@@ -8652,10 +8653,10 @@
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>716</v>
+      </c>
+      <c r="C361" t="s">
         <v>717</v>
-      </c>
-      <c r="C361" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
@@ -8663,10 +8664,10 @@
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>718</v>
+      </c>
+      <c r="C362" t="s">
         <v>719</v>
-      </c>
-      <c r="C362" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -8674,10 +8675,10 @@
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>720</v>
+      </c>
+      <c r="C363" t="s">
         <v>721</v>
-      </c>
-      <c r="C363" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
@@ -8685,10 +8686,10 @@
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>722</v>
+      </c>
+      <c r="C364" t="s">
         <v>723</v>
-      </c>
-      <c r="C364" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
@@ -8696,10 +8697,10 @@
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>724</v>
+      </c>
+      <c r="C365" t="s">
         <v>725</v>
-      </c>
-      <c r="C365" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
@@ -8707,10 +8708,10 @@
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>726</v>
+      </c>
+      <c r="C366" t="s">
         <v>727</v>
-      </c>
-      <c r="C366" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
@@ -8718,10 +8719,10 @@
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>728</v>
+      </c>
+      <c r="C367" t="s">
         <v>729</v>
-      </c>
-      <c r="C367" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
@@ -8729,10 +8730,10 @@
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>730</v>
+      </c>
+      <c r="C368" t="s">
         <v>731</v>
-      </c>
-      <c r="C368" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
@@ -8740,10 +8741,10 @@
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>732</v>
+      </c>
+      <c r="C369" t="s">
         <v>733</v>
-      </c>
-      <c r="C369" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
@@ -8751,10 +8752,10 @@
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>734</v>
+      </c>
+      <c r="C370" t="s">
         <v>735</v>
-      </c>
-      <c r="C370" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
@@ -8762,10 +8763,10 @@
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>736</v>
+      </c>
+      <c r="C371" t="s">
         <v>737</v>
-      </c>
-      <c r="C371" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
@@ -8773,10 +8774,10 @@
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>738</v>
+      </c>
+      <c r="C372" t="s">
         <v>739</v>
-      </c>
-      <c r="C372" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
@@ -8784,10 +8785,10 @@
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>740</v>
+      </c>
+      <c r="C373" t="s">
         <v>741</v>
-      </c>
-      <c r="C373" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -8795,10 +8796,10 @@
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>742</v>
+      </c>
+      <c r="C374" t="s">
         <v>743</v>
-      </c>
-      <c r="C374" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -8806,10 +8807,10 @@
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>744</v>
+      </c>
+      <c r="C375" t="s">
         <v>745</v>
-      </c>
-      <c r="C375" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
@@ -8817,10 +8818,10 @@
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>746</v>
+      </c>
+      <c r="C376" t="s">
         <v>747</v>
-      </c>
-      <c r="C376" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
@@ -8828,10 +8829,10 @@
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>748</v>
+      </c>
+      <c r="C377" t="s">
         <v>749</v>
-      </c>
-      <c r="C377" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
@@ -8839,10 +8840,10 @@
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>750</v>
+      </c>
+      <c r="C378" t="s">
         <v>751</v>
-      </c>
-      <c r="C378" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -8850,10 +8851,10 @@
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>752</v>
+      </c>
+      <c r="C379" t="s">
         <v>753</v>
-      </c>
-      <c r="C379" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
@@ -8861,10 +8862,10 @@
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>754</v>
+      </c>
+      <c r="C380" t="s">
         <v>755</v>
-      </c>
-      <c r="C380" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
@@ -8872,10 +8873,10 @@
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>756</v>
+      </c>
+      <c r="C381" t="s">
         <v>757</v>
-      </c>
-      <c r="C381" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
@@ -8883,10 +8884,10 @@
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>758</v>
+      </c>
+      <c r="C382" t="s">
         <v>759</v>
-      </c>
-      <c r="C382" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
@@ -8894,10 +8895,10 @@
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>760</v>
+      </c>
+      <c r="C383" t="s">
         <v>761</v>
-      </c>
-      <c r="C383" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
@@ -8905,10 +8906,10 @@
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>762</v>
+      </c>
+      <c r="C384" t="s">
         <v>763</v>
-      </c>
-      <c r="C384" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
@@ -8916,10 +8917,10 @@
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>764</v>
+      </c>
+      <c r="C385" t="s">
         <v>765</v>
-      </c>
-      <c r="C385" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -8927,10 +8928,10 @@
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>766</v>
+      </c>
+      <c r="C386" t="s">
         <v>767</v>
-      </c>
-      <c r="C386" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -8938,10 +8939,10 @@
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>768</v>
+      </c>
+      <c r="C387" t="s">
         <v>769</v>
-      </c>
-      <c r="C387" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
@@ -8949,10 +8950,10 @@
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>770</v>
+      </c>
+      <c r="C388" t="s">
         <v>771</v>
-      </c>
-      <c r="C388" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
@@ -8960,10 +8961,10 @@
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>772</v>
+      </c>
+      <c r="C389" t="s">
         <v>773</v>
-      </c>
-      <c r="C389" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -8971,10 +8972,10 @@
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>774</v>
+      </c>
+      <c r="C390" t="s">
         <v>775</v>
-      </c>
-      <c r="C390" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
@@ -8982,10 +8983,10 @@
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>776</v>
+      </c>
+      <c r="C391" t="s">
         <v>777</v>
-      </c>
-      <c r="C391" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -8993,10 +8994,10 @@
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>778</v>
+      </c>
+      <c r="C392" t="s">
         <v>779</v>
-      </c>
-      <c r="C392" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
@@ -9004,10 +9005,10 @@
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>780</v>
+      </c>
+      <c r="C393" t="s">
         <v>781</v>
-      </c>
-      <c r="C393" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
@@ -9015,10 +9016,10 @@
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>782</v>
+      </c>
+      <c r="C394" t="s">
         <v>783</v>
-      </c>
-      <c r="C394" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -9026,10 +9027,10 @@
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>784</v>
+      </c>
+      <c r="C395" t="s">
         <v>785</v>
-      </c>
-      <c r="C395" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
@@ -9037,10 +9038,10 @@
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>786</v>
+      </c>
+      <c r="C396" t="s">
         <v>787</v>
-      </c>
-      <c r="C396" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
@@ -9048,10 +9049,10 @@
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>788</v>
+      </c>
+      <c r="C397" t="s">
         <v>789</v>
-      </c>
-      <c r="C397" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
@@ -9059,10 +9060,10 @@
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>790</v>
+      </c>
+      <c r="C398" t="s">
         <v>791</v>
-      </c>
-      <c r="C398" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
@@ -9070,10 +9071,10 @@
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>792</v>
+      </c>
+      <c r="C399" t="s">
         <v>793</v>
-      </c>
-      <c r="C399" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -9081,10 +9082,10 @@
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>794</v>
+      </c>
+      <c r="C400" t="s">
         <v>795</v>
-      </c>
-      <c r="C400" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
@@ -9092,10 +9093,10 @@
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>796</v>
+      </c>
+      <c r="C401" t="s">
         <v>797</v>
-      </c>
-      <c r="C401" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -9103,10 +9104,10 @@
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>798</v>
+      </c>
+      <c r="C402" t="s">
         <v>799</v>
-      </c>
-      <c r="C402" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
@@ -9114,10 +9115,10 @@
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>800</v>
+      </c>
+      <c r="C403" t="s">
         <v>801</v>
-      </c>
-      <c r="C403" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
@@ -9125,10 +9126,10 @@
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>802</v>
+      </c>
+      <c r="C404" t="s">
         <v>803</v>
-      </c>
-      <c r="C404" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
@@ -9136,10 +9137,10 @@
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>804</v>
+      </c>
+      <c r="C405" t="s">
         <v>805</v>
-      </c>
-      <c r="C405" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
@@ -9147,10 +9148,10 @@
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>806</v>
+      </c>
+      <c r="C406" t="s">
         <v>807</v>
-      </c>
-      <c r="C406" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
@@ -9158,10 +9159,10 @@
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>808</v>
+      </c>
+      <c r="C407" t="s">
         <v>809</v>
-      </c>
-      <c r="C407" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
@@ -9169,10 +9170,10 @@
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>810</v>
+      </c>
+      <c r="C408" t="s">
         <v>811</v>
-      </c>
-      <c r="C408" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -9180,10 +9181,10 @@
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>812</v>
+      </c>
+      <c r="C409" t="s">
         <v>813</v>
-      </c>
-      <c r="C409" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -9191,10 +9192,10 @@
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>814</v>
+      </c>
+      <c r="C410" t="s">
         <v>815</v>
-      </c>
-      <c r="C410" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
@@ -9202,10 +9203,10 @@
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>816</v>
+      </c>
+      <c r="C411" t="s">
         <v>817</v>
-      </c>
-      <c r="C411" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
@@ -9213,10 +9214,10 @@
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>818</v>
+      </c>
+      <c r="C412" t="s">
         <v>819</v>
-      </c>
-      <c r="C412" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
@@ -9224,10 +9225,10 @@
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>820</v>
+      </c>
+      <c r="C413" t="s">
         <v>821</v>
-      </c>
-      <c r="C413" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
@@ -9235,10 +9236,10 @@
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>822</v>
+      </c>
+      <c r="C414" t="s">
         <v>823</v>
-      </c>
-      <c r="C414" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
@@ -9246,10 +9247,10 @@
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>824</v>
+      </c>
+      <c r="C415" t="s">
         <v>825</v>
-      </c>
-      <c r="C415" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -9257,10 +9258,10 @@
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>826</v>
+      </c>
+      <c r="C416" t="s">
         <v>827</v>
-      </c>
-      <c r="C416" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
@@ -9268,10 +9269,10 @@
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>828</v>
+      </c>
+      <c r="C417" t="s">
         <v>829</v>
-      </c>
-      <c r="C417" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
@@ -9279,10 +9280,10 @@
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>830</v>
+      </c>
+      <c r="C418" t="s">
         <v>831</v>
-      </c>
-      <c r="C418" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
@@ -9290,10 +9291,10 @@
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>832</v>
+      </c>
+      <c r="C419" t="s">
         <v>833</v>
-      </c>
-      <c r="C419" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -9301,10 +9302,10 @@
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>834</v>
+      </c>
+      <c r="C420" t="s">
         <v>835</v>
-      </c>
-      <c r="C420" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
@@ -9312,10 +9313,10 @@
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>836</v>
+      </c>
+      <c r="C421" t="s">
         <v>837</v>
-      </c>
-      <c r="C421" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -9323,10 +9324,10 @@
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>838</v>
+      </c>
+      <c r="C422" t="s">
         <v>839</v>
-      </c>
-      <c r="C422" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
@@ -9334,10 +9335,10 @@
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>840</v>
+      </c>
+      <c r="C423" t="s">
         <v>841</v>
-      </c>
-      <c r="C423" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
@@ -9345,10 +9346,10 @@
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>842</v>
+      </c>
+      <c r="C424" t="s">
         <v>843</v>
-      </c>
-      <c r="C424" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
@@ -9356,10 +9357,10 @@
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>844</v>
+      </c>
+      <c r="C425" t="s">
         <v>845</v>
-      </c>
-      <c r="C425" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
@@ -9367,10 +9368,10 @@
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>846</v>
+      </c>
+      <c r="C426" t="s">
         <v>847</v>
-      </c>
-      <c r="C426" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
@@ -9378,10 +9379,10 @@
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>848</v>
+      </c>
+      <c r="C427" t="s">
         <v>849</v>
-      </c>
-      <c r="C427" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
@@ -9389,10 +9390,10 @@
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C428" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
@@ -9400,10 +9401,10 @@
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C429" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
@@ -9411,10 +9412,10 @@
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>852</v>
+      </c>
+      <c r="C430" t="s">
         <v>853</v>
-      </c>
-      <c r="C430" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
@@ -9422,10 +9423,10 @@
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>854</v>
+      </c>
+      <c r="C431" t="s">
         <v>855</v>
-      </c>
-      <c r="C431" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -9433,10 +9434,10 @@
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>856</v>
+      </c>
+      <c r="C432" t="s">
         <v>857</v>
-      </c>
-      <c r="C432" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
@@ -9444,10 +9445,10 @@
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>858</v>
+      </c>
+      <c r="C433" t="s">
         <v>859</v>
-      </c>
-      <c r="C433" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -9455,10 +9456,10 @@
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>860</v>
+      </c>
+      <c r="C434" t="s">
         <v>861</v>
-      </c>
-      <c r="C434" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
@@ -9466,10 +9467,10 @@
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>862</v>
+      </c>
+      <c r="C435" t="s">
         <v>863</v>
-      </c>
-      <c r="C435" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
@@ -9477,10 +9478,10 @@
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>864</v>
+      </c>
+      <c r="C436" t="s">
         <v>865</v>
-      </c>
-      <c r="C436" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
@@ -9488,10 +9489,10 @@
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>866</v>
+      </c>
+      <c r="C437" t="s">
         <v>867</v>
-      </c>
-      <c r="C437" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -9499,10 +9500,10 @@
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>868</v>
+      </c>
+      <c r="C438" t="s">
         <v>869</v>
-      </c>
-      <c r="C438" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
@@ -9510,10 +9511,10 @@
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>870</v>
+      </c>
+      <c r="C439" t="s">
         <v>871</v>
-      </c>
-      <c r="C439" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
@@ -9521,10 +9522,10 @@
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>872</v>
+      </c>
+      <c r="C440" t="s">
         <v>873</v>
-      </c>
-      <c r="C440" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -9532,10 +9533,10 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>874</v>
+      </c>
+      <c r="C441" t="s">
         <v>875</v>
-      </c>
-      <c r="C441" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -9543,10 +9544,10 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>876</v>
+      </c>
+      <c r="C442" t="s">
         <v>877</v>
-      </c>
-      <c r="C442" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -9554,10 +9555,10 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>878</v>
+      </c>
+      <c r="C443" t="s">
         <v>879</v>
-      </c>
-      <c r="C443" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
@@ -9565,10 +9566,10 @@
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>880</v>
+      </c>
+      <c r="C444" t="s">
         <v>881</v>
-      </c>
-      <c r="C444" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
@@ -9576,10 +9577,10 @@
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>882</v>
+      </c>
+      <c r="C445" t="s">
         <v>883</v>
-      </c>
-      <c r="C445" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
@@ -9587,10 +9588,10 @@
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>884</v>
+      </c>
+      <c r="C446" t="s">
         <v>885</v>
-      </c>
-      <c r="C446" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
@@ -9598,10 +9599,10 @@
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>886</v>
+      </c>
+      <c r="C447" t="s">
         <v>887</v>
-      </c>
-      <c r="C447" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
@@ -9609,10 +9610,10 @@
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>888</v>
+      </c>
+      <c r="C448" t="s">
         <v>889</v>
-      </c>
-      <c r="C448" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
@@ -9620,10 +9621,10 @@
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>890</v>
+      </c>
+      <c r="C449" t="s">
         <v>891</v>
-      </c>
-      <c r="C449" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
@@ -9631,10 +9632,10 @@
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>892</v>
+      </c>
+      <c r="C450" t="s">
         <v>893</v>
-      </c>
-      <c r="C450" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
@@ -9642,10 +9643,10 @@
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C451" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
@@ -9653,10 +9654,10 @@
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>895</v>
+      </c>
+      <c r="C452" t="s">
         <v>896</v>
-      </c>
-      <c r="C452" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
@@ -9664,10 +9665,10 @@
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>897</v>
+      </c>
+      <c r="C453" t="s">
         <v>898</v>
-      </c>
-      <c r="C453" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
@@ -9675,10 +9676,10 @@
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>899</v>
+      </c>
+      <c r="C454" t="s">
         <v>900</v>
-      </c>
-      <c r="C454" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
@@ -9686,10 +9687,10 @@
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>901</v>
+      </c>
+      <c r="C455" t="s">
         <v>902</v>
-      </c>
-      <c r="C455" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
@@ -9697,10 +9698,10 @@
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C456" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -9708,10 +9709,10 @@
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>904</v>
+      </c>
+      <c r="C457" t="s">
         <v>905</v>
-      </c>
-      <c r="C457" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
@@ -9719,10 +9720,10 @@
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>906</v>
+      </c>
+      <c r="C458" t="s">
         <v>907</v>
-      </c>
-      <c r="C458" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
@@ -9730,10 +9731,10 @@
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>908</v>
+      </c>
+      <c r="C459" t="s">
         <v>909</v>
-      </c>
-      <c r="C459" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
@@ -9741,7 +9742,7 @@
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -9749,10 +9750,10 @@
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>911</v>
+      </c>
+      <c r="C461" t="s">
         <v>912</v>
-      </c>
-      <c r="C461" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -9760,10 +9761,10 @@
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>913</v>
+      </c>
+      <c r="C462" t="s">
         <v>914</v>
-      </c>
-      <c r="C462" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
@@ -9771,10 +9772,10 @@
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>915</v>
+      </c>
+      <c r="C463" t="s">
         <v>916</v>
-      </c>
-      <c r="C463" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -9782,10 +9783,10 @@
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>917</v>
+      </c>
+      <c r="C464" t="s">
         <v>918</v>
-      </c>
-      <c r="C464" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
@@ -9793,10 +9794,10 @@
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>919</v>
+      </c>
+      <c r="C465" t="s">
         <v>920</v>
-      </c>
-      <c r="C465" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
@@ -9804,10 +9805,10 @@
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>921</v>
+      </c>
+      <c r="C466" t="s">
         <v>922</v>
-      </c>
-      <c r="C466" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -9815,10 +9816,10 @@
         <v>478</v>
       </c>
       <c r="B467" t="s">
+        <v>923</v>
+      </c>
+      <c r="C467" t="s">
         <v>924</v>
-      </c>
-      <c r="C467" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9826,10 +9827,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>925</v>
+      </c>
+      <c r="C468" t="s">
         <v>926</v>
-      </c>
-      <c r="C468" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9837,10 +9838,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>927</v>
+      </c>
+      <c r="C469" t="s">
         <v>928</v>
-      </c>
-      <c r="C469" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9848,10 +9849,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>929</v>
+      </c>
+      <c r="C470" t="s">
         <v>930</v>
-      </c>
-      <c r="C470" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9859,10 +9860,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>931</v>
+      </c>
+      <c r="C471" t="s">
         <v>932</v>
-      </c>
-      <c r="C471" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9870,10 +9871,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>933</v>
+      </c>
+      <c r="C472" t="s">
         <v>934</v>
-      </c>
-      <c r="C472" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9881,10 +9882,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>935</v>
+      </c>
+      <c r="C473" t="s">
         <v>936</v>
-      </c>
-      <c r="C473" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9892,10 +9893,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>937</v>
+      </c>
+      <c r="C474" t="s">
         <v>938</v>
-      </c>
-      <c r="C474" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9903,10 +9904,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>939</v>
+      </c>
+      <c r="C475" t="s">
         <v>940</v>
-      </c>
-      <c r="C475" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9914,10 +9915,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>941</v>
+      </c>
+      <c r="C476" t="s">
         <v>942</v>
-      </c>
-      <c r="C476" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9925,10 +9926,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>943</v>
+      </c>
+      <c r="C477" t="s">
         <v>944</v>
-      </c>
-      <c r="C477" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9936,10 +9937,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C478" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9947,10 +9948,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>946</v>
+      </c>
+      <c r="C479" t="s">
         <v>947</v>
-      </c>
-      <c r="C479" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9958,10 +9959,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>948</v>
+      </c>
+      <c r="C480" t="s">
         <v>949</v>
-      </c>
-      <c r="C480" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -9969,10 +9970,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>950</v>
+      </c>
+      <c r="C481" t="s">
         <v>951</v>
-      </c>
-      <c r="C481" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -9980,10 +9981,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>952</v>
+      </c>
+      <c r="C482" t="s">
         <v>953</v>
-      </c>
-      <c r="C482" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -9991,10 +9992,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>954</v>
+      </c>
+      <c r="C483" t="s">
         <v>955</v>
-      </c>
-      <c r="C483" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10002,10 +10003,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>956</v>
+      </c>
+      <c r="C484" t="s">
         <v>957</v>
-      </c>
-      <c r="C484" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10013,10 +10014,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>958</v>
+      </c>
+      <c r="C485" t="s">
         <v>959</v>
-      </c>
-      <c r="C485" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10024,10 +10025,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>960</v>
+      </c>
+      <c r="C486" t="s">
         <v>961</v>
-      </c>
-      <c r="C486" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10035,10 +10036,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>962</v>
+      </c>
+      <c r="C487" t="s">
         <v>963</v>
-      </c>
-      <c r="C487" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10046,10 +10047,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>964</v>
+      </c>
+      <c r="C488" t="s">
         <v>965</v>
-      </c>
-      <c r="C488" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10057,10 +10058,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>966</v>
+      </c>
+      <c r="C489" t="s">
         <v>967</v>
-      </c>
-      <c r="C489" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10068,10 +10069,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>968</v>
+      </c>
+      <c r="C490" t="s">
         <v>969</v>
-      </c>
-      <c r="C490" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10079,10 +10080,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>970</v>
+      </c>
+      <c r="C491" t="s">
         <v>971</v>
-      </c>
-      <c r="C491" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10090,10 +10091,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>972</v>
+      </c>
+      <c r="C492" t="s">
         <v>973</v>
-      </c>
-      <c r="C492" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10101,10 +10102,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>974</v>
+      </c>
+      <c r="C493" t="s">
         <v>975</v>
-      </c>
-      <c r="C493" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10112,10 +10113,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>976</v>
+      </c>
+      <c r="C494" t="s">
         <v>977</v>
-      </c>
-      <c r="C494" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10123,10 +10124,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>978</v>
+      </c>
+      <c r="C495" t="s">
         <v>979</v>
-      </c>
-      <c r="C495" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10134,10 +10135,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>980</v>
+      </c>
+      <c r="C496" t="s">
         <v>981</v>
-      </c>
-      <c r="C496" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10145,10 +10146,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>982</v>
+      </c>
+      <c r="C497" t="s">
         <v>983</v>
-      </c>
-      <c r="C497" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10156,10 +10157,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>984</v>
+      </c>
+      <c r="C498" t="s">
         <v>985</v>
-      </c>
-      <c r="C498" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10167,7 +10168,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10175,10 +10176,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>987</v>
+      </c>
+      <c r="C500" t="s">
         <v>988</v>
-      </c>
-      <c r="C500" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10186,10 +10187,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>989</v>
+      </c>
+      <c r="C501" t="s">
         <v>990</v>
-      </c>
-      <c r="C501" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10197,10 +10198,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>991</v>
+      </c>
+      <c r="C502" t="s">
         <v>992</v>
-      </c>
-      <c r="C502" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10208,10 +10209,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
+        <v>993</v>
+      </c>
+      <c r="C503" t="s">
         <v>994</v>
-      </c>
-      <c r="C503" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10219,10 +10220,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>995</v>
+      </c>
+      <c r="C504" t="s">
         <v>996</v>
-      </c>
-      <c r="C504" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10230,10 +10231,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>997</v>
+      </c>
+      <c r="C505" t="s">
         <v>998</v>
-      </c>
-      <c r="C505" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10241,10 +10242,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>999</v>
+      </c>
+      <c r="C506" t="s">
         <v>1000</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10252,10 +10253,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C507" t="s">
         <v>1002</v>
-      </c>
-      <c r="C507" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10263,10 +10264,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C508" t="s">
         <v>1004</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10274,10 +10275,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C509" t="s">
         <v>1006</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10285,10 +10286,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C510" t="s">
         <v>1008</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10296,10 +10297,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C511" t="s">
         <v>1010</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10307,10 +10308,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C512" t="s">
         <v>1012</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10318,10 +10319,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C513" t="s">
         <v>1014</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10329,10 +10330,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C514" t="s">
         <v>1016</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10340,10 +10341,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C515" t="s">
         <v>1018</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10351,10 +10352,10 @@
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C516" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10362,10 +10363,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C517" t="s">
         <v>1021</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10373,7 +10374,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10381,10 +10382,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C519" t="s">
         <v>1024</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10392,10 +10393,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C520" t="s">
         <v>1026</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10403,10 +10404,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C521" t="s">
         <v>1028</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10414,10 +10415,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C522" t="s">
         <v>1030</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10425,10 +10426,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C523" t="s">
         <v>1032</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10436,10 +10437,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C524" t="s">
         <v>1034</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10447,10 +10448,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C525" t="s">
         <v>1036</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10458,10 +10459,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C526" t="s">
         <v>1038</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10469,10 +10470,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C527" t="s">
         <v>1040</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10480,10 +10481,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C528" t="s">
         <v>1042</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10491,10 +10492,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C529" t="s">
         <v>1044</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10502,10 +10503,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C530" t="s">
         <v>1046</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10513,10 +10514,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C531" t="s">
         <v>1048</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10524,10 +10525,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C532" t="s">
         <v>1050</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10535,10 +10536,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C533" t="s">
         <v>1052</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10546,10 +10547,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C534" t="s">
         <v>1054</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10557,10 +10558,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C535" t="s">
         <v>1056</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10568,10 +10569,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C536" t="s">
         <v>1058</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10579,10 +10580,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C537" t="s">
         <v>1060</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10590,10 +10591,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C538" t="s">
         <v>1062</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10601,10 +10602,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C539" t="s">
         <v>1064</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10612,10 +10613,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C540" t="s">
         <v>1066</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10623,10 +10624,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C541" t="s">
         <v>1068</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10634,10 +10635,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C542" t="s">
         <v>1070</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10645,10 +10646,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C543" t="s">
         <v>1072</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10656,10 +10657,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C544" t="s">
         <v>1074</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10667,10 +10668,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C545" t="s">
         <v>1076</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10678,10 +10679,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C546" t="s">
         <v>1078</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10689,7 +10690,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10697,10 +10698,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C548" t="s">
         <v>1081</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10708,10 +10709,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C549" t="s">
         <v>1083</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10719,10 +10720,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C550" t="s">
         <v>1085</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10730,10 +10731,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C551" t="s">
         <v>1087</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1088</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10741,10 +10742,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C552" t="s">
         <v>1089</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1090</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10752,10 +10753,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C553" t="s">
         <v>1091</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10763,10 +10764,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C554" t="s">
         <v>1093</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10774,10 +10775,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C555" t="s">
         <v>1095</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10785,10 +10786,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C556" t="s">
         <v>1097</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10796,10 +10797,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C557" t="s">
         <v>1099</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10807,10 +10808,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C558" t="s">
         <v>1101</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10818,7 +10819,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10826,10 +10827,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C560" t="s">
         <v>1104</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10837,10 +10838,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C561" t="s">
         <v>1106</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1107</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10848,10 +10849,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C562" t="s">
         <v>1108</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10859,10 +10860,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C563" t="s">
         <v>1110</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10870,10 +10871,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C564" t="s">
         <v>1112</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10881,10 +10882,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C565" t="s">
         <v>1114</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10892,10 +10893,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C566" t="s">
         <v>1116</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10903,10 +10904,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C567" t="s">
         <v>1118</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10914,10 +10915,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C568" t="s">
         <v>1120</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10925,10 +10926,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C569" t="s">
         <v>1122</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10936,10 +10937,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C570" t="s">
         <v>1124</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10947,10 +10948,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C571" t="s">
         <v>1126</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10958,10 +10959,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C572" t="s">
         <v>1128</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10969,10 +10970,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C573" t="s">
         <v>1130</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -10980,10 +10981,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C574" t="s">
         <v>1132</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -10991,10 +10992,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11002,10 +11003,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C576" t="s">
         <v>1135</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11013,10 +11014,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C577" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11024,10 +11025,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C578" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11035,10 +11036,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C579" t="s">
         <v>1139</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11046,10 +11047,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C580" t="s">
         <v>1141</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11057,10 +11058,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C581" t="s">
         <v>1143</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11068,10 +11069,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C582" t="s">
         <v>1145</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11079,10 +11080,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11090,10 +11091,10 @@
         <v>612</v>
       </c>
       <c r="B584" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C584" t="s">
         <v>1148</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11101,10 +11102,10 @@
         <v>615</v>
       </c>
       <c r="B585" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C585" t="s">
         <v>1150</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11112,10 +11113,10 @@
         <v>617</v>
       </c>
       <c r="B586" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C586" t="s">
         <v>1152</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11123,10 +11124,10 @@
         <v>618</v>
       </c>
       <c r="B587" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C587" t="s">
         <v>1154</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11134,10 +11135,10 @@
         <v>625</v>
       </c>
       <c r="B588" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C588" t="s">
         <v>1156</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11145,10 +11146,10 @@
         <v>624</v>
       </c>
       <c r="B589" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C589" t="s">
         <v>1158</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11156,10 +11157,10 @@
         <v>626</v>
       </c>
       <c r="B590" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C590" t="s">
         <v>1160</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11167,10 +11168,10 @@
         <v>629</v>
       </c>
       <c r="B591" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C591" t="s">
         <v>1162</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11178,10 +11179,10 @@
         <v>630</v>
       </c>
       <c r="B592" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C592" t="s">
         <v>1164</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11189,7 +11190,7 @@
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11197,10 +11198,10 @@
         <v>633</v>
       </c>
       <c r="B594" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C594" t="s">
         <v>1167</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11208,10 +11209,10 @@
         <v>635</v>
       </c>
       <c r="B595" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C595" t="s">
         <v>1169</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11219,10 +11220,10 @@
         <v>636</v>
       </c>
       <c r="B596" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C596" t="s">
         <v>1171</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11230,10 +11231,10 @@
         <v>642</v>
       </c>
       <c r="B597" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C597" t="s">
         <v>1173</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11241,10 +11242,10 @@
         <v>644</v>
       </c>
       <c r="B598" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C598" t="s">
         <v>1175</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11252,10 +11253,10 @@
         <v>646</v>
       </c>
       <c r="B599" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C599" t="s">
         <v>1177</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11263,10 +11264,10 @@
         <v>649</v>
       </c>
       <c r="B600" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C600" t="s">
         <v>1179</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11274,10 +11275,10 @@
         <v>650</v>
       </c>
       <c r="B601" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11285,10 +11286,10 @@
         <v>651</v>
       </c>
       <c r="B602" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C602" t="s">
         <v>1182</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11296,10 +11297,10 @@
         <v>653</v>
       </c>
       <c r="B603" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C603" t="s">
         <v>1184</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11307,10 +11308,10 @@
         <v>654</v>
       </c>
       <c r="B604" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C604" t="s">
         <v>1186</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11318,10 +11319,10 @@
         <v>655</v>
       </c>
       <c r="B605" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C605" t="s">
         <v>1188</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11329,10 +11330,10 @@
         <v>659</v>
       </c>
       <c r="B606" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C606" t="s">
         <v>1190</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11340,10 +11341,10 @@
         <v>660</v>
       </c>
       <c r="B607" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C607" t="s">
         <v>1192</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11351,10 +11352,10 @@
         <v>661</v>
       </c>
       <c r="B608" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C608" t="s">
         <v>1194</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11362,10 +11363,10 @@
         <v>663</v>
       </c>
       <c r="B609" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C609" t="s">
         <v>1196</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11373,10 +11374,10 @@
         <v>667</v>
       </c>
       <c r="B610" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C610" t="s">
         <v>1198</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11384,10 +11385,10 @@
         <v>670</v>
       </c>
       <c r="B611" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C611" t="s">
         <v>1200</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11395,10 +11396,10 @@
         <v>673</v>
       </c>
       <c r="B612" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C612" t="s">
         <v>1202</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11406,10 +11407,10 @@
         <v>674</v>
       </c>
       <c r="B613" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C613" t="s">
         <v>1204</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11417,10 +11418,10 @@
         <v>675</v>
       </c>
       <c r="B614" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C614" t="s">
         <v>1206</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11428,10 +11429,10 @@
         <v>680</v>
       </c>
       <c r="B615" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C615" t="s">
         <v>1208</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11439,10 +11440,10 @@
         <v>681</v>
       </c>
       <c r="B616" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C616" t="s">
         <v>1210</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11450,10 +11451,10 @@
         <v>682</v>
       </c>
       <c r="B617" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C617" t="s">
         <v>1212</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11461,10 +11462,10 @@
         <v>683</v>
       </c>
       <c r="B618" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C618" t="s">
         <v>1214</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11472,10 +11473,10 @@
         <v>684</v>
       </c>
       <c r="B619" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C619" t="s">
         <v>1216</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11483,10 +11484,10 @@
         <v>685</v>
       </c>
       <c r="B620" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C620" t="s">
         <v>1218</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11494,10 +11495,10 @@
         <v>686</v>
       </c>
       <c r="B621" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C621" t="s">
         <v>1220</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11505,10 +11506,10 @@
         <v>689</v>
       </c>
       <c r="B622" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C622" t="s">
         <v>1222</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11516,10 +11517,10 @@
         <v>697</v>
       </c>
       <c r="B623" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C623" t="s">
         <v>1224</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11527,10 +11528,10 @@
         <v>701</v>
       </c>
       <c r="B624" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C624" t="s">
         <v>1226</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11538,10 +11539,10 @@
         <v>702</v>
       </c>
       <c r="B625" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C625" t="s">
         <v>1228</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1229</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11549,10 +11550,10 @@
         <v>704</v>
       </c>
       <c r="B626" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C626" t="s">
         <v>1230</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11560,10 +11561,10 @@
         <v>705</v>
       </c>
       <c r="B627" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C627" t="s">
         <v>1232</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11571,10 +11572,10 @@
         <v>710</v>
       </c>
       <c r="B628" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C628" t="s">
         <v>1234</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11582,10 +11583,10 @@
         <v>711</v>
       </c>
       <c r="B629" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C629" t="s">
         <v>1236</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11593,10 +11594,10 @@
         <v>712</v>
       </c>
       <c r="B630" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C630" t="s">
         <v>1238</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11604,10 +11605,10 @@
         <v>714</v>
       </c>
       <c r="B631" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11615,10 +11616,10 @@
         <v>717</v>
       </c>
       <c r="B632" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C632" t="s">
         <v>1241</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11626,10 +11627,10 @@
         <v>718</v>
       </c>
       <c r="B633" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C633" t="s">
         <v>1243</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11637,10 +11638,10 @@
         <v>719</v>
       </c>
       <c r="B634" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C634" t="s">
         <v>1245</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11648,10 +11649,10 @@
         <v>721</v>
       </c>
       <c r="B635" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C635" t="s">
         <v>1247</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11659,10 +11660,10 @@
         <v>722</v>
       </c>
       <c r="B636" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C636" t="s">
         <v>1249</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11670,10 +11671,10 @@
         <v>723</v>
       </c>
       <c r="B637" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C637" t="s">
         <v>1251</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11681,10 +11682,10 @@
         <v>725</v>
       </c>
       <c r="B638" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C638" t="s">
         <v>1253</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11692,10 +11693,10 @@
         <v>726</v>
       </c>
       <c r="B639" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C639" t="s">
         <v>1255</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11703,10 +11704,10 @@
         <v>727</v>
       </c>
       <c r="B640" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C640" t="s">
         <v>1257</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11714,10 +11715,10 @@
         <v>728</v>
       </c>
       <c r="B641" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C641" t="s">
         <v>1259</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11725,10 +11726,10 @@
         <v>729</v>
       </c>
       <c r="B642" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C642" t="s">
         <v>1261</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11736,10 +11737,10 @@
         <v>730</v>
       </c>
       <c r="B643" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C643" t="s">
         <v>1263</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11747,10 +11748,10 @@
         <v>731</v>
       </c>
       <c r="B644" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11758,10 +11759,10 @@
         <v>733</v>
       </c>
       <c r="B645" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C645" t="s">
         <v>1266</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11769,10 +11770,10 @@
         <v>735</v>
       </c>
       <c r="B646" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C646" t="s">
         <v>1268</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11780,10 +11781,10 @@
         <v>736</v>
       </c>
       <c r="B647" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C647" t="s">
         <v>1270</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11791,10 +11792,10 @@
         <v>737</v>
       </c>
       <c r="B648" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C648" t="s">
         <v>1272</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11802,10 +11803,10 @@
         <v>738</v>
       </c>
       <c r="B649" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C649" t="s">
         <v>1274</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11813,10 +11814,10 @@
         <v>739</v>
       </c>
       <c r="B650" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C650" t="s">
         <v>1276</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11824,10 +11825,10 @@
         <v>740</v>
       </c>
       <c r="B651" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C651" t="s">
         <v>1278</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11835,10 +11836,10 @@
         <v>741</v>
       </c>
       <c r="B652" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C652" t="s">
         <v>1280</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11846,10 +11847,10 @@
         <v>742</v>
       </c>
       <c r="B653" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C653" t="s">
         <v>1282</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11857,10 +11858,10 @@
         <v>743</v>
       </c>
       <c r="B654" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C654" t="s">
         <v>1284</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11868,10 +11869,10 @@
         <v>744</v>
       </c>
       <c r="B655" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C655" t="s">
         <v>1286</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11879,10 +11880,10 @@
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C656" t="s">
         <v>1288</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11890,10 +11891,10 @@
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C657" t="s">
         <v>1290</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11901,10 +11902,10 @@
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C658" t="s">
         <v>1292</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11912,10 +11913,10 @@
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C659" t="s">
         <v>1294</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11923,10 +11924,10 @@
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C660" t="s">
         <v>1296</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11934,10 +11935,10 @@
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C661" t="s">
         <v>1298</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11945,10 +11946,10 @@
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C662" t="s">
         <v>1300</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11956,10 +11957,10 @@
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C663" t="s">
         <v>1302</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11967,10 +11968,10 @@
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C664" t="s">
         <v>1304</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11978,10 +11979,10 @@
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C665" t="s">
         <v>1306</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -11989,10 +11990,10 @@
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C666" t="s">
         <v>1308</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12000,10 +12001,10 @@
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C667" t="s">
         <v>1310</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12011,10 +12012,10 @@
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C668" t="s">
         <v>1312</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12022,10 +12023,10 @@
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C669" t="s">
         <v>1314</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12033,10 +12034,10 @@
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C670" t="s">
         <v>1316</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12044,10 +12045,10 @@
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C671" t="s">
         <v>1318</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12055,10 +12056,10 @@
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C672" t="s">
         <v>1320</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12072,10 +12073,10 @@
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C674" t="s">
         <v>1322</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12084,7 +12085,7 @@
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12092,10 +12093,10 @@
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C676" t="s">
         <v>1325</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12103,10 +12104,10 @@
         <v>772</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C677" s="3" t="s">
         <v>1331</v>
-      </c>
-      <c r="C677" s="3" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12115,7 +12116,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12124,7 +12125,7 @@
       </c>
       <c r="B679" s="1"/>
       <c r="C679" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12133,7 +12134,7 @@
       </c>
       <c r="B680" s="1"/>
       <c r="C680" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12142,7 +12143,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12151,7 +12152,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12160,7 +12161,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12169,7 +12170,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12178,7 +12179,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12186,10 +12187,10 @@
         <v>10001</v>
       </c>
       <c r="B686" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C686" t="s">
         <v>1327</v>
-      </c>
-      <c r="C686" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12197,10 +12198,10 @@
         <v>10003</v>
       </c>
       <c r="B687" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C687" t="s">
         <v>1325</v>
-      </c>
-      <c r="C687" t="s">
-        <v>1326</v>
       </c>
     </row>
   </sheetData>
@@ -12208,7 +12209,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A686:C686 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A296:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A686:C686 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA22ED44-7BC1-41F0-9915-91E0C7321087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74A70CC-CB35-404A-B271-774D2AB218C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2856,9 +2856,6 @@
     <t>五等分の気持ち</t>
   </si>
   <si>
-    <t>五等分的新娘,五等分的花嫁</t>
-  </si>
-  <si>
     <t>命に嫌われている</t>
   </si>
   <si>
@@ -4258,6 +4255,10 @@
   </si>
   <si>
     <t>SOS,sos,苍蓝钢铁,效率,救救,s</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>五等分的新娘,五等分的花嫁,五等份的新娘,五等份的花嫁</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5928,7 +5929,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -7941,7 +7942,7 @@
         <v>589</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -8403,7 +8404,7 @@
         <v>672</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8414,7 +8415,7 @@
         <v>673</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -9818,8 +9819,8 @@
       <c r="B467" t="s">
         <v>923</v>
       </c>
-      <c r="C467" t="s">
-        <v>924</v>
+      <c r="C467" s="3" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -9827,10 +9828,10 @@
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>924</v>
+      </c>
+      <c r="C468" t="s">
         <v>925</v>
-      </c>
-      <c r="C468" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -9838,10 +9839,10 @@
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>926</v>
+      </c>
+      <c r="C469" t="s">
         <v>927</v>
-      </c>
-      <c r="C469" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
@@ -9849,10 +9850,10 @@
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>928</v>
+      </c>
+      <c r="C470" t="s">
         <v>929</v>
-      </c>
-      <c r="C470" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
@@ -9860,10 +9861,10 @@
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>930</v>
+      </c>
+      <c r="C471" t="s">
         <v>931</v>
-      </c>
-      <c r="C471" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -9871,10 +9872,10 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>932</v>
+      </c>
+      <c r="C472" t="s">
         <v>933</v>
-      </c>
-      <c r="C472" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
@@ -9882,10 +9883,10 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>934</v>
+      </c>
+      <c r="C473" t="s">
         <v>935</v>
-      </c>
-      <c r="C473" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
@@ -9893,10 +9894,10 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>936</v>
+      </c>
+      <c r="C474" t="s">
         <v>937</v>
-      </c>
-      <c r="C474" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
@@ -9904,10 +9905,10 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>938</v>
+      </c>
+      <c r="C475" t="s">
         <v>939</v>
-      </c>
-      <c r="C475" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
@@ -9915,10 +9916,10 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>940</v>
+      </c>
+      <c r="C476" t="s">
         <v>941</v>
-      </c>
-      <c r="C476" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -9926,10 +9927,10 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>942</v>
+      </c>
+      <c r="C477" t="s">
         <v>943</v>
-      </c>
-      <c r="C477" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
@@ -9937,10 +9938,10 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C478" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
@@ -9948,10 +9949,10 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>945</v>
+      </c>
+      <c r="C479" t="s">
         <v>946</v>
-      </c>
-      <c r="C479" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -9959,10 +9960,10 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>947</v>
+      </c>
+      <c r="C480" t="s">
         <v>948</v>
-      </c>
-      <c r="C480" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
@@ -9970,10 +9971,10 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>949</v>
+      </c>
+      <c r="C481" t="s">
         <v>950</v>
-      </c>
-      <c r="C481" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -9981,10 +9982,10 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>951</v>
+      </c>
+      <c r="C482" t="s">
         <v>952</v>
-      </c>
-      <c r="C482" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
@@ -9992,10 +9993,10 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>953</v>
+      </c>
+      <c r="C483" t="s">
         <v>954</v>
-      </c>
-      <c r="C483" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
@@ -10003,10 +10004,10 @@
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>955</v>
+      </c>
+      <c r="C484" t="s">
         <v>956</v>
-      </c>
-      <c r="C484" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
@@ -10014,10 +10015,10 @@
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>957</v>
+      </c>
+      <c r="C485" t="s">
         <v>958</v>
-      </c>
-      <c r="C485" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
@@ -10025,10 +10026,10 @@
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>959</v>
+      </c>
+      <c r="C486" t="s">
         <v>960</v>
-      </c>
-      <c r="C486" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
@@ -10036,10 +10037,10 @@
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>961</v>
+      </c>
+      <c r="C487" t="s">
         <v>962</v>
-      </c>
-      <c r="C487" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
@@ -10047,10 +10048,10 @@
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>963</v>
+      </c>
+      <c r="C488" t="s">
         <v>964</v>
-      </c>
-      <c r="C488" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
@@ -10058,10 +10059,10 @@
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>965</v>
+      </c>
+      <c r="C489" t="s">
         <v>966</v>
-      </c>
-      <c r="C489" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
@@ -10069,10 +10070,10 @@
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>967</v>
+      </c>
+      <c r="C490" t="s">
         <v>968</v>
-      </c>
-      <c r="C490" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -10080,10 +10081,10 @@
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>969</v>
+      </c>
+      <c r="C491" t="s">
         <v>970</v>
-      </c>
-      <c r="C491" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
@@ -10091,10 +10092,10 @@
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>971</v>
+      </c>
+      <c r="C492" t="s">
         <v>972</v>
-      </c>
-      <c r="C492" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
@@ -10102,10 +10103,10 @@
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>973</v>
+      </c>
+      <c r="C493" t="s">
         <v>974</v>
-      </c>
-      <c r="C493" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
@@ -10113,10 +10114,10 @@
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>975</v>
+      </c>
+      <c r="C494" t="s">
         <v>976</v>
-      </c>
-      <c r="C494" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
@@ -10124,10 +10125,10 @@
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>977</v>
+      </c>
+      <c r="C495" t="s">
         <v>978</v>
-      </c>
-      <c r="C495" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
@@ -10135,10 +10136,10 @@
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>979</v>
+      </c>
+      <c r="C496" t="s">
         <v>980</v>
-      </c>
-      <c r="C496" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -10146,10 +10147,10 @@
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>981</v>
+      </c>
+      <c r="C497" t="s">
         <v>982</v>
-      </c>
-      <c r="C497" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -10157,10 +10158,10 @@
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>983</v>
+      </c>
+      <c r="C498" t="s">
         <v>984</v>
-      </c>
-      <c r="C498" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
@@ -10168,7 +10169,7 @@
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
@@ -10176,10 +10177,10 @@
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>986</v>
+      </c>
+      <c r="C500" t="s">
         <v>987</v>
-      </c>
-      <c r="C500" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
@@ -10187,10 +10188,10 @@
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>988</v>
+      </c>
+      <c r="C501" t="s">
         <v>989</v>
-      </c>
-      <c r="C501" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
@@ -10198,10 +10199,10 @@
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>990</v>
+      </c>
+      <c r="C502" t="s">
         <v>991</v>
-      </c>
-      <c r="C502" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
@@ -10209,10 +10210,10 @@
         <v>515</v>
       </c>
       <c r="B503" t="s">
+        <v>992</v>
+      </c>
+      <c r="C503" t="s">
         <v>993</v>
-      </c>
-      <c r="C503" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
@@ -10220,10 +10221,10 @@
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>994</v>
+      </c>
+      <c r="C504" t="s">
         <v>995</v>
-      </c>
-      <c r="C504" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -10231,10 +10232,10 @@
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>996</v>
+      </c>
+      <c r="C505" t="s">
         <v>997</v>
-      </c>
-      <c r="C505" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
@@ -10242,10 +10243,10 @@
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>998</v>
+      </c>
+      <c r="C506" t="s">
         <v>999</v>
-      </c>
-      <c r="C506" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
@@ -10253,10 +10254,10 @@
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C507" t="s">
         <v>1001</v>
-      </c>
-      <c r="C507" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -10264,10 +10265,10 @@
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C508" t="s">
         <v>1003</v>
-      </c>
-      <c r="C508" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
@@ -10275,10 +10276,10 @@
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C509" t="s">
         <v>1005</v>
-      </c>
-      <c r="C509" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
@@ -10286,10 +10287,10 @@
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C510" t="s">
         <v>1007</v>
-      </c>
-      <c r="C510" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
@@ -10297,10 +10298,10 @@
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C511" t="s">
         <v>1009</v>
-      </c>
-      <c r="C511" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
@@ -10308,10 +10309,10 @@
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C512" t="s">
         <v>1011</v>
-      </c>
-      <c r="C512" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
@@ -10319,10 +10320,10 @@
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C513" t="s">
         <v>1013</v>
-      </c>
-      <c r="C513" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
@@ -10330,10 +10331,10 @@
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C514" t="s">
         <v>1015</v>
-      </c>
-      <c r="C514" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -10341,10 +10342,10 @@
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C515" t="s">
         <v>1017</v>
-      </c>
-      <c r="C515" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -10355,7 +10356,7 @@
         <v>728</v>
       </c>
       <c r="C516" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
@@ -10363,10 +10364,10 @@
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C517" t="s">
         <v>1020</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -10374,7 +10375,7 @@
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
@@ -10382,10 +10383,10 @@
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C519" t="s">
         <v>1023</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -10393,10 +10394,10 @@
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C520" t="s">
         <v>1025</v>
-      </c>
-      <c r="C520" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
@@ -10404,10 +10405,10 @@
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C521" t="s">
         <v>1027</v>
-      </c>
-      <c r="C521" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
@@ -10415,10 +10416,10 @@
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C522" t="s">
         <v>1029</v>
-      </c>
-      <c r="C522" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
@@ -10426,10 +10427,10 @@
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C523" t="s">
         <v>1031</v>
-      </c>
-      <c r="C523" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
@@ -10437,10 +10438,10 @@
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C524" t="s">
         <v>1033</v>
-      </c>
-      <c r="C524" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
@@ -10448,10 +10449,10 @@
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C525" t="s">
         <v>1035</v>
-      </c>
-      <c r="C525" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -10459,10 +10460,10 @@
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C526" t="s">
         <v>1037</v>
-      </c>
-      <c r="C526" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
@@ -10470,10 +10471,10 @@
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C527" t="s">
         <v>1039</v>
-      </c>
-      <c r="C527" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
@@ -10481,10 +10482,10 @@
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C528" t="s">
         <v>1041</v>
-      </c>
-      <c r="C528" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -10492,10 +10493,10 @@
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C529" t="s">
         <v>1043</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
@@ -10503,10 +10504,10 @@
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C530" t="s">
         <v>1045</v>
-      </c>
-      <c r="C530" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -10514,10 +10515,10 @@
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C531" t="s">
         <v>1047</v>
-      </c>
-      <c r="C531" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -10525,10 +10526,10 @@
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C532" t="s">
         <v>1049</v>
-      </c>
-      <c r="C532" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
@@ -10536,10 +10537,10 @@
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C533" t="s">
         <v>1051</v>
-      </c>
-      <c r="C533" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -10547,10 +10548,10 @@
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C534" t="s">
         <v>1053</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
@@ -10558,10 +10559,10 @@
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C535" t="s">
         <v>1055</v>
-      </c>
-      <c r="C535" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -10569,10 +10570,10 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C536" t="s">
         <v>1057</v>
-      </c>
-      <c r="C536" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
@@ -10580,10 +10581,10 @@
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C537" t="s">
         <v>1059</v>
-      </c>
-      <c r="C537" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
@@ -10591,10 +10592,10 @@
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C538" t="s">
         <v>1061</v>
-      </c>
-      <c r="C538" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
@@ -10602,10 +10603,10 @@
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C539" t="s">
         <v>1063</v>
-      </c>
-      <c r="C539" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
@@ -10613,10 +10614,10 @@
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C540" t="s">
         <v>1065</v>
-      </c>
-      <c r="C540" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -10624,10 +10625,10 @@
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C541" t="s">
         <v>1067</v>
-      </c>
-      <c r="C541" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
@@ -10635,10 +10636,10 @@
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C542" t="s">
         <v>1069</v>
-      </c>
-      <c r="C542" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
@@ -10646,10 +10647,10 @@
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C543" t="s">
         <v>1071</v>
-      </c>
-      <c r="C543" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
@@ -10657,10 +10658,10 @@
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C544" t="s">
         <v>1073</v>
-      </c>
-      <c r="C544" t="s">
-        <v>1074</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
@@ -10668,10 +10669,10 @@
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C545" t="s">
         <v>1075</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
@@ -10679,10 +10680,10 @@
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C546" t="s">
         <v>1077</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
@@ -10690,7 +10691,7 @@
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -10698,10 +10699,10 @@
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C548" t="s">
         <v>1080</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
@@ -10709,10 +10710,10 @@
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C549" t="s">
         <v>1082</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -10720,10 +10721,10 @@
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C550" t="s">
         <v>1084</v>
-      </c>
-      <c r="C550" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -10731,10 +10732,10 @@
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C551" t="s">
         <v>1086</v>
-      </c>
-      <c r="C551" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -10742,10 +10743,10 @@
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C552" t="s">
         <v>1088</v>
-      </c>
-      <c r="C552" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
@@ -10753,10 +10754,10 @@
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C553" t="s">
         <v>1090</v>
-      </c>
-      <c r="C553" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
@@ -10764,10 +10765,10 @@
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C554" t="s">
         <v>1092</v>
-      </c>
-      <c r="C554" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
@@ -10775,10 +10776,10 @@
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C555" t="s">
         <v>1094</v>
-      </c>
-      <c r="C555" t="s">
-        <v>1095</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
@@ -10786,10 +10787,10 @@
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C556" t="s">
         <v>1096</v>
-      </c>
-      <c r="C556" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
@@ -10797,10 +10798,10 @@
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C557" t="s">
         <v>1098</v>
-      </c>
-      <c r="C557" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
@@ -10808,10 +10809,10 @@
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C558" t="s">
         <v>1100</v>
-      </c>
-      <c r="C558" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
@@ -10819,7 +10820,7 @@
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -10827,10 +10828,10 @@
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C560" t="s">
         <v>1103</v>
-      </c>
-      <c r="C560" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
@@ -10838,10 +10839,10 @@
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C561" t="s">
         <v>1105</v>
-      </c>
-      <c r="C561" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
@@ -10849,10 +10850,10 @@
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C562" t="s">
         <v>1107</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
@@ -10860,10 +10861,10 @@
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C563" t="s">
         <v>1109</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
@@ -10871,10 +10872,10 @@
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C564" t="s">
         <v>1111</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
@@ -10882,10 +10883,10 @@
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C565" t="s">
         <v>1113</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
@@ -10893,10 +10894,10 @@
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C566" t="s">
         <v>1115</v>
-      </c>
-      <c r="C566" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
@@ -10904,10 +10905,10 @@
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C567" t="s">
         <v>1117</v>
-      </c>
-      <c r="C567" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
@@ -10915,10 +10916,10 @@
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C568" t="s">
         <v>1119</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
@@ -10926,10 +10927,10 @@
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C569" t="s">
         <v>1121</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -10937,10 +10938,10 @@
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C570" t="s">
         <v>1123</v>
-      </c>
-      <c r="C570" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
@@ -10948,10 +10949,10 @@
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C571" t="s">
         <v>1125</v>
-      </c>
-      <c r="C571" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -10959,10 +10960,10 @@
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C572" t="s">
         <v>1127</v>
-      </c>
-      <c r="C572" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -10970,10 +10971,10 @@
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C573" t="s">
         <v>1129</v>
-      </c>
-      <c r="C573" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
@@ -10981,10 +10982,10 @@
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C574" t="s">
         <v>1131</v>
-      </c>
-      <c r="C574" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
@@ -10992,10 +10993,10 @@
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11003,10 +11004,10 @@
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C576" t="s">
         <v>1134</v>
-      </c>
-      <c r="C576" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -11014,10 +11015,10 @@
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C577" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11025,10 +11026,10 @@
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C578" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11036,10 +11037,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C579" t="s">
         <v>1138</v>
-      </c>
-      <c r="C579" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11047,10 +11048,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C580" t="s">
         <v>1140</v>
-      </c>
-      <c r="C580" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11058,10 +11059,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C581" t="s">
         <v>1142</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11069,10 +11070,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C582" t="s">
         <v>1144</v>
-      </c>
-      <c r="C582" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11080,10 +11081,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11091,10 +11092,10 @@
         <v>612</v>
       </c>
       <c r="B584" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C584" t="s">
         <v>1147</v>
-      </c>
-      <c r="C584" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11102,10 +11103,10 @@
         <v>615</v>
       </c>
       <c r="B585" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C585" t="s">
         <v>1149</v>
-      </c>
-      <c r="C585" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11113,10 +11114,10 @@
         <v>617</v>
       </c>
       <c r="B586" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C586" t="s">
         <v>1151</v>
-      </c>
-      <c r="C586" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11124,10 +11125,10 @@
         <v>618</v>
       </c>
       <c r="B587" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C587" t="s">
         <v>1153</v>
-      </c>
-      <c r="C587" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11135,10 +11136,10 @@
         <v>625</v>
       </c>
       <c r="B588" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C588" t="s">
         <v>1155</v>
-      </c>
-      <c r="C588" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11146,10 +11147,10 @@
         <v>624</v>
       </c>
       <c r="B589" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C589" t="s">
         <v>1157</v>
-      </c>
-      <c r="C589" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11157,10 +11158,10 @@
         <v>626</v>
       </c>
       <c r="B590" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C590" t="s">
         <v>1159</v>
-      </c>
-      <c r="C590" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11168,10 +11169,10 @@
         <v>629</v>
       </c>
       <c r="B591" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C591" t="s">
         <v>1161</v>
-      </c>
-      <c r="C591" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11179,10 +11180,10 @@
         <v>630</v>
       </c>
       <c r="B592" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C592" t="s">
         <v>1163</v>
-      </c>
-      <c r="C592" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11190,7 +11191,7 @@
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11198,10 +11199,10 @@
         <v>633</v>
       </c>
       <c r="B594" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C594" t="s">
         <v>1166</v>
-      </c>
-      <c r="C594" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11209,10 +11210,10 @@
         <v>635</v>
       </c>
       <c r="B595" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C595" t="s">
         <v>1168</v>
-      </c>
-      <c r="C595" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11220,10 +11221,10 @@
         <v>636</v>
       </c>
       <c r="B596" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C596" t="s">
         <v>1170</v>
-      </c>
-      <c r="C596" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11231,10 +11232,10 @@
         <v>642</v>
       </c>
       <c r="B597" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C597" t="s">
         <v>1172</v>
-      </c>
-      <c r="C597" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11242,10 +11243,10 @@
         <v>644</v>
       </c>
       <c r="B598" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C598" t="s">
         <v>1174</v>
-      </c>
-      <c r="C598" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11253,10 +11254,10 @@
         <v>646</v>
       </c>
       <c r="B599" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C599" t="s">
         <v>1176</v>
-      </c>
-      <c r="C599" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11264,10 +11265,10 @@
         <v>649</v>
       </c>
       <c r="B600" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C600" t="s">
         <v>1178</v>
-      </c>
-      <c r="C600" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11275,10 +11276,10 @@
         <v>650</v>
       </c>
       <c r="B601" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11286,10 +11287,10 @@
         <v>651</v>
       </c>
       <c r="B602" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C602" t="s">
         <v>1181</v>
-      </c>
-      <c r="C602" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11297,10 +11298,10 @@
         <v>653</v>
       </c>
       <c r="B603" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C603" t="s">
         <v>1183</v>
-      </c>
-      <c r="C603" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11308,10 +11309,10 @@
         <v>654</v>
       </c>
       <c r="B604" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C604" t="s">
         <v>1185</v>
-      </c>
-      <c r="C604" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11319,10 +11320,10 @@
         <v>655</v>
       </c>
       <c r="B605" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C605" t="s">
         <v>1187</v>
-      </c>
-      <c r="C605" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11330,10 +11331,10 @@
         <v>659</v>
       </c>
       <c r="B606" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C606" t="s">
         <v>1189</v>
-      </c>
-      <c r="C606" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11341,10 +11342,10 @@
         <v>660</v>
       </c>
       <c r="B607" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C607" t="s">
         <v>1191</v>
-      </c>
-      <c r="C607" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11352,10 +11353,10 @@
         <v>661</v>
       </c>
       <c r="B608" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C608" t="s">
         <v>1193</v>
-      </c>
-      <c r="C608" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11363,10 +11364,10 @@
         <v>663</v>
       </c>
       <c r="B609" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C609" t="s">
         <v>1195</v>
-      </c>
-      <c r="C609" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11374,10 +11375,10 @@
         <v>667</v>
       </c>
       <c r="B610" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C610" t="s">
         <v>1197</v>
-      </c>
-      <c r="C610" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11385,10 +11386,10 @@
         <v>670</v>
       </c>
       <c r="B611" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C611" t="s">
         <v>1199</v>
-      </c>
-      <c r="C611" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11396,10 +11397,10 @@
         <v>673</v>
       </c>
       <c r="B612" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C612" t="s">
         <v>1201</v>
-      </c>
-      <c r="C612" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11407,10 +11408,10 @@
         <v>674</v>
       </c>
       <c r="B613" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C613" t="s">
         <v>1203</v>
-      </c>
-      <c r="C613" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11418,10 +11419,10 @@
         <v>675</v>
       </c>
       <c r="B614" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C614" t="s">
         <v>1205</v>
-      </c>
-      <c r="C614" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11429,10 +11430,10 @@
         <v>680</v>
       </c>
       <c r="B615" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C615" t="s">
         <v>1207</v>
-      </c>
-      <c r="C615" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11440,10 +11441,10 @@
         <v>681</v>
       </c>
       <c r="B616" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C616" t="s">
         <v>1209</v>
-      </c>
-      <c r="C616" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11451,10 +11452,10 @@
         <v>682</v>
       </c>
       <c r="B617" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C617" t="s">
         <v>1211</v>
-      </c>
-      <c r="C617" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11462,10 +11463,10 @@
         <v>683</v>
       </c>
       <c r="B618" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C618" t="s">
         <v>1213</v>
-      </c>
-      <c r="C618" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11473,10 +11474,10 @@
         <v>684</v>
       </c>
       <c r="B619" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C619" t="s">
         <v>1215</v>
-      </c>
-      <c r="C619" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11484,10 +11485,10 @@
         <v>685</v>
       </c>
       <c r="B620" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C620" t="s">
         <v>1217</v>
-      </c>
-      <c r="C620" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11495,10 +11496,10 @@
         <v>686</v>
       </c>
       <c r="B621" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C621" t="s">
         <v>1219</v>
-      </c>
-      <c r="C621" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11506,10 +11507,10 @@
         <v>689</v>
       </c>
       <c r="B622" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C622" t="s">
         <v>1221</v>
-      </c>
-      <c r="C622" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11517,10 +11518,10 @@
         <v>697</v>
       </c>
       <c r="B623" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C623" t="s">
         <v>1223</v>
-      </c>
-      <c r="C623" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11528,10 +11529,10 @@
         <v>701</v>
       </c>
       <c r="B624" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C624" t="s">
         <v>1225</v>
-      </c>
-      <c r="C624" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11539,10 +11540,10 @@
         <v>702</v>
       </c>
       <c r="B625" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C625" t="s">
         <v>1227</v>
-      </c>
-      <c r="C625" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11550,10 +11551,10 @@
         <v>704</v>
       </c>
       <c r="B626" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C626" t="s">
         <v>1229</v>
-      </c>
-      <c r="C626" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11561,10 +11562,10 @@
         <v>705</v>
       </c>
       <c r="B627" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C627" t="s">
         <v>1231</v>
-      </c>
-      <c r="C627" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11572,10 +11573,10 @@
         <v>710</v>
       </c>
       <c r="B628" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C628" t="s">
         <v>1233</v>
-      </c>
-      <c r="C628" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11583,10 +11584,10 @@
         <v>711</v>
       </c>
       <c r="B629" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C629" t="s">
         <v>1235</v>
-      </c>
-      <c r="C629" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11594,10 +11595,10 @@
         <v>712</v>
       </c>
       <c r="B630" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C630" t="s">
         <v>1237</v>
-      </c>
-      <c r="C630" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11605,10 +11606,10 @@
         <v>714</v>
       </c>
       <c r="B631" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11616,10 +11617,10 @@
         <v>717</v>
       </c>
       <c r="B632" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C632" t="s">
         <v>1240</v>
-      </c>
-      <c r="C632" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11627,10 +11628,10 @@
         <v>718</v>
       </c>
       <c r="B633" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C633" t="s">
         <v>1242</v>
-      </c>
-      <c r="C633" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11638,10 +11639,10 @@
         <v>719</v>
       </c>
       <c r="B634" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C634" t="s">
         <v>1244</v>
-      </c>
-      <c r="C634" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11649,10 +11650,10 @@
         <v>721</v>
       </c>
       <c r="B635" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C635" t="s">
         <v>1246</v>
-      </c>
-      <c r="C635" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11660,10 +11661,10 @@
         <v>722</v>
       </c>
       <c r="B636" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C636" t="s">
         <v>1248</v>
-      </c>
-      <c r="C636" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11671,10 +11672,10 @@
         <v>723</v>
       </c>
       <c r="B637" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C637" t="s">
         <v>1250</v>
-      </c>
-      <c r="C637" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11682,10 +11683,10 @@
         <v>725</v>
       </c>
       <c r="B638" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C638" t="s">
         <v>1252</v>
-      </c>
-      <c r="C638" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11693,10 +11694,10 @@
         <v>726</v>
       </c>
       <c r="B639" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C639" t="s">
         <v>1254</v>
-      </c>
-      <c r="C639" t="s">
-        <v>1255</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11704,10 +11705,10 @@
         <v>727</v>
       </c>
       <c r="B640" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C640" t="s">
         <v>1256</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11715,10 +11716,10 @@
         <v>728</v>
       </c>
       <c r="B641" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C641" t="s">
         <v>1258</v>
-      </c>
-      <c r="C641" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11726,10 +11727,10 @@
         <v>729</v>
       </c>
       <c r="B642" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C642" t="s">
         <v>1260</v>
-      </c>
-      <c r="C642" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11737,10 +11738,10 @@
         <v>730</v>
       </c>
       <c r="B643" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C643" t="s">
         <v>1262</v>
-      </c>
-      <c r="C643" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11748,10 +11749,10 @@
         <v>731</v>
       </c>
       <c r="B644" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11759,10 +11760,10 @@
         <v>733</v>
       </c>
       <c r="B645" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C645" t="s">
         <v>1265</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11770,10 +11771,10 @@
         <v>735</v>
       </c>
       <c r="B646" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C646" t="s">
         <v>1267</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11781,10 +11782,10 @@
         <v>736</v>
       </c>
       <c r="B647" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C647" t="s">
         <v>1269</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11792,10 +11793,10 @@
         <v>737</v>
       </c>
       <c r="B648" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C648" t="s">
         <v>1271</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11803,10 +11804,10 @@
         <v>738</v>
       </c>
       <c r="B649" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C649" t="s">
         <v>1273</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11814,10 +11815,10 @@
         <v>739</v>
       </c>
       <c r="B650" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C650" t="s">
         <v>1275</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11825,10 +11826,10 @@
         <v>740</v>
       </c>
       <c r="B651" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C651" t="s">
         <v>1277</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11836,10 +11837,10 @@
         <v>741</v>
       </c>
       <c r="B652" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C652" t="s">
         <v>1279</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11847,10 +11848,10 @@
         <v>742</v>
       </c>
       <c r="B653" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C653" t="s">
         <v>1281</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11858,10 +11859,10 @@
         <v>743</v>
       </c>
       <c r="B654" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C654" t="s">
         <v>1283</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11869,10 +11870,10 @@
         <v>744</v>
       </c>
       <c r="B655" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C655" t="s">
         <v>1285</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11880,10 +11881,10 @@
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C656" t="s">
         <v>1287</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11891,10 +11892,10 @@
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C657" t="s">
         <v>1289</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11902,10 +11903,10 @@
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C658" t="s">
         <v>1291</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11913,10 +11914,10 @@
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C659" t="s">
         <v>1293</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11924,10 +11925,10 @@
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C660" t="s">
         <v>1295</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11935,10 +11936,10 @@
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C661" t="s">
         <v>1297</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11946,10 +11947,10 @@
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C662" t="s">
         <v>1299</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11957,10 +11958,10 @@
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C663" t="s">
         <v>1301</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11968,10 +11969,10 @@
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C664" t="s">
         <v>1303</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11979,10 +11980,10 @@
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C665" t="s">
         <v>1305</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -11990,10 +11991,10 @@
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C666" t="s">
         <v>1307</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12001,10 +12002,10 @@
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C667" t="s">
         <v>1309</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12012,10 +12013,10 @@
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C668" t="s">
         <v>1311</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12023,10 +12024,10 @@
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C669" t="s">
         <v>1313</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12034,10 +12035,10 @@
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C670" t="s">
         <v>1315</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12045,10 +12046,10 @@
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C671" t="s">
         <v>1317</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12056,10 +12057,10 @@
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C672" t="s">
         <v>1319</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12073,10 +12074,10 @@
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C674" t="s">
         <v>1321</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12085,7 +12086,7 @@
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12093,10 +12094,10 @@
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C676" t="s">
         <v>1324</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12104,10 +12105,10 @@
         <v>772</v>
       </c>
       <c r="B677" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C677" s="3" t="s">
         <v>1330</v>
-      </c>
-      <c r="C677" s="3" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12116,7 +12117,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" s="3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12125,7 +12126,7 @@
       </c>
       <c r="B679" s="1"/>
       <c r="C679" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12134,7 +12135,7 @@
       </c>
       <c r="B680" s="1"/>
       <c r="C680" s="3" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12143,7 +12144,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12152,7 +12153,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12161,7 +12162,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12170,7 +12171,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12179,7 +12180,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12187,10 +12188,10 @@
         <v>10001</v>
       </c>
       <c r="B686" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C686" t="s">
         <v>1326</v>
-      </c>
-      <c r="C686" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12198,10 +12199,10 @@
         <v>10003</v>
       </c>
       <c r="B687" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C687" t="s">
         <v>1324</v>
-      </c>
-      <c r="C687" t="s">
-        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -12209,7 +12210,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A686:C686 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C468 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A686:C686 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74A70CC-CB35-404A-B271-774D2AB218C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8191E671-BB0F-4FCC-A1D2-0F5AFB5E2F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3519,12 +3519,6 @@
     <t>33ssfk,33ssfkk,超高难易度ssfkk,超高难度ssfkk,ssfkkssp</t>
   </si>
   <si>
-    <t>33hoh,超高难易度hoh,超高难度hoh,hohssp</t>
-  </si>
-  <si>
-    <t>35lzn,超高难易度六兆年,超高难度六兆年,lznssp</t>
-  </si>
-  <si>
     <t>トレモロアイズ</t>
   </si>
   <si>
@@ -4259,6 +4253,14 @@
   </si>
   <si>
     <t>五等分的新娘,五等分的花嫁,五等份的新娘,五等份的花嫁</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>35lzn,超高难易度六兆年,超高难度六兆年,lznssp,六兆年ssp,六兆年 ssp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>33hoh,超高难易度hoh,超高难度hoh,hohssp</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5929,7 +5931,7 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -7942,7 +7944,7 @@
         <v>589</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -8404,7 +8406,7 @@
         <v>672</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -8415,7 +8417,7 @@
         <v>673</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -9820,7 +9822,7 @@
         <v>923</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
@@ -10996,7 +10998,7 @@
         <v>1132</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
@@ -11017,8 +11019,8 @@
       <c r="B577" t="s">
         <v>938</v>
       </c>
-      <c r="C577" t="s">
-        <v>1135</v>
+      <c r="C577" s="3" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
@@ -11028,8 +11030,8 @@
       <c r="B578" t="s">
         <v>940</v>
       </c>
-      <c r="C578" t="s">
-        <v>1136</v>
+      <c r="C578" s="3" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
@@ -11037,10 +11039,10 @@
         <v>599</v>
       </c>
       <c r="B579" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C579" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
@@ -11048,10 +11050,10 @@
         <v>601</v>
       </c>
       <c r="B580" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C580" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -11059,10 +11061,10 @@
         <v>602</v>
       </c>
       <c r="B581" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C581" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
@@ -11070,10 +11072,10 @@
         <v>604</v>
       </c>
       <c r="B582" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C582" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
@@ -11081,10 +11083,10 @@
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
@@ -11092,10 +11094,10 @@
         <v>612</v>
       </c>
       <c r="B584" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C584" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
@@ -11103,10 +11105,10 @@
         <v>615</v>
       </c>
       <c r="B585" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C585" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
@@ -11114,10 +11116,10 @@
         <v>617</v>
       </c>
       <c r="B586" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C586" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
@@ -11125,10 +11127,10 @@
         <v>618</v>
       </c>
       <c r="B587" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C587" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
@@ -11136,10 +11138,10 @@
         <v>625</v>
       </c>
       <c r="B588" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C588" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
@@ -11147,10 +11149,10 @@
         <v>624</v>
       </c>
       <c r="B589" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C589" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
@@ -11158,10 +11160,10 @@
         <v>626</v>
       </c>
       <c r="B590" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C590" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
@@ -11169,10 +11171,10 @@
         <v>629</v>
       </c>
       <c r="B591" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C591" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
@@ -11180,10 +11182,10 @@
         <v>630</v>
       </c>
       <c r="B592" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C592" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
@@ -11191,7 +11193,7 @@
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -11199,10 +11201,10 @@
         <v>633</v>
       </c>
       <c r="B594" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C594" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
@@ -11210,10 +11212,10 @@
         <v>635</v>
       </c>
       <c r="B595" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C595" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -11221,10 +11223,10 @@
         <v>636</v>
       </c>
       <c r="B596" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C596" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
@@ -11232,10 +11234,10 @@
         <v>642</v>
       </c>
       <c r="B597" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C597" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
@@ -11243,10 +11245,10 @@
         <v>644</v>
       </c>
       <c r="B598" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C598" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
@@ -11254,10 +11256,10 @@
         <v>646</v>
       </c>
       <c r="B599" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C599" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
@@ -11265,10 +11267,10 @@
         <v>649</v>
       </c>
       <c r="B600" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C600" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
@@ -11276,10 +11278,10 @@
         <v>650</v>
       </c>
       <c r="B601" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
@@ -11287,10 +11289,10 @@
         <v>651</v>
       </c>
       <c r="B602" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C602" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -11298,10 +11300,10 @@
         <v>653</v>
       </c>
       <c r="B603" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C603" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.25">
@@ -11309,10 +11311,10 @@
         <v>654</v>
       </c>
       <c r="B604" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C604" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
@@ -11320,10 +11322,10 @@
         <v>655</v>
       </c>
       <c r="B605" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C605" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -11331,10 +11333,10 @@
         <v>659</v>
       </c>
       <c r="B606" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C606" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
@@ -11342,10 +11344,10 @@
         <v>660</v>
       </c>
       <c r="B607" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C607" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -11353,10 +11355,10 @@
         <v>661</v>
       </c>
       <c r="B608" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C608" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.25">
@@ -11364,10 +11366,10 @@
         <v>663</v>
       </c>
       <c r="B609" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C609" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -11375,10 +11377,10 @@
         <v>667</v>
       </c>
       <c r="B610" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C610" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.25">
@@ -11386,10 +11388,10 @@
         <v>670</v>
       </c>
       <c r="B611" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C611" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.25">
@@ -11397,10 +11399,10 @@
         <v>673</v>
       </c>
       <c r="B612" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C612" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
@@ -11408,10 +11410,10 @@
         <v>674</v>
       </c>
       <c r="B613" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C613" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
@@ -11419,10 +11421,10 @@
         <v>675</v>
       </c>
       <c r="B614" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C614" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -11430,10 +11432,10 @@
         <v>680</v>
       </c>
       <c r="B615" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C615" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.25">
@@ -11441,10 +11443,10 @@
         <v>681</v>
       </c>
       <c r="B616" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C616" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.25">
@@ -11452,10 +11454,10 @@
         <v>682</v>
       </c>
       <c r="B617" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C617" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
@@ -11463,10 +11465,10 @@
         <v>683</v>
       </c>
       <c r="B618" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C618" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -11474,10 +11476,10 @@
         <v>684</v>
       </c>
       <c r="B619" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C619" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.25">
@@ -11485,10 +11487,10 @@
         <v>685</v>
       </c>
       <c r="B620" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C620" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.25">
@@ -11496,10 +11498,10 @@
         <v>686</v>
       </c>
       <c r="B621" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C621" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.25">
@@ -11507,10 +11509,10 @@
         <v>689</v>
       </c>
       <c r="B622" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C622" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
@@ -11518,10 +11520,10 @@
         <v>697</v>
       </c>
       <c r="B623" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C623" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -11529,10 +11531,10 @@
         <v>701</v>
       </c>
       <c r="B624" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C624" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.25">
@@ -11540,10 +11542,10 @@
         <v>702</v>
       </c>
       <c r="B625" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C625" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.25">
@@ -11551,10 +11553,10 @@
         <v>704</v>
       </c>
       <c r="B626" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C626" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -11562,10 +11564,10 @@
         <v>705</v>
       </c>
       <c r="B627" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C627" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.25">
@@ -11573,10 +11575,10 @@
         <v>710</v>
       </c>
       <c r="B628" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C628" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
@@ -11584,10 +11586,10 @@
         <v>711</v>
       </c>
       <c r="B629" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C629" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -11595,10 +11597,10 @@
         <v>712</v>
       </c>
       <c r="B630" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C630" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.25">
@@ -11606,10 +11608,10 @@
         <v>714</v>
       </c>
       <c r="B631" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.25">
@@ -11617,10 +11619,10 @@
         <v>717</v>
       </c>
       <c r="B632" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C632" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
@@ -11628,10 +11630,10 @@
         <v>718</v>
       </c>
       <c r="B633" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C633" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -11639,10 +11641,10 @@
         <v>719</v>
       </c>
       <c r="B634" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C634" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11650,10 +11652,10 @@
         <v>721</v>
       </c>
       <c r="B635" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C635" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.25">
@@ -11661,10 +11663,10 @@
         <v>722</v>
       </c>
       <c r="B636" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C636" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.25">
@@ -11672,10 +11674,10 @@
         <v>723</v>
       </c>
       <c r="B637" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C637" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.25">
@@ -11683,10 +11685,10 @@
         <v>725</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C638" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.25">
@@ -11694,10 +11696,10 @@
         <v>726</v>
       </c>
       <c r="B639" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C639" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.25">
@@ -11705,10 +11707,10 @@
         <v>727</v>
       </c>
       <c r="B640" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C640" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11716,10 +11718,10 @@
         <v>728</v>
       </c>
       <c r="B641" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="C641" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11727,10 +11729,10 @@
         <v>729</v>
       </c>
       <c r="B642" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C642" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -11738,10 +11740,10 @@
         <v>730</v>
       </c>
       <c r="B643" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C643" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.25">
@@ -11749,10 +11751,10 @@
         <v>731</v>
       </c>
       <c r="B644" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -11760,10 +11762,10 @@
         <v>733</v>
       </c>
       <c r="B645" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C645" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.25">
@@ -11771,10 +11773,10 @@
         <v>735</v>
       </c>
       <c r="B646" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C646" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
@@ -11782,10 +11784,10 @@
         <v>736</v>
       </c>
       <c r="B647" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C647" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -11793,10 +11795,10 @@
         <v>737</v>
       </c>
       <c r="B648" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C648" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.25">
@@ -11804,10 +11806,10 @@
         <v>738</v>
       </c>
       <c r="B649" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C649" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -11815,10 +11817,10 @@
         <v>739</v>
       </c>
       <c r="B650" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C650" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.25">
@@ -11826,10 +11828,10 @@
         <v>740</v>
       </c>
       <c r="B651" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C651" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -11837,10 +11839,10 @@
         <v>741</v>
       </c>
       <c r="B652" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C652" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.25">
@@ -11848,10 +11850,10 @@
         <v>742</v>
       </c>
       <c r="B653" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="C653" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.25">
@@ -11859,10 +11861,10 @@
         <v>743</v>
       </c>
       <c r="B654" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="C654" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.25">
@@ -11870,10 +11872,10 @@
         <v>744</v>
       </c>
       <c r="B655" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C655" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
@@ -11881,10 +11883,10 @@
         <v>745</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="C656" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.25">
@@ -11892,10 +11894,10 @@
         <v>746</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C657" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.25">
@@ -11903,10 +11905,10 @@
         <v>747</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C658" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.25">
@@ -11914,10 +11916,10 @@
         <v>748</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C659" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.25">
@@ -11925,10 +11927,10 @@
         <v>749</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C660" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.25">
@@ -11936,10 +11938,10 @@
         <v>753</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="C661" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.25">
@@ -11947,10 +11949,10 @@
         <v>755</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C662" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.25">
@@ -11958,10 +11960,10 @@
         <v>756</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C663" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.25">
@@ -11969,10 +11971,10 @@
         <v>757</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C664" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.25">
@@ -11980,10 +11982,10 @@
         <v>758</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="C665" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.25">
@@ -11991,10 +11993,10 @@
         <v>759</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C666" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -12002,10 +12004,10 @@
         <v>760</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C667" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.25">
@@ -12013,10 +12015,10 @@
         <v>761</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C668" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.25">
@@ -12024,10 +12026,10 @@
         <v>762</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C669" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.25">
@@ -12035,10 +12037,10 @@
         <v>763</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="C670" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.25">
@@ -12046,10 +12048,10 @@
         <v>764</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="C671" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.25">
@@ -12057,10 +12059,10 @@
         <v>765</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="C672" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.25">
@@ -12074,10 +12076,10 @@
         <v>767</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="C674" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -12086,7 +12088,7 @@
       </c>
       <c r="B675" s="1"/>
       <c r="C675" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.25">
@@ -12094,10 +12096,10 @@
         <v>769</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C676" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.25">
@@ -12105,10 +12107,10 @@
         <v>772</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="C677" s="3" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.25">
@@ -12117,7 +12119,7 @@
       </c>
       <c r="B678" s="1"/>
       <c r="C678" s="3" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.25">
@@ -12126,7 +12128,7 @@
       </c>
       <c r="B679" s="1"/>
       <c r="C679" s="3" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
@@ -12135,7 +12137,7 @@
       </c>
       <c r="B680" s="1"/>
       <c r="C680" s="3" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -12144,7 +12146,7 @@
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
@@ -12153,7 +12155,7 @@
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -12162,7 +12164,7 @@
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -12171,7 +12173,7 @@
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
@@ -12180,7 +12182,7 @@
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -12188,10 +12190,10 @@
         <v>10001</v>
       </c>
       <c r="B686" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="C686" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -12199,10 +12201,10 @@
         <v>10003</v>
       </c>
       <c r="B687" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C687" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
   </sheetData>

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8191E671-BB0F-4FCC-A1D2-0F5AFB5E2F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1E4D67-778C-4315-814E-60AEEB429C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1348">
   <si>
     <t>Id</t>
   </si>
@@ -4261,6 +4261,10 @@
   </si>
   <si>
     <t>33hoh,超高难易度hoh,超高难度hoh,hohssp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>gcsp,游戏改变者,改变游戏者,</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4682,7 +4686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C687"/>
+  <dimension ref="A1:C688"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
@@ -12187,23 +12191,32 @@
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686">
-        <v>10001</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C686" t="s">
-        <v>1324</v>
+        <v>782</v>
+      </c>
+      <c r="B686" s="1"/>
+      <c r="C686" s="3" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687">
+        <v>10001</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A688">
         <v>10003</v>
       </c>
-      <c r="B687" t="s">
+      <c r="B688" t="s">
         <v>1321</v>
       </c>
-      <c r="C687" t="s">
+      <c r="C688" t="s">
         <v>1322</v>
       </c>
     </row>
@@ -12212,7 +12225,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A686:C686 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A687:C687 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1E4D67-778C-4315-814E-60AEEB429C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11BB4AE-A8CF-469A-A4D0-2B44991B43A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4264,7 +4264,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>gcsp,游戏改变者,改变游戏者,</t>
+    <t>gcsp,游戏改变者,改变游戏者,gc</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>

--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11BB4AE-A8CF-469A-A4D0-2B44991B43A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DBADC0-0718-478E-85BC-3495E49E29A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="1349">
   <si>
     <t>Id</t>
   </si>
@@ -3093,9 +3093,6 @@
     <t>碧天伴走</t>
   </si>
   <si>
-    <t>逆天伴走,爱灯,碧天绊走</t>
-  </si>
-  <si>
     <t>Get Wild</t>
   </si>
   <si>
@@ -4092,9 +4089,6 @@
     <t>Drown Out the Noise and Push Through the Trash</t>
   </si>
   <si>
-    <t>屏蔽噪音,穿过垃圾堆</t>
-  </si>
-  <si>
     <t>I wonder</t>
   </si>
   <si>
@@ -4265,6 +4259,18 @@
   </si>
   <si>
     <t>gcsp,游戏改变者,改变游戏者,gc</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rs</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>屏蔽噪音,穿过垃圾堆,跨越垃圾场</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆天伴走,爱灯,碧天绊走,碧天伴走</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4686,16 +4692,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C688"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C689"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.796875" customWidth="1"/>
-    <col min="2" max="2" width="50.796875" customWidth="1"/>
-    <col min="3" max="3" width="65.796875" customWidth="1"/>
-    <col min="4" max="4" width="55.69921875" customWidth="1"/>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="50.75" customWidth="1"/>
+    <col min="3" max="3" width="65.75" customWidth="1"/>
+    <col min="4" max="4" width="55.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4706,7 +4712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4717,7 +4723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4728,7 +4734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4739,7 +4745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4750,7 +4756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4761,7 +4767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4772,7 +4778,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4783,7 +4789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4794,7 +4800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4805,7 +4811,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4816,7 +4822,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4827,7 +4833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4838,7 +4844,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4849,7 +4855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4860,7 +4866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4871,7 +4877,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4882,7 +4888,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4893,7 +4899,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4904,7 +4910,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4915,7 +4921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4926,7 +4932,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4937,7 +4943,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>24</v>
       </c>
@@ -4948,7 +4954,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>25</v>
       </c>
@@ -4959,7 +4965,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>26</v>
       </c>
@@ -4970,7 +4976,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>27</v>
       </c>
@@ -4981,7 +4987,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>28</v>
       </c>
@@ -4992,7 +4998,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5003,7 +5009,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5014,7 +5020,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5025,7 +5031,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5036,7 +5042,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5047,7 +5053,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5058,7 +5064,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5080,7 +5086,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5091,7 +5097,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5102,7 +5108,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5113,7 +5119,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5124,7 +5130,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5135,7 +5141,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5146,7 +5152,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5157,7 +5163,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5168,7 +5174,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5179,7 +5185,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5190,7 +5196,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5201,7 +5207,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5212,7 +5218,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5223,7 +5229,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5234,7 +5240,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5245,7 +5251,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5256,7 +5262,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5267,7 +5273,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5278,7 +5284,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5289,7 +5295,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5300,7 +5306,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5311,7 +5317,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5322,7 +5328,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5333,7 +5339,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5344,7 +5350,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5355,7 +5361,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5366,7 +5372,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5377,7 +5383,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5388,7 +5394,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5399,7 +5405,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5410,7 +5416,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5421,7 +5427,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5432,7 +5438,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5443,7 +5449,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5454,7 +5460,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5465,7 +5471,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5476,7 +5482,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5487,7 +5493,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5498,7 +5504,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5509,7 +5515,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5520,7 +5526,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5531,7 +5537,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5542,7 +5548,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5553,7 +5559,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5564,7 +5570,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5575,7 +5581,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5586,7 +5592,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5597,7 +5603,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5608,7 +5614,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5619,7 +5625,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5630,7 +5636,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5641,7 +5647,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5652,7 +5658,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5663,7 +5669,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5674,7 +5680,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5685,7 +5691,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5696,7 +5702,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5707,7 +5713,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5718,7 +5724,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5729,7 +5735,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5740,7 +5746,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5751,7 +5757,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5762,7 +5768,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5773,7 +5779,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5784,7 +5790,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5795,7 +5801,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5806,7 +5812,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5817,7 +5823,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5828,7 +5834,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5839,7 +5845,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5850,7 +5856,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5861,7 +5867,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5872,7 +5878,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5883,7 +5889,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5894,7 +5900,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5905,7 +5911,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5916,7 +5922,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5927,7 +5933,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5935,10 +5941,10 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A114">
         <v>122</v>
       </c>
@@ -5949,7 +5955,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A115">
         <v>123</v>
       </c>
@@ -5960,7 +5966,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A116">
         <v>124</v>
       </c>
@@ -5971,7 +5977,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A117">
         <v>125</v>
       </c>
@@ -5982,7 +5988,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A118">
         <v>126</v>
       </c>
@@ -5993,7 +5999,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6004,7 +6010,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6015,7 +6021,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6026,7 +6032,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6037,7 +6043,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6048,7 +6054,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6059,7 +6065,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6070,7 +6076,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6081,7 +6087,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6092,7 +6098,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6103,7 +6109,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6114,7 +6120,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6125,7 +6131,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6136,7 +6142,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6147,7 +6153,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6158,7 +6164,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6169,7 +6175,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6180,7 +6186,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6191,7 +6197,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6202,7 +6208,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6213,7 +6219,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6224,7 +6230,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6235,7 +6241,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6246,7 +6252,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6257,7 +6263,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6268,7 +6274,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6279,7 +6285,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6290,7 +6296,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6301,7 +6307,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6312,7 +6318,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6323,7 +6329,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6334,7 +6340,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6345,7 +6351,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6356,7 +6362,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6367,7 +6373,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6378,7 +6384,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6389,7 +6395,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6400,7 +6406,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6411,7 +6417,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6422,7 +6428,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6433,7 +6439,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6444,7 +6450,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6455,7 +6461,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6466,7 +6472,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6477,7 +6483,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6488,7 +6494,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6499,7 +6505,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6510,7 +6516,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6521,7 +6527,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6532,7 +6538,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6543,7 +6549,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6554,7 +6560,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6565,7 +6571,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6576,7 +6582,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6587,7 +6593,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6598,7 +6604,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6609,7 +6615,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6620,7 +6626,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6631,7 +6637,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6642,7 +6648,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6653,7 +6659,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6664,7 +6670,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6675,7 +6681,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6686,7 +6692,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6697,7 +6703,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6708,7 +6714,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6719,7 +6725,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6730,7 +6736,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6741,7 +6747,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6752,7 +6758,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6763,7 +6769,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6774,7 +6780,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6785,7 +6791,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6796,7 +6802,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6807,7 +6813,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6818,7 +6824,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6829,7 +6835,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6840,7 +6846,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6851,7 +6857,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6862,7 +6868,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6873,7 +6879,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6884,7 +6890,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6895,7 +6901,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6906,7 +6912,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6917,7 +6923,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6928,7 +6934,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6939,7 +6945,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A205">
         <v>213</v>
       </c>
@@ -6950,7 +6956,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A206">
         <v>214</v>
       </c>
@@ -6961,7 +6967,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A207">
         <v>215</v>
       </c>
@@ -6972,7 +6978,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A208">
         <v>217</v>
       </c>
@@ -6983,7 +6989,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A209">
         <v>218</v>
       </c>
@@ -6994,7 +7000,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7005,7 +7011,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7016,7 +7022,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7027,7 +7033,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7038,7 +7044,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7049,7 +7055,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7060,7 +7066,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7071,7 +7077,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7082,7 +7088,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7093,7 +7099,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7104,7 +7110,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7115,7 +7121,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7126,7 +7132,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7137,7 +7143,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7148,7 +7154,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A224">
         <v>233</v>
       </c>
@@ -7159,7 +7165,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A225">
         <v>234</v>
       </c>
@@ -7170,7 +7176,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A226">
         <v>235</v>
       </c>
@@ -7181,7 +7187,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A227">
         <v>236</v>
       </c>
@@ -7192,7 +7198,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A228">
         <v>237</v>
       </c>
@@ -7203,7 +7209,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A229">
         <v>238</v>
       </c>
@@ -7214,7 +7220,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A230">
         <v>239</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A231">
         <v>240</v>
       </c>
@@ -7236,7 +7242,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A232">
         <v>241</v>
       </c>
@@ -7247,7 +7253,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A233">
         <v>242</v>
       </c>
@@ -7258,7 +7264,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A234">
         <v>243</v>
       </c>
@@ -7269,7 +7275,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A235">
         <v>244</v>
       </c>
@@ -7280,7 +7286,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A236">
         <v>245</v>
       </c>
@@ -7291,7 +7297,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A237">
         <v>246</v>
       </c>
@@ -7302,7 +7308,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A238">
         <v>247</v>
       </c>
@@ -7313,7 +7319,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A239">
         <v>248</v>
       </c>
@@ -7324,7 +7330,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A240">
         <v>249</v>
       </c>
@@ -7335,7 +7341,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A241">
         <v>250</v>
       </c>
@@ -7346,7 +7352,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A242">
         <v>251</v>
       </c>
@@ -7357,7 +7363,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A243">
         <v>252</v>
       </c>
@@ -7368,7 +7374,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A244">
         <v>253</v>
       </c>
@@ -7379,7 +7385,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A245">
         <v>254</v>
       </c>
@@ -7390,7 +7396,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A246">
         <v>255</v>
       </c>
@@ -7401,7 +7407,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A247">
         <v>256</v>
       </c>
@@ -7412,7 +7418,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A248">
         <v>257</v>
       </c>
@@ -7423,7 +7429,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A249">
         <v>258</v>
       </c>
@@ -7434,7 +7440,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A250">
         <v>259</v>
       </c>
@@ -7445,7 +7451,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A251">
         <v>260</v>
       </c>
@@ -7456,7 +7462,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A252">
         <v>261</v>
       </c>
@@ -7467,7 +7473,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A253">
         <v>262</v>
       </c>
@@ -7478,7 +7484,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A254">
         <v>263</v>
       </c>
@@ -7489,7 +7495,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A255">
         <v>264</v>
       </c>
@@ -7500,7 +7506,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A256">
         <v>265</v>
       </c>
@@ -7511,7 +7517,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A257">
         <v>266</v>
       </c>
@@ -7522,7 +7528,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A258">
         <v>267</v>
       </c>
@@ -7533,7 +7539,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A259">
         <v>268</v>
       </c>
@@ -7544,7 +7550,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A260">
         <v>269</v>
       </c>
@@ -7555,7 +7561,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A261">
         <v>270</v>
       </c>
@@ -7566,7 +7572,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A262">
         <v>271</v>
       </c>
@@ -7577,7 +7583,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A263">
         <v>272</v>
       </c>
@@ -7588,7 +7594,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A264">
         <v>274</v>
       </c>
@@ -7599,7 +7605,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A265">
         <v>275</v>
       </c>
@@ -7610,7 +7616,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A266">
         <v>276</v>
       </c>
@@ -7621,7 +7627,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A267">
         <v>277</v>
       </c>
@@ -7632,7 +7638,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A268">
         <v>278</v>
       </c>
@@ -7643,7 +7649,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A269">
         <v>279</v>
       </c>
@@ -7654,7 +7660,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A270">
         <v>280</v>
       </c>
@@ -7665,7 +7671,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A271">
         <v>281</v>
       </c>
@@ -7676,7 +7682,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A272">
         <v>282</v>
       </c>
@@ -7687,7 +7693,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A273">
         <v>283</v>
       </c>
@@ -7698,7 +7704,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A274">
         <v>284</v>
       </c>
@@ -7709,7 +7715,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A275">
         <v>285</v>
       </c>
@@ -7720,7 +7726,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A276">
         <v>286</v>
       </c>
@@ -7731,7 +7737,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A277">
         <v>287</v>
       </c>
@@ -7742,7 +7748,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A278">
         <v>288</v>
       </c>
@@ -7753,7 +7759,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A279">
         <v>289</v>
       </c>
@@ -7764,7 +7770,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A280">
         <v>290</v>
       </c>
@@ -7775,7 +7781,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A281">
         <v>291</v>
       </c>
@@ -7786,7 +7792,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A282">
         <v>292</v>
       </c>
@@ -7797,7 +7803,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A283">
         <v>293</v>
       </c>
@@ -7808,7 +7814,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A284">
         <v>294</v>
       </c>
@@ -7819,7 +7825,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A285">
         <v>295</v>
       </c>
@@ -7830,7 +7836,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A286">
         <v>296</v>
       </c>
@@ -7841,7 +7847,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A287">
         <v>297</v>
       </c>
@@ -7852,7 +7858,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A288">
         <v>298</v>
       </c>
@@ -7863,7 +7869,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A289">
         <v>299</v>
       </c>
@@ -7874,7 +7880,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A290">
         <v>300</v>
       </c>
@@ -7885,7 +7891,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A291">
         <v>301</v>
       </c>
@@ -7896,7 +7902,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A292">
         <v>302</v>
       </c>
@@ -7907,7 +7913,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A293">
         <v>303</v>
       </c>
@@ -7918,7 +7924,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A294">
         <v>304</v>
       </c>
@@ -7929,7 +7935,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A295">
         <v>305</v>
       </c>
@@ -7940,7 +7946,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A296">
         <v>306</v>
       </c>
@@ -7948,10 +7954,10 @@
         <v>589</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A297">
         <v>307</v>
       </c>
@@ -7962,7 +7968,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A298">
         <v>308</v>
       </c>
@@ -7973,7 +7979,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A299">
         <v>309</v>
       </c>
@@ -7984,7 +7990,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A300">
         <v>310</v>
       </c>
@@ -7995,7 +8001,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A301">
         <v>311</v>
       </c>
@@ -8006,7 +8012,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A302">
         <v>312</v>
       </c>
@@ -8017,7 +8023,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A303">
         <v>313</v>
       </c>
@@ -8028,7 +8034,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A304">
         <v>314</v>
       </c>
@@ -8039,7 +8045,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A305">
         <v>315</v>
       </c>
@@ -8050,7 +8056,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A306">
         <v>316</v>
       </c>
@@ -8061,7 +8067,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A307">
         <v>317</v>
       </c>
@@ -8072,7 +8078,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A308">
         <v>318</v>
       </c>
@@ -8083,7 +8089,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A309">
         <v>319</v>
       </c>
@@ -8094,7 +8100,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A310">
         <v>320</v>
       </c>
@@ -8105,7 +8111,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A311">
         <v>321</v>
       </c>
@@ -8116,7 +8122,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A312">
         <v>322</v>
       </c>
@@ -8127,7 +8133,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A313">
         <v>323</v>
       </c>
@@ -8138,7 +8144,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A314">
         <v>324</v>
       </c>
@@ -8149,7 +8155,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A315">
         <v>325</v>
       </c>
@@ -8160,7 +8166,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A316">
         <v>326</v>
       </c>
@@ -8171,7 +8177,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A317">
         <v>327</v>
       </c>
@@ -8182,7 +8188,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A318">
         <v>328</v>
       </c>
@@ -8193,7 +8199,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A319">
         <v>329</v>
       </c>
@@ -8204,7 +8210,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A320">
         <v>330</v>
       </c>
@@ -8215,7 +8221,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A321">
         <v>331</v>
       </c>
@@ -8226,7 +8232,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A322">
         <v>332</v>
       </c>
@@ -8237,7 +8243,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A323">
         <v>333</v>
       </c>
@@ -8248,7 +8254,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A324">
         <v>334</v>
       </c>
@@ -8259,7 +8265,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A325">
         <v>335</v>
       </c>
@@ -8270,7 +8276,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A326">
         <v>336</v>
       </c>
@@ -8281,7 +8287,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A327">
         <v>337</v>
       </c>
@@ -8292,7 +8298,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A328">
         <v>338</v>
       </c>
@@ -8303,7 +8309,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A329">
         <v>339</v>
       </c>
@@ -8314,7 +8320,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A330">
         <v>340</v>
       </c>
@@ -8325,7 +8331,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A331">
         <v>341</v>
       </c>
@@ -8336,7 +8342,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A332">
         <v>342</v>
       </c>
@@ -8347,7 +8353,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A333">
         <v>343</v>
       </c>
@@ -8358,7 +8364,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A334">
         <v>344</v>
       </c>
@@ -8369,7 +8375,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A335">
         <v>345</v>
       </c>
@@ -8380,7 +8386,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A336">
         <v>346</v>
       </c>
@@ -8391,7 +8397,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A337">
         <v>347</v>
       </c>
@@ -8402,7 +8408,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A338">
         <v>348</v>
       </c>
@@ -8410,10 +8416,10 @@
         <v>672</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A339">
         <v>349</v>
       </c>
@@ -8421,10 +8427,10 @@
         <v>673</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A340">
         <v>350</v>
       </c>
@@ -8435,7 +8441,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A341">
         <v>351</v>
       </c>
@@ -8446,7 +8452,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A342">
         <v>352</v>
       </c>
@@ -8457,7 +8463,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A343">
         <v>353</v>
       </c>
@@ -8468,7 +8474,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A344">
         <v>354</v>
       </c>
@@ -8479,7 +8485,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A345">
         <v>355</v>
       </c>
@@ -8490,7 +8496,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A346">
         <v>356</v>
       </c>
@@ -8501,7 +8507,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A347">
         <v>357</v>
       </c>
@@ -8512,7 +8518,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A348">
         <v>358</v>
       </c>
@@ -8523,7 +8529,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A349">
         <v>359</v>
       </c>
@@ -8534,7 +8540,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A350">
         <v>360</v>
       </c>
@@ -8545,7 +8551,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A351">
         <v>361</v>
       </c>
@@ -8556,7 +8562,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A352">
         <v>362</v>
       </c>
@@ -8567,7 +8573,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A353">
         <v>363</v>
       </c>
@@ -8578,7 +8584,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A354">
         <v>364</v>
       </c>
@@ -8589,7 +8595,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A355">
         <v>365</v>
       </c>
@@ -8600,7 +8606,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A356">
         <v>366</v>
       </c>
@@ -8611,7 +8617,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A357">
         <v>367</v>
       </c>
@@ -8622,7 +8628,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A358">
         <v>368</v>
       </c>
@@ -8633,7 +8639,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A359">
         <v>369</v>
       </c>
@@ -8644,7 +8650,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A360">
         <v>370</v>
       </c>
@@ -8655,7 +8661,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A361">
         <v>371</v>
       </c>
@@ -8666,7 +8672,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A362">
         <v>372</v>
       </c>
@@ -8677,7 +8683,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A363">
         <v>373</v>
       </c>
@@ -8688,7 +8694,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A364">
         <v>374</v>
       </c>
@@ -8699,7 +8705,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A365">
         <v>375</v>
       </c>
@@ -8710,7 +8716,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A366">
         <v>376</v>
       </c>
@@ -8721,7 +8727,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A367">
         <v>377</v>
       </c>
@@ -8732,7 +8738,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A368">
         <v>378</v>
       </c>
@@ -8743,7 +8749,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A369">
         <v>379</v>
       </c>
@@ -8754,7 +8760,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A370">
         <v>380</v>
       </c>
@@ -8765,7 +8771,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A371">
         <v>381</v>
       </c>
@@ -8776,7 +8782,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A372">
         <v>382</v>
       </c>
@@ -8787,7 +8793,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A373">
         <v>383</v>
       </c>
@@ -8798,7 +8804,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A374">
         <v>384</v>
       </c>
@@ -8809,7 +8815,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A375">
         <v>385</v>
       </c>
@@ -8820,7 +8826,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A376">
         <v>386</v>
       </c>
@@ -8831,7 +8837,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A377">
         <v>387</v>
       </c>
@@ -8842,7 +8848,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A378">
         <v>388</v>
       </c>
@@ -8853,7 +8859,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A379">
         <v>389</v>
       </c>
@@ -8864,7 +8870,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A380">
         <v>390</v>
       </c>
@@ -8875,7 +8881,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A381">
         <v>391</v>
       </c>
@@ -8886,7 +8892,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A382">
         <v>392</v>
       </c>
@@ -8897,7 +8903,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A383">
         <v>393</v>
       </c>
@@ -8908,7 +8914,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A384">
         <v>394</v>
       </c>
@@ -8919,7 +8925,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A385">
         <v>395</v>
       </c>
@@ -8930,7 +8936,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A386">
         <v>396</v>
       </c>
@@ -8941,7 +8947,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A387">
         <v>397</v>
       </c>
@@ -8952,7 +8958,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A388">
         <v>398</v>
       </c>
@@ -8963,7 +8969,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A389">
         <v>399</v>
       </c>
@@ -8974,7 +8980,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A390">
         <v>400</v>
       </c>
@@ -8985,7 +8991,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A391">
         <v>401</v>
       </c>
@@ -8996,7 +9002,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>402</v>
       </c>
@@ -9007,7 +9013,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A393">
         <v>403</v>
       </c>
@@ -9018,7 +9024,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A394">
         <v>404</v>
       </c>
@@ -9029,7 +9035,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A395">
         <v>405</v>
       </c>
@@ -9040,7 +9046,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A396">
         <v>406</v>
       </c>
@@ -9051,7 +9057,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A397">
         <v>407</v>
       </c>
@@ -9062,7 +9068,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A398">
         <v>408</v>
       </c>
@@ -9073,7 +9079,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A399">
         <v>409</v>
       </c>
@@ -9084,7 +9090,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A400">
         <v>410</v>
       </c>
@@ -9095,7 +9101,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A401">
         <v>411</v>
       </c>
@@ -9106,7 +9112,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A402">
         <v>412</v>
       </c>
@@ -9117,7 +9123,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A403">
         <v>413</v>
       </c>
@@ -9128,7 +9134,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A404">
         <v>414</v>
       </c>
@@ -9139,7 +9145,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A405">
         <v>415</v>
       </c>
@@ -9150,7 +9156,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A406">
         <v>416</v>
       </c>
@@ -9161,7 +9167,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A407">
         <v>417</v>
       </c>
@@ -9172,7 +9178,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A408">
         <v>418</v>
       </c>
@@ -9183,7 +9189,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A409">
         <v>419</v>
       </c>
@@ -9194,7 +9200,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A410">
         <v>420</v>
       </c>
@@ -9205,7 +9211,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A411">
         <v>421</v>
       </c>
@@ -9216,7 +9222,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A412">
         <v>422</v>
       </c>
@@ -9227,7 +9233,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A413">
         <v>423</v>
       </c>
@@ -9238,7 +9244,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A414">
         <v>424</v>
       </c>
@@ -9249,7 +9255,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A415">
         <v>425</v>
       </c>
@@ -9260,7 +9266,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A416">
         <v>426</v>
       </c>
@@ -9271,7 +9277,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A417">
         <v>427</v>
       </c>
@@ -9282,7 +9288,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A418">
         <v>428</v>
       </c>
@@ -9293,7 +9299,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A419">
         <v>429</v>
       </c>
@@ -9304,7 +9310,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A420">
         <v>430</v>
       </c>
@@ -9315,7 +9321,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A421">
         <v>431</v>
       </c>
@@ -9326,7 +9332,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A422">
         <v>432</v>
       </c>
@@ -9337,7 +9343,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A423">
         <v>433</v>
       </c>
@@ -9348,7 +9354,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A424">
         <v>434</v>
       </c>
@@ -9359,7 +9365,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A425">
         <v>435</v>
       </c>
@@ -9370,7 +9376,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A426">
         <v>436</v>
       </c>
@@ -9381,7 +9387,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A427">
         <v>437</v>
       </c>
@@ -9392,7 +9398,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A428">
         <v>438</v>
       </c>
@@ -9403,7 +9409,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A429">
         <v>439</v>
       </c>
@@ -9414,7 +9420,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A430">
         <v>440</v>
       </c>
@@ -9425,7 +9431,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A431">
         <v>441</v>
       </c>
@@ -9436,7 +9442,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A432">
         <v>442</v>
       </c>
@@ -9447,7 +9453,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A433">
         <v>443</v>
       </c>
@@ -9458,7 +9464,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A434">
         <v>444</v>
       </c>
@@ -9469,7 +9475,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A435">
         <v>445</v>
       </c>
@@ -9480,7 +9486,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A436">
         <v>446</v>
       </c>
@@ -9491,7 +9497,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A437">
         <v>447</v>
       </c>
@@ -9502,7 +9508,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A438">
         <v>448</v>
       </c>
@@ -9513,7 +9519,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A439">
         <v>449</v>
       </c>
@@ -9524,7 +9530,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A440">
         <v>450</v>
       </c>
@@ -9535,7 +9541,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A441">
         <v>451</v>
       </c>
@@ -9546,7 +9552,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A442">
         <v>452</v>
       </c>
@@ -9557,7 +9563,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A443">
         <v>453</v>
       </c>
@@ -9568,7 +9574,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A444">
         <v>455</v>
       </c>
@@ -9579,7 +9585,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A445">
         <v>456</v>
       </c>
@@ -9590,7 +9596,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A446">
         <v>457</v>
       </c>
@@ -9601,7 +9607,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A447">
         <v>458</v>
       </c>
@@ -9612,7 +9618,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A448">
         <v>459</v>
       </c>
@@ -9623,7 +9629,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A449">
         <v>460</v>
       </c>
@@ -9634,7 +9640,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A450">
         <v>461</v>
       </c>
@@ -9645,7 +9651,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A451">
         <v>462</v>
       </c>
@@ -9656,7 +9662,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A452">
         <v>463</v>
       </c>
@@ -9667,7 +9673,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A453">
         <v>464</v>
       </c>
@@ -9678,7 +9684,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A454">
         <v>465</v>
       </c>
@@ -9689,7 +9695,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A455">
         <v>466</v>
       </c>
@@ -9700,7 +9706,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A456">
         <v>467</v>
       </c>
@@ -9711,7 +9717,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A457">
         <v>468</v>
       </c>
@@ -9722,7 +9728,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A458">
         <v>469</v>
       </c>
@@ -9733,7 +9739,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A459">
         <v>470</v>
       </c>
@@ -9744,7 +9750,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A460">
         <v>471</v>
       </c>
@@ -9752,7 +9758,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A461">
         <v>472</v>
       </c>
@@ -9763,7 +9769,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A462">
         <v>473</v>
       </c>
@@ -9774,7 +9780,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A463">
         <v>474</v>
       </c>
@@ -9785,7 +9791,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A464">
         <v>475</v>
       </c>
@@ -9796,7 +9802,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A465">
         <v>476</v>
       </c>
@@ -9807,7 +9813,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A466">
         <v>477</v>
       </c>
@@ -9818,7 +9824,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A467">
         <v>478</v>
       </c>
@@ -9826,10 +9832,10 @@
         <v>923</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A468">
         <v>479</v>
       </c>
@@ -9840,7 +9846,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A469">
         <v>480</v>
       </c>
@@ -9851,7 +9857,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A470">
         <v>481</v>
       </c>
@@ -9862,7 +9868,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A471">
         <v>482</v>
       </c>
@@ -9873,7 +9879,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A472">
         <v>483</v>
       </c>
@@ -9884,7 +9890,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>484</v>
       </c>
@@ -9895,7 +9901,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A474">
         <v>485</v>
       </c>
@@ -9906,7 +9912,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A475">
         <v>486</v>
       </c>
@@ -9917,7 +9923,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A476">
         <v>487</v>
       </c>
@@ -9928,7 +9934,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A477">
         <v>488</v>
       </c>
@@ -9939,7 +9945,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A478">
         <v>489</v>
       </c>
@@ -9950,7 +9956,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A479">
         <v>490</v>
       </c>
@@ -9961,7 +9967,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A480">
         <v>491</v>
       </c>
@@ -9972,7 +9978,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A481">
         <v>492</v>
       </c>
@@ -9983,7 +9989,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A482">
         <v>493</v>
       </c>
@@ -9994,7 +10000,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A483">
         <v>494</v>
       </c>
@@ -10005,7 +10011,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A484">
         <v>496</v>
       </c>
@@ -10016,7 +10022,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A485">
         <v>497</v>
       </c>
@@ -10027,7 +10033,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A486">
         <v>498</v>
       </c>
@@ -10038,7 +10044,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A487">
         <v>499</v>
       </c>
@@ -10049,7 +10055,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A488">
         <v>500</v>
       </c>
@@ -10060,7 +10066,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A489">
         <v>501</v>
       </c>
@@ -10071,7 +10077,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A490">
         <v>502</v>
       </c>
@@ -10082,7 +10088,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A491">
         <v>503</v>
       </c>
@@ -10093,7 +10099,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A492">
         <v>504</v>
       </c>
@@ -10104,7 +10110,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A493">
         <v>505</v>
       </c>
@@ -10115,7 +10121,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A494">
         <v>506</v>
       </c>
@@ -10126,7 +10132,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A495">
         <v>507</v>
       </c>
@@ -10137,7 +10143,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A496">
         <v>508</v>
       </c>
@@ -10148,7 +10154,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A497">
         <v>509</v>
       </c>
@@ -10159,7 +10165,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A498">
         <v>510</v>
       </c>
@@ -10170,7 +10176,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A499">
         <v>511</v>
       </c>
@@ -10178,7 +10184,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A500">
         <v>512</v>
       </c>
@@ -10189,7 +10195,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A501">
         <v>513</v>
       </c>
@@ -10200,7 +10206,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A502">
         <v>514</v>
       </c>
@@ -10211,150 +10217,150 @@
         <v>991</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A503">
         <v>515</v>
       </c>
       <c r="B503" t="s">
         <v>992</v>
       </c>
-      <c r="C503" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C503" s="3" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A504">
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>993</v>
+      </c>
+      <c r="C504" t="s">
         <v>994</v>
       </c>
-      <c r="C504" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A505">
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>995</v>
+      </c>
+      <c r="C505" t="s">
         <v>996</v>
       </c>
-      <c r="C505" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A506">
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>997</v>
+      </c>
+      <c r="C506" t="s">
         <v>998</v>
       </c>
-      <c r="C506" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A507">
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>999</v>
+      </c>
+      <c r="C507" t="s">
         <v>1000</v>
       </c>
-      <c r="C507" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A508">
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C508" t="s">
         <v>1002</v>
       </c>
-      <c r="C508" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A509">
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C509" t="s">
         <v>1004</v>
       </c>
-      <c r="C509" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A510">
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C510" t="s">
         <v>1006</v>
       </c>
-      <c r="C510" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A511">
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C511" t="s">
         <v>1008</v>
       </c>
-      <c r="C511" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A512">
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C512" t="s">
         <v>1010</v>
       </c>
-      <c r="C512" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A513">
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C513" t="s">
         <v>1012</v>
       </c>
-      <c r="C513" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A514">
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C514" t="s">
         <v>1014</v>
       </c>
-      <c r="C514" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A515">
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C515" t="s">
         <v>1016</v>
       </c>
-      <c r="C515" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A516">
         <v>528</v>
       </c>
@@ -10362,661 +10368,661 @@
         <v>728</v>
       </c>
       <c r="C516" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A517">
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C517" t="s">
         <v>1019</v>
       </c>
-      <c r="C517" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A518">
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A519">
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C519" t="s">
         <v>1022</v>
       </c>
-      <c r="C519" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A520">
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C520" t="s">
         <v>1024</v>
       </c>
-      <c r="C520" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A521">
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C521" t="s">
         <v>1026</v>
       </c>
-      <c r="C521" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A522">
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C522" t="s">
         <v>1028</v>
       </c>
-      <c r="C522" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A523">
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C523" t="s">
         <v>1030</v>
       </c>
-      <c r="C523" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A524">
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C524" t="s">
         <v>1032</v>
       </c>
-      <c r="C524" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A525">
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C525" t="s">
         <v>1034</v>
       </c>
-      <c r="C525" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A526">
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C526" t="s">
         <v>1036</v>
       </c>
-      <c r="C526" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A527">
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C527" t="s">
         <v>1038</v>
       </c>
-      <c r="C527" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A528">
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C528" t="s">
         <v>1040</v>
       </c>
-      <c r="C528" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A529">
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C529" t="s">
         <v>1042</v>
       </c>
-      <c r="C529" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A530">
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C530" t="s">
         <v>1044</v>
       </c>
-      <c r="C530" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A531">
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C531" t="s">
         <v>1046</v>
       </c>
-      <c r="C531" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A532">
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C532" t="s">
         <v>1048</v>
       </c>
-      <c r="C532" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A533">
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C533" t="s">
         <v>1050</v>
       </c>
-      <c r="C533" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A534">
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C534" t="s">
         <v>1052</v>
       </c>
-      <c r="C534" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A535">
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C535" t="s">
         <v>1054</v>
       </c>
-      <c r="C535" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A536">
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C536" t="s">
         <v>1056</v>
       </c>
-      <c r="C536" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A537">
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C537" t="s">
         <v>1058</v>
       </c>
-      <c r="C537" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A538">
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C538" t="s">
         <v>1060</v>
       </c>
-      <c r="C538" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A539">
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C539" t="s">
         <v>1062</v>
       </c>
-      <c r="C539" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A540">
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C540" t="s">
         <v>1064</v>
       </c>
-      <c r="C540" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A541">
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C541" t="s">
         <v>1066</v>
       </c>
-      <c r="C541" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A542">
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C542" t="s">
         <v>1068</v>
       </c>
-      <c r="C542" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A543">
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C543" t="s">
         <v>1070</v>
       </c>
-      <c r="C543" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A544">
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C544" t="s">
         <v>1072</v>
       </c>
-      <c r="C544" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A545">
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C545" t="s">
         <v>1074</v>
       </c>
-      <c r="C545" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A546">
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C546" t="s">
         <v>1076</v>
       </c>
-      <c r="C546" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A547">
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A548">
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C548" t="s">
         <v>1079</v>
       </c>
-      <c r="C548" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A549">
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C549" t="s">
         <v>1081</v>
       </c>
-      <c r="C549" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A550">
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C550" t="s">
         <v>1083</v>
       </c>
-      <c r="C550" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A551">
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C551" t="s">
         <v>1085</v>
       </c>
-      <c r="C551" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A552">
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C552" t="s">
         <v>1087</v>
       </c>
-      <c r="C552" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A553">
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C553" t="s">
         <v>1089</v>
       </c>
-      <c r="C553" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A554">
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C554" t="s">
         <v>1091</v>
       </c>
-      <c r="C554" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A555">
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C555" t="s">
         <v>1093</v>
       </c>
-      <c r="C555" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A556">
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C556" t="s">
         <v>1095</v>
       </c>
-      <c r="C556" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A557">
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C557" t="s">
         <v>1097</v>
       </c>
-      <c r="C557" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A558">
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C558" t="s">
         <v>1099</v>
       </c>
-      <c r="C558" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A559">
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A560">
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C560" t="s">
         <v>1102</v>
       </c>
-      <c r="C560" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A561">
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C561" t="s">
         <v>1104</v>
       </c>
-      <c r="C561" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A562">
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C562" t="s">
         <v>1106</v>
       </c>
-      <c r="C562" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A563">
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C563" t="s">
         <v>1108</v>
       </c>
-      <c r="C563" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A564">
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C564" t="s">
         <v>1110</v>
       </c>
-      <c r="C564" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A565">
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C565" t="s">
         <v>1112</v>
       </c>
-      <c r="C565" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A566">
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C566" t="s">
         <v>1114</v>
       </c>
-      <c r="C566" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A567">
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C567" t="s">
         <v>1116</v>
       </c>
-      <c r="C567" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A568">
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C568" t="s">
         <v>1118</v>
       </c>
-      <c r="C568" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A569">
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C569" t="s">
         <v>1120</v>
       </c>
-      <c r="C569" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A570">
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C570" t="s">
         <v>1122</v>
       </c>
-      <c r="C570" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A571">
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C571" t="s">
         <v>1124</v>
       </c>
-      <c r="C571" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A572">
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C572" t="s">
         <v>1126</v>
       </c>
-      <c r="C572" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A573">
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C573" t="s">
         <v>1128</v>
       </c>
-      <c r="C573" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A574">
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C574" t="s">
         <v>1130</v>
       </c>
-      <c r="C574" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A575">
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A576">
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C576" t="s">
         <v>1133</v>
       </c>
-      <c r="C576" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A577">
         <v>597</v>
       </c>
@@ -11024,10 +11030,10 @@
         <v>938</v>
       </c>
       <c r="C577" s="3" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A578">
         <v>598</v>
       </c>
@@ -11035,1189 +11041,1197 @@
         <v>940</v>
       </c>
       <c r="C578" s="3" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A579">
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C579" t="s">
         <v>1135</v>
       </c>
-      <c r="C579" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A580">
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C580" t="s">
         <v>1137</v>
       </c>
-      <c r="C580" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A581">
         <v>602</v>
       </c>
       <c r="B581" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C581" t="s">
         <v>1139</v>
       </c>
-      <c r="C581" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A582">
         <v>604</v>
       </c>
       <c r="B582" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C582" t="s">
         <v>1141</v>
       </c>
-      <c r="C582" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A583">
         <v>606</v>
       </c>
       <c r="B583" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C583" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A584">
         <v>612</v>
       </c>
       <c r="B584" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C584" t="s">
         <v>1144</v>
       </c>
-      <c r="C584" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A585">
         <v>615</v>
       </c>
       <c r="B585" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C585" t="s">
         <v>1146</v>
       </c>
-      <c r="C585" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A586">
         <v>617</v>
       </c>
       <c r="B586" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C586" t="s">
         <v>1148</v>
       </c>
-      <c r="C586" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A587">
         <v>618</v>
       </c>
       <c r="B587" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C587" t="s">
         <v>1150</v>
       </c>
-      <c r="C587" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A588">
         <v>625</v>
       </c>
       <c r="B588" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C588" t="s">
         <v>1152</v>
       </c>
-      <c r="C588" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A589">
         <v>624</v>
       </c>
       <c r="B589" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C589" t="s">
         <v>1154</v>
       </c>
-      <c r="C589" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A590">
         <v>626</v>
       </c>
       <c r="B590" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C590" t="s">
         <v>1156</v>
       </c>
-      <c r="C590" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A591">
         <v>629</v>
       </c>
       <c r="B591" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C591" t="s">
         <v>1158</v>
       </c>
-      <c r="C591" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A592">
         <v>630</v>
       </c>
       <c r="B592" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C592" t="s">
         <v>1160</v>
       </c>
-      <c r="C592" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A593">
         <v>632</v>
       </c>
       <c r="C593" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A594">
         <v>633</v>
       </c>
       <c r="B594" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C594" t="s">
         <v>1163</v>
       </c>
-      <c r="C594" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A595">
         <v>635</v>
       </c>
       <c r="B595" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C595" t="s">
         <v>1165</v>
       </c>
-      <c r="C595" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A596">
         <v>636</v>
       </c>
       <c r="B596" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C596" t="s">
         <v>1167</v>
       </c>
-      <c r="C596" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A597">
         <v>642</v>
       </c>
       <c r="B597" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C597" t="s">
         <v>1169</v>
       </c>
-      <c r="C597" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A598">
         <v>644</v>
       </c>
       <c r="B598" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C598" t="s">
         <v>1171</v>
       </c>
-      <c r="C598" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A599">
         <v>646</v>
       </c>
       <c r="B599" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C599" t="s">
         <v>1173</v>
       </c>
-      <c r="C599" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A600">
         <v>649</v>
       </c>
       <c r="B600" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C600" t="s">
         <v>1175</v>
       </c>
-      <c r="C600" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A601">
         <v>650</v>
       </c>
       <c r="B601" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A602">
         <v>651</v>
       </c>
       <c r="B602" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C602" t="s">
         <v>1178</v>
       </c>
-      <c r="C602" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A603">
         <v>653</v>
       </c>
       <c r="B603" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C603" t="s">
         <v>1180</v>
       </c>
-      <c r="C603" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A604">
         <v>654</v>
       </c>
       <c r="B604" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C604" t="s">
         <v>1182</v>
       </c>
-      <c r="C604" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A605">
         <v>655</v>
       </c>
       <c r="B605" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C605" t="s">
         <v>1184</v>
       </c>
-      <c r="C605" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A606">
         <v>659</v>
       </c>
       <c r="B606" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C606" t="s">
         <v>1186</v>
       </c>
-      <c r="C606" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A607">
         <v>660</v>
       </c>
       <c r="B607" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C607" t="s">
         <v>1188</v>
       </c>
-      <c r="C607" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A608">
         <v>661</v>
       </c>
       <c r="B608" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C608" t="s">
         <v>1190</v>
       </c>
-      <c r="C608" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A609">
         <v>663</v>
       </c>
       <c r="B609" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C609" t="s">
         <v>1192</v>
       </c>
-      <c r="C609" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A610">
         <v>667</v>
       </c>
       <c r="B610" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C610" t="s">
         <v>1194</v>
       </c>
-      <c r="C610" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A611">
         <v>670</v>
       </c>
       <c r="B611" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C611" t="s">
         <v>1196</v>
       </c>
-      <c r="C611" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A612">
         <v>673</v>
       </c>
       <c r="B612" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C612" t="s">
         <v>1198</v>
       </c>
-      <c r="C612" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A613">
         <v>674</v>
       </c>
       <c r="B613" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C613" t="s">
         <v>1200</v>
       </c>
-      <c r="C613" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A614">
         <v>675</v>
       </c>
       <c r="B614" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C614" t="s">
         <v>1202</v>
       </c>
-      <c r="C614" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A615">
         <v>680</v>
       </c>
       <c r="B615" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C615" t="s">
         <v>1204</v>
       </c>
-      <c r="C615" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A616">
         <v>681</v>
       </c>
       <c r="B616" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C616" t="s">
         <v>1206</v>
       </c>
-      <c r="C616" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A617">
         <v>682</v>
       </c>
       <c r="B617" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C617" t="s">
         <v>1208</v>
       </c>
-      <c r="C617" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A618">
         <v>683</v>
       </c>
       <c r="B618" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C618" t="s">
         <v>1210</v>
       </c>
-      <c r="C618" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A619">
         <v>684</v>
       </c>
       <c r="B619" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C619" t="s">
         <v>1212</v>
       </c>
-      <c r="C619" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A620">
         <v>685</v>
       </c>
       <c r="B620" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C620" t="s">
         <v>1214</v>
       </c>
-      <c r="C620" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A621">
         <v>686</v>
       </c>
       <c r="B621" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C621" t="s">
         <v>1216</v>
       </c>
-      <c r="C621" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A622">
         <v>689</v>
       </c>
       <c r="B622" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C622" t="s">
         <v>1218</v>
       </c>
-      <c r="C622" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A623">
         <v>697</v>
       </c>
       <c r="B623" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C623" t="s">
         <v>1220</v>
       </c>
-      <c r="C623" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A624">
         <v>701</v>
       </c>
       <c r="B624" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C624" t="s">
         <v>1222</v>
       </c>
-      <c r="C624" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A625">
         <v>702</v>
       </c>
       <c r="B625" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C625" t="s">
         <v>1224</v>
       </c>
-      <c r="C625" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A626">
         <v>704</v>
       </c>
       <c r="B626" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C626" t="s">
         <v>1226</v>
       </c>
-      <c r="C626" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A627">
         <v>705</v>
       </c>
       <c r="B627" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C627" t="s">
         <v>1228</v>
       </c>
-      <c r="C627" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A628">
         <v>710</v>
       </c>
       <c r="B628" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C628" t="s">
         <v>1230</v>
       </c>
-      <c r="C628" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A629">
         <v>711</v>
       </c>
       <c r="B629" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C629" t="s">
         <v>1232</v>
       </c>
-      <c r="C629" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A630">
         <v>712</v>
       </c>
       <c r="B630" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C630" t="s">
         <v>1234</v>
       </c>
-      <c r="C630" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A631">
         <v>714</v>
       </c>
       <c r="B631" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A632">
         <v>717</v>
       </c>
       <c r="B632" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C632" t="s">
         <v>1237</v>
       </c>
-      <c r="C632" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A633">
         <v>718</v>
       </c>
       <c r="B633" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C633" t="s">
         <v>1239</v>
       </c>
-      <c r="C633" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A634">
         <v>719</v>
       </c>
       <c r="B634" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C634" t="s">
         <v>1241</v>
       </c>
-      <c r="C634" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
+    </row>
+    <row r="635" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A635">
         <v>721</v>
       </c>
       <c r="B635" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C635" t="s">
         <v>1243</v>
       </c>
-      <c r="C635" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A636">
         <v>722</v>
       </c>
       <c r="B636" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C636" t="s">
         <v>1245</v>
       </c>
-      <c r="C636" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A637">
         <v>723</v>
       </c>
       <c r="B637" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C637" t="s">
         <v>1247</v>
       </c>
-      <c r="C637" t="s">
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A638">
+        <v>724</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A639">
+        <v>725</v>
+      </c>
+      <c r="B639" s="2" t="s">
         <v>1248</v>
       </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A638">
-        <v>725</v>
-      </c>
-      <c r="B638" s="2" t="s">
+      <c r="C639" t="s">
         <v>1249</v>
       </c>
-      <c r="C638" t="s">
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A640">
+        <v>726</v>
+      </c>
+      <c r="B640" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A639">
-        <v>726</v>
-      </c>
-      <c r="B639" t="s">
+      <c r="C640" t="s">
         <v>1251</v>
       </c>
-      <c r="C639" t="s">
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A641">
+        <v>727</v>
+      </c>
+      <c r="B641" t="s">
         <v>1252</v>
       </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A640">
-        <v>727</v>
-      </c>
-      <c r="B640" t="s">
+      <c r="C641" t="s">
         <v>1253</v>
       </c>
-      <c r="C640" t="s">
+    </row>
+    <row r="642" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A642">
+        <v>728</v>
+      </c>
+      <c r="B642" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="641" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A641">
-        <v>728</v>
-      </c>
-      <c r="B641" t="s">
+      <c r="C642" t="s">
         <v>1255</v>
       </c>
-      <c r="C641" t="s">
+    </row>
+    <row r="643" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A643">
+        <v>729</v>
+      </c>
+      <c r="B643" t="s">
         <v>1256</v>
       </c>
-    </row>
-    <row r="642" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A642">
-        <v>729</v>
-      </c>
-      <c r="B642" t="s">
+      <c r="C643" t="s">
         <v>1257</v>
       </c>
-      <c r="C642" t="s">
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A644">
+        <v>730</v>
+      </c>
+      <c r="B644" t="s">
         <v>1258</v>
       </c>
-    </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A643">
-        <v>730</v>
-      </c>
-      <c r="B643" t="s">
+      <c r="C644" t="s">
         <v>1259</v>
       </c>
-      <c r="C643" t="s">
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A645">
+        <v>731</v>
+      </c>
+      <c r="B645" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A644">
-        <v>731</v>
-      </c>
-      <c r="B644" t="s">
+      <c r="C645" s="3" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A646">
+        <v>733</v>
+      </c>
+      <c r="B646" t="s">
         <v>1261</v>
       </c>
-      <c r="C644" s="3" t="s">
+      <c r="C646" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A647">
+        <v>735</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C647" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A648">
+        <v>736</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C648" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A649">
+        <v>737</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C649" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A650">
+        <v>738</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C650" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A651">
+        <v>739</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C651" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A652">
+        <v>740</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C652" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A653">
+        <v>741</v>
+      </c>
+      <c r="B653" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C653" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A654">
+        <v>742</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A655">
+        <v>743</v>
+      </c>
+      <c r="B655" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C655" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A656">
+        <v>744</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C656" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A657">
+        <v>745</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C657" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A658">
+        <v>746</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C658" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A659">
+        <v>747</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C659" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A660">
+        <v>748</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C660" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A661">
+        <v>749</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C661" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A662">
+        <v>753</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C662" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A663">
+        <v>755</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A664">
+        <v>756</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C664" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A665">
+        <v>757</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C665" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A666">
+        <v>758</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C666" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A667">
+        <v>759</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C667" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A668">
+        <v>760</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A669">
+        <v>761</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A670">
+        <v>762</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C670" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A671">
+        <v>763</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C671" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A672">
+        <v>764</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C672" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A673">
+        <v>765</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C673" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A674">
+        <v>766</v>
+      </c>
+      <c r="B674" s="1"/>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A675">
+        <v>767</v>
+      </c>
+      <c r="B675" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A676">
+        <v>768</v>
+      </c>
+      <c r="B676" s="1"/>
+      <c r="C676" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A677">
+        <v>769</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A678">
+        <v>772</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C678" s="3" t="s">
         <v>1326</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A645">
-        <v>733</v>
-      </c>
-      <c r="B645" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C645" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A646">
-        <v>735</v>
-      </c>
-      <c r="B646" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C646" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A647">
-        <v>736</v>
-      </c>
-      <c r="B647" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C647" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A648">
-        <v>737</v>
-      </c>
-      <c r="B648" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C648" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A649">
-        <v>738</v>
-      </c>
-      <c r="B649" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C649" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A650">
-        <v>739</v>
-      </c>
-      <c r="B650" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C650" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A651">
-        <v>740</v>
-      </c>
-      <c r="B651" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C651" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A652">
-        <v>741</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C652" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A653">
-        <v>742</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C653" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A654">
-        <v>743</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C654" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A655">
-        <v>744</v>
-      </c>
-      <c r="B655" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C655" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" ht="19.8" x14ac:dyDescent="0.5">
-      <c r="A656">
-        <v>745</v>
-      </c>
-      <c r="B656" s="1" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C656" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A657">
-        <v>746</v>
-      </c>
-      <c r="B657" s="1" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C657" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A658">
-        <v>747</v>
-      </c>
-      <c r="B658" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C658" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A659">
-        <v>748</v>
-      </c>
-      <c r="B659" s="1" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C659" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A660">
-        <v>749</v>
-      </c>
-      <c r="B660" s="1" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C660" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A661">
-        <v>753</v>
-      </c>
-      <c r="B661" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C661" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A662">
-        <v>755</v>
-      </c>
-      <c r="B662" s="1" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C662" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A663">
-        <v>756</v>
-      </c>
-      <c r="B663" s="1" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C663" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A664">
-        <v>757</v>
-      </c>
-      <c r="B664" s="1" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C664" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A665">
-        <v>758</v>
-      </c>
-      <c r="B665" s="1" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C665" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A666">
-        <v>759</v>
-      </c>
-      <c r="B666" s="1" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C666" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A667">
-        <v>760</v>
-      </c>
-      <c r="B667" s="1" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C667" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A668">
-        <v>761</v>
-      </c>
-      <c r="B668" s="1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C668" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A669">
-        <v>762</v>
-      </c>
-      <c r="B669" s="1" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C669" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A670">
-        <v>763</v>
-      </c>
-      <c r="B670" s="1" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C670" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A671">
-        <v>764</v>
-      </c>
-      <c r="B671" s="1" t="s">
-        <v>1314</v>
-      </c>
-      <c r="C671" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A672">
-        <v>765</v>
-      </c>
-      <c r="B672" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="C672" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A673">
-        <v>766</v>
-      </c>
-      <c r="B673" s="1"/>
-    </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A674">
-        <v>767</v>
-      </c>
-      <c r="B674" s="1" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C674" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A675">
-        <v>768</v>
-      </c>
-      <c r="B675" s="1"/>
-      <c r="C675" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A676">
-        <v>769</v>
-      </c>
-      <c r="B676" s="1" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C676" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A677">
-        <v>772</v>
-      </c>
-      <c r="B677" s="1" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C677" s="3" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A678">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A679">
         <v>773</v>
-      </c>
-      <c r="B678" s="1"/>
-      <c r="C678" s="3" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A679">
-        <v>774</v>
       </c>
       <c r="B679" s="1"/>
       <c r="C679" s="3" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A680">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B680" s="1"/>
       <c r="C680" s="3" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A681">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B681" s="1"/>
       <c r="C681" s="3" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A682">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B682" s="1"/>
       <c r="C682" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A683">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B683" s="1"/>
       <c r="C683" s="3" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A684">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B684" s="1"/>
       <c r="C684" s="3" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A685">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B685" s="1"/>
       <c r="C685" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A686">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B686" s="1"/>
       <c r="C686" s="3" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A687">
+        <v>782</v>
+      </c>
+      <c r="B687" s="1"/>
+      <c r="C687" s="3" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A688">
         <v>10001</v>
-      </c>
-      <c r="B687" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C687" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A688">
-        <v>10003</v>
       </c>
       <c r="B688" t="s">
         <v>1321</v>
       </c>
       <c r="C688" t="s">
         <v>1322</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A689">
+        <v>10003</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1320</v>
       </c>
     </row>
   </sheetData>
@@ -12225,7 +12239,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A687:C687 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467" numberStoredAsText="1"/>
+    <ignoredError sqref="A32:C35 A36:B36 A37:C37 A1:C1 A121:C127 A120:B120 A688:C688 A315:B315 A316:C326 A352:C352 A351:B351 A590:C590 A575 A574:B574 A460:C463 A459:B459 A617:C617 A235:C246 A247:B247 A248:C249 A234:B234 A95:C98 A146:C149 A145:B145 A541:C549 A540:B540 A55:C57 A558:C564 A29:C29 A28:B28 A579:C579 A308:C312 A307:B307 A53:B54 A457:C458 A516:C516 A93:B94 A554:C555 A553:B553 A346:C348 A345:B345 A52:C52 A51:B51 A72:C78 A70:B70 A163:C166 A162:B162 A378:C378 A377:B377 A620:C622 A258:C259 A257:B257 A6:C7 A573:C573 A567:C568 A566 A608:C608 A21:C22 A20:B20 A420:C420 A115:C119 A114:B114 A287:C294 A418:B419 A80:C84 A79:B79 A504:C504 A503 A151:C153 A150:B150 A481:C486 A480:B480 A520:C520 A519:B519 A532:C535 A531:B531 A615:B615 A576:B578 A513:B515 A501:C502 A453:C454 A424:C424 A14:C14 A13:B13 A2:B5 A582:C582 A580:B580 A450:C450 A449:B449 A551:C552 A550:B550 A539:C539 A518:C518 A517:B517 A508:C508 A509:B509 A510:C512 A507:B507 A466:C466 A448:C448 A447:B447 A433:C446 A432:B432 A425:B425 A403:C405 A402:B402 A281:C284 A269:C278 A268:B268 A261:C267 A260:B260 A252:C256 A250:B251 A231:C233 A229:B230 A108:C112 A107:B107 A59:C69 A58:B58 A155:C161 A154:B154 A129:C132 A128:B128 A71 A9:C12 A8:B8 A595:C597 A380:C382 A383:B383 A384:C385 A379:B379 A451:B452 A523:C530 A521:B522 A506:C506 A505:B505 A470:C472 A469:B469 A455:B456 A100:C106 A99:B99 A40:C42 A16:C19 A15:B15 A565:B565 A556:B557 A478:C479 A477:B477 A408:C411 A407:B407 A387:C389 A386:B386 A328:C337 A327 A297:C306 A295:B295 A44:C50 A43:B43 A602:C603 A599:B599 A594:B594 A354:C373 A353:B353 A464:B465 A350:C350 A349:B349 A475:C476 A473 A86:C92 A85:B85 A30:B31 A38:B39 A171:C207 A170:B170 A605:C605 A586:C587 A584:B584 A569:B572 A24:C27 A23:B23 A499:B500 A414:C417 A412:A413 C412:C413 A406 A375:C376 A374:B374 A279:B280 A536:B538 A474:B474 A610:B610 A591:B591 A134:C144 A133:B133 A314:C314 A313:B313 A209:C228 A208:B208 A421:B423 A488:C498 A487:B487 A285:B286 A168:C169 A167:B167 A391:C391 A390:B390 A393:C401 A392 A612:B613 A426:C431 A601:B601 A113:B113 A340:C344 A338:B338 A339:B339 A296:B296 A468:C468 A467:B467" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/config/nickname_song.xlsx
+++ b/config/nickname_song.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Tsugu-Backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DBADC0-0718-478E-85BC-3495E49E29A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282F8804-6B5A-4DF2-B248-8BACE74DBA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="3012" windowWidth="13176" windowHeight="22536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="1350">
   <si>
     <t>Id</t>
   </si>
@@ -1406,9 +1406,6 @@
     <t>天ノ弱</t>
   </si>
   <si>
-    <t>天弱,天之弱,迫害佐仓,天之强</t>
-  </si>
-  <si>
     <t>White Afternoon</t>
   </si>
   <si>
@@ -4242,10 +4239,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>SOS,sos,苍蓝钢铁,效率,救救,s</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>五等分的新娘,五等分的花嫁,五等份的新娘,五等份的花嫁</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -4271,6 +4264,18 @@
   </si>
   <si>
     <t>逆天伴走,爱灯,碧天绊走,碧天伴走</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOS,sos,苍蓝钢铁,效率,救救,s,太阳之子</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>天弱,天之弱,迫害佐仓,天之强,天之若</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>微笑颂歌,微笑赞歌</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -4692,16 +4697,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C689"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C690"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="50.75" customWidth="1"/>
-    <col min="3" max="3" width="65.75" customWidth="1"/>
-    <col min="4" max="4" width="55.75" customWidth="1"/>
+    <col min="1" max="1" width="10.69921875" customWidth="1"/>
+    <col min="2" max="2" width="50.69921875" customWidth="1"/>
+    <col min="3" max="3" width="65.69921875" customWidth="1"/>
+    <col min="4" max="4" width="55.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4712,7 +4717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4723,7 +4728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4734,7 +4739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4745,7 +4750,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4756,7 +4761,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4767,7 +4772,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4778,7 +4783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4789,7 +4794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4800,7 +4805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4811,7 +4816,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4822,7 +4827,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4833,7 +4838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4844,7 +4849,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4855,7 +4860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4866,7 +4871,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4877,7 +4882,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4888,7 +4893,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4899,7 +4904,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4910,7 +4915,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4921,7 +4926,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4932,7 +4937,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4943,7 +4948,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>24</v>
       </c>
@@ -4954,7 +4959,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25</v>
       </c>
@@ -4965,7 +4970,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26</v>
       </c>
@@ -4976,7 +4981,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>27</v>
       </c>
@@ -4987,7 +4992,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
@@ -4998,7 +5003,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
@@ -5009,7 +5014,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
@@ -5020,7 +5025,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31</v>
       </c>
@@ -5031,7 +5036,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>32</v>
       </c>
@@ -5042,7 +5047,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>33</v>
       </c>
@@ -5053,7 +5058,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>34</v>
       </c>
@@ -5064,7 +5069,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>35</v>
       </c>
@@ -5075,7 +5080,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>36</v>
       </c>
@@ -5086,7 +5091,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>37</v>
       </c>
@@ -5097,7 +5102,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
@@ -5108,7 +5113,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>41</v>
       </c>
@@ -5119,7 +5124,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>42</v>
       </c>
@@ -5130,7 +5135,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>43</v>
       </c>
@@ -5141,7 +5146,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>44</v>
       </c>
@@ -5152,7 +5157,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>45</v>
       </c>
@@ -5163,7 +5168,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>46</v>
       </c>
@@ -5174,7 +5179,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>47</v>
       </c>
@@ -5185,7 +5190,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>48</v>
       </c>
@@ -5196,7 +5201,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>49</v>
       </c>
@@ -5207,7 +5212,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>50</v>
       </c>
@@ -5218,7 +5223,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>51</v>
       </c>
@@ -5229,7 +5234,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>52</v>
       </c>
@@ -5240,7 +5245,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>53</v>
       </c>
@@ -5251,7 +5256,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>54</v>
       </c>
@@ -5262,7 +5267,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>55</v>
       </c>
@@ -5273,7 +5278,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>56</v>
       </c>
@@ -5284,7 +5289,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>57</v>
       </c>
@@ -5295,7 +5300,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>58</v>
       </c>
@@ -5306,7 +5311,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>59</v>
       </c>
@@ -5317,7 +5322,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>60</v>
       </c>
@@ -5328,7 +5333,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>61</v>
       </c>
@@ -5339,7 +5344,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>62</v>
       </c>
@@ -5350,7 +5355,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>63</v>
       </c>
@@ -5361,7 +5366,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>64</v>
       </c>
@@ -5372,7 +5377,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>65</v>
       </c>
@@ -5383,7 +5388,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>66</v>
       </c>
@@ -5394,7 +5399,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>67</v>
       </c>
@@ -5405,7 +5410,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>68</v>
       </c>
@@ -5416,7 +5421,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>69</v>
       </c>
@@ -5427,7 +5432,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>70</v>
       </c>
@@ -5438,7 +5443,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>71</v>
       </c>
@@ -5449,7 +5454,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>72</v>
       </c>
@@ -5460,7 +5465,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>73</v>
       </c>
@@ -5471,7 +5476,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>74</v>
       </c>
@@ -5482,7 +5487,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>75</v>
       </c>
@@ -5493,7 +5498,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>76</v>
       </c>
@@ -5504,7 +5509,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>77</v>
       </c>
@@ -5515,7 +5520,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>78</v>
       </c>
@@ -5526,7 +5531,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>79</v>
       </c>
@@ -5537,7 +5542,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>80</v>
       </c>
@@ -5548,7 +5553,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>81</v>
       </c>
@@ -5559,7 +5564,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>82</v>
       </c>
@@ -5570,7 +5575,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>83</v>
       </c>
@@ -5581,7 +5586,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>84</v>
       </c>
@@ -5592,7 +5597,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>85</v>
       </c>
@@ -5603,7 +5608,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>86</v>
       </c>
@@ -5614,7 +5619,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>87</v>
       </c>
@@ -5625,7 +5630,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>88</v>
       </c>
@@ -5636,7 +5641,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>89</v>
       </c>
@@ -5647,7 +5652,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>90</v>
       </c>
@@ -5658,7 +5663,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>91</v>
       </c>
@@ -5669,7 +5674,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>92</v>
       </c>
@@ -5680,7 +5685,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>93</v>
       </c>
@@ -5691,7 +5696,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>94</v>
       </c>
@@ -5702,7 +5707,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>95</v>
       </c>
@@ -5713,7 +5718,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>96</v>
       </c>
@@ -5724,7 +5729,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5735,7 +5740,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5746,7 +5751,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5757,7 +5762,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5768,7 +5773,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5779,7 +5784,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5790,7 +5795,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5801,7 +5806,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5812,7 +5817,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5823,7 +5828,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5834,7 +5839,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5845,7 +5850,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5856,7 +5861,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5867,7 +5872,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5878,7 +5883,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5889,7 +5894,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5900,7 +5905,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5911,7 +5916,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5922,7 +5927,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5933,7 +5938,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5941,10 +5946,10 @@
         <v>225</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>122</v>
       </c>
@@ -5955,7 +5960,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>123</v>
       </c>
@@ -5966,7 +5971,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>124</v>
       </c>
@@ -5977,7 +5982,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>125</v>
       </c>
@@ -5988,7 +5993,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126</v>
       </c>
@@ -5999,7 +6004,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>127</v>
       </c>
@@ -6010,7 +6015,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>128</v>
       </c>
@@ -6021,7 +6026,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>129</v>
       </c>
@@ -6032,7 +6037,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>130</v>
       </c>
@@ -6043,7 +6048,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>131</v>
       </c>
@@ -6054,7 +6059,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>132</v>
       </c>
@@ -6065,7 +6070,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>133</v>
       </c>
@@ -6076,7 +6081,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>134</v>
       </c>
@@ -6087,7 +6092,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>135</v>
       </c>
@@ -6098,7 +6103,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>136</v>
       </c>
@@ -6109,7 +6114,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>137</v>
       </c>
@@ -6120,7 +6125,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>138</v>
       </c>
@@ -6131,7 +6136,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>139</v>
       </c>
@@ -6142,7 +6147,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>140</v>
       </c>
@@ -6153,7 +6158,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>141</v>
       </c>
@@ -6164,7 +6169,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>142</v>
       </c>
@@ -6175,7 +6180,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>143</v>
       </c>
@@ -6186,7 +6191,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>144</v>
       </c>
@@ -6197,7 +6202,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>145</v>
       </c>
@@ -6208,7 +6213,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>146</v>
       </c>
@@ -6219,7 +6224,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>147</v>
       </c>
@@ -6230,7 +6235,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>148</v>
       </c>
@@ -6241,7 +6246,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>149</v>
       </c>
@@ -6252,7 +6257,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>150</v>
       </c>
@@ -6263,7 +6268,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>151</v>
       </c>
@@ -6274,7 +6279,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>152</v>
       </c>
@@ -6285,7 +6290,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>153</v>
       </c>
@@ -6296,7 +6301,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>154</v>
       </c>
@@ -6307,7 +6312,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>155</v>
       </c>
@@ -6318,7 +6323,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>156</v>
       </c>
@@ -6329,7 +6334,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>157</v>
       </c>
@@ -6340,7 +6345,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>158</v>
       </c>
@@ -6351,7 +6356,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>159</v>
       </c>
@@ -6362,7 +6367,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>160</v>
       </c>
@@ -6373,7 +6378,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>161</v>
       </c>
@@ -6384,7 +6389,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>162</v>
       </c>
@@ -6395,7 +6400,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>163</v>
       </c>
@@ -6406,7 +6411,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>164</v>
       </c>
@@ -6417,7 +6422,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>165</v>
       </c>
@@ -6428,7 +6433,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>166</v>
       </c>
@@ -6439,7 +6444,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>167</v>
       </c>
@@ -6450,7 +6455,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>168</v>
       </c>
@@ -6461,7 +6466,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>169</v>
       </c>
@@ -6472,7 +6477,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>170</v>
       </c>
@@ -6483,7 +6488,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>171</v>
       </c>
@@ -6494,7 +6499,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>172</v>
       </c>
@@ -6505,7 +6510,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>173</v>
       </c>
@@ -6516,7 +6521,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>174</v>
       </c>
@@ -6527,7 +6532,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>175</v>
       </c>
@@ -6538,7 +6543,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>176</v>
       </c>
@@ -6549,7 +6554,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>177</v>
       </c>
@@ -6560,7 +6565,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>178</v>
       </c>
@@ -6571,7 +6576,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>179</v>
       </c>
@@ -6582,7 +6587,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>180</v>
       </c>
@@ -6593,7 +6598,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>181</v>
       </c>
@@ -6604,7 +6609,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>182</v>
       </c>
@@ -6615,7 +6620,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>183</v>
       </c>
@@ -6626,7 +6631,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>184</v>
       </c>
@@ -6637,7 +6642,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>185</v>
       </c>
@@ -6648,7 +6653,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>186</v>
       </c>
@@ -6659,7 +6664,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>187</v>
       </c>
@@ -6670,7 +6675,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>188</v>
       </c>
@@ -6681,7 +6686,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>189</v>
       </c>
@@ -6692,7 +6697,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>190</v>
       </c>
@@ -6703,7 +6708,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>191</v>
       </c>
@@ -6714,7 +6719,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>192</v>
       </c>
@@ -6725,7 +6730,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6736,7 +6741,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6747,7 +6752,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6758,7 +6763,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6769,7 +6774,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6780,7 +6785,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6791,7 +6796,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6802,7 +6807,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6813,7 +6818,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6824,7 +6829,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6835,7 +6840,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6846,7 +6851,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6857,7 +6862,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6868,7 +6873,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6879,7 +6884,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6890,7 +6895,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6901,7 +6906,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6912,7 +6917,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6923,7 +6928,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6934,7 +6939,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6945,7 +6950,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>213</v>
       </c>
@@ -6956,7 +6961,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>214</v>
       </c>
@@ -6967,7 +6972,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>215</v>
       </c>
@@ -6978,7 +6983,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>217</v>
       </c>
@@ -6989,7 +6994,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>218</v>
       </c>
@@ -7000,7 +7005,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>219</v>
       </c>
@@ -7011,7 +7016,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>220</v>
       </c>
@@ -7022,7 +7027,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>221</v>
       </c>
@@ -7033,7 +7038,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>222</v>
       </c>
@@ -7044,7 +7049,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>223</v>
       </c>
@@ -7055,7 +7060,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>224</v>
       </c>
@@ -7066,7 +7071,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>225</v>
       </c>
@@ -7077,7 +7082,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>226</v>
       </c>
@@ -7088,7 +7093,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>227</v>
       </c>
@@ -7099,7 +7104,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>228</v>
       </c>
@@ -7110,7 +7115,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>229</v>
       </c>
@@ -7121,7 +7126,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>230</v>
       </c>
@@ -7132,7 +7137,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>231</v>
       </c>
@@ -7143,7 +7148,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>232</v>
       </c>
@@ -7154,5084 +7159,5093 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>233</v>
       </c>
       <c r="B224" t="s">
         <v>446</v>
       </c>
-      <c r="C224" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C224" s="3" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>234</v>
       </c>
       <c r="B225" t="s">
+        <v>447</v>
+      </c>
+      <c r="C225" t="s">
         <v>448</v>
       </c>
-      <c r="C225" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>235</v>
       </c>
       <c r="B226" t="s">
+        <v>449</v>
+      </c>
+      <c r="C226" t="s">
         <v>450</v>
       </c>
-      <c r="C226" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>236</v>
       </c>
       <c r="B227" t="s">
+        <v>451</v>
+      </c>
+      <c r="C227" t="s">
         <v>452</v>
       </c>
-      <c r="C227" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>237</v>
       </c>
       <c r="B228" t="s">
+        <v>453</v>
+      </c>
+      <c r="C228" t="s">
         <v>454</v>
       </c>
-      <c r="C228" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>238</v>
       </c>
       <c r="B229" t="s">
+        <v>455</v>
+      </c>
+      <c r="C229" t="s">
         <v>456</v>
       </c>
-      <c r="C229" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>239</v>
       </c>
       <c r="B230" t="s">
+        <v>457</v>
+      </c>
+      <c r="C230" t="s">
         <v>458</v>
       </c>
-      <c r="C230" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>240</v>
       </c>
       <c r="B231" t="s">
+        <v>459</v>
+      </c>
+      <c r="C231" t="s">
         <v>460</v>
       </c>
-      <c r="C231" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>241</v>
       </c>
       <c r="B232" t="s">
+        <v>461</v>
+      </c>
+      <c r="C232" t="s">
         <v>462</v>
       </c>
-      <c r="C232" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>242</v>
       </c>
       <c r="B233" t="s">
+        <v>463</v>
+      </c>
+      <c r="C233" t="s">
         <v>464</v>
       </c>
-      <c r="C233" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>243</v>
       </c>
       <c r="B234" t="s">
+        <v>465</v>
+      </c>
+      <c r="C234" t="s">
         <v>466</v>
       </c>
-      <c r="C234" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>244</v>
       </c>
       <c r="B235" t="s">
+        <v>467</v>
+      </c>
+      <c r="C235" t="s">
         <v>468</v>
       </c>
-      <c r="C235" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>245</v>
       </c>
       <c r="B236" t="s">
+        <v>469</v>
+      </c>
+      <c r="C236" t="s">
         <v>470</v>
       </c>
-      <c r="C236" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>246</v>
       </c>
       <c r="B237" t="s">
+        <v>471</v>
+      </c>
+      <c r="C237" t="s">
         <v>472</v>
       </c>
-      <c r="C237" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>247</v>
       </c>
       <c r="B238" t="s">
+        <v>473</v>
+      </c>
+      <c r="C238" t="s">
         <v>474</v>
       </c>
-      <c r="C238" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>248</v>
       </c>
       <c r="B239" t="s">
+        <v>475</v>
+      </c>
+      <c r="C239" t="s">
         <v>476</v>
       </c>
-      <c r="C239" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>249</v>
       </c>
       <c r="B240" t="s">
+        <v>477</v>
+      </c>
+      <c r="C240" t="s">
         <v>478</v>
       </c>
-      <c r="C240" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>250</v>
       </c>
       <c r="B241" t="s">
+        <v>479</v>
+      </c>
+      <c r="C241" t="s">
         <v>480</v>
       </c>
-      <c r="C241" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>251</v>
       </c>
       <c r="B242" t="s">
+        <v>481</v>
+      </c>
+      <c r="C242" t="s">
         <v>482</v>
       </c>
-      <c r="C242" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>252</v>
       </c>
       <c r="B243" t="s">
+        <v>483</v>
+      </c>
+      <c r="C243" t="s">
         <v>484</v>
       </c>
-      <c r="C243" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>253</v>
       </c>
       <c r="B244" t="s">
+        <v>485</v>
+      </c>
+      <c r="C244" t="s">
         <v>486</v>
       </c>
-      <c r="C244" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>254</v>
       </c>
       <c r="B245" t="s">
+        <v>487</v>
+      </c>
+      <c r="C245" t="s">
         <v>488</v>
       </c>
-      <c r="C245" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>255</v>
       </c>
       <c r="B246" t="s">
+        <v>489</v>
+      </c>
+      <c r="C246" t="s">
         <v>490</v>
       </c>
-      <c r="C246" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>256</v>
       </c>
       <c r="B247" t="s">
+        <v>491</v>
+      </c>
+      <c r="C247" t="s">
         <v>492</v>
       </c>
-      <c r="C247" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>257</v>
       </c>
       <c r="B248" t="s">
+        <v>493</v>
+      </c>
+      <c r="C248" t="s">
         <v>494</v>
       </c>
-      <c r="C248" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>258</v>
       </c>
       <c r="B249" t="s">
+        <v>495</v>
+      </c>
+      <c r="C249" t="s">
         <v>496</v>
       </c>
-      <c r="C249" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>259</v>
       </c>
       <c r="B250" t="s">
+        <v>497</v>
+      </c>
+      <c r="C250" t="s">
         <v>498</v>
       </c>
-      <c r="C250" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>260</v>
       </c>
       <c r="B251" t="s">
+        <v>499</v>
+      </c>
+      <c r="C251" t="s">
         <v>500</v>
       </c>
-      <c r="C251" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>261</v>
       </c>
       <c r="B252" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C252" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.15">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>262</v>
       </c>
       <c r="B253" t="s">
+        <v>502</v>
+      </c>
+      <c r="C253" t="s">
         <v>503</v>
       </c>
-      <c r="C253" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>263</v>
       </c>
       <c r="B254" t="s">
+        <v>504</v>
+      </c>
+      <c r="C254" t="s">
         <v>505</v>
       </c>
-      <c r="C254" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>264</v>
       </c>
       <c r="B255" t="s">
+        <v>506</v>
+      </c>
+      <c r="C255" t="s">
         <v>507</v>
       </c>
-      <c r="C255" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>265</v>
       </c>
       <c r="B256" t="s">
+        <v>508</v>
+      </c>
+      <c r="C256" t="s">
         <v>509</v>
       </c>
-      <c r="C256" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>266</v>
       </c>
       <c r="B257" t="s">
+        <v>510</v>
+      </c>
+      <c r="C257" t="s">
         <v>511</v>
       </c>
-      <c r="C257" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>267</v>
       </c>
       <c r="B258" t="s">
+        <v>512</v>
+      </c>
+      <c r="C258" t="s">
         <v>513</v>
       </c>
-      <c r="C258" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>268</v>
       </c>
       <c r="B259" t="s">
+        <v>514</v>
+      </c>
+      <c r="C259" t="s">
         <v>515</v>
       </c>
-      <c r="C259" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>269</v>
       </c>
       <c r="B260" t="s">
+        <v>516</v>
+      </c>
+      <c r="C260" t="s">
         <v>517</v>
       </c>
-      <c r="C260" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>270</v>
       </c>
       <c r="B261" t="s">
+        <v>518</v>
+      </c>
+      <c r="C261" t="s">
         <v>519</v>
       </c>
-      <c r="C261" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>271</v>
       </c>
       <c r="B262" t="s">
+        <v>520</v>
+      </c>
+      <c r="C262" t="s">
         <v>521</v>
       </c>
-      <c r="C262" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>272</v>
       </c>
       <c r="B263" t="s">
+        <v>522</v>
+      </c>
+      <c r="C263" t="s">
         <v>523</v>
       </c>
-      <c r="C263" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>274</v>
       </c>
       <c r="B264" t="s">
+        <v>524</v>
+      </c>
+      <c r="C264" t="s">
         <v>525</v>
       </c>
-      <c r="C264" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>275</v>
       </c>
       <c r="B265" t="s">
+        <v>526</v>
+      </c>
+      <c r="C265" t="s">
         <v>527</v>
       </c>
-      <c r="C265" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>276</v>
       </c>
       <c r="B266" t="s">
+        <v>528</v>
+      </c>
+      <c r="C266" t="s">
         <v>529</v>
       </c>
-      <c r="C266" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>277</v>
       </c>
       <c r="B267" t="s">
+        <v>530</v>
+      </c>
+      <c r="C267" t="s">
         <v>531</v>
       </c>
-      <c r="C267" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>278</v>
       </c>
       <c r="B268" t="s">
+        <v>532</v>
+      </c>
+      <c r="C268" t="s">
         <v>533</v>
       </c>
-      <c r="C268" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>279</v>
       </c>
       <c r="B269" t="s">
+        <v>534</v>
+      </c>
+      <c r="C269" t="s">
         <v>535</v>
       </c>
-      <c r="C269" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>280</v>
       </c>
       <c r="B270" t="s">
+        <v>536</v>
+      </c>
+      <c r="C270" t="s">
         <v>537</v>
       </c>
-      <c r="C270" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>281</v>
       </c>
       <c r="B271" t="s">
+        <v>538</v>
+      </c>
+      <c r="C271" t="s">
         <v>539</v>
       </c>
-      <c r="C271" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>282</v>
       </c>
       <c r="B272" t="s">
+        <v>540</v>
+      </c>
+      <c r="C272" t="s">
         <v>541</v>
       </c>
-      <c r="C272" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>283</v>
       </c>
       <c r="B273" t="s">
+        <v>542</v>
+      </c>
+      <c r="C273" t="s">
         <v>543</v>
       </c>
-      <c r="C273" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>284</v>
       </c>
       <c r="B274" t="s">
+        <v>544</v>
+      </c>
+      <c r="C274" t="s">
         <v>545</v>
       </c>
-      <c r="C274" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>285</v>
       </c>
       <c r="B275" t="s">
+        <v>546</v>
+      </c>
+      <c r="C275" t="s">
         <v>547</v>
       </c>
-      <c r="C275" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>286</v>
       </c>
       <c r="B276" t="s">
+        <v>548</v>
+      </c>
+      <c r="C276" t="s">
         <v>549</v>
       </c>
-      <c r="C276" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>287</v>
       </c>
       <c r="B277" t="s">
+        <v>550</v>
+      </c>
+      <c r="C277" t="s">
         <v>551</v>
       </c>
-      <c r="C277" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>288</v>
       </c>
       <c r="B278" t="s">
+        <v>552</v>
+      </c>
+      <c r="C278" t="s">
         <v>553</v>
       </c>
-      <c r="C278" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>289</v>
       </c>
       <c r="B279" t="s">
+        <v>554</v>
+      </c>
+      <c r="C279" t="s">
         <v>555</v>
       </c>
-      <c r="C279" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>290</v>
       </c>
       <c r="B280" t="s">
+        <v>556</v>
+      </c>
+      <c r="C280" t="s">
         <v>557</v>
       </c>
-      <c r="C280" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>291</v>
       </c>
       <c r="B281" t="s">
+        <v>558</v>
+      </c>
+      <c r="C281" t="s">
         <v>559</v>
       </c>
-      <c r="C281" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>292</v>
       </c>
       <c r="B282" t="s">
+        <v>560</v>
+      </c>
+      <c r="C282" t="s">
         <v>561</v>
       </c>
-      <c r="C282" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>293</v>
       </c>
       <c r="B283" t="s">
+        <v>562</v>
+      </c>
+      <c r="C283" t="s">
         <v>563</v>
       </c>
-      <c r="C283" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>294</v>
       </c>
       <c r="B284" t="s">
+        <v>564</v>
+      </c>
+      <c r="C284" t="s">
         <v>565</v>
       </c>
-      <c r="C284" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>295</v>
       </c>
       <c r="B285" t="s">
+        <v>566</v>
+      </c>
+      <c r="C285" t="s">
         <v>567</v>
       </c>
-      <c r="C285" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>296</v>
       </c>
       <c r="B286" t="s">
+        <v>568</v>
+      </c>
+      <c r="C286" t="s">
         <v>569</v>
       </c>
-      <c r="C286" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>297</v>
       </c>
       <c r="B287" t="s">
+        <v>570</v>
+      </c>
+      <c r="C287" t="s">
         <v>571</v>
       </c>
-      <c r="C287" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>298</v>
       </c>
       <c r="B288" t="s">
+        <v>572</v>
+      </c>
+      <c r="C288" t="s">
         <v>573</v>
       </c>
-      <c r="C288" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>299</v>
       </c>
       <c r="B289" t="s">
+        <v>574</v>
+      </c>
+      <c r="C289" t="s">
         <v>575</v>
       </c>
-      <c r="C289" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>300</v>
       </c>
       <c r="B290" t="s">
+        <v>576</v>
+      </c>
+      <c r="C290" t="s">
         <v>577</v>
       </c>
-      <c r="C290" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>301</v>
       </c>
       <c r="B291" t="s">
+        <v>578</v>
+      </c>
+      <c r="C291" t="s">
         <v>579</v>
       </c>
-      <c r="C291" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>302</v>
       </c>
       <c r="B292" t="s">
+        <v>580</v>
+      </c>
+      <c r="C292" t="s">
         <v>581</v>
       </c>
-      <c r="C292" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>303</v>
       </c>
       <c r="B293" t="s">
+        <v>582</v>
+      </c>
+      <c r="C293" t="s">
         <v>583</v>
       </c>
-      <c r="C293" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>304</v>
       </c>
       <c r="B294" t="s">
+        <v>584</v>
+      </c>
+      <c r="C294" t="s">
         <v>585</v>
       </c>
-      <c r="C294" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>305</v>
       </c>
       <c r="B295" t="s">
+        <v>586</v>
+      </c>
+      <c r="C295" t="s">
         <v>587</v>
       </c>
-      <c r="C295" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>306</v>
       </c>
       <c r="B296" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>307</v>
       </c>
       <c r="B297" t="s">
+        <v>589</v>
+      </c>
+      <c r="C297" t="s">
         <v>590</v>
       </c>
-      <c r="C297" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>308</v>
       </c>
       <c r="B298" t="s">
+        <v>591</v>
+      </c>
+      <c r="C298" t="s">
         <v>592</v>
       </c>
-      <c r="C298" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>309</v>
       </c>
       <c r="B299" t="s">
+        <v>593</v>
+      </c>
+      <c r="C299" t="s">
         <v>594</v>
       </c>
-      <c r="C299" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>310</v>
       </c>
       <c r="B300" t="s">
+        <v>595</v>
+      </c>
+      <c r="C300" t="s">
         <v>596</v>
       </c>
-      <c r="C300" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>311</v>
       </c>
       <c r="B301" t="s">
+        <v>597</v>
+      </c>
+      <c r="C301" t="s">
         <v>598</v>
       </c>
-      <c r="C301" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>312</v>
       </c>
       <c r="B302" t="s">
+        <v>599</v>
+      </c>
+      <c r="C302" t="s">
         <v>600</v>
       </c>
-      <c r="C302" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>313</v>
       </c>
       <c r="B303" t="s">
+        <v>601</v>
+      </c>
+      <c r="C303" t="s">
         <v>602</v>
       </c>
-      <c r="C303" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>314</v>
       </c>
       <c r="B304" t="s">
+        <v>603</v>
+      </c>
+      <c r="C304" t="s">
         <v>604</v>
       </c>
-      <c r="C304" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>315</v>
       </c>
       <c r="B305" t="s">
+        <v>605</v>
+      </c>
+      <c r="C305" t="s">
         <v>606</v>
       </c>
-      <c r="C305" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>316</v>
       </c>
       <c r="B306" t="s">
+        <v>607</v>
+      </c>
+      <c r="C306" t="s">
         <v>608</v>
       </c>
-      <c r="C306" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>317</v>
       </c>
       <c r="B307" t="s">
+        <v>609</v>
+      </c>
+      <c r="C307" t="s">
         <v>610</v>
       </c>
-      <c r="C307" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>318</v>
       </c>
       <c r="B308" t="s">
+        <v>611</v>
+      </c>
+      <c r="C308" t="s">
         <v>612</v>
       </c>
-      <c r="C308" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>319</v>
       </c>
       <c r="B309" t="s">
+        <v>613</v>
+      </c>
+      <c r="C309" t="s">
         <v>614</v>
       </c>
-      <c r="C309" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>320</v>
       </c>
       <c r="B310" t="s">
+        <v>615</v>
+      </c>
+      <c r="C310" t="s">
         <v>616</v>
       </c>
-      <c r="C310" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>321</v>
       </c>
       <c r="B311" t="s">
+        <v>617</v>
+      </c>
+      <c r="C311" t="s">
         <v>618</v>
       </c>
-      <c r="C311" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>322</v>
       </c>
       <c r="B312" t="s">
+        <v>619</v>
+      </c>
+      <c r="C312" t="s">
         <v>620</v>
       </c>
-      <c r="C312" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>323</v>
       </c>
       <c r="B313" t="s">
+        <v>621</v>
+      </c>
+      <c r="C313" t="s">
         <v>622</v>
       </c>
-      <c r="C313" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>324</v>
       </c>
       <c r="B314" t="s">
+        <v>623</v>
+      </c>
+      <c r="C314" t="s">
         <v>624</v>
       </c>
-      <c r="C314" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>325</v>
       </c>
       <c r="B315" t="s">
+        <v>625</v>
+      </c>
+      <c r="C315" t="s">
         <v>626</v>
       </c>
-      <c r="C315" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>627</v>
+      </c>
+      <c r="C316" t="s">
         <v>628</v>
       </c>
-      <c r="C316" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>629</v>
+      </c>
+      <c r="C317" t="s">
         <v>630</v>
       </c>
-      <c r="C317" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>631</v>
+      </c>
+      <c r="C318" t="s">
         <v>632</v>
       </c>
-      <c r="C318" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>633</v>
+      </c>
+      <c r="C319" t="s">
         <v>634</v>
       </c>
-      <c r="C319" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>635</v>
+      </c>
+      <c r="C320" t="s">
         <v>636</v>
       </c>
-      <c r="C320" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>637</v>
+      </c>
+      <c r="C321" t="s">
         <v>638</v>
       </c>
-      <c r="C321" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>639</v>
+      </c>
+      <c r="C322" t="s">
         <v>640</v>
       </c>
-      <c r="C322" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>641</v>
+      </c>
+      <c r="C323" t="s">
         <v>642</v>
       </c>
-      <c r="C323" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>643</v>
+      </c>
+      <c r="C324" t="s">
         <v>644</v>
       </c>
-      <c r="C324" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>645</v>
+      </c>
+      <c r="C325" t="s">
         <v>646</v>
       </c>
-      <c r="C325" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>647</v>
+      </c>
+      <c r="C326" t="s">
         <v>648</v>
       </c>
-      <c r="C326" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>649</v>
+      </c>
+      <c r="C327" t="s">
         <v>650</v>
       </c>
-      <c r="C327" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>651</v>
+      </c>
+      <c r="C328" t="s">
         <v>652</v>
       </c>
-      <c r="C328" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>653</v>
+      </c>
+      <c r="C329" t="s">
         <v>654</v>
       </c>
-      <c r="C329" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>655</v>
+      </c>
+      <c r="C330" t="s">
         <v>656</v>
       </c>
-      <c r="C330" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>657</v>
+      </c>
+      <c r="C331" t="s">
         <v>658</v>
       </c>
-      <c r="C331" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>659</v>
+      </c>
+      <c r="C332" t="s">
         <v>660</v>
       </c>
-      <c r="C332" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>661</v>
+      </c>
+      <c r="C333" t="s">
         <v>662</v>
       </c>
-      <c r="C333" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>663</v>
+      </c>
+      <c r="C334" t="s">
         <v>664</v>
       </c>
-      <c r="C334" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>665</v>
+      </c>
+      <c r="C335" t="s">
         <v>666</v>
       </c>
-      <c r="C335" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>667</v>
+      </c>
+      <c r="C336" t="s">
         <v>668</v>
       </c>
-      <c r="C336" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>669</v>
+      </c>
+      <c r="C337" t="s">
         <v>670</v>
       </c>
-      <c r="C337" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>348</v>
       </c>
       <c r="B338" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>349</v>
       </c>
       <c r="B339" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>673</v>
+      </c>
+      <c r="C340" t="s">
         <v>674</v>
       </c>
-      <c r="C340" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>675</v>
+      </c>
+      <c r="C341" t="s">
         <v>676</v>
       </c>
-      <c r="C341" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>677</v>
+      </c>
+      <c r="C342" t="s">
         <v>678</v>
       </c>
-      <c r="C342" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>679</v>
+      </c>
+      <c r="C343" t="s">
         <v>680</v>
       </c>
-      <c r="C343" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>681</v>
+      </c>
+      <c r="C344" t="s">
         <v>682</v>
       </c>
-      <c r="C344" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>683</v>
+      </c>
+      <c r="C345" t="s">
         <v>684</v>
       </c>
-      <c r="C345" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>685</v>
+      </c>
+      <c r="C346" t="s">
         <v>686</v>
       </c>
-      <c r="C346" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>687</v>
+      </c>
+      <c r="C347" t="s">
         <v>688</v>
       </c>
-      <c r="C347" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>689</v>
+      </c>
+      <c r="C348" t="s">
         <v>690</v>
       </c>
-      <c r="C348" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>691</v>
+      </c>
+      <c r="C349" t="s">
         <v>692</v>
       </c>
-      <c r="C349" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>693</v>
+      </c>
+      <c r="C350" t="s">
         <v>694</v>
       </c>
-      <c r="C350" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>695</v>
+      </c>
+      <c r="C351" t="s">
         <v>696</v>
       </c>
-      <c r="C351" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>697</v>
+      </c>
+      <c r="C352" t="s">
         <v>698</v>
       </c>
-      <c r="C352" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>699</v>
+      </c>
+      <c r="C353" t="s">
         <v>700</v>
       </c>
-      <c r="C353" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>701</v>
+      </c>
+      <c r="C354" t="s">
         <v>702</v>
       </c>
-      <c r="C354" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>703</v>
+      </c>
+      <c r="C355" t="s">
         <v>704</v>
       </c>
-      <c r="C355" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>705</v>
+      </c>
+      <c r="C356" t="s">
         <v>706</v>
       </c>
-      <c r="C356" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>707</v>
+      </c>
+      <c r="C357" t="s">
         <v>708</v>
       </c>
-      <c r="C357" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>709</v>
+      </c>
+      <c r="C358" t="s">
         <v>710</v>
       </c>
-      <c r="C358" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>711</v>
+      </c>
+      <c r="C359" t="s">
         <v>712</v>
       </c>
-      <c r="C359" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>713</v>
+      </c>
+      <c r="C360" t="s">
         <v>714</v>
       </c>
-      <c r="C360" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>715</v>
+      </c>
+      <c r="C361" t="s">
         <v>716</v>
       </c>
-      <c r="C361" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>717</v>
+      </c>
+      <c r="C362" t="s">
         <v>718</v>
       </c>
-      <c r="C362" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>719</v>
+      </c>
+      <c r="C363" t="s">
         <v>720</v>
       </c>
-      <c r="C363" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>721</v>
+      </c>
+      <c r="C364" t="s">
         <v>722</v>
       </c>
-      <c r="C364" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>723</v>
+      </c>
+      <c r="C365" t="s">
         <v>724</v>
       </c>
-      <c r="C365" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>725</v>
+      </c>
+      <c r="C366" t="s">
         <v>726</v>
       </c>
-      <c r="C366" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>727</v>
+      </c>
+      <c r="C367" t="s">
         <v>728</v>
       </c>
-      <c r="C367" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>729</v>
+      </c>
+      <c r="C368" t="s">
         <v>730</v>
       </c>
-      <c r="C368" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>731</v>
+      </c>
+      <c r="C369" t="s">
         <v>732</v>
       </c>
-      <c r="C369" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>733</v>
+      </c>
+      <c r="C370" t="s">
         <v>734</v>
       </c>
-      <c r="C370" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>735</v>
+      </c>
+      <c r="C371" t="s">
         <v>736</v>
       </c>
-      <c r="C371" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>737</v>
+      </c>
+      <c r="C372" t="s">
         <v>738</v>
       </c>
-      <c r="C372" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>739</v>
+      </c>
+      <c r="C373" t="s">
         <v>740</v>
       </c>
-      <c r="C373" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>741</v>
+      </c>
+      <c r="C374" t="s">
         <v>742</v>
       </c>
-      <c r="C374" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>743</v>
+      </c>
+      <c r="C375" t="s">
         <v>744</v>
       </c>
-      <c r="C375" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>745</v>
+      </c>
+      <c r="C376" t="s">
         <v>746</v>
       </c>
-      <c r="C376" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>747</v>
+      </c>
+      <c r="C377" t="s">
         <v>748</v>
       </c>
-      <c r="C377" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>749</v>
+      </c>
+      <c r="C378" t="s">
         <v>750</v>
       </c>
-      <c r="C378" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>751</v>
+      </c>
+      <c r="C379" t="s">
         <v>752</v>
       </c>
-      <c r="C379" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>753</v>
+      </c>
+      <c r="C380" t="s">
         <v>754</v>
       </c>
-      <c r="C380" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>755</v>
+      </c>
+      <c r="C381" t="s">
         <v>756</v>
       </c>
-      <c r="C381" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>757</v>
+      </c>
+      <c r="C382" t="s">
         <v>758</v>
       </c>
-      <c r="C382" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>759</v>
+      </c>
+      <c r="C383" t="s">
         <v>760</v>
       </c>
-      <c r="C383" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>761</v>
+      </c>
+      <c r="C384" t="s">
         <v>762</v>
       </c>
-      <c r="C384" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>763</v>
+      </c>
+      <c r="C385" t="s">
         <v>764</v>
       </c>
-      <c r="C385" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>765</v>
+      </c>
+      <c r="C386" t="s">
         <v>766</v>
       </c>
-      <c r="C386" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>767</v>
+      </c>
+      <c r="C387" t="s">
         <v>768</v>
       </c>
-      <c r="C387" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>769</v>
+      </c>
+      <c r="C388" t="s">
         <v>770</v>
       </c>
-      <c r="C388" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>771</v>
+      </c>
+      <c r="C389" t="s">
         <v>772</v>
       </c>
-      <c r="C389" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>773</v>
+      </c>
+      <c r="C390" t="s">
         <v>774</v>
       </c>
-      <c r="C390" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>775</v>
+      </c>
+      <c r="C391" t="s">
         <v>776</v>
       </c>
-      <c r="C391" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>777</v>
+      </c>
+      <c r="C392" t="s">
         <v>778</v>
       </c>
-      <c r="C392" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>779</v>
+      </c>
+      <c r="C393" t="s">
         <v>780</v>
       </c>
-      <c r="C393" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>781</v>
+      </c>
+      <c r="C394" t="s">
         <v>782</v>
       </c>
-      <c r="C394" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>783</v>
+      </c>
+      <c r="C395" t="s">
         <v>784</v>
       </c>
-      <c r="C395" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>785</v>
+      </c>
+      <c r="C396" t="s">
         <v>786</v>
       </c>
-      <c r="C396" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>787</v>
+      </c>
+      <c r="C397" t="s">
         <v>788</v>
       </c>
-      <c r="C397" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>789</v>
+      </c>
+      <c r="C398" t="s">
         <v>790</v>
       </c>
-      <c r="C398" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>791</v>
+      </c>
+      <c r="C399" t="s">
         <v>792</v>
       </c>
-      <c r="C399" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>793</v>
+      </c>
+      <c r="C400" t="s">
         <v>794</v>
       </c>
-      <c r="C400" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>795</v>
+      </c>
+      <c r="C401" t="s">
         <v>796</v>
       </c>
-      <c r="C401" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>797</v>
+      </c>
+      <c r="C402" t="s">
         <v>798</v>
       </c>
-      <c r="C402" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>799</v>
+      </c>
+      <c r="C403" t="s">
         <v>800</v>
       </c>
-      <c r="C403" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>801</v>
+      </c>
+      <c r="C404" t="s">
         <v>802</v>
       </c>
-      <c r="C404" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>803</v>
+      </c>
+      <c r="C405" t="s">
         <v>804</v>
       </c>
-      <c r="C405" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>805</v>
+      </c>
+      <c r="C406" t="s">
         <v>806</v>
       </c>
-      <c r="C406" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>417</v>
       </c>
       <c r="B407" t="s">
+        <v>807</v>
+      </c>
+      <c r="C407" t="s">
         <v>808</v>
       </c>
-      <c r="C407" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>809</v>
+      </c>
+      <c r="C408" t="s">
         <v>810</v>
       </c>
-      <c r="C408" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>811</v>
+      </c>
+      <c r="C409" t="s">
         <v>812</v>
       </c>
-      <c r="C409" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>813</v>
+      </c>
+      <c r="C410" t="s">
         <v>814</v>
       </c>
-      <c r="C410" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>815</v>
+      </c>
+      <c r="C411" t="s">
         <v>816</v>
       </c>
-      <c r="C411" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>817</v>
+      </c>
+      <c r="C412" t="s">
         <v>818</v>
       </c>
-      <c r="C412" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>819</v>
+      </c>
+      <c r="C413" t="s">
         <v>820</v>
       </c>
-      <c r="C413" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>821</v>
+      </c>
+      <c r="C414" t="s">
         <v>822</v>
       </c>
-      <c r="C414" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>823</v>
+      </c>
+      <c r="C415" t="s">
         <v>824</v>
       </c>
-      <c r="C415" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>825</v>
+      </c>
+      <c r="C416" t="s">
         <v>826</v>
       </c>
-      <c r="C416" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>827</v>
+      </c>
+      <c r="C417" t="s">
         <v>828</v>
       </c>
-      <c r="C417" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>829</v>
+      </c>
+      <c r="C418" t="s">
         <v>830</v>
       </c>
-      <c r="C418" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>831</v>
+      </c>
+      <c r="C419" t="s">
         <v>832</v>
       </c>
-      <c r="C419" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>833</v>
+      </c>
+      <c r="C420" t="s">
         <v>834</v>
       </c>
-      <c r="C420" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>835</v>
+      </c>
+      <c r="C421" t="s">
         <v>836</v>
       </c>
-      <c r="C421" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>837</v>
+      </c>
+      <c r="C422" t="s">
         <v>838</v>
       </c>
-      <c r="C422" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>839</v>
+      </c>
+      <c r="C423" t="s">
         <v>840</v>
       </c>
-      <c r="C423" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>841</v>
+      </c>
+      <c r="C424" t="s">
         <v>842</v>
       </c>
-      <c r="C424" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>843</v>
+      </c>
+      <c r="C425" t="s">
         <v>844</v>
       </c>
-      <c r="C425" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>845</v>
+      </c>
+      <c r="C426" t="s">
         <v>846</v>
       </c>
-      <c r="C426" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>847</v>
+      </c>
+      <c r="C427" t="s">
         <v>848</v>
       </c>
-      <c r="C427" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C428" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.15">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C429" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.15">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>851</v>
+      </c>
+      <c r="C430" t="s">
         <v>852</v>
       </c>
-      <c r="C430" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>853</v>
+      </c>
+      <c r="C431" t="s">
         <v>854</v>
       </c>
-      <c r="C431" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>855</v>
+      </c>
+      <c r="C432" t="s">
         <v>856</v>
       </c>
-      <c r="C432" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>857</v>
+      </c>
+      <c r="C433" t="s">
         <v>858</v>
       </c>
-      <c r="C433" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>859</v>
+      </c>
+      <c r="C434" t="s">
         <v>860</v>
       </c>
-      <c r="C434" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>861</v>
+      </c>
+      <c r="C435" t="s">
         <v>862</v>
       </c>
-      <c r="C435" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>863</v>
+      </c>
+      <c r="C436" t="s">
         <v>864</v>
       </c>
-      <c r="C436" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>865</v>
+      </c>
+      <c r="C437" t="s">
         <v>866</v>
       </c>
-      <c r="C437" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>867</v>
+      </c>
+      <c r="C438" t="s">
         <v>868</v>
       </c>
-      <c r="C438" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>869</v>
+      </c>
+      <c r="C439" t="s">
         <v>870</v>
       </c>
-      <c r="C439" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>871</v>
+      </c>
+      <c r="C440" t="s">
         <v>872</v>
       </c>
-      <c r="C440" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>873</v>
+      </c>
+      <c r="C441" t="s">
         <v>874</v>
       </c>
-      <c r="C441" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>875</v>
+      </c>
+      <c r="C442" t="s">
         <v>876</v>
       </c>
-      <c r="C442" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>877</v>
+      </c>
+      <c r="C443" t="s">
         <v>878</v>
       </c>
-      <c r="C443" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>879</v>
+      </c>
+      <c r="C444" t="s">
         <v>880</v>
       </c>
-      <c r="C444" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>881</v>
+      </c>
+      <c r="C445" t="s">
         <v>882</v>
       </c>
-      <c r="C445" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>883</v>
+      </c>
+      <c r="C446" t="s">
         <v>884</v>
       </c>
-      <c r="C446" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>885</v>
+      </c>
+      <c r="C447" t="s">
         <v>886</v>
       </c>
-      <c r="C447" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>887</v>
+      </c>
+      <c r="C448" t="s">
         <v>888</v>
       </c>
-      <c r="C448" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>889</v>
+      </c>
+      <c r="C449" t="s">
         <v>890</v>
       </c>
-      <c r="C449" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>891</v>
+      </c>
+      <c r="C450" t="s">
         <v>892</v>
       </c>
-      <c r="C450" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C451" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.15">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>894</v>
+      </c>
+      <c r="C452" t="s">
         <v>895</v>
       </c>
-      <c r="C452" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>896</v>
+      </c>
+      <c r="C453" t="s">
         <v>897</v>
       </c>
-      <c r="C453" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>898</v>
+      </c>
+      <c r="C454" t="s">
         <v>899</v>
       </c>
-      <c r="C454" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>900</v>
+      </c>
+      <c r="C455" t="s">
         <v>901</v>
       </c>
-      <c r="C455" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C456" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.15">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>903</v>
+      </c>
+      <c r="C457" t="s">
         <v>904</v>
       </c>
-      <c r="C457" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>905</v>
+      </c>
+      <c r="C458" t="s">
         <v>906</v>
       </c>
-      <c r="C458" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>470</v>
       </c>
       <c r="B459" t="s">
+        <v>907</v>
+      </c>
+      <c r="C459" t="s">
         <v>908</v>
       </c>
-      <c r="C459" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.15">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>910</v>
+      </c>
+      <c r="C461" t="s">
         <v>911</v>
       </c>
-      <c r="C461" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>912</v>
+      </c>
+      <c r="C462" t="s">
         <v>913</v>
       </c>
-      <c r="C462" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>914</v>
+      </c>
+      <c r="C463" t="s">
         <v>915</v>
       </c>
-      <c r="C463" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>916</v>
+      </c>
+      <c r="C464" t="s">
         <v>917</v>
       </c>
-      <c r="C464" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>918</v>
+      </c>
+      <c r="C465" t="s">
         <v>919</v>
       </c>
-      <c r="C465" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>920</v>
+      </c>
+      <c r="C466" t="s">
         <v>921</v>
       </c>
-      <c r="C466" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>478</v>
       </c>
       <c r="B467" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>923</v>
+      </c>
+      <c r="C468" t="s">
         <v>924</v>
       </c>
-      <c r="C468" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>925</v>
+      </c>
+      <c r="C469" t="s">
         <v>926</v>
       </c>
-      <c r="C469" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>927</v>
+      </c>
+      <c r="C470" t="s">
         <v>928</v>
       </c>
-      <c r="C470" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>929</v>
+      </c>
+      <c r="C471" t="s">
         <v>930</v>
       </c>
-      <c r="C471" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>931</v>
+      </c>
+      <c r="C472" t="s">
         <v>932</v>
       </c>
-      <c r="C472" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="17.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="473" spans="1:3" ht="19.2" x14ac:dyDescent="0.45">
       <c r="A473">
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>933</v>
+      </c>
+      <c r="C473" t="s">
         <v>934</v>
       </c>
-      <c r="C473" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>935</v>
+      </c>
+      <c r="C474" t="s">
         <v>936</v>
       </c>
-      <c r="C474" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>937</v>
+      </c>
+      <c r="C475" t="s">
         <v>938</v>
       </c>
-      <c r="C475" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>939</v>
+      </c>
+      <c r="C476" t="s">
         <v>940</v>
       </c>
-      <c r="C476" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>941</v>
+      </c>
+      <c r="C477" t="s">
         <v>942</v>
       </c>
-      <c r="C477" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C478" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.15">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>944</v>
+      </c>
+      <c r="C479" t="s">
         <v>945</v>
       </c>
-      <c r="C479" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>946</v>
+      </c>
+      <c r="C480" t="s">
         <v>947</v>
       </c>
-      <c r="C480" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>948</v>
+      </c>
+      <c r="C481" t="s">
         <v>949</v>
       </c>
-      <c r="C481" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>950</v>
+      </c>
+      <c r="C482" t="s">
         <v>951</v>
       </c>
-      <c r="C482" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>952</v>
+      </c>
+      <c r="C483" t="s">
         <v>953</v>
       </c>
-      <c r="C483" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>954</v>
+      </c>
+      <c r="C484" t="s">
         <v>955</v>
       </c>
-      <c r="C484" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>956</v>
+      </c>
+      <c r="C485" t="s">
         <v>957</v>
       </c>
-      <c r="C485" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>958</v>
+      </c>
+      <c r="C486" t="s">
         <v>959</v>
       </c>
-      <c r="C486" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>960</v>
+      </c>
+      <c r="C487" t="s">
         <v>961</v>
       </c>
-      <c r="C487" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>962</v>
+      </c>
+      <c r="C488" t="s">
         <v>963</v>
       </c>
-      <c r="C488" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>964</v>
+      </c>
+      <c r="C489" t="s">
         <v>965</v>
       </c>
-      <c r="C489" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>966</v>
+      </c>
+      <c r="C490" t="s">
         <v>967</v>
       </c>
-      <c r="C490" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>968</v>
+      </c>
+      <c r="C491" t="s">
         <v>969</v>
       </c>
-      <c r="C491" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>970</v>
+      </c>
+      <c r="C492" t="s">
         <v>971</v>
       </c>
-      <c r="C492" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>972</v>
+      </c>
+      <c r="C493" t="s">
         <v>973</v>
       </c>
-      <c r="C493" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>974</v>
+      </c>
+      <c r="C494" t="s">
         <v>975</v>
       </c>
-      <c r="C494" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>976</v>
+      </c>
+      <c r="C495" t="s">
         <v>977</v>
       </c>
-      <c r="C495" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>978</v>
+      </c>
+      <c r="C496" t="s">
         <v>979</v>
       </c>
-      <c r="C496" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>980</v>
+      </c>
+      <c r="C497" t="s">
         <v>981</v>
       </c>
-      <c r="C497" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>982</v>
+      </c>
+      <c r="C498" t="s">
         <v>983</v>
       </c>
-      <c r="C498" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.15">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>985</v>
+      </c>
+      <c r="C500" t="s">
         <v>986</v>
       </c>
-      <c r="C500" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>987</v>
+      </c>
+      <c r="C501" t="s">
         <v>988</v>
       </c>
-      <c r="C501" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>989</v>
+      </c>
+      <c r="C502" t="s">
         <v>990</v>
       </c>
-      <c r="C502" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>515</v>
       </c>
       <c r="B503" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>992</v>
+      </c>
+      <c r="C504" t="s">
         <v>993</v>
       </c>
-      <c r="C504" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>517</v>
       </c>
       <c r="B505" t="s">
+        <v>994</v>
+      </c>
+      <c r="C505" t="s">
         <v>995</v>
       </c>
-      <c r="C505" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>996</v>
+      </c>
+      <c r="C506" t="s">
         <v>997</v>
       </c>
-      <c r="C506" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>998</v>
+      </c>
+      <c r="C507" t="s">
         <v>999</v>
       </c>
-      <c r="C507" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C508" t="s">
         <v>1001</v>
       </c>
-      <c r="C508" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C509" t="s">
         <v>1003</v>
       </c>
-      <c r="C509" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C510" t="s">
         <v>1005</v>
       </c>
-      <c r="C510" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C511" t="s">
         <v>1007</v>
       </c>
-      <c r="C511" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C512" t="s">
         <v>1009</v>
       </c>
-      <c r="C512" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C513" t="s">
         <v>1011</v>
       </c>
-      <c r="C513" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C514" t="s">
         <v>1013</v>
       </c>
-      <c r="C514" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C515" t="s">
         <v>1015</v>
       </c>
-      <c r="C515" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C516" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C517" t="s">
         <v>1018</v>
       </c>
-      <c r="C517" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C519" t="s">
         <v>1021</v>
       </c>
-      <c r="C519" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C520" t="s">
         <v>1023</v>
       </c>
-      <c r="C520" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C521" t="s">
         <v>1025</v>
       </c>
-      <c r="C521" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C522" t="s">
         <v>1027</v>
       </c>
-      <c r="C522" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C523" t="s">
         <v>1029</v>
       </c>
-      <c r="C523" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C524" t="s">
         <v>1031</v>
       </c>
-      <c r="C524" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C525" t="s">
         <v>1033</v>
       </c>
-      <c r="C525" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C526" t="s">
         <v>1035</v>
       </c>
-      <c r="C526" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C527" t="s">
         <v>1037</v>
       </c>
-      <c r="C527" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C528" t="s">
         <v>1039</v>
       </c>
-      <c r="C528" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C529" t="s">
         <v>1041</v>
       </c>
-      <c r="C529" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C530" t="s">
         <v>1043</v>
       </c>
-      <c r="C530" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C531" t="s">
         <v>1045</v>
       </c>
-      <c r="C531" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C532" t="s">
         <v>1047</v>
       </c>
-      <c r="C532" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C533" t="s">
         <v>1049</v>
       </c>
-      <c r="C533" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C534" t="s">
         <v>1051</v>
       </c>
-      <c r="C534" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C535" t="s">
         <v>1053</v>
       </c>
-      <c r="C535" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C536" t="s">
         <v>1055</v>
       </c>
-      <c r="C536" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>551</v>
       </c>
       <c r="B537" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C537" t="s">
         <v>1057</v>
       </c>
-      <c r="C537" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C538" t="s">
         <v>1059</v>
       </c>
-      <c r="C538" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C539" t="s">
         <v>1061</v>
       </c>
-      <c r="C539" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C540" t="s">
         <v>1063</v>
       </c>
-      <c r="C540" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C541" t="s">
         <v>1065</v>
       </c>
-      <c r="C541" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C542" t="s">
         <v>1067</v>
       </c>
-      <c r="C542" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C543" t="s">
         <v>1069</v>
       </c>
-      <c r="C543" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C544" t="s">
         <v>1071</v>
       </c>
-      <c r="C544" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C545" t="s">
         <v>1073</v>
       </c>
-      <c r="C545" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C546" t="s">
         <v>1075</v>
       </c>
-      <c r="C546" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C548" t="s">
         <v>1078</v>
       </c>
-      <c r="C548" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C549" t="s">
         <v>1080</v>
       </c>
-      <c r="C549" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C550" t="s">
         <v>1082</v>
       </c>
-      <c r="C550" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C551" t="s">
         <v>1084</v>
       </c>
-      <c r="C551" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C552" t="s">
         <v>1086</v>
       </c>
-      <c r="C552" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C553" t="s">
         <v>1088</v>
       </c>
-      <c r="C553" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C554" t="s">
         <v>1090</v>
       </c>
-      <c r="C554" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C555" t="s">
         <v>1092</v>
       </c>
-      <c r="C555" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>572</v>
       </c>
       <c r="B556" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C556" t="s">
         <v>1094</v>
       </c>
-      <c r="C556" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>577</v>
       </c>
       <c r="B557" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C557" t="s">
         <v>1096</v>
       </c>
-      <c r="C557" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C558" t="s">
         <v>1098</v>
       </c>
-      <c r="C558" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C560" t="s">
         <v>1101</v>
       </c>
-      <c r="C560" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C561" t="s">
         <v>1103</v>
       </c>
-      <c r="C561" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C562" t="s">
         <v>1105</v>
       </c>
-      <c r="C562" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C563" t="s">
         <v>1107</v>
       </c>
-      <c r="C563" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C564" t="s">
         <v>1109</v>
       </c>
-      <c r="C564" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>585</v>
       </c>
       <c r="B565" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C565" t="s">
         <v>1111</v>
       </c>
-      <c r="C565" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C566" t="s">
         <v>1113</v>
       </c>
-      <c r="C566" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C567" t="s">
         <v>1115</v>
       </c>
-      <c r="C567" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C568" t="s">
         <v>1117</v>
       </c>
-      <c r="C568" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C569" t="s">
         <v>1119</v>
       </c>
-      <c r="C569" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C570" t="s">
         <v>1121</v>
       </c>
-      <c r="C570" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C571" t="s">
         <v>1123</v>
       </c>
-      <c r="C571" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C572" t="s">
         <v>1125</v>
       </c>
-      <c r="C572" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C573" t="s">
         <v>1127</v>
       </c>
-      <c r="C573" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C574" t="s">
         <v>1129</v>
       </c>
-      <c r="C574" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.15">
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>595</v>
       </c>
       <c r="B575" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C575" s="3" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.15">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>596</v>
       </c>
       <c r="B576" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C576" t="s">
         <v>1132</v>
       </c>
-      <c r="C576" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" x14ac:d